--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1329,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2902,7 +2902,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ8">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4756,7 +4756,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ17">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -8052,7 +8052,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ33">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ35">
         <v>1.5</v>
@@ -12169,7 +12169,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ53">
         <v>1.8</v>
@@ -15056,7 +15056,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ67">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR67">
         <v>1.32</v>
@@ -18143,7 +18143,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ82">
         <v>0.36</v>
@@ -18970,7 +18970,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ86">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -21236,7 +21236,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ97">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR97">
         <v>1.35</v>
@@ -23293,7 +23293,7 @@
         <v>0.75</v>
       </c>
       <c r="AP107">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
@@ -26589,7 +26589,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ123">
         <v>0.9</v>
@@ -29270,7 +29270,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ136">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR136">
         <v>1.38</v>
@@ -29473,7 +29473,7 @@
         <v>1.8</v>
       </c>
       <c r="AP137">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>2</v>
@@ -32978,7 +32978,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ154">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR154">
         <v>1.29</v>
@@ -33387,7 +33387,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ156">
         <v>1.4</v>
@@ -36686,7 +36686,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ172">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR172">
         <v>1.52</v>
@@ -38331,7 +38331,7 @@
         <v>1.75</v>
       </c>
       <c r="AP180">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ180">
         <v>1.64</v>
@@ -38746,7 +38746,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ182">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR182">
         <v>1.81</v>
@@ -41215,7 +41215,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ194">
         <v>1.8</v>
@@ -42248,7 +42248,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ199">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -44796,6 +44796,212 @@
       </c>
       <c r="BP211">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7465206</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45688.70833333334</v>
+      </c>
+      <c r="F212">
+        <v>22</v>
+      </c>
+      <c r="G212" t="s">
+        <v>85</v>
+      </c>
+      <c r="H212" t="s">
+        <v>88</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212" t="s">
+        <v>104</v>
+      </c>
+      <c r="P212" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q212">
+        <v>3.75</v>
+      </c>
+      <c r="R212">
+        <v>1.91</v>
+      </c>
+      <c r="S212">
+        <v>3.4</v>
+      </c>
+      <c r="T212">
+        <v>1.57</v>
+      </c>
+      <c r="U212">
+        <v>2.25</v>
+      </c>
+      <c r="V212">
+        <v>3.75</v>
+      </c>
+      <c r="W212">
+        <v>1.25</v>
+      </c>
+      <c r="X212">
+        <v>13</v>
+      </c>
+      <c r="Y212">
+        <v>1.04</v>
+      </c>
+      <c r="Z212">
+        <v>3</v>
+      </c>
+      <c r="AA212">
+        <v>3</v>
+      </c>
+      <c r="AB212">
+        <v>2.5</v>
+      </c>
+      <c r="AC212">
+        <v>1.12</v>
+      </c>
+      <c r="AD212">
+        <v>7</v>
+      </c>
+      <c r="AE212">
+        <v>1.53</v>
+      </c>
+      <c r="AF212">
+        <v>2.37</v>
+      </c>
+      <c r="AG212">
+        <v>2.63</v>
+      </c>
+      <c r="AH212">
+        <v>1.5</v>
+      </c>
+      <c r="AI212">
+        <v>2.1</v>
+      </c>
+      <c r="AJ212">
+        <v>1.67</v>
+      </c>
+      <c r="AK212">
+        <v>1.5</v>
+      </c>
+      <c r="AL212">
+        <v>1.37</v>
+      </c>
+      <c r="AM212">
+        <v>1.37</v>
+      </c>
+      <c r="AN212">
+        <v>1.3</v>
+      </c>
+      <c r="AO212">
+        <v>1.27</v>
+      </c>
+      <c r="AP212">
+        <v>1.18</v>
+      </c>
+      <c r="AQ212">
+        <v>1.42</v>
+      </c>
+      <c r="AR212">
+        <v>0.97</v>
+      </c>
+      <c r="AS212">
+        <v>1.05</v>
+      </c>
+      <c r="AT212">
+        <v>2.02</v>
+      </c>
+      <c r="AU212">
+        <v>2</v>
+      </c>
+      <c r="AV212">
+        <v>4</v>
+      </c>
+      <c r="AW212">
+        <v>4</v>
+      </c>
+      <c r="AX212">
+        <v>16</v>
+      </c>
+      <c r="AY212">
+        <v>8</v>
+      </c>
+      <c r="AZ212">
+        <v>24</v>
+      </c>
+      <c r="BA212">
+        <v>2</v>
+      </c>
+      <c r="BB212">
+        <v>9</v>
+      </c>
+      <c r="BC212">
+        <v>11</v>
+      </c>
+      <c r="BD212">
+        <v>2.1</v>
+      </c>
+      <c r="BE212">
+        <v>6.25</v>
+      </c>
+      <c r="BF212">
+        <v>1.91</v>
+      </c>
+      <c r="BG212">
+        <v>1.41</v>
+      </c>
+      <c r="BH212">
+        <v>2.65</v>
+      </c>
+      <c r="BI212">
+        <v>1.68</v>
+      </c>
+      <c r="BJ212">
+        <v>2.02</v>
+      </c>
+      <c r="BK212">
+        <v>2.1</v>
+      </c>
+      <c r="BL212">
+        <v>1.64</v>
+      </c>
+      <c r="BM212">
+        <v>2.7</v>
+      </c>
+      <c r="BN212">
+        <v>1.4</v>
+      </c>
+      <c r="BO212">
+        <v>3.65</v>
+      </c>
+      <c r="BP212">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,12 @@
     <t>['3', '8', '14', '24', '45+4', '66', '75']</t>
   </si>
   <si>
+    <t>['42', '64', '70', '86', '90+1']</t>
+  </si>
+  <si>
+    <t>['26', '90+3']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1329,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1591,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1997,7 +2003,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2078,7 +2084,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ4">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2203,7 +2209,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2284,7 +2290,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ5">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2409,7 +2415,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2615,7 +2621,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2821,7 +2827,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3027,7 +3033,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3108,7 +3114,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3439,7 +3445,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3517,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ11">
         <v>1.8</v>
@@ -3851,7 +3857,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4138,7 +4144,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
         <v>1.83</v>
@@ -4341,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ15">
         <v>1.8</v>
@@ -4547,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ16">
         <v>1.4</v>
@@ -4753,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
         <v>1.42</v>
@@ -4962,7 +4968,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ18">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5577,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ21">
         <v>1.09</v>
@@ -5705,7 +5711,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -5783,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ22">
         <v>0.5</v>
@@ -5992,7 +5998,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ23">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR23">
         <v>1.51</v>
@@ -6117,7 +6123,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6813,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ27">
         <v>0.2</v>
@@ -6941,7 +6947,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7022,7 +7028,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ28">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -7434,7 +7440,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ30">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR30">
         <v>1.44</v>
@@ -7637,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ31">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR31">
         <v>1.51</v>
@@ -8049,7 +8055,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ33">
         <v>1.42</v>
@@ -8177,7 +8183,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8464,7 +8470,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8795,7 +8801,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9001,7 +9007,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9285,7 +9291,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
         <v>1.4</v>
@@ -9825,7 +9831,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10031,7 +10037,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10109,10 +10115,10 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR43">
         <v>1.17</v>
@@ -10443,7 +10449,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10524,7 +10530,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR45">
         <v>1.14</v>
@@ -10730,7 +10736,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ46">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR46">
         <v>1.11</v>
@@ -10855,7 +10861,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11061,7 +11067,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11345,7 +11351,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ49">
         <v>0.36</v>
@@ -12091,7 +12097,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12378,7 +12384,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ54">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR54">
         <v>1.07</v>
@@ -12709,7 +12715,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13121,7 +13127,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13405,7 +13411,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
         <v>0.91</v>
@@ -13739,7 +13745,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13817,7 +13823,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
         <v>2</v>
@@ -14151,7 +14157,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14232,7 +14238,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
         <v>1.68</v>
@@ -14563,7 +14569,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14644,7 +14650,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14769,7 +14775,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14850,7 +14856,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ66">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR66">
         <v>2.43</v>
@@ -15259,7 +15265,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ68">
         <v>0.8</v>
@@ -15387,7 +15393,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15465,7 +15471,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ69">
         <v>1.64</v>
@@ -15593,7 +15599,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16005,7 +16011,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16086,7 +16092,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR72">
         <v>1.16</v>
@@ -16289,10 +16295,10 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ73">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16829,7 +16835,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17322,7 +17328,7 @@
         <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17653,7 +17659,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17731,10 +17737,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR80">
         <v>1.69</v>
@@ -17859,7 +17865,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17937,7 +17943,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18349,10 +18355,10 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ83">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR83">
         <v>1.07</v>
@@ -18555,7 +18561,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ84">
         <v>0.8</v>
@@ -18889,7 +18895,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19301,7 +19307,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19507,7 +19513,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19919,7 +19925,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20125,7 +20131,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20206,7 +20212,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ92">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR92">
         <v>1.06</v>
@@ -20537,7 +20543,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20949,7 +20955,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21030,7 +21036,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ96">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -21439,7 +21445,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ98">
         <v>0.91</v>
@@ -21645,7 +21651,7 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ99">
         <v>0.8</v>
@@ -21851,10 +21857,10 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ100">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -21979,7 +21985,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22185,7 +22191,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22263,10 +22269,10 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ102">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR102">
         <v>1.07</v>
@@ -22391,7 +22397,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22678,7 +22684,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR104">
         <v>1.49</v>
@@ -23009,7 +23015,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23499,7 +23505,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ108">
         <v>0.36</v>
@@ -23833,7 +23839,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24326,7 +24332,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ112">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR112">
         <v>1.08</v>
@@ -24532,7 +24538,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ113">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24657,7 +24663,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24941,7 +24947,7 @@
         <v>0.6</v>
       </c>
       <c r="AP115">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25069,7 +25075,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25147,7 +25153,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ116">
         <v>0.2</v>
@@ -25275,7 +25281,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25481,7 +25487,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25893,7 +25899,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26383,10 +26389,10 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ122">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR122">
         <v>1.57</v>
@@ -26592,7 +26598,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ123">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR123">
         <v>1.08</v>
@@ -26717,7 +26723,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27207,7 +27213,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ126">
         <v>1.09</v>
@@ -27825,10 +27831,10 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ129">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR129">
         <v>1.27</v>
@@ -27953,7 +27959,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28237,10 +28243,10 @@
         <v>0.43</v>
       </c>
       <c r="AP131">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ131">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28365,7 +28371,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28446,7 +28452,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ132">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28777,7 +28783,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28983,7 +28989,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29395,7 +29401,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29476,7 +29482,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ137">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -29807,7 +29813,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30013,7 +30019,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30091,7 +30097,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -30503,7 +30509,7 @@
         <v>0.67</v>
       </c>
       <c r="AP142">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ142">
         <v>0.5</v>
@@ -30631,7 +30637,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30837,7 +30843,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -30915,7 +30921,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ144">
         <v>1.09</v>
@@ -31249,7 +31255,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31867,7 +31873,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32073,7 +32079,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32154,7 +32160,7 @@
         <v>2</v>
       </c>
       <c r="AQ150">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32360,7 +32366,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ151">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR151">
         <v>1.39</v>
@@ -32566,7 +32572,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ152">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR152">
         <v>1.35</v>
@@ -32691,7 +32697,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33103,7 +33109,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33184,7 +33190,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ155">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR155">
         <v>1.38</v>
@@ -33309,7 +33315,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33721,7 +33727,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33802,7 +33808,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ158">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR158">
         <v>1.47</v>
@@ -33927,7 +33933,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34005,10 +34011,10 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ159">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34211,7 +34217,7 @@
         <v>0.14</v>
       </c>
       <c r="AP160">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ160">
         <v>0.2</v>
@@ -34623,7 +34629,7 @@
         <v>0.86</v>
       </c>
       <c r="AP162">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ162">
         <v>0.8</v>
@@ -35163,7 +35169,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35244,7 +35250,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ165">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR165">
         <v>1.64</v>
@@ -35447,7 +35453,7 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ166">
         <v>0.8</v>
@@ -35575,7 +35581,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35987,7 +35993,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36065,7 +36071,7 @@
         <v>0.75</v>
       </c>
       <c r="AP169">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ169">
         <v>1.09</v>
@@ -36271,7 +36277,7 @@
         <v>0.63</v>
       </c>
       <c r="AP170">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ170">
         <v>0.91</v>
@@ -36399,7 +36405,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36477,7 +36483,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ171">
         <v>0.36</v>
@@ -36683,7 +36689,7 @@
         <v>1.38</v>
       </c>
       <c r="AP172">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ172">
         <v>1.42</v>
@@ -36892,7 +36898,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ173">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR173">
         <v>1.37</v>
@@ -37095,10 +37101,10 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
+        <v>1.33</v>
+      </c>
+      <c r="AQ174">
         <v>1.36</v>
-      </c>
-      <c r="AQ174">
-        <v>1.5</v>
       </c>
       <c r="AR174">
         <v>1.33</v>
@@ -37635,7 +37641,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37713,7 +37719,7 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ177">
         <v>1.8</v>
@@ -37841,7 +37847,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37922,7 +37928,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ178">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR178">
         <v>1.38</v>
@@ -38047,7 +38053,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38128,7 +38134,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ179">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR179">
         <v>1.81</v>
@@ -38253,7 +38259,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38871,7 +38877,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -38952,7 +38958,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ183">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR183">
         <v>1.35</v>
@@ -39283,7 +39289,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39773,7 +39779,7 @@
         <v>0.89</v>
       </c>
       <c r="AP187">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ187">
         <v>0.91</v>
@@ -40107,7 +40113,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40391,7 +40397,7 @@
         <v>0.88</v>
       </c>
       <c r="AP190">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ190">
         <v>0.8</v>
@@ -40803,10 +40809,10 @@
         <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ192">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR192">
         <v>1.16</v>
@@ -40931,7 +40937,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41012,7 +41018,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ193">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR193">
         <v>1.37</v>
@@ -41343,7 +41349,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41424,7 +41430,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ195">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR195">
         <v>1.78</v>
@@ -41627,7 +41633,7 @@
         <v>2.09</v>
       </c>
       <c r="AP196">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ196">
         <v>2</v>
@@ -41755,7 +41761,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41961,7 +41967,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42657,10 +42663,10 @@
         <v>1.67</v>
       </c>
       <c r="AP201">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ201">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR201">
         <v>1.52</v>
@@ -42991,7 +42997,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43197,7 +43203,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43275,7 +43281,7 @@
         <v>1.7</v>
       </c>
       <c r="AP204">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ204">
         <v>1.64</v>
@@ -43403,7 +43409,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43609,7 +43615,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43690,7 +43696,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ206">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AR206">
         <v>1.01</v>
@@ -44021,7 +44027,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44511,7 +44517,7 @@
         <v>0.4</v>
       </c>
       <c r="AP210">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ210">
         <v>0.36</v>
@@ -44639,7 +44645,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44845,7 +44851,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45002,6 +45008,1036 @@
       </c>
       <c r="BP212">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7465202</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45689.41666666666</v>
+      </c>
+      <c r="F213">
+        <v>22</v>
+      </c>
+      <c r="G213" t="s">
+        <v>83</v>
+      </c>
+      <c r="H213" t="s">
+        <v>80</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213" t="s">
+        <v>104</v>
+      </c>
+      <c r="P213" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q213">
+        <v>3.4</v>
+      </c>
+      <c r="R213">
+        <v>1.83</v>
+      </c>
+      <c r="S213">
+        <v>4</v>
+      </c>
+      <c r="T213">
+        <v>1.67</v>
+      </c>
+      <c r="U213">
+        <v>2.1</v>
+      </c>
+      <c r="V213">
+        <v>4</v>
+      </c>
+      <c r="W213">
+        <v>1.22</v>
+      </c>
+      <c r="X213">
+        <v>15</v>
+      </c>
+      <c r="Y213">
+        <v>1.03</v>
+      </c>
+      <c r="Z213">
+        <v>2.4</v>
+      </c>
+      <c r="AA213">
+        <v>3</v>
+      </c>
+      <c r="AB213">
+        <v>3.2</v>
+      </c>
+      <c r="AC213">
+        <v>1.13</v>
+      </c>
+      <c r="AD213">
+        <v>6.5</v>
+      </c>
+      <c r="AE213">
+        <v>1.57</v>
+      </c>
+      <c r="AF213">
+        <v>2.25</v>
+      </c>
+      <c r="AG213">
+        <v>2.75</v>
+      </c>
+      <c r="AH213">
+        <v>1.44</v>
+      </c>
+      <c r="AI213">
+        <v>2.25</v>
+      </c>
+      <c r="AJ213">
+        <v>1.57</v>
+      </c>
+      <c r="AK213">
+        <v>1.34</v>
+      </c>
+      <c r="AL213">
+        <v>1.37</v>
+      </c>
+      <c r="AM213">
+        <v>1.55</v>
+      </c>
+      <c r="AN213">
+        <v>1.36</v>
+      </c>
+      <c r="AO213">
+        <v>0.9</v>
+      </c>
+      <c r="AP213">
+        <v>1.33</v>
+      </c>
+      <c r="AQ213">
+        <v>0.91</v>
+      </c>
+      <c r="AR213">
+        <v>1.36</v>
+      </c>
+      <c r="AS213">
+        <v>1.19</v>
+      </c>
+      <c r="AT213">
+        <v>2.55</v>
+      </c>
+      <c r="AU213">
+        <v>2</v>
+      </c>
+      <c r="AV213">
+        <v>2</v>
+      </c>
+      <c r="AW213">
+        <v>5</v>
+      </c>
+      <c r="AX213">
+        <v>12</v>
+      </c>
+      <c r="AY213">
+        <v>8</v>
+      </c>
+      <c r="AZ213">
+        <v>17</v>
+      </c>
+      <c r="BA213">
+        <v>6</v>
+      </c>
+      <c r="BB213">
+        <v>5</v>
+      </c>
+      <c r="BC213">
+        <v>11</v>
+      </c>
+      <c r="BD213">
+        <v>1.79</v>
+      </c>
+      <c r="BE213">
+        <v>6.25</v>
+      </c>
+      <c r="BF213">
+        <v>2.23</v>
+      </c>
+      <c r="BG213">
+        <v>1.47</v>
+      </c>
+      <c r="BH213">
+        <v>2.43</v>
+      </c>
+      <c r="BI213">
+        <v>1.81</v>
+      </c>
+      <c r="BJ213">
+        <v>1.88</v>
+      </c>
+      <c r="BK213">
+        <v>2.3</v>
+      </c>
+      <c r="BL213">
+        <v>1.54</v>
+      </c>
+      <c r="BM213">
+        <v>3</v>
+      </c>
+      <c r="BN213">
+        <v>1.32</v>
+      </c>
+      <c r="BO213">
+        <v>4.1</v>
+      </c>
+      <c r="BP213">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7465205</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45689.51041666666</v>
+      </c>
+      <c r="F214">
+        <v>22</v>
+      </c>
+      <c r="G214" t="s">
+        <v>79</v>
+      </c>
+      <c r="H214" t="s">
+        <v>78</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>5</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>6</v>
+      </c>
+      <c r="O214" t="s">
+        <v>233</v>
+      </c>
+      <c r="P214" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q214">
+        <v>1.62</v>
+      </c>
+      <c r="R214">
+        <v>2.88</v>
+      </c>
+      <c r="S214">
+        <v>9</v>
+      </c>
+      <c r="T214">
+        <v>1.25</v>
+      </c>
+      <c r="U214">
+        <v>3.75</v>
+      </c>
+      <c r="V214">
+        <v>2.1</v>
+      </c>
+      <c r="W214">
+        <v>1.67</v>
+      </c>
+      <c r="X214">
+        <v>5</v>
+      </c>
+      <c r="Y214">
+        <v>1.17</v>
+      </c>
+      <c r="Z214">
+        <v>1.22</v>
+      </c>
+      <c r="AA214">
+        <v>6.5</v>
+      </c>
+      <c r="AB214">
+        <v>12</v>
+      </c>
+      <c r="AC214">
+        <v>1.01</v>
+      </c>
+      <c r="AD214">
+        <v>17</v>
+      </c>
+      <c r="AE214">
+        <v>1.13</v>
+      </c>
+      <c r="AF214">
+        <v>6</v>
+      </c>
+      <c r="AG214">
+        <v>1.5</v>
+      </c>
+      <c r="AH214">
+        <v>2.63</v>
+      </c>
+      <c r="AI214">
+        <v>1.95</v>
+      </c>
+      <c r="AJ214">
+        <v>1.8</v>
+      </c>
+      <c r="AK214">
+        <v>1.04</v>
+      </c>
+      <c r="AL214">
+        <v>1.11</v>
+      </c>
+      <c r="AM214">
+        <v>4.1</v>
+      </c>
+      <c r="AN214">
+        <v>1.6</v>
+      </c>
+      <c r="AO214">
+        <v>0.3</v>
+      </c>
+      <c r="AP214">
+        <v>1.73</v>
+      </c>
+      <c r="AQ214">
+        <v>0.27</v>
+      </c>
+      <c r="AR214">
+        <v>1.55</v>
+      </c>
+      <c r="AS214">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT214">
+        <v>2.49</v>
+      </c>
+      <c r="AU214">
+        <v>9</v>
+      </c>
+      <c r="AV214">
+        <v>3</v>
+      </c>
+      <c r="AW214">
+        <v>14</v>
+      </c>
+      <c r="AX214">
+        <v>5</v>
+      </c>
+      <c r="AY214">
+        <v>26</v>
+      </c>
+      <c r="AZ214">
+        <v>9</v>
+      </c>
+      <c r="BA214">
+        <v>3</v>
+      </c>
+      <c r="BB214">
+        <v>6</v>
+      </c>
+      <c r="BC214">
+        <v>9</v>
+      </c>
+      <c r="BD214">
+        <v>1.24</v>
+      </c>
+      <c r="BE214">
+        <v>8</v>
+      </c>
+      <c r="BF214">
+        <v>4.35</v>
+      </c>
+      <c r="BG214">
+        <v>1.29</v>
+      </c>
+      <c r="BH214">
+        <v>3.2</v>
+      </c>
+      <c r="BI214">
+        <v>1.5</v>
+      </c>
+      <c r="BJ214">
+        <v>2.38</v>
+      </c>
+      <c r="BK214">
+        <v>1.83</v>
+      </c>
+      <c r="BL214">
+        <v>1.85</v>
+      </c>
+      <c r="BM214">
+        <v>2.3</v>
+      </c>
+      <c r="BN214">
+        <v>1.53</v>
+      </c>
+      <c r="BO214">
+        <v>2.95</v>
+      </c>
+      <c r="BP214">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7465201</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45689.60416666666</v>
+      </c>
+      <c r="F215">
+        <v>22</v>
+      </c>
+      <c r="G215" t="s">
+        <v>87</v>
+      </c>
+      <c r="H215" t="s">
+        <v>77</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>2</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>2</v>
+      </c>
+      <c r="O215" t="s">
+        <v>234</v>
+      </c>
+      <c r="P215" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q215">
+        <v>2</v>
+      </c>
+      <c r="R215">
+        <v>2.2</v>
+      </c>
+      <c r="S215">
+        <v>8.5</v>
+      </c>
+      <c r="T215">
+        <v>1.5</v>
+      </c>
+      <c r="U215">
+        <v>2.5</v>
+      </c>
+      <c r="V215">
+        <v>3.4</v>
+      </c>
+      <c r="W215">
+        <v>1.3</v>
+      </c>
+      <c r="X215">
+        <v>10</v>
+      </c>
+      <c r="Y215">
+        <v>1.06</v>
+      </c>
+      <c r="Z215">
+        <v>1.4</v>
+      </c>
+      <c r="AA215">
+        <v>4.5</v>
+      </c>
+      <c r="AB215">
+        <v>8.5</v>
+      </c>
+      <c r="AC215">
+        <v>1.07</v>
+      </c>
+      <c r="AD215">
+        <v>9.5</v>
+      </c>
+      <c r="AE215">
+        <v>1.4</v>
+      </c>
+      <c r="AF215">
+        <v>2.95</v>
+      </c>
+      <c r="AG215">
+        <v>2.05</v>
+      </c>
+      <c r="AH215">
+        <v>1.67</v>
+      </c>
+      <c r="AI215">
+        <v>2.5</v>
+      </c>
+      <c r="AJ215">
+        <v>1.5</v>
+      </c>
+      <c r="AK215">
+        <v>1.07</v>
+      </c>
+      <c r="AL215">
+        <v>1.2</v>
+      </c>
+      <c r="AM215">
+        <v>2.9</v>
+      </c>
+      <c r="AN215">
+        <v>2.45</v>
+      </c>
+      <c r="AO215">
+        <v>1.5</v>
+      </c>
+      <c r="AP215">
+        <v>2.5</v>
+      </c>
+      <c r="AQ215">
+        <v>1.36</v>
+      </c>
+      <c r="AR215">
+        <v>1.74</v>
+      </c>
+      <c r="AS215">
+        <v>1.19</v>
+      </c>
+      <c r="AT215">
+        <v>2.93</v>
+      </c>
+      <c r="AU215">
+        <v>6</v>
+      </c>
+      <c r="AV215">
+        <v>2</v>
+      </c>
+      <c r="AW215">
+        <v>12</v>
+      </c>
+      <c r="AX215">
+        <v>9</v>
+      </c>
+      <c r="AY215">
+        <v>21</v>
+      </c>
+      <c r="AZ215">
+        <v>14</v>
+      </c>
+      <c r="BA215">
+        <v>10</v>
+      </c>
+      <c r="BB215">
+        <v>4</v>
+      </c>
+      <c r="BC215">
+        <v>14</v>
+      </c>
+      <c r="BD215">
+        <v>1.3</v>
+      </c>
+      <c r="BE215">
+        <v>7</v>
+      </c>
+      <c r="BF215">
+        <v>3.8</v>
+      </c>
+      <c r="BG215">
+        <v>1.38</v>
+      </c>
+      <c r="BH215">
+        <v>2.75</v>
+      </c>
+      <c r="BI215">
+        <v>1.65</v>
+      </c>
+      <c r="BJ215">
+        <v>2.08</v>
+      </c>
+      <c r="BK215">
+        <v>2.05</v>
+      </c>
+      <c r="BL215">
+        <v>1.67</v>
+      </c>
+      <c r="BM215">
+        <v>2.65</v>
+      </c>
+      <c r="BN215">
+        <v>1.41</v>
+      </c>
+      <c r="BO215">
+        <v>3.45</v>
+      </c>
+      <c r="BP215">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7469586</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45689.70833333334</v>
+      </c>
+      <c r="F216">
+        <v>22</v>
+      </c>
+      <c r="G216" t="s">
+        <v>82</v>
+      </c>
+      <c r="H216" t="s">
+        <v>84</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>1</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
+        <v>149</v>
+      </c>
+      <c r="P216" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q216">
+        <v>8</v>
+      </c>
+      <c r="R216">
+        <v>2.6</v>
+      </c>
+      <c r="S216">
+        <v>1.8</v>
+      </c>
+      <c r="T216">
+        <v>1.3</v>
+      </c>
+      <c r="U216">
+        <v>3.4</v>
+      </c>
+      <c r="V216">
+        <v>2.38</v>
+      </c>
+      <c r="W216">
+        <v>1.53</v>
+      </c>
+      <c r="X216">
+        <v>6</v>
+      </c>
+      <c r="Y216">
+        <v>1.13</v>
+      </c>
+      <c r="Z216">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA216">
+        <v>5.35</v>
+      </c>
+      <c r="AB216">
+        <v>1.32</v>
+      </c>
+      <c r="AC216">
+        <v>1.02</v>
+      </c>
+      <c r="AD216">
+        <v>17</v>
+      </c>
+      <c r="AE216">
+        <v>1.19</v>
+      </c>
+      <c r="AF216">
+        <v>4.75</v>
+      </c>
+      <c r="AG216">
+        <v>1.65</v>
+      </c>
+      <c r="AH216">
+        <v>2.15</v>
+      </c>
+      <c r="AI216">
+        <v>2</v>
+      </c>
+      <c r="AJ216">
+        <v>1.75</v>
+      </c>
+      <c r="AK216">
+        <v>3.1</v>
+      </c>
+      <c r="AL216">
+        <v>1.16</v>
+      </c>
+      <c r="AM216">
+        <v>1.07</v>
+      </c>
+      <c r="AN216">
+        <v>1.64</v>
+      </c>
+      <c r="AO216">
+        <v>2</v>
+      </c>
+      <c r="AP216">
+        <v>1.75</v>
+      </c>
+      <c r="AQ216">
+        <v>1.83</v>
+      </c>
+      <c r="AR216">
+        <v>1.18</v>
+      </c>
+      <c r="AS216">
+        <v>1.63</v>
+      </c>
+      <c r="AT216">
+        <v>2.81</v>
+      </c>
+      <c r="AU216">
+        <v>3</v>
+      </c>
+      <c r="AV216">
+        <v>8</v>
+      </c>
+      <c r="AW216">
+        <v>3</v>
+      </c>
+      <c r="AX216">
+        <v>14</v>
+      </c>
+      <c r="AY216">
+        <v>7</v>
+      </c>
+      <c r="AZ216">
+        <v>26</v>
+      </c>
+      <c r="BA216">
+        <v>1</v>
+      </c>
+      <c r="BB216">
+        <v>8</v>
+      </c>
+      <c r="BC216">
+        <v>9</v>
+      </c>
+      <c r="BD216">
+        <v>3.8</v>
+      </c>
+      <c r="BE216">
+        <v>7.5</v>
+      </c>
+      <c r="BF216">
+        <v>1.3</v>
+      </c>
+      <c r="BG216">
+        <v>1.3</v>
+      </c>
+      <c r="BH216">
+        <v>3.15</v>
+      </c>
+      <c r="BI216">
+        <v>1.52</v>
+      </c>
+      <c r="BJ216">
+        <v>2.33</v>
+      </c>
+      <c r="BK216">
+        <v>1.83</v>
+      </c>
+      <c r="BL216">
+        <v>1.85</v>
+      </c>
+      <c r="BM216">
+        <v>2.3</v>
+      </c>
+      <c r="BN216">
+        <v>1.54</v>
+      </c>
+      <c r="BO216">
+        <v>2.95</v>
+      </c>
+      <c r="BP216">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7465209</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45690.41666666666</v>
+      </c>
+      <c r="F217">
+        <v>22</v>
+      </c>
+      <c r="G217" t="s">
+        <v>81</v>
+      </c>
+      <c r="H217" t="s">
+        <v>86</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>1</v>
+      </c>
+      <c r="O217" t="s">
+        <v>190</v>
+      </c>
+      <c r="P217" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q217">
+        <v>1.57</v>
+      </c>
+      <c r="R217">
+        <v>3</v>
+      </c>
+      <c r="S217">
+        <v>9</v>
+      </c>
+      <c r="T217">
+        <v>1.2</v>
+      </c>
+      <c r="U217">
+        <v>4.33</v>
+      </c>
+      <c r="V217">
+        <v>2</v>
+      </c>
+      <c r="W217">
+        <v>1.73</v>
+      </c>
+      <c r="X217">
+        <v>4</v>
+      </c>
+      <c r="Y217">
+        <v>1.22</v>
+      </c>
+      <c r="Z217">
+        <v>1.2</v>
+      </c>
+      <c r="AA217">
+        <v>7.28</v>
+      </c>
+      <c r="AB217">
+        <v>13.28</v>
+      </c>
+      <c r="AC217">
+        <v>1.01</v>
+      </c>
+      <c r="AD217">
+        <v>29</v>
+      </c>
+      <c r="AE217">
+        <v>1.11</v>
+      </c>
+      <c r="AF217">
+        <v>6.5</v>
+      </c>
+      <c r="AG217">
+        <v>1.36</v>
+      </c>
+      <c r="AH217">
+        <v>3.2</v>
+      </c>
+      <c r="AI217">
+        <v>1.91</v>
+      </c>
+      <c r="AJ217">
+        <v>1.91</v>
+      </c>
+      <c r="AK217">
+        <v>1.04</v>
+      </c>
+      <c r="AL217">
+        <v>1.1</v>
+      </c>
+      <c r="AM217">
+        <v>4.4</v>
+      </c>
+      <c r="AN217">
+        <v>2</v>
+      </c>
+      <c r="AO217">
+        <v>0.73</v>
+      </c>
+      <c r="AP217">
+        <v>2.1</v>
+      </c>
+      <c r="AQ217">
+        <v>0.67</v>
+      </c>
+      <c r="AR217">
+        <v>2.09</v>
+      </c>
+      <c r="AS217">
+        <v>1.17</v>
+      </c>
+      <c r="AT217">
+        <v>3.26</v>
+      </c>
+      <c r="AU217">
+        <v>5</v>
+      </c>
+      <c r="AV217">
+        <v>0</v>
+      </c>
+      <c r="AW217">
+        <v>7</v>
+      </c>
+      <c r="AX217">
+        <v>4</v>
+      </c>
+      <c r="AY217">
+        <v>14</v>
+      </c>
+      <c r="AZ217">
+        <v>6</v>
+      </c>
+      <c r="BA217">
+        <v>5</v>
+      </c>
+      <c r="BB217">
+        <v>2</v>
+      </c>
+      <c r="BC217">
+        <v>7</v>
+      </c>
+      <c r="BD217">
+        <v>1.19</v>
+      </c>
+      <c r="BE217">
+        <v>8.5</v>
+      </c>
+      <c r="BF217">
+        <v>5.1</v>
+      </c>
+      <c r="BG217">
+        <v>1.25</v>
+      </c>
+      <c r="BH217">
+        <v>3.4</v>
+      </c>
+      <c r="BI217">
+        <v>1.44</v>
+      </c>
+      <c r="BJ217">
+        <v>2.55</v>
+      </c>
+      <c r="BK217">
+        <v>1.72</v>
+      </c>
+      <c r="BL217">
+        <v>1.98</v>
+      </c>
+      <c r="BM217">
+        <v>2.1</v>
+      </c>
+      <c r="BN217">
+        <v>1.63</v>
+      </c>
+      <c r="BO217">
+        <v>2.65</v>
+      </c>
+      <c r="BP217">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="325">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -721,6 +721,18 @@
     <t>['26', '90+3']</t>
   </si>
   <si>
+    <t>['44', '68']</t>
+  </si>
+  <si>
+    <t>['34', '74']</t>
+  </si>
+  <si>
+    <t>['15', '45+2']</t>
+  </si>
+  <si>
+    <t>['8', '79']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -974,6 +986,9 @@
   </si>
   <si>
     <t>['66']</t>
+  </si>
+  <si>
+    <t>['33', '69']</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1591,7 +1606,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1875,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ3">
         <v>1.09</v>
@@ -2003,7 +2018,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2209,7 +2224,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2415,7 +2430,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2493,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ6">
         <v>0.91</v>
@@ -2621,7 +2636,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2699,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2827,7 +2842,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3033,7 +3048,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3445,7 +3460,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3857,7 +3872,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4141,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ14">
         <v>1.36</v>
@@ -4350,7 +4365,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ15">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4556,7 +4571,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ16">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5174,7 +5189,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5711,7 +5726,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -5792,7 +5807,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ22">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR22">
         <v>1.08</v>
@@ -6123,7 +6138,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6947,7 +6962,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7231,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
         <v>0.8</v>
@@ -8183,7 +8198,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8261,7 +8276,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
         <v>1.64</v>
@@ -8676,7 +8691,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR36">
         <v>0.71</v>
@@ -8801,7 +8816,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8879,10 +8894,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -9007,7 +9022,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9294,7 +9309,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR39">
         <v>1.12</v>
@@ -9703,7 +9718,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ41">
         <v>0.91</v>
@@ -9831,7 +9846,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10037,7 +10052,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10449,7 +10464,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10861,7 +10876,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10939,7 +10954,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ47">
         <v>2</v>
@@ -11067,7 +11082,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11148,7 +11163,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ48">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11766,7 +11781,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR51">
         <v>1.4</v>
@@ -11969,7 +11984,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ52">
         <v>0.8</v>
@@ -12097,7 +12112,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12178,7 +12193,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ53">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR53">
         <v>1.17</v>
@@ -12590,7 +12605,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ55">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -12715,7 +12730,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12793,10 +12808,10 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -12999,7 +13014,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57">
         <v>1.09</v>
@@ -13127,7 +13142,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13620,7 +13635,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -13745,7 +13760,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14157,7 +14172,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14235,7 +14250,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ63">
         <v>1.36</v>
@@ -14441,7 +14456,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ64">
         <v>0.8</v>
@@ -14569,7 +14584,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14775,7 +14790,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15059,7 +15074,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67">
         <v>1.42</v>
@@ -15393,7 +15408,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15599,7 +15614,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16011,7 +16026,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16835,7 +16850,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -16913,7 +16928,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ76">
         <v>2</v>
@@ -17531,7 +17546,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ79">
         <v>0.2</v>
@@ -17659,7 +17674,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17865,7 +17880,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17946,7 +17961,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -18770,7 +18785,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ85">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR85">
         <v>1.24</v>
@@ -18895,7 +18910,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19307,7 +19322,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19385,10 +19400,10 @@
         <v>2</v>
       </c>
       <c r="AP88">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ88">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19513,7 +19528,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19925,7 +19940,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20131,7 +20146,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20543,7 +20558,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20621,7 +20636,7 @@
         <v>0.5</v>
       </c>
       <c r="AP94">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ94">
         <v>1.09</v>
@@ -20827,10 +20842,10 @@
         <v>1.25</v>
       </c>
       <c r="AP95">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ95">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -20955,7 +20970,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21985,7 +22000,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22063,10 +22078,10 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR101">
         <v>1.21</v>
@@ -22191,7 +22206,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22397,7 +22412,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23015,7 +23030,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23302,7 +23317,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR107">
         <v>1.1</v>
@@ -23711,7 +23726,7 @@
         <v>1.8</v>
       </c>
       <c r="AP109">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ109">
         <v>1.8</v>
@@ -23839,7 +23854,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24126,7 +24141,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ111">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR111">
         <v>1.44</v>
@@ -24535,7 +24550,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ113">
         <v>0.27</v>
@@ -24663,7 +24678,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24741,7 +24756,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ114">
         <v>0.91</v>
@@ -24950,7 +24965,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25075,7 +25090,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25281,7 +25296,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25362,7 +25377,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ117">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR117">
         <v>1.53</v>
@@ -25487,7 +25502,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25899,7 +25914,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25980,7 +25995,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR120">
         <v>1.55</v>
@@ -26723,7 +26738,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26801,10 +26816,10 @@
         <v>0.6</v>
       </c>
       <c r="AP124">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ124">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR124">
         <v>1.82</v>
@@ -27422,7 +27437,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ127">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -27959,7 +27974,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28037,7 +28052,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ130">
         <v>1.09</v>
@@ -28371,7 +28386,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28655,7 +28670,7 @@
         <v>0.17</v>
       </c>
       <c r="AP133">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ133">
         <v>0.2</v>
@@ -28783,7 +28798,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28989,7 +29004,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29067,7 +29082,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ135">
         <v>1.64</v>
@@ -29401,7 +29416,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29688,7 +29703,7 @@
         <v>2</v>
       </c>
       <c r="AQ138">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR138">
         <v>1.36</v>
@@ -29813,7 +29828,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30019,7 +30034,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30100,7 +30115,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR140">
         <v>1.94</v>
@@ -30512,7 +30527,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ142">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR142">
         <v>1.12</v>
@@ -30637,7 +30652,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30843,7 +30858,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31255,7 +31270,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31336,7 +31351,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR146">
         <v>1.72</v>
@@ -31873,7 +31888,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32079,7 +32094,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32697,7 +32712,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32775,7 +32790,7 @@
         <v>2.2</v>
       </c>
       <c r="AP153">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ153">
         <v>2</v>
@@ -32981,7 +32996,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154">
         <v>1.42</v>
@@ -33109,7 +33124,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33187,7 +33202,7 @@
         <v>1.71</v>
       </c>
       <c r="AP155">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ155">
         <v>1.83</v>
@@ -33315,7 +33330,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33396,7 +33411,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ156">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR156">
         <v>0.98</v>
@@ -33727,7 +33742,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33805,7 +33820,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ158">
         <v>0.67</v>
@@ -33933,7 +33948,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -35044,7 +35059,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ164">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR164">
         <v>1.37</v>
@@ -35169,7 +35184,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35581,7 +35596,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35662,7 +35677,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ167">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR167">
         <v>1.17</v>
@@ -35868,7 +35883,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ168">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR168">
         <v>1.43</v>
@@ -35993,7 +36008,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36405,7 +36420,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36895,7 +36910,7 @@
         <v>0.38</v>
       </c>
       <c r="AP173">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ173">
         <v>0.27</v>
@@ -37310,7 +37325,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ175">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR175">
         <v>1.41</v>
@@ -37513,10 +37528,10 @@
         <v>1.5</v>
       </c>
       <c r="AP176">
+        <v>1.83</v>
+      </c>
+      <c r="AQ176">
         <v>1.73</v>
-      </c>
-      <c r="AQ176">
-        <v>1.8</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37641,7 +37656,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37847,7 +37862,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37925,7 +37940,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ178">
         <v>0.67</v>
@@ -38053,7 +38068,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38259,7 +38274,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38749,7 +38764,7 @@
         <v>1.33</v>
       </c>
       <c r="AP182">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ182">
         <v>1.42</v>
@@ -38877,7 +38892,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -38955,7 +38970,7 @@
         <v>1.78</v>
       </c>
       <c r="AP183">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ183">
         <v>1.83</v>
@@ -39164,7 +39179,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ184">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR184">
         <v>1.61</v>
@@ -39289,7 +39304,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40113,7 +40128,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40937,7 +40952,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41015,7 +41030,7 @@
         <v>0.67</v>
       </c>
       <c r="AP193">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ193">
         <v>0.91</v>
@@ -41349,7 +41364,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41427,7 +41442,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ195">
         <v>0.67</v>
@@ -41761,7 +41776,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41842,7 +41857,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ197">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR197">
         <v>1.41</v>
@@ -41967,7 +41982,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42048,7 +42063,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ198">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR198">
         <v>1.8</v>
@@ -42251,7 +42266,7 @@
         <v>1.3</v>
       </c>
       <c r="AP199">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ199">
         <v>1.42</v>
@@ -42457,10 +42472,10 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ200">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR200">
         <v>1.33</v>
@@ -42997,7 +43012,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43203,7 +43218,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43409,7 +43424,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43615,7 +43630,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44027,7 +44042,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44645,7 +44660,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44726,7 +44741,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ211">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR211">
         <v>1.16</v>
@@ -44851,7 +44866,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -46038,6 +46053,830 @@
       </c>
       <c r="BP217">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7465208</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45690.51041666666</v>
+      </c>
+      <c r="F218">
+        <v>22</v>
+      </c>
+      <c r="G218" t="s">
+        <v>75</v>
+      </c>
+      <c r="H218" t="s">
+        <v>72</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>2</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>3</v>
+      </c>
+      <c r="O218" t="s">
+        <v>235</v>
+      </c>
+      <c r="P218" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q218">
+        <v>3.2</v>
+      </c>
+      <c r="R218">
+        <v>2</v>
+      </c>
+      <c r="S218">
+        <v>3.75</v>
+      </c>
+      <c r="T218">
+        <v>1.5</v>
+      </c>
+      <c r="U218">
+        <v>2.5</v>
+      </c>
+      <c r="V218">
+        <v>3.4</v>
+      </c>
+      <c r="W218">
+        <v>1.3</v>
+      </c>
+      <c r="X218">
+        <v>10</v>
+      </c>
+      <c r="Y218">
+        <v>1.06</v>
+      </c>
+      <c r="Z218">
+        <v>2.49</v>
+      </c>
+      <c r="AA218">
+        <v>3.1</v>
+      </c>
+      <c r="AB218">
+        <v>3.24</v>
+      </c>
+      <c r="AC218">
+        <v>1.1</v>
+      </c>
+      <c r="AD218">
+        <v>8</v>
+      </c>
+      <c r="AE218">
+        <v>1.44</v>
+      </c>
+      <c r="AF218">
+        <v>2.8</v>
+      </c>
+      <c r="AG218">
+        <v>2.2</v>
+      </c>
+      <c r="AH218">
+        <v>1.61</v>
+      </c>
+      <c r="AI218">
+        <v>1.95</v>
+      </c>
+      <c r="AJ218">
+        <v>1.8</v>
+      </c>
+      <c r="AK218">
+        <v>1.38</v>
+      </c>
+      <c r="AL218">
+        <v>1.35</v>
+      </c>
+      <c r="AM218">
+        <v>1.52</v>
+      </c>
+      <c r="AN218">
+        <v>1.2</v>
+      </c>
+      <c r="AO218">
+        <v>0.5</v>
+      </c>
+      <c r="AP218">
+        <v>1.36</v>
+      </c>
+      <c r="AQ218">
+        <v>0.45</v>
+      </c>
+      <c r="AR218">
+        <v>1.3</v>
+      </c>
+      <c r="AS218">
+        <v>1.28</v>
+      </c>
+      <c r="AT218">
+        <v>2.58</v>
+      </c>
+      <c r="AU218">
+        <v>6</v>
+      </c>
+      <c r="AV218">
+        <v>3</v>
+      </c>
+      <c r="AW218">
+        <v>3</v>
+      </c>
+      <c r="AX218">
+        <v>1</v>
+      </c>
+      <c r="AY218">
+        <v>10</v>
+      </c>
+      <c r="AZ218">
+        <v>4</v>
+      </c>
+      <c r="BA218">
+        <v>5</v>
+      </c>
+      <c r="BB218">
+        <v>2</v>
+      </c>
+      <c r="BC218">
+        <v>7</v>
+      </c>
+      <c r="BD218">
+        <v>1.66</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>2.48</v>
+      </c>
+      <c r="BG218">
+        <v>1.41</v>
+      </c>
+      <c r="BH218">
+        <v>2.65</v>
+      </c>
+      <c r="BI218">
+        <v>1.68</v>
+      </c>
+      <c r="BJ218">
+        <v>2.02</v>
+      </c>
+      <c r="BK218">
+        <v>2.08</v>
+      </c>
+      <c r="BL218">
+        <v>1.65</v>
+      </c>
+      <c r="BM218">
+        <v>2.65</v>
+      </c>
+      <c r="BN218">
+        <v>1.4</v>
+      </c>
+      <c r="BO218">
+        <v>3.55</v>
+      </c>
+      <c r="BP218">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7465204</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45690.60416666666</v>
+      </c>
+      <c r="F219">
+        <v>22</v>
+      </c>
+      <c r="G219" t="s">
+        <v>74</v>
+      </c>
+      <c r="H219" t="s">
+        <v>76</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>2</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>3</v>
+      </c>
+      <c r="O219" t="s">
+        <v>236</v>
+      </c>
+      <c r="P219" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q219">
+        <v>3.75</v>
+      </c>
+      <c r="R219">
+        <v>1.91</v>
+      </c>
+      <c r="S219">
+        <v>3.5</v>
+      </c>
+      <c r="T219">
+        <v>1.62</v>
+      </c>
+      <c r="U219">
+        <v>2.2</v>
+      </c>
+      <c r="V219">
+        <v>4</v>
+      </c>
+      <c r="W219">
+        <v>1.22</v>
+      </c>
+      <c r="X219">
+        <v>13</v>
+      </c>
+      <c r="Y219">
+        <v>1.04</v>
+      </c>
+      <c r="Z219">
+        <v>3</v>
+      </c>
+      <c r="AA219">
+        <v>3</v>
+      </c>
+      <c r="AB219">
+        <v>2.5</v>
+      </c>
+      <c r="AC219">
+        <v>1.12</v>
+      </c>
+      <c r="AD219">
+        <v>6.5</v>
+      </c>
+      <c r="AE219">
+        <v>1.5</v>
+      </c>
+      <c r="AF219">
+        <v>2.4</v>
+      </c>
+      <c r="AG219">
+        <v>2.75</v>
+      </c>
+      <c r="AH219">
+        <v>1.44</v>
+      </c>
+      <c r="AI219">
+        <v>2.1</v>
+      </c>
+      <c r="AJ219">
+        <v>1.67</v>
+      </c>
+      <c r="AK219">
+        <v>1.49</v>
+      </c>
+      <c r="AL219">
+        <v>1.38</v>
+      </c>
+      <c r="AM219">
+        <v>1.37</v>
+      </c>
+      <c r="AN219">
+        <v>1.73</v>
+      </c>
+      <c r="AO219">
+        <v>1.4</v>
+      </c>
+      <c r="AP219">
+        <v>1.83</v>
+      </c>
+      <c r="AQ219">
+        <v>1.27</v>
+      </c>
+      <c r="AR219">
+        <v>1.48</v>
+      </c>
+      <c r="AS219">
+        <v>1.08</v>
+      </c>
+      <c r="AT219">
+        <v>2.56</v>
+      </c>
+      <c r="AU219">
+        <v>5</v>
+      </c>
+      <c r="AV219">
+        <v>4</v>
+      </c>
+      <c r="AW219">
+        <v>7</v>
+      </c>
+      <c r="AX219">
+        <v>10</v>
+      </c>
+      <c r="AY219">
+        <v>14</v>
+      </c>
+      <c r="AZ219">
+        <v>16</v>
+      </c>
+      <c r="BA219">
+        <v>3</v>
+      </c>
+      <c r="BB219">
+        <v>5</v>
+      </c>
+      <c r="BC219">
+        <v>8</v>
+      </c>
+      <c r="BD219">
+        <v>1.98</v>
+      </c>
+      <c r="BE219">
+        <v>6.5</v>
+      </c>
+      <c r="BF219">
+        <v>1.98</v>
+      </c>
+      <c r="BG219">
+        <v>1.3</v>
+      </c>
+      <c r="BH219">
+        <v>3.15</v>
+      </c>
+      <c r="BI219">
+        <v>1.53</v>
+      </c>
+      <c r="BJ219">
+        <v>2.32</v>
+      </c>
+      <c r="BK219">
+        <v>1.85</v>
+      </c>
+      <c r="BL219">
+        <v>1.83</v>
+      </c>
+      <c r="BM219">
+        <v>2.33</v>
+      </c>
+      <c r="BN219">
+        <v>1.52</v>
+      </c>
+      <c r="BO219">
+        <v>3.05</v>
+      </c>
+      <c r="BP219">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7465207</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45690.70833333334</v>
+      </c>
+      <c r="F220">
+        <v>22</v>
+      </c>
+      <c r="G220" t="s">
+        <v>71</v>
+      </c>
+      <c r="H220" t="s">
+        <v>70</v>
+      </c>
+      <c r="I220">
+        <v>2</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>3</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>2</v>
+      </c>
+      <c r="N220">
+        <v>4</v>
+      </c>
+      <c r="O220" t="s">
+        <v>237</v>
+      </c>
+      <c r="P220" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q220">
+        <v>3.6</v>
+      </c>
+      <c r="R220">
+        <v>2</v>
+      </c>
+      <c r="S220">
+        <v>3.25</v>
+      </c>
+      <c r="T220">
+        <v>1.5</v>
+      </c>
+      <c r="U220">
+        <v>2.5</v>
+      </c>
+      <c r="V220">
+        <v>3.4</v>
+      </c>
+      <c r="W220">
+        <v>1.3</v>
+      </c>
+      <c r="X220">
+        <v>10</v>
+      </c>
+      <c r="Y220">
+        <v>1.06</v>
+      </c>
+      <c r="Z220">
+        <v>3</v>
+      </c>
+      <c r="AA220">
+        <v>3.2</v>
+      </c>
+      <c r="AB220">
+        <v>2.4</v>
+      </c>
+      <c r="AC220">
+        <v>1.08</v>
+      </c>
+      <c r="AD220">
+        <v>9</v>
+      </c>
+      <c r="AE220">
+        <v>1.4</v>
+      </c>
+      <c r="AF220">
+        <v>3</v>
+      </c>
+      <c r="AG220">
+        <v>2.2</v>
+      </c>
+      <c r="AH220">
+        <v>1.6</v>
+      </c>
+      <c r="AI220">
+        <v>1.95</v>
+      </c>
+      <c r="AJ220">
+        <v>1.8</v>
+      </c>
+      <c r="AK220">
+        <v>1.55</v>
+      </c>
+      <c r="AL220">
+        <v>1.33</v>
+      </c>
+      <c r="AM220">
+        <v>1.37</v>
+      </c>
+      <c r="AN220">
+        <v>1.6</v>
+      </c>
+      <c r="AO220">
+        <v>1.8</v>
+      </c>
+      <c r="AP220">
+        <v>1.55</v>
+      </c>
+      <c r="AQ220">
+        <v>1.73</v>
+      </c>
+      <c r="AR220">
+        <v>1.72</v>
+      </c>
+      <c r="AS220">
+        <v>1.36</v>
+      </c>
+      <c r="AT220">
+        <v>3.08</v>
+      </c>
+      <c r="AU220">
+        <v>7</v>
+      </c>
+      <c r="AV220">
+        <v>5</v>
+      </c>
+      <c r="AW220">
+        <v>4</v>
+      </c>
+      <c r="AX220">
+        <v>8</v>
+      </c>
+      <c r="AY220">
+        <v>11</v>
+      </c>
+      <c r="AZ220">
+        <v>14</v>
+      </c>
+      <c r="BA220">
+        <v>3</v>
+      </c>
+      <c r="BB220">
+        <v>7</v>
+      </c>
+      <c r="BC220">
+        <v>10</v>
+      </c>
+      <c r="BD220">
+        <v>2</v>
+      </c>
+      <c r="BE220">
+        <v>6.4</v>
+      </c>
+      <c r="BF220">
+        <v>1.98</v>
+      </c>
+      <c r="BG220">
+        <v>1.32</v>
+      </c>
+      <c r="BH220">
+        <v>3.05</v>
+      </c>
+      <c r="BI220">
+        <v>1.55</v>
+      </c>
+      <c r="BJ220">
+        <v>2.25</v>
+      </c>
+      <c r="BK220">
+        <v>1.88</v>
+      </c>
+      <c r="BL220">
+        <v>1.8</v>
+      </c>
+      <c r="BM220">
+        <v>2.4</v>
+      </c>
+      <c r="BN220">
+        <v>1.5</v>
+      </c>
+      <c r="BO220">
+        <v>3.05</v>
+      </c>
+      <c r="BP220">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7465203</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45691.70833333334</v>
+      </c>
+      <c r="F221">
+        <v>22</v>
+      </c>
+      <c r="G221" t="s">
+        <v>89</v>
+      </c>
+      <c r="H221" t="s">
+        <v>73</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
+      </c>
+      <c r="L221">
+        <v>2</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>3</v>
+      </c>
+      <c r="O221" t="s">
+        <v>238</v>
+      </c>
+      <c r="P221" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q221">
+        <v>2.2</v>
+      </c>
+      <c r="R221">
+        <v>2.3</v>
+      </c>
+      <c r="S221">
+        <v>5.5</v>
+      </c>
+      <c r="T221">
+        <v>1.36</v>
+      </c>
+      <c r="U221">
+        <v>3</v>
+      </c>
+      <c r="V221">
+        <v>2.63</v>
+      </c>
+      <c r="W221">
+        <v>1.44</v>
+      </c>
+      <c r="X221">
+        <v>7</v>
+      </c>
+      <c r="Y221">
+        <v>1.1</v>
+      </c>
+      <c r="Z221">
+        <v>1.63</v>
+      </c>
+      <c r="AA221">
+        <v>4.13</v>
+      </c>
+      <c r="AB221">
+        <v>5.5</v>
+      </c>
+      <c r="AC221">
+        <v>1.04</v>
+      </c>
+      <c r="AD221">
+        <v>13</v>
+      </c>
+      <c r="AE221">
+        <v>1.26</v>
+      </c>
+      <c r="AF221">
+        <v>4</v>
+      </c>
+      <c r="AG221">
+        <v>1.84</v>
+      </c>
+      <c r="AH221">
+        <v>2.06</v>
+      </c>
+      <c r="AI221">
+        <v>1.91</v>
+      </c>
+      <c r="AJ221">
+        <v>1.91</v>
+      </c>
+      <c r="AK221">
+        <v>1.16</v>
+      </c>
+      <c r="AL221">
+        <v>1.24</v>
+      </c>
+      <c r="AM221">
+        <v>2.2</v>
+      </c>
+      <c r="AN221">
+        <v>1.6</v>
+      </c>
+      <c r="AO221">
+        <v>1</v>
+      </c>
+      <c r="AP221">
+        <v>1.73</v>
+      </c>
+      <c r="AQ221">
+        <v>0.91</v>
+      </c>
+      <c r="AR221">
+        <v>1.35</v>
+      </c>
+      <c r="AS221">
+        <v>1.03</v>
+      </c>
+      <c r="AT221">
+        <v>2.38</v>
+      </c>
+      <c r="AU221">
+        <v>5</v>
+      </c>
+      <c r="AV221">
+        <v>3</v>
+      </c>
+      <c r="AW221">
+        <v>8</v>
+      </c>
+      <c r="AX221">
+        <v>8</v>
+      </c>
+      <c r="AY221">
+        <v>16</v>
+      </c>
+      <c r="AZ221">
+        <v>15</v>
+      </c>
+      <c r="BA221">
+        <v>11</v>
+      </c>
+      <c r="BB221">
+        <v>3</v>
+      </c>
+      <c r="BC221">
+        <v>14</v>
+      </c>
+      <c r="BD221">
+        <v>1.38</v>
+      </c>
+      <c r="BE221">
+        <v>6.75</v>
+      </c>
+      <c r="BF221">
+        <v>3.4</v>
+      </c>
+      <c r="BG221">
+        <v>1.38</v>
+      </c>
+      <c r="BH221">
+        <v>2.7</v>
+      </c>
+      <c r="BI221">
+        <v>1.66</v>
+      </c>
+      <c r="BJ221">
+        <v>2.06</v>
+      </c>
+      <c r="BK221">
+        <v>2.06</v>
+      </c>
+      <c r="BL221">
+        <v>1.66</v>
+      </c>
+      <c r="BM221">
+        <v>2.65</v>
+      </c>
+      <c r="BN221">
+        <v>1.41</v>
+      </c>
+      <c r="BO221">
+        <v>3.45</v>
+      </c>
+      <c r="BP221">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,9 @@
     <t>['8', '79']</t>
   </si>
   <si>
+    <t>['71']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1350,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1606,7 +1609,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2018,7 +2021,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2224,7 +2227,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2430,7 +2433,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2636,7 +2639,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2842,7 +2845,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3048,7 +3051,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3460,7 +3463,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3872,7 +3875,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4983,7 +4986,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ18">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5726,7 +5729,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6138,7 +6141,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6216,7 +6219,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
         <v>2</v>
@@ -6962,7 +6965,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7661,7 +7664,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ31">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR31">
         <v>1.51</v>
@@ -8198,7 +8201,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8816,7 +8819,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9022,7 +9025,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9846,7 +9849,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10052,7 +10055,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10464,7 +10467,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10751,7 +10754,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ46">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR46">
         <v>1.11</v>
@@ -10876,7 +10879,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11082,7 +11085,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11572,7 +11575,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ50">
         <v>0.8</v>
@@ -12112,7 +12115,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12730,7 +12733,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13142,7 +13145,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13760,7 +13763,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14044,7 +14047,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ62">
         <v>1.8</v>
@@ -14172,7 +14175,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14584,7 +14587,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14665,7 +14668,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ65">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14790,7 +14793,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15408,7 +15411,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15614,7 +15617,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16026,7 +16029,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16516,7 +16519,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ74">
         <v>0.91</v>
@@ -16850,7 +16853,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17674,7 +17677,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17880,7 +17883,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18910,7 +18913,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19322,7 +19325,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19528,7 +19531,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19940,7 +19943,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20146,7 +20149,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20227,7 +20230,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ92">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR92">
         <v>1.06</v>
@@ -20558,7 +20561,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20970,7 +20973,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -22000,7 +22003,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22206,7 +22209,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22412,7 +22415,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22696,7 +22699,7 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
         <v>0.67</v>
@@ -23030,7 +23033,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23854,7 +23857,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24553,7 +24556,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ113">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24678,7 +24681,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25090,7 +25093,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25296,7 +25299,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25502,7 +25505,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25914,7 +25917,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25992,7 +25995,7 @@
         <v>0.5</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ120">
         <v>0.91</v>
@@ -26738,7 +26741,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27849,7 +27852,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ129">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR129">
         <v>1.27</v>
@@ -27974,7 +27977,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28386,7 +28389,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28798,7 +28801,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29004,7 +29007,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29416,7 +29419,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29828,7 +29831,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30034,7 +30037,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30652,7 +30655,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30858,7 +30861,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31270,7 +31273,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31348,7 +31351,7 @@
         <v>1.33</v>
       </c>
       <c r="AP146">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ146">
         <v>1.73</v>
@@ -31888,7 +31891,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32094,7 +32097,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32587,7 +32590,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ152">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR152">
         <v>1.35</v>
@@ -32712,7 +32715,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33124,7 +33127,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33330,7 +33333,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33742,7 +33745,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33948,7 +33951,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -35184,7 +35187,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35262,7 +35265,7 @@
         <v>1.88</v>
       </c>
       <c r="AP165">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ165">
         <v>1.83</v>
@@ -35596,7 +35599,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36008,7 +36011,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36420,7 +36423,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36913,7 +36916,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ173">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR173">
         <v>1.37</v>
@@ -37656,7 +37659,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37862,7 +37865,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38068,7 +38071,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38274,7 +38277,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38892,7 +38895,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39176,7 +39179,7 @@
         <v>0.5</v>
       </c>
       <c r="AP184">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ184">
         <v>0.45</v>
@@ -39304,7 +39307,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40128,7 +40131,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40827,7 +40830,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ192">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR192">
         <v>1.16</v>
@@ -40952,7 +40955,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41364,7 +41367,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41776,7 +41779,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41982,7 +41985,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -43012,7 +43015,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43218,7 +43221,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43424,7 +43427,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43630,7 +43633,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43914,7 +43917,7 @@
         <v>1.2</v>
       </c>
       <c r="AP207">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ207">
         <v>1.09</v>
@@ -44042,7 +44045,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44660,7 +44663,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44866,7 +44869,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45359,7 +45362,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ214">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR214">
         <v>1.55</v>
@@ -46514,7 +46517,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -46877,6 +46880,212 @@
       </c>
       <c r="BP221">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7465212</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45695.70833333334</v>
+      </c>
+      <c r="F222">
+        <v>23</v>
+      </c>
+      <c r="G222" t="s">
+        <v>88</v>
+      </c>
+      <c r="H222" t="s">
+        <v>78</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>1</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>239</v>
+      </c>
+      <c r="P222" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q222">
+        <v>2.05</v>
+      </c>
+      <c r="R222">
+        <v>2.2</v>
+      </c>
+      <c r="S222">
+        <v>7</v>
+      </c>
+      <c r="T222">
+        <v>1.44</v>
+      </c>
+      <c r="U222">
+        <v>2.63</v>
+      </c>
+      <c r="V222">
+        <v>3</v>
+      </c>
+      <c r="W222">
+        <v>1.36</v>
+      </c>
+      <c r="X222">
+        <v>9</v>
+      </c>
+      <c r="Y222">
+        <v>1.07</v>
+      </c>
+      <c r="Z222">
+        <v>1.48</v>
+      </c>
+      <c r="AA222">
+        <v>4</v>
+      </c>
+      <c r="AB222">
+        <v>7</v>
+      </c>
+      <c r="AC222">
+        <v>1.05</v>
+      </c>
+      <c r="AD222">
+        <v>11</v>
+      </c>
+      <c r="AE222">
+        <v>1.33</v>
+      </c>
+      <c r="AF222">
+        <v>3.4</v>
+      </c>
+      <c r="AG222">
+        <v>2.1</v>
+      </c>
+      <c r="AH222">
+        <v>1.73</v>
+      </c>
+      <c r="AI222">
+        <v>2.2</v>
+      </c>
+      <c r="AJ222">
+        <v>1.62</v>
+      </c>
+      <c r="AK222">
+        <v>1.11</v>
+      </c>
+      <c r="AL222">
+        <v>1.23</v>
+      </c>
+      <c r="AM222">
+        <v>2.5</v>
+      </c>
+      <c r="AN222">
+        <v>1.5</v>
+      </c>
+      <c r="AO222">
+        <v>0.27</v>
+      </c>
+      <c r="AP222">
+        <v>1.64</v>
+      </c>
+      <c r="AQ222">
+        <v>0.25</v>
+      </c>
+      <c r="AR222">
+        <v>1.62</v>
+      </c>
+      <c r="AS222">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT222">
+        <v>2.56</v>
+      </c>
+      <c r="AU222">
+        <v>7</v>
+      </c>
+      <c r="AV222">
+        <v>4</v>
+      </c>
+      <c r="AW222">
+        <v>14</v>
+      </c>
+      <c r="AX222">
+        <v>5</v>
+      </c>
+      <c r="AY222">
+        <v>26</v>
+      </c>
+      <c r="AZ222">
+        <v>9</v>
+      </c>
+      <c r="BA222">
+        <v>4</v>
+      </c>
+      <c r="BB222">
+        <v>2</v>
+      </c>
+      <c r="BC222">
+        <v>6</v>
+      </c>
+      <c r="BD222">
+        <v>1.3</v>
+      </c>
+      <c r="BE222">
+        <v>7.5</v>
+      </c>
+      <c r="BF222">
+        <v>3.8</v>
+      </c>
+      <c r="BG222">
+        <v>1.3</v>
+      </c>
+      <c r="BH222">
+        <v>3.15</v>
+      </c>
+      <c r="BI222">
+        <v>1.52</v>
+      </c>
+      <c r="BJ222">
+        <v>2.33</v>
+      </c>
+      <c r="BK222">
+        <v>1.85</v>
+      </c>
+      <c r="BL222">
+        <v>1.83</v>
+      </c>
+      <c r="BM222">
+        <v>2.32</v>
+      </c>
+      <c r="BN222">
+        <v>1.52</v>
+      </c>
+      <c r="BO222">
+        <v>3</v>
+      </c>
+      <c r="BP222">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,12 @@
     <t>['71']</t>
   </si>
   <si>
+    <t>['63', '65', '87']</t>
+  </si>
+  <si>
+    <t>['42', '45+1', '79']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -992,6 +998,12 @@
   </si>
   <si>
     <t>['33', '69']</t>
+  </si>
+  <si>
+    <t>['10', '22']</t>
+  </si>
+  <si>
+    <t>['53', '66']</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1621,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1687,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ2">
         <v>0.8</v>
@@ -1896,7 +1908,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ3">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2021,7 +2033,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2099,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4">
         <v>0.67</v>
@@ -2227,7 +2239,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2305,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ5">
         <v>0.91</v>
@@ -2433,7 +2445,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2639,7 +2651,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2845,7 +2857,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3051,7 +3063,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3463,7 +3475,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3544,7 +3556,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ11">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3747,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
         <v>0.36</v>
@@ -3875,7 +3887,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3956,7 +3968,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ13">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4983,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ18">
         <v>0.25</v>
@@ -5398,7 +5410,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ20">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5604,7 +5616,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ21">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5729,7 +5741,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6141,7 +6153,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6425,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ25">
         <v>0.36</v>
@@ -6965,7 +6977,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7455,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ30">
         <v>1.83</v>
@@ -7867,10 +7879,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ32">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -8201,7 +8213,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8282,7 +8294,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR34">
         <v>0.87</v>
@@ -8819,7 +8831,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9025,7 +9037,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9106,7 +9118,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ38">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.9</v>
@@ -9515,10 +9527,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ40">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>2.11</v>
@@ -9849,7 +9861,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9930,7 +9942,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ42">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR42">
         <v>1.48</v>
@@ -10055,7 +10067,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10467,7 +10479,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10751,7 +10763,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ46">
         <v>0.25</v>
@@ -10879,7 +10891,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11085,7 +11097,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11163,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ48">
         <v>1.73</v>
@@ -12115,7 +12127,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12733,7 +12745,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13020,7 +13032,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ57">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.38</v>
@@ -13145,7 +13157,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13223,7 +13235,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ58">
         <v>0.2</v>
@@ -13635,7 +13647,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60">
         <v>0.45</v>
@@ -13763,7 +13775,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14050,7 +14062,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ62">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR62">
         <v>1.49</v>
@@ -14175,7 +14187,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14587,7 +14599,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14793,7 +14805,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14871,7 +14883,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ66">
         <v>0.67</v>
@@ -15411,7 +15423,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15492,7 +15504,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ69">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR69">
         <v>1.13</v>
@@ -15617,7 +15629,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15695,10 +15707,10 @@
         <v>0.5</v>
       </c>
       <c r="AP70">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ70">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.36</v>
@@ -15901,10 +15913,10 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ71">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR71">
         <v>1.29</v>
@@ -16029,7 +16041,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16853,7 +16865,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17137,10 +17149,10 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ77">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.31</v>
@@ -17343,7 +17355,7 @@
         <v>0.67</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ78">
         <v>0.91</v>
@@ -17677,7 +17689,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17883,7 +17895,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18785,7 +18797,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ85">
         <v>0.45</v>
@@ -18913,7 +18925,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19197,10 +19209,10 @@
         <v>2.5</v>
       </c>
       <c r="AP87">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ87">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR87">
         <v>2.14</v>
@@ -19325,7 +19337,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19531,7 +19543,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19818,7 +19830,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ90">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.55</v>
@@ -19943,7 +19955,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20024,7 +20036,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR91">
         <v>1.21</v>
@@ -20149,7 +20161,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20433,7 +20445,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ93">
         <v>0.2</v>
@@ -20561,7 +20573,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20642,7 +20654,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -20973,7 +20985,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21051,7 +21063,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96">
         <v>1.83</v>
@@ -22003,7 +22015,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22209,7 +22221,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22415,7 +22427,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22496,7 +22508,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ103">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR103">
         <v>1.21</v>
@@ -22905,10 +22917,10 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ105">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR105">
         <v>1.4</v>
@@ -23033,7 +23045,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23111,7 +23123,7 @@
         <v>2.5</v>
       </c>
       <c r="AP106">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ106">
         <v>2</v>
@@ -23732,7 +23744,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ109">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR109">
         <v>1.79</v>
@@ -23857,7 +23869,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24681,7 +24693,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25093,7 +25105,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25299,7 +25311,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25505,7 +25517,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25583,10 +25595,10 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ118">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25789,7 +25801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP119">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ119">
         <v>0.8</v>
@@ -25917,7 +25929,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26201,7 +26213,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ121">
         <v>0.8</v>
@@ -26741,7 +26753,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27028,7 +27040,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ125">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR125">
         <v>1.29</v>
@@ -27234,7 +27246,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ126">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -27977,7 +27989,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28058,7 +28070,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ130">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.31</v>
@@ -28389,7 +28401,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28467,7 +28479,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ132">
         <v>1.36</v>
@@ -28801,7 +28813,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28879,7 +28891,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134">
         <v>2</v>
@@ -29007,7 +29019,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29088,7 +29100,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -29419,7 +29431,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29703,7 +29715,7 @@
         <v>1.83</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ138">
         <v>1.27</v>
@@ -29831,7 +29843,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30037,7 +30049,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30655,7 +30667,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30736,7 +30748,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ143">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR143">
         <v>1.13</v>
@@ -30861,7 +30873,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -30942,7 +30954,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ144">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.51</v>
@@ -31145,7 +31157,7 @@
         <v>0.33</v>
       </c>
       <c r="AP145">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ145">
         <v>0.8</v>
@@ -31273,7 +31285,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31560,7 +31572,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ147">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR147">
         <v>1.56</v>
@@ -31891,7 +31903,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32097,7 +32109,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32175,7 +32187,7 @@
         <v>2</v>
       </c>
       <c r="AP150">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ150">
         <v>1.83</v>
@@ -32381,7 +32393,7 @@
         <v>1.71</v>
       </c>
       <c r="AP151">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ151">
         <v>1.36</v>
@@ -32587,7 +32599,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ152">
         <v>0.25</v>
@@ -32715,7 +32727,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33127,7 +33139,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33333,7 +33345,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33617,10 +33629,10 @@
         <v>2</v>
       </c>
       <c r="AP157">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ157">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -33745,7 +33757,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33951,7 +33963,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34856,7 +34868,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ163">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR163">
         <v>1.23</v>
@@ -35187,7 +35199,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35599,7 +35611,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36011,7 +36023,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36092,7 +36104,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ169">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36423,7 +36435,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37325,7 +37337,7 @@
         <v>1.75</v>
       </c>
       <c r="AP175">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175">
         <v>1.27</v>
@@ -37659,7 +37671,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37740,7 +37752,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ177">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR177">
         <v>2</v>
@@ -37865,7 +37877,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38071,7 +38083,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38149,7 +38161,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ179">
         <v>0.91</v>
@@ -38277,7 +38289,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38358,7 +38370,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ180">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR180">
         <v>0.99</v>
@@ -38561,7 +38573,7 @@
         <v>0.13</v>
       </c>
       <c r="AP181">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ181">
         <v>0.2</v>
@@ -38895,7 +38907,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39307,7 +39319,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39388,7 +39400,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ185">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR185">
         <v>1.15</v>
@@ -39594,7 +39606,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ186">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR186">
         <v>1.03</v>
@@ -40131,7 +40143,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40209,7 +40221,7 @@
         <v>0.25</v>
       </c>
       <c r="AP189">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ189">
         <v>0.8</v>
@@ -40624,7 +40636,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ191">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR191">
         <v>1.44</v>
@@ -40955,7 +40967,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41242,7 +41254,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ194">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR194">
         <v>0.96</v>
@@ -41367,7 +41379,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41779,7 +41791,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41857,7 +41869,7 @@
         <v>1.67</v>
       </c>
       <c r="AP197">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ197">
         <v>1.73</v>
@@ -41985,7 +41997,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42063,7 +42075,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ198">
         <v>0.91</v>
@@ -42887,7 +42899,7 @@
         <v>0.78</v>
       </c>
       <c r="AP202">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ202">
         <v>0.8</v>
@@ -43015,7 +43027,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43096,7 +43108,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ203">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR203">
         <v>1.2</v>
@@ -43221,7 +43233,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43302,7 +43314,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ204">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR204">
         <v>1.67</v>
@@ -43427,7 +43439,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43633,7 +43645,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43920,7 +43932,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ207">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR207">
         <v>1.57</v>
@@ -44045,7 +44057,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44329,7 +44341,7 @@
         <v>0.9</v>
       </c>
       <c r="AP209">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ209">
         <v>0.91</v>
@@ -44663,7 +44675,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44869,7 +44881,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -46517,7 +46529,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47086,6 +47098,830 @@
       </c>
       <c r="BP222">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7465217</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45696.41666666666</v>
+      </c>
+      <c r="F223">
+        <v>23</v>
+      </c>
+      <c r="G223" t="s">
+        <v>72</v>
+      </c>
+      <c r="H223" t="s">
+        <v>71</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>2</v>
+      </c>
+      <c r="K223">
+        <v>2</v>
+      </c>
+      <c r="L223">
+        <v>3</v>
+      </c>
+      <c r="M223">
+        <v>2</v>
+      </c>
+      <c r="N223">
+        <v>5</v>
+      </c>
+      <c r="O223" t="s">
+        <v>240</v>
+      </c>
+      <c r="P223" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q223">
+        <v>3</v>
+      </c>
+      <c r="R223">
+        <v>2.05</v>
+      </c>
+      <c r="S223">
+        <v>4</v>
+      </c>
+      <c r="T223">
+        <v>1.44</v>
+      </c>
+      <c r="U223">
+        <v>2.63</v>
+      </c>
+      <c r="V223">
+        <v>3.25</v>
+      </c>
+      <c r="W223">
+        <v>1.33</v>
+      </c>
+      <c r="X223">
+        <v>10</v>
+      </c>
+      <c r="Y223">
+        <v>1.06</v>
+      </c>
+      <c r="Z223">
+        <v>2.25</v>
+      </c>
+      <c r="AA223">
+        <v>3.3</v>
+      </c>
+      <c r="AB223">
+        <v>3.2</v>
+      </c>
+      <c r="AC223">
+        <v>1.07</v>
+      </c>
+      <c r="AD223">
+        <v>9</v>
+      </c>
+      <c r="AE223">
+        <v>1.4</v>
+      </c>
+      <c r="AF223">
+        <v>3</v>
+      </c>
+      <c r="AG223">
+        <v>2.1</v>
+      </c>
+      <c r="AH223">
+        <v>1.73</v>
+      </c>
+      <c r="AI223">
+        <v>1.91</v>
+      </c>
+      <c r="AJ223">
+        <v>1.91</v>
+      </c>
+      <c r="AK223">
+        <v>1.36</v>
+      </c>
+      <c r="AL223">
+        <v>1.3</v>
+      </c>
+      <c r="AM223">
+        <v>1.65</v>
+      </c>
+      <c r="AN223">
+        <v>1.82</v>
+      </c>
+      <c r="AO223">
+        <v>1.09</v>
+      </c>
+      <c r="AP223">
+        <v>1.92</v>
+      </c>
+      <c r="AQ223">
+        <v>1</v>
+      </c>
+      <c r="AR223">
+        <v>1.34</v>
+      </c>
+      <c r="AS223">
+        <v>1.22</v>
+      </c>
+      <c r="AT223">
+        <v>2.56</v>
+      </c>
+      <c r="AU223">
+        <v>7</v>
+      </c>
+      <c r="AV223">
+        <v>6</v>
+      </c>
+      <c r="AW223">
+        <v>8</v>
+      </c>
+      <c r="AX223">
+        <v>7</v>
+      </c>
+      <c r="AY223">
+        <v>15</v>
+      </c>
+      <c r="AZ223">
+        <v>13</v>
+      </c>
+      <c r="BA223">
+        <v>4</v>
+      </c>
+      <c r="BB223">
+        <v>7</v>
+      </c>
+      <c r="BC223">
+        <v>11</v>
+      </c>
+      <c r="BD223">
+        <v>1.93</v>
+      </c>
+      <c r="BE223">
+        <v>6.25</v>
+      </c>
+      <c r="BF223">
+        <v>2.07</v>
+      </c>
+      <c r="BG223">
+        <v>1.4</v>
+      </c>
+      <c r="BH223">
+        <v>2.65</v>
+      </c>
+      <c r="BI223">
+        <v>1.68</v>
+      </c>
+      <c r="BJ223">
+        <v>2.02</v>
+      </c>
+      <c r="BK223">
+        <v>2.1</v>
+      </c>
+      <c r="BL223">
+        <v>1.64</v>
+      </c>
+      <c r="BM223">
+        <v>2.7</v>
+      </c>
+      <c r="BN223">
+        <v>1.4</v>
+      </c>
+      <c r="BO223">
+        <v>3.65</v>
+      </c>
+      <c r="BP223">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7465210</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45696.51041666666</v>
+      </c>
+      <c r="F224">
+        <v>23</v>
+      </c>
+      <c r="G224" t="s">
+        <v>70</v>
+      </c>
+      <c r="H224" t="s">
+        <v>89</v>
+      </c>
+      <c r="I224">
+        <v>2</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>2</v>
+      </c>
+      <c r="L224">
+        <v>3</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>3</v>
+      </c>
+      <c r="O224" t="s">
+        <v>241</v>
+      </c>
+      <c r="P224" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q224">
+        <v>2.3</v>
+      </c>
+      <c r="R224">
+        <v>2.1</v>
+      </c>
+      <c r="S224">
+        <v>5.5</v>
+      </c>
+      <c r="T224">
+        <v>1.44</v>
+      </c>
+      <c r="U224">
+        <v>2.63</v>
+      </c>
+      <c r="V224">
+        <v>3.25</v>
+      </c>
+      <c r="W224">
+        <v>1.33</v>
+      </c>
+      <c r="X224">
+        <v>10</v>
+      </c>
+      <c r="Y224">
+        <v>1.06</v>
+      </c>
+      <c r="Z224">
+        <v>1.67</v>
+      </c>
+      <c r="AA224">
+        <v>3.75</v>
+      </c>
+      <c r="AB224">
+        <v>5</v>
+      </c>
+      <c r="AC224">
+        <v>1.06</v>
+      </c>
+      <c r="AD224">
+        <v>10</v>
+      </c>
+      <c r="AE224">
+        <v>1.36</v>
+      </c>
+      <c r="AF224">
+        <v>3.2</v>
+      </c>
+      <c r="AG224">
+        <v>2.1</v>
+      </c>
+      <c r="AH224">
+        <v>1.73</v>
+      </c>
+      <c r="AI224">
+        <v>2.1</v>
+      </c>
+      <c r="AJ224">
+        <v>1.67</v>
+      </c>
+      <c r="AK224">
+        <v>1.15</v>
+      </c>
+      <c r="AL224">
+        <v>1.22</v>
+      </c>
+      <c r="AM224">
+        <v>2.25</v>
+      </c>
+      <c r="AN224">
+        <v>2</v>
+      </c>
+      <c r="AO224">
+        <v>1.09</v>
+      </c>
+      <c r="AP224">
+        <v>2.08</v>
+      </c>
+      <c r="AQ224">
+        <v>1</v>
+      </c>
+      <c r="AR224">
+        <v>1.44</v>
+      </c>
+      <c r="AS224">
+        <v>1.13</v>
+      </c>
+      <c r="AT224">
+        <v>2.57</v>
+      </c>
+      <c r="AU224">
+        <v>9</v>
+      </c>
+      <c r="AV224">
+        <v>2</v>
+      </c>
+      <c r="AW224">
+        <v>16</v>
+      </c>
+      <c r="AX224">
+        <v>2</v>
+      </c>
+      <c r="AY224">
+        <v>30</v>
+      </c>
+      <c r="AZ224">
+        <v>4</v>
+      </c>
+      <c r="BA224">
+        <v>11</v>
+      </c>
+      <c r="BB224">
+        <v>2</v>
+      </c>
+      <c r="BC224">
+        <v>13</v>
+      </c>
+      <c r="BD224">
+        <v>1.46</v>
+      </c>
+      <c r="BE224">
+        <v>6.75</v>
+      </c>
+      <c r="BF224">
+        <v>3.05</v>
+      </c>
+      <c r="BG224">
+        <v>1.4</v>
+      </c>
+      <c r="BH224">
+        <v>2.7</v>
+      </c>
+      <c r="BI224">
+        <v>1.66</v>
+      </c>
+      <c r="BJ224">
+        <v>2.07</v>
+      </c>
+      <c r="BK224">
+        <v>2.06</v>
+      </c>
+      <c r="BL224">
+        <v>1.66</v>
+      </c>
+      <c r="BM224">
+        <v>2.65</v>
+      </c>
+      <c r="BN224">
+        <v>1.4</v>
+      </c>
+      <c r="BO224">
+        <v>3.45</v>
+      </c>
+      <c r="BP224">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7465213</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45696.60416666666</v>
+      </c>
+      <c r="F225">
+        <v>23</v>
+      </c>
+      <c r="G225" t="s">
+        <v>73</v>
+      </c>
+      <c r="H225" t="s">
+        <v>79</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>2</v>
+      </c>
+      <c r="N225">
+        <v>3</v>
+      </c>
+      <c r="O225" t="s">
+        <v>158</v>
+      </c>
+      <c r="P225" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q225">
+        <v>4.5</v>
+      </c>
+      <c r="R225">
+        <v>2.3</v>
+      </c>
+      <c r="S225">
+        <v>2.35</v>
+      </c>
+      <c r="T225">
+        <v>1.33</v>
+      </c>
+      <c r="U225">
+        <v>3.4</v>
+      </c>
+      <c r="V225">
+        <v>2.5</v>
+      </c>
+      <c r="W225">
+        <v>1.52</v>
+      </c>
+      <c r="X225">
+        <v>6</v>
+      </c>
+      <c r="Y225">
+        <v>1.12</v>
+      </c>
+      <c r="Z225">
+        <v>4.33</v>
+      </c>
+      <c r="AA225">
+        <v>4</v>
+      </c>
+      <c r="AB225">
+        <v>1.8</v>
+      </c>
+      <c r="AC225">
+        <v>1.03</v>
+      </c>
+      <c r="AD225">
+        <v>15</v>
+      </c>
+      <c r="AE225">
+        <v>1.2</v>
+      </c>
+      <c r="AF225">
+        <v>4.5</v>
+      </c>
+      <c r="AG225">
+        <v>1.66</v>
+      </c>
+      <c r="AH225">
+        <v>2.25</v>
+      </c>
+      <c r="AI225">
+        <v>1.63</v>
+      </c>
+      <c r="AJ225">
+        <v>2.25</v>
+      </c>
+      <c r="AK225">
+        <v>2.05</v>
+      </c>
+      <c r="AL225">
+        <v>1.22</v>
+      </c>
+      <c r="AM225">
+        <v>1.22</v>
+      </c>
+      <c r="AN225">
+        <v>1.18</v>
+      </c>
+      <c r="AO225">
+        <v>1.64</v>
+      </c>
+      <c r="AP225">
+        <v>1.08</v>
+      </c>
+      <c r="AQ225">
+        <v>1.75</v>
+      </c>
+      <c r="AR225">
+        <v>1.41</v>
+      </c>
+      <c r="AS225">
+        <v>1.49</v>
+      </c>
+      <c r="AT225">
+        <v>2.9</v>
+      </c>
+      <c r="AU225">
+        <v>5</v>
+      </c>
+      <c r="AV225">
+        <v>5</v>
+      </c>
+      <c r="AW225">
+        <v>11</v>
+      </c>
+      <c r="AX225">
+        <v>2</v>
+      </c>
+      <c r="AY225">
+        <v>21</v>
+      </c>
+      <c r="AZ225">
+        <v>10</v>
+      </c>
+      <c r="BA225">
+        <v>6</v>
+      </c>
+      <c r="BB225">
+        <v>5</v>
+      </c>
+      <c r="BC225">
+        <v>11</v>
+      </c>
+      <c r="BD225">
+        <v>2.32</v>
+      </c>
+      <c r="BE225">
+        <v>6.4</v>
+      </c>
+      <c r="BF225">
+        <v>1.74</v>
+      </c>
+      <c r="BG225">
+        <v>1.32</v>
+      </c>
+      <c r="BH225">
+        <v>3.05</v>
+      </c>
+      <c r="BI225">
+        <v>1.55</v>
+      </c>
+      <c r="BJ225">
+        <v>2.28</v>
+      </c>
+      <c r="BK225">
+        <v>1.89</v>
+      </c>
+      <c r="BL225">
+        <v>1.8</v>
+      </c>
+      <c r="BM225">
+        <v>2.4</v>
+      </c>
+      <c r="BN225">
+        <v>1.5</v>
+      </c>
+      <c r="BO225">
+        <v>3.1</v>
+      </c>
+      <c r="BP225">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7465215</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45696.70833333334</v>
+      </c>
+      <c r="F226">
+        <v>23</v>
+      </c>
+      <c r="G226" t="s">
+        <v>84</v>
+      </c>
+      <c r="H226" t="s">
+        <v>87</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="K226">
+        <v>1</v>
+      </c>
+      <c r="L226">
+        <v>1</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>2</v>
+      </c>
+      <c r="O226" t="s">
+        <v>157</v>
+      </c>
+      <c r="P226" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q226">
+        <v>2.4</v>
+      </c>
+      <c r="R226">
+        <v>2.3</v>
+      </c>
+      <c r="S226">
+        <v>4.5</v>
+      </c>
+      <c r="T226">
+        <v>1.33</v>
+      </c>
+      <c r="U226">
+        <v>3.25</v>
+      </c>
+      <c r="V226">
+        <v>2.63</v>
+      </c>
+      <c r="W226">
+        <v>1.44</v>
+      </c>
+      <c r="X226">
+        <v>7</v>
+      </c>
+      <c r="Y226">
+        <v>1.1</v>
+      </c>
+      <c r="Z226">
+        <v>1.8</v>
+      </c>
+      <c r="AA226">
+        <v>3.6</v>
+      </c>
+      <c r="AB226">
+        <v>4.5</v>
+      </c>
+      <c r="AC226">
+        <v>1.04</v>
+      </c>
+      <c r="AD226">
+        <v>13</v>
+      </c>
+      <c r="AE226">
+        <v>1.25</v>
+      </c>
+      <c r="AF226">
+        <v>4</v>
+      </c>
+      <c r="AG226">
+        <v>1.73</v>
+      </c>
+      <c r="AH226">
+        <v>2.1</v>
+      </c>
+      <c r="AI226">
+        <v>1.67</v>
+      </c>
+      <c r="AJ226">
+        <v>2.1</v>
+      </c>
+      <c r="AK226">
+        <v>1.22</v>
+      </c>
+      <c r="AL226">
+        <v>1.24</v>
+      </c>
+      <c r="AM226">
+        <v>2</v>
+      </c>
+      <c r="AN226">
+        <v>2.7</v>
+      </c>
+      <c r="AO226">
+        <v>1.8</v>
+      </c>
+      <c r="AP226">
+        <v>2.55</v>
+      </c>
+      <c r="AQ226">
+        <v>1.73</v>
+      </c>
+      <c r="AR226">
+        <v>1.93</v>
+      </c>
+      <c r="AS226">
+        <v>1.17</v>
+      </c>
+      <c r="AT226">
+        <v>3.1</v>
+      </c>
+      <c r="AU226">
+        <v>10</v>
+      </c>
+      <c r="AV226">
+        <v>2</v>
+      </c>
+      <c r="AW226">
+        <v>14</v>
+      </c>
+      <c r="AX226">
+        <v>9</v>
+      </c>
+      <c r="AY226">
+        <v>29</v>
+      </c>
+      <c r="AZ226">
+        <v>13</v>
+      </c>
+      <c r="BA226">
+        <v>6</v>
+      </c>
+      <c r="BB226">
+        <v>1</v>
+      </c>
+      <c r="BC226">
+        <v>7</v>
+      </c>
+      <c r="BD226">
+        <v>1.5</v>
+      </c>
+      <c r="BE226">
+        <v>6.75</v>
+      </c>
+      <c r="BF226">
+        <v>2.9</v>
+      </c>
+      <c r="BG226">
+        <v>1.32</v>
+      </c>
+      <c r="BH226">
+        <v>3</v>
+      </c>
+      <c r="BI226">
+        <v>1.56</v>
+      </c>
+      <c r="BJ226">
+        <v>2.23</v>
+      </c>
+      <c r="BK226">
+        <v>1.91</v>
+      </c>
+      <c r="BL226">
+        <v>1.78</v>
+      </c>
+      <c r="BM226">
+        <v>2.4</v>
+      </c>
+      <c r="BN226">
+        <v>1.49</v>
+      </c>
+      <c r="BO226">
+        <v>3.05</v>
+      </c>
+      <c r="BP226">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="333">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,6 +742,12 @@
     <t>['42', '45+1', '79']</t>
   </si>
   <si>
+    <t>['30', '41']</t>
+  </si>
+  <si>
+    <t>['1', '84']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1004,6 +1010,9 @@
   </si>
   <si>
     <t>['53', '66']</t>
+  </si>
+  <si>
+    <t>['7', '46', '55', '89']</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1621,7 +1630,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1702,7 +1711,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2033,7 +2042,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2239,7 +2248,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2445,7 +2454,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2526,7 +2535,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ6">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2651,7 +2660,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2729,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2857,7 +2866,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2935,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ8">
         <v>1.42</v>
@@ -3063,7 +3072,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3350,7 +3359,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ10">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3475,7 +3484,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3887,7 +3896,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3965,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>1.75</v>
@@ -5407,7 +5416,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5741,7 +5750,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6153,7 +6162,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6234,7 +6243,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6646,7 +6655,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ26">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -6852,7 +6861,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ27">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR27">
         <v>1.31</v>
@@ -6977,7 +6986,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7055,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ28">
         <v>0.67</v>
@@ -8213,7 +8222,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8291,7 +8300,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
         <v>1.75</v>
@@ -8703,7 +8712,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ36">
         <v>0.91</v>
@@ -8831,7 +8840,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9037,7 +9046,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9115,7 +9124,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9736,7 +9745,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ41">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR41">
         <v>1.59</v>
@@ -9861,7 +9870,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10067,7 +10076,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10351,10 +10360,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10479,7 +10488,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10557,7 +10566,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ45">
         <v>1.83</v>
@@ -10891,7 +10900,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10972,7 +10981,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR47">
         <v>1.41</v>
@@ -11097,7 +11106,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12002,7 +12011,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ52">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12127,7 +12136,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12411,7 +12420,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ54">
         <v>0.91</v>
@@ -12745,7 +12754,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13029,7 +13038,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13157,7 +13166,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -13238,7 +13247,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ58">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR58">
         <v>2.01</v>
@@ -13444,7 +13453,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR59">
         <v>1.14</v>
@@ -13775,7 +13784,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13856,7 +13865,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -14187,7 +14196,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14471,7 +14480,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
         <v>0.8</v>
@@ -14599,7 +14608,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14677,7 +14686,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
         <v>0.25</v>
@@ -14805,7 +14814,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15298,7 +15307,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.97</v>
@@ -15423,7 +15432,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15629,7 +15638,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16041,7 +16050,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16534,7 +16543,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ74">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR74">
         <v>1.48</v>
@@ -16737,7 +16746,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ75">
         <v>0.36</v>
@@ -16865,7 +16874,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -16946,7 +16955,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ76">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR76">
         <v>1.49</v>
@@ -17564,7 +17573,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ79">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR79">
         <v>1.68</v>
@@ -17689,7 +17698,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17895,7 +17904,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18925,7 +18934,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19337,7 +19346,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19543,7 +19552,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19621,10 +19630,10 @@
         <v>2.4</v>
       </c>
       <c r="AP89">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR89">
         <v>1.08</v>
@@ -19827,7 +19836,7 @@
         <v>0.67</v>
       </c>
       <c r="AP90">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19955,7 +19964,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20033,7 +20042,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
         <v>1.73</v>
@@ -20161,7 +20170,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20239,7 +20248,7 @@
         <v>0</v>
       </c>
       <c r="AP92">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ92">
         <v>0.25</v>
@@ -20448,7 +20457,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ93">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -20573,7 +20582,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20985,7 +20994,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21478,7 +21487,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ98">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR98">
         <v>1.58</v>
@@ -21684,7 +21693,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ99">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.66</v>
@@ -22015,7 +22024,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22093,7 +22102,7 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101">
         <v>0.91</v>
@@ -22221,7 +22230,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22427,7 +22436,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23045,7 +23054,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23126,7 +23135,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ106">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR106">
         <v>1.96</v>
@@ -23869,7 +23878,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23947,7 +23956,7 @@
         <v>0.5</v>
       </c>
       <c r="AP110">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
         <v>0.8</v>
@@ -24359,7 +24368,7 @@
         <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ112">
         <v>1.36</v>
@@ -24693,7 +24702,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24774,7 +24783,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ114">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR114">
         <v>1.33</v>
@@ -25105,7 +25114,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25186,7 +25195,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ116">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR116">
         <v>1.93</v>
@@ -25311,7 +25320,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25389,7 +25398,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ117">
         <v>1.27</v>
@@ -25517,7 +25526,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25804,7 +25813,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ119">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -25929,7 +25938,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26753,7 +26762,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27655,10 +27664,10 @@
         <v>2.57</v>
       </c>
       <c r="AP128">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ128">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -27989,7 +27998,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28067,7 +28076,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28401,7 +28410,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28688,7 +28697,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ133">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR133">
         <v>1.36</v>
@@ -28813,7 +28822,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28894,7 +28903,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ134">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR134">
         <v>1.32</v>
@@ -29019,7 +29028,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29303,7 +29312,7 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ136">
         <v>1.42</v>
@@ -29431,7 +29440,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29843,7 +29852,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -30049,7 +30058,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30333,10 +30342,10 @@
         <v>0.57</v>
       </c>
       <c r="AP141">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ141">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR141">
         <v>1.08</v>
@@ -30667,7 +30676,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30873,7 +30882,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31160,7 +31169,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ145">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR145">
         <v>1.86</v>
@@ -31285,7 +31294,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31569,7 +31578,7 @@
         <v>0.86</v>
       </c>
       <c r="AP147">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ147">
         <v>1</v>
@@ -31775,7 +31784,7 @@
         <v>0.83</v>
       </c>
       <c r="AP148">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ148">
         <v>0.8</v>
@@ -31903,7 +31912,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -31984,7 +31993,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ149">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR149">
         <v>1.29</v>
@@ -32109,7 +32118,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32727,7 +32736,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32808,7 +32817,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ153">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR153">
         <v>1.84</v>
@@ -33011,7 +33020,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154">
         <v>1.42</v>
@@ -33139,7 +33148,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33345,7 +33354,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33757,7 +33766,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33963,7 +33972,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34250,7 +34259,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR160">
         <v>1.3</v>
@@ -35071,7 +35080,7 @@
         <v>0.57</v>
       </c>
       <c r="AP164">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ164">
         <v>0.45</v>
@@ -35199,7 +35208,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35486,7 +35495,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ166">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR166">
         <v>1.77</v>
@@ -35611,7 +35620,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35689,7 +35698,7 @@
         <v>1.57</v>
       </c>
       <c r="AP167">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ167">
         <v>1.73</v>
@@ -35895,7 +35904,7 @@
         <v>1.13</v>
       </c>
       <c r="AP168">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ168">
         <v>0.91</v>
@@ -36023,7 +36032,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36310,7 +36319,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ170">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR170">
         <v>1.98</v>
@@ -36435,7 +36444,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37671,7 +37680,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37877,7 +37886,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37955,7 +37964,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ178">
         <v>0.67</v>
@@ -38083,7 +38092,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38289,7 +38298,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38576,7 +38585,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ181">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR181">
         <v>1.34</v>
@@ -38907,7 +38916,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -38985,7 +38994,7 @@
         <v>1.78</v>
       </c>
       <c r="AP183">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ183">
         <v>1.83</v>
@@ -39319,7 +39328,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39397,7 +39406,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39812,7 +39821,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ187">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR187">
         <v>1.12</v>
@@ -40015,7 +40024,7 @@
         <v>0.33</v>
       </c>
       <c r="AP188">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ188">
         <v>0.36</v>
@@ -40143,7 +40152,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40224,7 +40233,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ189">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -40633,7 +40642,7 @@
         <v>1.89</v>
       </c>
       <c r="AP191">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ191">
         <v>1.75</v>
@@ -40967,7 +40976,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41379,7 +41388,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41666,7 +41675,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ196">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR196">
         <v>1.38</v>
@@ -41791,7 +41800,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41997,7 +42006,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42487,7 +42496,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ200">
         <v>1.27</v>
@@ -43027,7 +43036,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43233,7 +43242,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43439,7 +43448,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43517,10 +43526,10 @@
         <v>0.11</v>
       </c>
       <c r="AP205">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ205">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR205">
         <v>1.35</v>
@@ -43645,7 +43654,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44057,7 +44066,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44135,10 +44144,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP208">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ208">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR208">
         <v>1.41</v>
@@ -44344,7 +44353,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ209">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR209">
         <v>1.31</v>
@@ -44675,7 +44684,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44753,7 +44762,7 @@
         <v>0.44</v>
       </c>
       <c r="AP211">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ211">
         <v>0.45</v>
@@ -44881,7 +44890,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -46195,7 +46204,7 @@
         <v>0.5</v>
       </c>
       <c r="AP218">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ218">
         <v>0.45</v>
@@ -46529,7 +46538,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47147,7 +47156,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47559,7 +47568,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -47922,6 +47931,830 @@
       </c>
       <c r="BP226">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7465214</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45697.41666666666</v>
+      </c>
+      <c r="F227">
+        <v>23</v>
+      </c>
+      <c r="G227" t="s">
+        <v>86</v>
+      </c>
+      <c r="H227" t="s">
+        <v>83</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>1</v>
+      </c>
+      <c r="O227" t="s">
+        <v>104</v>
+      </c>
+      <c r="P227" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q227">
+        <v>3.25</v>
+      </c>
+      <c r="R227">
+        <v>1.8</v>
+      </c>
+      <c r="S227">
+        <v>4.5</v>
+      </c>
+      <c r="T227">
+        <v>1.67</v>
+      </c>
+      <c r="U227">
+        <v>2.1</v>
+      </c>
+      <c r="V227">
+        <v>4.33</v>
+      </c>
+      <c r="W227">
+        <v>1.2</v>
+      </c>
+      <c r="X227">
+        <v>15</v>
+      </c>
+      <c r="Y227">
+        <v>1.03</v>
+      </c>
+      <c r="Z227">
+        <v>2.3</v>
+      </c>
+      <c r="AA227">
+        <v>2.9</v>
+      </c>
+      <c r="AB227">
+        <v>3.5</v>
+      </c>
+      <c r="AC227">
+        <v>1.15</v>
+      </c>
+      <c r="AD227">
+        <v>5.5</v>
+      </c>
+      <c r="AE227">
+        <v>1.61</v>
+      </c>
+      <c r="AF227">
+        <v>2.2</v>
+      </c>
+      <c r="AG227">
+        <v>3.2</v>
+      </c>
+      <c r="AH227">
+        <v>1.36</v>
+      </c>
+      <c r="AI227">
+        <v>2.38</v>
+      </c>
+      <c r="AJ227">
+        <v>1.53</v>
+      </c>
+      <c r="AK227">
+        <v>1.28</v>
+      </c>
+      <c r="AL227">
+        <v>1.39</v>
+      </c>
+      <c r="AM227">
+        <v>1.6</v>
+      </c>
+      <c r="AN227">
+        <v>1.3</v>
+      </c>
+      <c r="AO227">
+        <v>0.8</v>
+      </c>
+      <c r="AP227">
+        <v>1.18</v>
+      </c>
+      <c r="AQ227">
+        <v>1</v>
+      </c>
+      <c r="AR227">
+        <v>1.1</v>
+      </c>
+      <c r="AS227">
+        <v>1.11</v>
+      </c>
+      <c r="AT227">
+        <v>2.21</v>
+      </c>
+      <c r="AU227">
+        <v>5</v>
+      </c>
+      <c r="AV227">
+        <v>4</v>
+      </c>
+      <c r="AW227">
+        <v>8</v>
+      </c>
+      <c r="AX227">
+        <v>1</v>
+      </c>
+      <c r="AY227">
+        <v>16</v>
+      </c>
+      <c r="AZ227">
+        <v>5</v>
+      </c>
+      <c r="BA227">
+        <v>8</v>
+      </c>
+      <c r="BB227">
+        <v>3</v>
+      </c>
+      <c r="BC227">
+        <v>11</v>
+      </c>
+      <c r="BD227">
+        <v>1.61</v>
+      </c>
+      <c r="BE227">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF227">
+        <v>2.89</v>
+      </c>
+      <c r="BG227">
+        <v>1.46</v>
+      </c>
+      <c r="BH227">
+        <v>2.45</v>
+      </c>
+      <c r="BI227">
+        <v>1.85</v>
+      </c>
+      <c r="BJ227">
+        <v>1.85</v>
+      </c>
+      <c r="BK227">
+        <v>2.4</v>
+      </c>
+      <c r="BL227">
+        <v>1.48</v>
+      </c>
+      <c r="BM227">
+        <v>3.28</v>
+      </c>
+      <c r="BN227">
+        <v>1.25</v>
+      </c>
+      <c r="BO227">
+        <v>4.7</v>
+      </c>
+      <c r="BP227">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7465218</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45697.51041666666</v>
+      </c>
+      <c r="F228">
+        <v>23</v>
+      </c>
+      <c r="G228" t="s">
+        <v>75</v>
+      </c>
+      <c r="H228" t="s">
+        <v>85</v>
+      </c>
+      <c r="I228">
+        <v>2</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>2</v>
+      </c>
+      <c r="L228">
+        <v>2</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>2</v>
+      </c>
+      <c r="O228" t="s">
+        <v>242</v>
+      </c>
+      <c r="P228" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q228">
+        <v>2.6</v>
+      </c>
+      <c r="R228">
+        <v>1.95</v>
+      </c>
+      <c r="S228">
+        <v>6</v>
+      </c>
+      <c r="T228">
+        <v>1.57</v>
+      </c>
+      <c r="U228">
+        <v>2.25</v>
+      </c>
+      <c r="V228">
+        <v>3.75</v>
+      </c>
+      <c r="W228">
+        <v>1.25</v>
+      </c>
+      <c r="X228">
+        <v>13</v>
+      </c>
+      <c r="Y228">
+        <v>1.04</v>
+      </c>
+      <c r="Z228">
+        <v>1.8</v>
+      </c>
+      <c r="AA228">
+        <v>3.1</v>
+      </c>
+      <c r="AB228">
+        <v>5.5</v>
+      </c>
+      <c r="AC228">
+        <v>1.1</v>
+      </c>
+      <c r="AD228">
+        <v>7.5</v>
+      </c>
+      <c r="AE228">
+        <v>1.53</v>
+      </c>
+      <c r="AF228">
+        <v>2.37</v>
+      </c>
+      <c r="AG228">
+        <v>2.63</v>
+      </c>
+      <c r="AH228">
+        <v>1.5</v>
+      </c>
+      <c r="AI228">
+        <v>2.25</v>
+      </c>
+      <c r="AJ228">
+        <v>1.57</v>
+      </c>
+      <c r="AK228">
+        <v>1.17</v>
+      </c>
+      <c r="AL228">
+        <v>1.33</v>
+      </c>
+      <c r="AM228">
+        <v>1.93</v>
+      </c>
+      <c r="AN228">
+        <v>1.36</v>
+      </c>
+      <c r="AO228">
+        <v>0.91</v>
+      </c>
+      <c r="AP228">
+        <v>1.5</v>
+      </c>
+      <c r="AQ228">
+        <v>0.83</v>
+      </c>
+      <c r="AR228">
+        <v>1.3</v>
+      </c>
+      <c r="AS228">
+        <v>0.88</v>
+      </c>
+      <c r="AT228">
+        <v>2.18</v>
+      </c>
+      <c r="AU228">
+        <v>5</v>
+      </c>
+      <c r="AV228">
+        <v>5</v>
+      </c>
+      <c r="AW228">
+        <v>14</v>
+      </c>
+      <c r="AX228">
+        <v>8</v>
+      </c>
+      <c r="AY228">
+        <v>22</v>
+      </c>
+      <c r="AZ228">
+        <v>14</v>
+      </c>
+      <c r="BA228">
+        <v>9</v>
+      </c>
+      <c r="BB228">
+        <v>3</v>
+      </c>
+      <c r="BC228">
+        <v>12</v>
+      </c>
+      <c r="BD228">
+        <v>1.37</v>
+      </c>
+      <c r="BE228">
+        <v>9.6</v>
+      </c>
+      <c r="BF228">
+        <v>3.94</v>
+      </c>
+      <c r="BG228">
+        <v>1.29</v>
+      </c>
+      <c r="BH228">
+        <v>3.04</v>
+      </c>
+      <c r="BI228">
+        <v>1.56</v>
+      </c>
+      <c r="BJ228">
+        <v>2.21</v>
+      </c>
+      <c r="BK228">
+        <v>1.98</v>
+      </c>
+      <c r="BL228">
+        <v>1.74</v>
+      </c>
+      <c r="BM228">
+        <v>2.57</v>
+      </c>
+      <c r="BN228">
+        <v>1.42</v>
+      </c>
+      <c r="BO228">
+        <v>3.5</v>
+      </c>
+      <c r="BP228">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7469683</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45697.60416666666</v>
+      </c>
+      <c r="F229">
+        <v>23</v>
+      </c>
+      <c r="G229" t="s">
+        <v>76</v>
+      </c>
+      <c r="H229" t="s">
+        <v>82</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="L229">
+        <v>2</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>3</v>
+      </c>
+      <c r="O229" t="s">
+        <v>243</v>
+      </c>
+      <c r="P229" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q229">
+        <v>2.25</v>
+      </c>
+      <c r="R229">
+        <v>2.1</v>
+      </c>
+      <c r="S229">
+        <v>6.5</v>
+      </c>
+      <c r="T229">
+        <v>1.5</v>
+      </c>
+      <c r="U229">
+        <v>2.5</v>
+      </c>
+      <c r="V229">
+        <v>3.4</v>
+      </c>
+      <c r="W229">
+        <v>1.3</v>
+      </c>
+      <c r="X229">
+        <v>10</v>
+      </c>
+      <c r="Y229">
+        <v>1.06</v>
+      </c>
+      <c r="Z229">
+        <v>1.57</v>
+      </c>
+      <c r="AA229">
+        <v>3.9</v>
+      </c>
+      <c r="AB229">
+        <v>5.75</v>
+      </c>
+      <c r="AC229">
+        <v>1.08</v>
+      </c>
+      <c r="AD229">
+        <v>9</v>
+      </c>
+      <c r="AE229">
+        <v>1.42</v>
+      </c>
+      <c r="AF229">
+        <v>2.9</v>
+      </c>
+      <c r="AG229">
+        <v>2.2</v>
+      </c>
+      <c r="AH229">
+        <v>1.67</v>
+      </c>
+      <c r="AI229">
+        <v>2.25</v>
+      </c>
+      <c r="AJ229">
+        <v>1.57</v>
+      </c>
+      <c r="AK229">
+        <v>1.12</v>
+      </c>
+      <c r="AL229">
+        <v>1.25</v>
+      </c>
+      <c r="AM229">
+        <v>2.3</v>
+      </c>
+      <c r="AN229">
+        <v>1.27</v>
+      </c>
+      <c r="AO229">
+        <v>0.2</v>
+      </c>
+      <c r="AP229">
+        <v>1.42</v>
+      </c>
+      <c r="AQ229">
+        <v>0.18</v>
+      </c>
+      <c r="AR229">
+        <v>1.42</v>
+      </c>
+      <c r="AS229">
+        <v>0.83</v>
+      </c>
+      <c r="AT229">
+        <v>2.25</v>
+      </c>
+      <c r="AU229">
+        <v>4</v>
+      </c>
+      <c r="AV229">
+        <v>2</v>
+      </c>
+      <c r="AW229">
+        <v>10</v>
+      </c>
+      <c r="AX229">
+        <v>3</v>
+      </c>
+      <c r="AY229">
+        <v>18</v>
+      </c>
+      <c r="AZ229">
+        <v>6</v>
+      </c>
+      <c r="BA229">
+        <v>6</v>
+      </c>
+      <c r="BB229">
+        <v>0</v>
+      </c>
+      <c r="BC229">
+        <v>6</v>
+      </c>
+      <c r="BD229">
+        <v>1.32</v>
+      </c>
+      <c r="BE229">
+        <v>10.25</v>
+      </c>
+      <c r="BF229">
+        <v>4.33</v>
+      </c>
+      <c r="BG229">
+        <v>1.24</v>
+      </c>
+      <c r="BH229">
+        <v>3.34</v>
+      </c>
+      <c r="BI229">
+        <v>1.48</v>
+      </c>
+      <c r="BJ229">
+        <v>2.4</v>
+      </c>
+      <c r="BK229">
+        <v>1.85</v>
+      </c>
+      <c r="BL229">
+        <v>1.85</v>
+      </c>
+      <c r="BM229">
+        <v>2.38</v>
+      </c>
+      <c r="BN229">
+        <v>1.49</v>
+      </c>
+      <c r="BO229">
+        <v>3.14</v>
+      </c>
+      <c r="BP229">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7465216</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45697.70833333334</v>
+      </c>
+      <c r="F230">
+        <v>23</v>
+      </c>
+      <c r="G230" t="s">
+        <v>80</v>
+      </c>
+      <c r="H230" t="s">
+        <v>81</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230">
+        <v>1</v>
+      </c>
+      <c r="K230">
+        <v>2</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>4</v>
+      </c>
+      <c r="N230">
+        <v>5</v>
+      </c>
+      <c r="O230" t="s">
+        <v>145</v>
+      </c>
+      <c r="P230" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q230">
+        <v>5</v>
+      </c>
+      <c r="R230">
+        <v>2.6</v>
+      </c>
+      <c r="S230">
+        <v>2.05</v>
+      </c>
+      <c r="T230">
+        <v>1.25</v>
+      </c>
+      <c r="U230">
+        <v>3.75</v>
+      </c>
+      <c r="V230">
+        <v>2.2</v>
+      </c>
+      <c r="W230">
+        <v>1.62</v>
+      </c>
+      <c r="X230">
+        <v>5</v>
+      </c>
+      <c r="Y230">
+        <v>1.17</v>
+      </c>
+      <c r="Z230">
+        <v>5.5</v>
+      </c>
+      <c r="AA230">
+        <v>4.33</v>
+      </c>
+      <c r="AB230">
+        <v>1.53</v>
+      </c>
+      <c r="AC230">
+        <v>1.01</v>
+      </c>
+      <c r="AD230">
+        <v>23</v>
+      </c>
+      <c r="AE230">
+        <v>1.14</v>
+      </c>
+      <c r="AF230">
+        <v>6</v>
+      </c>
+      <c r="AG230">
+        <v>1.44</v>
+      </c>
+      <c r="AH230">
+        <v>2.75</v>
+      </c>
+      <c r="AI230">
+        <v>1.53</v>
+      </c>
+      <c r="AJ230">
+        <v>2.38</v>
+      </c>
+      <c r="AK230">
+        <v>2.35</v>
+      </c>
+      <c r="AL230">
+        <v>1.2</v>
+      </c>
+      <c r="AM230">
+        <v>1.16</v>
+      </c>
+      <c r="AN230">
+        <v>1.64</v>
+      </c>
+      <c r="AO230">
+        <v>2</v>
+      </c>
+      <c r="AP230">
+        <v>1.5</v>
+      </c>
+      <c r="AQ230">
+        <v>2.08</v>
+      </c>
+      <c r="AR230">
+        <v>1.46</v>
+      </c>
+      <c r="AS230">
+        <v>1.7</v>
+      </c>
+      <c r="AT230">
+        <v>3.16</v>
+      </c>
+      <c r="AU230">
+        <v>5</v>
+      </c>
+      <c r="AV230">
+        <v>7</v>
+      </c>
+      <c r="AW230">
+        <v>4</v>
+      </c>
+      <c r="AX230">
+        <v>4</v>
+      </c>
+      <c r="AY230">
+        <v>9</v>
+      </c>
+      <c r="AZ230">
+        <v>12</v>
+      </c>
+      <c r="BA230">
+        <v>5</v>
+      </c>
+      <c r="BB230">
+        <v>6</v>
+      </c>
+      <c r="BC230">
+        <v>11</v>
+      </c>
+      <c r="BD230">
+        <v>3.58</v>
+      </c>
+      <c r="BE230">
+        <v>9.6</v>
+      </c>
+      <c r="BF230">
+        <v>1.42</v>
+      </c>
+      <c r="BG230">
+        <v>1.23</v>
+      </c>
+      <c r="BH230">
+        <v>3.42</v>
+      </c>
+      <c r="BI230">
+        <v>1.45</v>
+      </c>
+      <c r="BJ230">
+        <v>2.48</v>
+      </c>
+      <c r="BK230">
+        <v>1.81</v>
+      </c>
+      <c r="BL230">
+        <v>1.89</v>
+      </c>
+      <c r="BM230">
+        <v>2.3</v>
+      </c>
+      <c r="BN230">
+        <v>1.52</v>
+      </c>
+      <c r="BO230">
+        <v>3.05</v>
+      </c>
+      <c r="BP230">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="333">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1374,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP230"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
         <v>1.83</v>
@@ -6034,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ23">
         <v>0.91</v>
@@ -7273,7 +7273,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ29">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -9948,7 +9948,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
         <v>1.75</v>
@@ -11599,7 +11599,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ50">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR50">
         <v>1.14</v>
@@ -11802,7 +11802,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51">
         <v>1.27</v>
@@ -14483,7 +14483,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR64">
         <v>1.24</v>
@@ -18603,7 +18603,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ84">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR84">
         <v>1.3</v>
@@ -21278,7 +21278,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97">
         <v>1.42</v>
@@ -23959,7 +23959,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -24162,7 +24162,7 @@
         <v>1.5</v>
       </c>
       <c r="AP111">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ111">
         <v>1.73</v>
@@ -26225,7 +26225,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ121">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR121">
         <v>1.83</v>
@@ -27046,7 +27046,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ125">
         <v>1.73</v>
@@ -29930,7 +29930,7 @@
         <v>0.33</v>
       </c>
       <c r="AP139">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ139">
         <v>0.36</v>
@@ -31787,7 +31787,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ148">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR148">
         <v>1.35</v>
@@ -31990,7 +31990,7 @@
         <v>2.11</v>
       </c>
       <c r="AP149">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ149">
         <v>2.08</v>
@@ -34671,7 +34671,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ162">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -34874,7 +34874,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ163">
         <v>1</v>
@@ -40439,7 +40439,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ190">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -42911,7 +42911,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ202">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR202">
         <v>1.36</v>
@@ -43114,7 +43114,7 @@
         <v>0.9</v>
       </c>
       <c r="AP203">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ203">
         <v>1</v>
@@ -48755,6 +48755,212 @@
       </c>
       <c r="BP230">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7465211</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45698.70833333334</v>
+      </c>
+      <c r="F231">
+        <v>23</v>
+      </c>
+      <c r="G231" t="s">
+        <v>77</v>
+      </c>
+      <c r="H231" t="s">
+        <v>74</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>1</v>
+      </c>
+      <c r="M231">
+        <v>1</v>
+      </c>
+      <c r="N231">
+        <v>2</v>
+      </c>
+      <c r="O231" t="s">
+        <v>148</v>
+      </c>
+      <c r="P231" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q231">
+        <v>2.88</v>
+      </c>
+      <c r="R231">
+        <v>1.91</v>
+      </c>
+      <c r="S231">
+        <v>5</v>
+      </c>
+      <c r="T231">
+        <v>1.62</v>
+      </c>
+      <c r="U231">
+        <v>2.2</v>
+      </c>
+      <c r="V231">
+        <v>4</v>
+      </c>
+      <c r="W231">
+        <v>1.22</v>
+      </c>
+      <c r="X231">
+        <v>13</v>
+      </c>
+      <c r="Y231">
+        <v>1.04</v>
+      </c>
+      <c r="Z231">
+        <v>2</v>
+      </c>
+      <c r="AA231">
+        <v>3</v>
+      </c>
+      <c r="AB231">
+        <v>4.33</v>
+      </c>
+      <c r="AC231">
+        <v>1.12</v>
+      </c>
+      <c r="AD231">
+        <v>6.5</v>
+      </c>
+      <c r="AE231">
+        <v>1.55</v>
+      </c>
+      <c r="AF231">
+        <v>2.3</v>
+      </c>
+      <c r="AG231">
+        <v>2.75</v>
+      </c>
+      <c r="AH231">
+        <v>1.44</v>
+      </c>
+      <c r="AI231">
+        <v>2.25</v>
+      </c>
+      <c r="AJ231">
+        <v>1.57</v>
+      </c>
+      <c r="AK231">
+        <v>1.22</v>
+      </c>
+      <c r="AL231">
+        <v>1.36</v>
+      </c>
+      <c r="AM231">
+        <v>1.75</v>
+      </c>
+      <c r="AN231">
+        <v>1.36</v>
+      </c>
+      <c r="AO231">
+        <v>0.8</v>
+      </c>
+      <c r="AP231">
+        <v>1.33</v>
+      </c>
+      <c r="AQ231">
+        <v>0.82</v>
+      </c>
+      <c r="AR231">
+        <v>1.25</v>
+      </c>
+      <c r="AS231">
+        <v>0.84</v>
+      </c>
+      <c r="AT231">
+        <v>2.09</v>
+      </c>
+      <c r="AU231">
+        <v>3</v>
+      </c>
+      <c r="AV231">
+        <v>5</v>
+      </c>
+      <c r="AW231">
+        <v>8</v>
+      </c>
+      <c r="AX231">
+        <v>15</v>
+      </c>
+      <c r="AY231">
+        <v>13</v>
+      </c>
+      <c r="AZ231">
+        <v>22</v>
+      </c>
+      <c r="BA231">
+        <v>7</v>
+      </c>
+      <c r="BB231">
+        <v>11</v>
+      </c>
+      <c r="BC231">
+        <v>18</v>
+      </c>
+      <c r="BD231">
+        <v>1.65</v>
+      </c>
+      <c r="BE231">
+        <v>6.75</v>
+      </c>
+      <c r="BF231">
+        <v>2.5</v>
+      </c>
+      <c r="BG231">
+        <v>1.41</v>
+      </c>
+      <c r="BH231">
+        <v>2.65</v>
+      </c>
+      <c r="BI231">
+        <v>1.68</v>
+      </c>
+      <c r="BJ231">
+        <v>2.04</v>
+      </c>
+      <c r="BK231">
+        <v>2.08</v>
+      </c>
+      <c r="BL231">
+        <v>1.65</v>
+      </c>
+      <c r="BM231">
+        <v>2.7</v>
+      </c>
+      <c r="BN231">
+        <v>1.4</v>
+      </c>
+      <c r="BO231">
+        <v>3.55</v>
+      </c>
+      <c r="BP231">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="334">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -748,6 +748,9 @@
     <t>['1', '84']</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -812,9 +815,6 @@
   </si>
   <si>
     <t>['41']</t>
-  </si>
-  <si>
-    <t>['54']</t>
   </si>
   <si>
     <t>['20', '35', '58', '75', '83']</t>
@@ -1013,6 +1013,9 @@
   </si>
   <si>
     <t>['7', '46', '55', '89']</t>
+  </si>
+  <si>
+    <t>['3', '62']</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1630,7 +1633,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1711,7 +1714,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2042,7 +2045,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2248,7 +2251,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2454,7 +2457,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2660,7 +2663,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2866,7 +2869,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3072,7 +3075,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3484,7 +3487,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3896,7 +3899,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -5750,7 +5753,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6162,7 +6165,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6986,7 +6989,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7270,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ29">
         <v>0.82</v>
@@ -8222,7 +8225,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8840,7 +8843,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9046,7 +9049,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9870,7 +9873,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10076,7 +10079,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10363,7 +10366,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10488,7 +10491,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10900,7 +10903,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10978,7 +10981,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ47">
         <v>2.08</v>
@@ -11106,7 +11109,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12011,7 +12014,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12136,7 +12139,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12754,7 +12757,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13166,7 +13169,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="Q58">
         <v>1.51</v>
@@ -15098,7 +15101,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ67">
         <v>1.42</v>
@@ -15307,7 +15310,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR68">
         <v>1.97</v>
@@ -17698,7 +17701,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -19346,7 +19349,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19424,7 +19427,7 @@
         <v>2</v>
       </c>
       <c r="AP88">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ88">
         <v>1.73</v>
@@ -20866,7 +20869,7 @@
         <v>1.25</v>
       </c>
       <c r="AP95">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ95">
         <v>1.27</v>
@@ -21693,7 +21696,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR99">
         <v>1.66</v>
@@ -24780,7 +24783,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ114">
         <v>0.83</v>
@@ -25813,7 +25816,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -28694,7 +28697,7 @@
         <v>0.17</v>
       </c>
       <c r="AP133">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ133">
         <v>0.18</v>
@@ -31169,7 +31172,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ145">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR145">
         <v>1.86</v>
@@ -33226,7 +33229,7 @@
         <v>1.71</v>
       </c>
       <c r="AP155">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ155">
         <v>1.83</v>
@@ -35495,7 +35498,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ166">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR166">
         <v>1.77</v>
@@ -36934,7 +36937,7 @@
         <v>0.38</v>
       </c>
       <c r="AP173">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ173">
         <v>0.25</v>
@@ -40233,7 +40236,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ189">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -41054,7 +41057,7 @@
         <v>0.67</v>
       </c>
       <c r="AP193">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ193">
         <v>0.91</v>
@@ -44147,7 +44150,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ208">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR208">
         <v>1.41</v>
@@ -46822,7 +46825,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ221">
         <v>0.91</v>
@@ -48061,7 +48064,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ227">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR227">
         <v>1.1</v>
@@ -48961,6 +48964,212 @@
       </c>
       <c r="BP231">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7465223</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45702.70833333334</v>
+      </c>
+      <c r="F232">
+        <v>24</v>
+      </c>
+      <c r="G232" t="s">
+        <v>89</v>
+      </c>
+      <c r="H232" t="s">
+        <v>83</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="L232">
+        <v>1</v>
+      </c>
+      <c r="M232">
+        <v>2</v>
+      </c>
+      <c r="N232">
+        <v>3</v>
+      </c>
+      <c r="O232" t="s">
+        <v>244</v>
+      </c>
+      <c r="P232" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q232">
+        <v>2.63</v>
+      </c>
+      <c r="R232">
+        <v>1.95</v>
+      </c>
+      <c r="S232">
+        <v>5</v>
+      </c>
+      <c r="T232">
+        <v>1.53</v>
+      </c>
+      <c r="U232">
+        <v>2.38</v>
+      </c>
+      <c r="V232">
+        <v>3.75</v>
+      </c>
+      <c r="W232">
+        <v>1.25</v>
+      </c>
+      <c r="X232">
+        <v>11</v>
+      </c>
+      <c r="Y232">
+        <v>1.05</v>
+      </c>
+      <c r="Z232">
+        <v>1.9</v>
+      </c>
+      <c r="AA232">
+        <v>3.3</v>
+      </c>
+      <c r="AB232">
+        <v>4.2</v>
+      </c>
+      <c r="AC232">
+        <v>1.1</v>
+      </c>
+      <c r="AD232">
+        <v>7.5</v>
+      </c>
+      <c r="AE232">
+        <v>1.48</v>
+      </c>
+      <c r="AF232">
+        <v>2.7</v>
+      </c>
+      <c r="AG232">
+        <v>2.5</v>
+      </c>
+      <c r="AH232">
+        <v>1.53</v>
+      </c>
+      <c r="AI232">
+        <v>2.2</v>
+      </c>
+      <c r="AJ232">
+        <v>1.62</v>
+      </c>
+      <c r="AK232">
+        <v>1.21</v>
+      </c>
+      <c r="AL232">
+        <v>1.33</v>
+      </c>
+      <c r="AM232">
+        <v>1.83</v>
+      </c>
+      <c r="AN232">
+        <v>1.73</v>
+      </c>
+      <c r="AO232">
+        <v>1</v>
+      </c>
+      <c r="AP232">
+        <v>1.58</v>
+      </c>
+      <c r="AQ232">
+        <v>1.17</v>
+      </c>
+      <c r="AR232">
+        <v>1.36</v>
+      </c>
+      <c r="AS232">
+        <v>1.08</v>
+      </c>
+      <c r="AT232">
+        <v>2.44</v>
+      </c>
+      <c r="AU232">
+        <v>5</v>
+      </c>
+      <c r="AV232">
+        <v>7</v>
+      </c>
+      <c r="AW232">
+        <v>10</v>
+      </c>
+      <c r="AX232">
+        <v>4</v>
+      </c>
+      <c r="AY232">
+        <v>19</v>
+      </c>
+      <c r="AZ232">
+        <v>13</v>
+      </c>
+      <c r="BA232">
+        <v>3</v>
+      </c>
+      <c r="BB232">
+        <v>3</v>
+      </c>
+      <c r="BC232">
+        <v>6</v>
+      </c>
+      <c r="BD232">
+        <v>1.5</v>
+      </c>
+      <c r="BE232">
+        <v>6.4</v>
+      </c>
+      <c r="BF232">
+        <v>2.9</v>
+      </c>
+      <c r="BG232">
+        <v>1.65</v>
+      </c>
+      <c r="BH232">
+        <v>2.08</v>
+      </c>
+      <c r="BI232">
+        <v>2.06</v>
+      </c>
+      <c r="BJ232">
+        <v>1.66</v>
+      </c>
+      <c r="BK232">
+        <v>2.65</v>
+      </c>
+      <c r="BL232">
+        <v>1.41</v>
+      </c>
+      <c r="BM232">
+        <v>3.55</v>
+      </c>
+      <c r="BN232">
+        <v>1.24</v>
+      </c>
+      <c r="BO232">
+        <v>4.8</v>
+      </c>
+      <c r="BP232">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,12 @@
     <t>['54']</t>
   </si>
   <si>
+    <t>['10', '37', '88']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -910,9 +916,6 @@
     <t>['43', '66', '85']</t>
   </si>
   <si>
-    <t>['32']</t>
-  </si>
-  <si>
     <t>['49', '67']</t>
   </si>
   <si>
@@ -1016,6 +1019,9 @@
   </si>
   <si>
     <t>['3', '62']</t>
+  </si>
+  <si>
+    <t>['25', '50', '68']</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP236"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1633,7 +1639,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2045,7 +2051,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2126,7 +2132,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2251,7 +2257,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2457,7 +2463,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2535,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ6">
         <v>0.83</v>
@@ -2663,7 +2669,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2869,7 +2875,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3075,7 +3081,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3156,7 +3162,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3487,7 +3493,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3565,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11">
         <v>1.73</v>
@@ -3774,7 +3780,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ12">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR12">
         <v>1.07</v>
@@ -3899,7 +3905,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4183,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ14">
         <v>1.36</v>
@@ -5213,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
         <v>0.91</v>
@@ -5625,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -5753,7 +5759,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -5831,10 +5837,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR22">
         <v>1.08</v>
@@ -6165,7 +6171,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6452,7 +6458,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ25">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR25">
         <v>0.96</v>
@@ -6861,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ27">
         <v>0.18</v>
@@ -6989,7 +6995,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7070,7 +7076,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ28">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -7482,7 +7488,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ30">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR30">
         <v>1.44</v>
@@ -8225,7 +8231,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8509,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35">
         <v>1.36</v>
@@ -8843,7 +8849,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8921,10 +8927,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ37">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -9049,7 +9055,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9873,7 +9879,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10079,7 +10085,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10160,7 +10166,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR43">
         <v>1.17</v>
@@ -10491,7 +10497,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10572,7 +10578,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ45">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR45">
         <v>1.14</v>
@@ -10903,7 +10909,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11109,7 +11115,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11393,10 +11399,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ49">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR49">
         <v>1.74</v>
@@ -12139,7 +12145,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12217,7 +12223,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ53">
         <v>1.73</v>
@@ -12757,7 +12763,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12835,7 +12841,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ56">
         <v>0.91</v>
@@ -13662,7 +13668,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -13787,7 +13793,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13865,7 +13871,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61">
         <v>2.08</v>
@@ -14199,7 +14205,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14611,7 +14617,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14817,7 +14823,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14898,7 +14904,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ66">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR66">
         <v>2.43</v>
@@ -15435,7 +15441,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15641,7 +15647,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16053,7 +16059,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16340,7 +16346,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ73">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16752,7 +16758,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ75">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR75">
         <v>1.11</v>
@@ -16877,7 +16883,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -16955,7 +16961,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ76">
         <v>2.08</v>
@@ -17701,7 +17707,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17779,10 +17785,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ80">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR80">
         <v>1.69</v>
@@ -17907,7 +17913,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17985,7 +17991,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ81">
         <v>0.91</v>
@@ -18191,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ82">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR82">
         <v>1.25</v>
@@ -18812,7 +18818,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ85">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR85">
         <v>1.24</v>
@@ -18937,7 +18943,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19349,7 +19355,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19555,7 +19561,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19967,7 +19973,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20173,7 +20179,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20585,7 +20591,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20663,7 +20669,7 @@
         <v>0.5</v>
       </c>
       <c r="AP94">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20997,7 +21003,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21078,7 +21084,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ96">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -21487,7 +21493,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ98">
         <v>0.83</v>
@@ -21693,7 +21699,7 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
         <v>1.17</v>
@@ -22027,7 +22033,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22233,7 +22239,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22439,7 +22445,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22726,7 +22732,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR104">
         <v>1.49</v>
@@ -23057,7 +23063,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23341,10 +23347,10 @@
         <v>0.75</v>
       </c>
       <c r="AP107">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ107">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.1</v>
@@ -23550,7 +23556,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ108">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -23881,7 +23887,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24577,7 +24583,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ113">
         <v>0.25</v>
@@ -24705,7 +24711,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24989,7 +24995,7 @@
         <v>0.6</v>
       </c>
       <c r="AP115">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ115">
         <v>0.91</v>
@@ -25117,7 +25123,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25323,7 +25329,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25529,7 +25535,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25941,7 +25947,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26431,10 +26437,10 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR122">
         <v>1.57</v>
@@ -26637,7 +26643,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ123">
         <v>0.91</v>
@@ -26765,7 +26771,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26846,7 +26852,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ124">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR124">
         <v>1.82</v>
@@ -28001,7 +28007,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28285,10 +28291,10 @@
         <v>0.43</v>
       </c>
       <c r="AP131">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ131">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28413,7 +28419,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28825,7 +28831,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29031,7 +29037,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29109,7 +29115,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ135">
         <v>1.75</v>
@@ -29443,7 +29449,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29521,10 +29527,10 @@
         <v>1.8</v>
       </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ137">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -29855,7 +29861,7 @@
         <v>189</v>
       </c>
       <c r="P139" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -29936,7 +29942,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ139">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR139">
         <v>1.33</v>
@@ -30061,7 +30067,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30554,7 +30560,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ142">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR142">
         <v>1.12</v>
@@ -30679,7 +30685,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30885,7 +30891,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -30963,7 +30969,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -31297,7 +31303,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31915,7 +31921,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32121,7 +32127,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32202,7 +32208,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ150">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32739,7 +32745,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33151,7 +33157,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33232,7 +33238,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ155">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR155">
         <v>1.38</v>
@@ -33357,7 +33363,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33435,7 +33441,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ156">
         <v>1.27</v>
@@ -33769,7 +33775,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33847,10 +33853,10 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ158">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR158">
         <v>1.47</v>
@@ -33975,7 +33981,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34053,7 +34059,7 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ159">
         <v>0.91</v>
@@ -34468,7 +34474,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ161">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR161">
         <v>1.1</v>
@@ -35086,7 +35092,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ164">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR164">
         <v>1.37</v>
@@ -35211,7 +35217,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35292,7 +35298,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ165">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR165">
         <v>1.64</v>
@@ -35495,7 +35501,7 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ166">
         <v>1.17</v>
@@ -35623,7 +35629,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36035,7 +36041,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36113,7 +36119,7 @@
         <v>0.75</v>
       </c>
       <c r="AP169">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ169">
         <v>1</v>
@@ -36447,7 +36453,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36528,7 +36534,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ171">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR171">
         <v>1.12</v>
@@ -36731,7 +36737,7 @@
         <v>1.38</v>
       </c>
       <c r="AP172">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ172">
         <v>1.42</v>
@@ -37555,7 +37561,7 @@
         <v>1.5</v>
       </c>
       <c r="AP176">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ176">
         <v>1.73</v>
@@ -37683,7 +37689,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37889,7 +37895,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -37970,7 +37976,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ178">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR178">
         <v>1.38</v>
@@ -38095,7 +38101,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38301,7 +38307,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38379,7 +38385,7 @@
         <v>1.75</v>
       </c>
       <c r="AP180">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ180">
         <v>1.75</v>
@@ -38919,7 +38925,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39000,7 +39006,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ183">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR183">
         <v>1.35</v>
@@ -39206,7 +39212,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ184">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR184">
         <v>1.61</v>
@@ -39331,7 +39337,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40030,7 +40036,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ188">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR188">
         <v>1.34</v>
@@ -40155,7 +40161,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40439,7 +40445,7 @@
         <v>0.88</v>
       </c>
       <c r="AP190">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ190">
         <v>0.82</v>
@@ -40979,7 +40985,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41263,7 +41269,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ194">
         <v>1.73</v>
@@ -41391,7 +41397,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41472,7 +41478,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ195">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR195">
         <v>1.78</v>
@@ -41803,7 +41809,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42009,7 +42015,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42293,7 +42299,7 @@
         <v>1.3</v>
       </c>
       <c r="AP199">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ199">
         <v>1.42</v>
@@ -42705,7 +42711,7 @@
         <v>1.67</v>
       </c>
       <c r="AP201">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ201">
         <v>1.36</v>
@@ -43039,7 +43045,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43245,7 +43251,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43323,7 +43329,7 @@
         <v>1.7</v>
       </c>
       <c r="AP204">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ204">
         <v>1.75</v>
@@ -43451,7 +43457,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43657,7 +43663,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43738,7 +43744,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ206">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR206">
         <v>1.01</v>
@@ -44069,7 +44075,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44562,7 +44568,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ210">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR210">
         <v>2.02</v>
@@ -44687,7 +44693,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44768,7 +44774,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ211">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR211">
         <v>1.16</v>
@@ -44893,7 +44899,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -44971,7 +44977,7 @@
         <v>1.27</v>
       </c>
       <c r="AP212">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ212">
         <v>1.42</v>
@@ -45383,7 +45389,7 @@
         <v>0.3</v>
       </c>
       <c r="AP214">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ214">
         <v>0.25</v>
@@ -45589,7 +45595,7 @@
         <v>1.5</v>
       </c>
       <c r="AP215">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ215">
         <v>1.36</v>
@@ -45798,7 +45804,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ216">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR216">
         <v>1.18</v>
@@ -46004,7 +46010,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ217">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR217">
         <v>2.09</v>
@@ -46210,7 +46216,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ218">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AR218">
         <v>1.3</v>
@@ -46413,7 +46419,7 @@
         <v>1.4</v>
       </c>
       <c r="AP219">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ219">
         <v>1.27</v>
@@ -46541,7 +46547,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47159,7 +47165,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47571,7 +47577,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48601,7 +48607,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49013,7 +49019,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49170,6 +49176,830 @@
       </c>
       <c r="BP232">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7465227</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45703.41666666666</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>85</v>
+      </c>
+      <c r="H233" t="s">
+        <v>86</v>
+      </c>
+      <c r="I233">
+        <v>2</v>
+      </c>
+      <c r="J233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>3</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>3</v>
+      </c>
+      <c r="N233">
+        <v>6</v>
+      </c>
+      <c r="O233" t="s">
+        <v>245</v>
+      </c>
+      <c r="P233" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q233">
+        <v>3.75</v>
+      </c>
+      <c r="R233">
+        <v>1.91</v>
+      </c>
+      <c r="S233">
+        <v>3.4</v>
+      </c>
+      <c r="T233">
+        <v>1.57</v>
+      </c>
+      <c r="U233">
+        <v>2.25</v>
+      </c>
+      <c r="V233">
+        <v>3.75</v>
+      </c>
+      <c r="W233">
+        <v>1.25</v>
+      </c>
+      <c r="X233">
+        <v>13</v>
+      </c>
+      <c r="Y233">
+        <v>1.04</v>
+      </c>
+      <c r="Z233">
+        <v>3.15</v>
+      </c>
+      <c r="AA233">
+        <v>2.89</v>
+      </c>
+      <c r="AB233">
+        <v>2.63</v>
+      </c>
+      <c r="AC233">
+        <v>1.13</v>
+      </c>
+      <c r="AD233">
+        <v>6</v>
+      </c>
+      <c r="AE233">
+        <v>1.5</v>
+      </c>
+      <c r="AF233">
+        <v>2.4</v>
+      </c>
+      <c r="AG233">
+        <v>2.75</v>
+      </c>
+      <c r="AH233">
+        <v>1.44</v>
+      </c>
+      <c r="AI233">
+        <v>2.1</v>
+      </c>
+      <c r="AJ233">
+        <v>1.67</v>
+      </c>
+      <c r="AK233">
+        <v>1.49</v>
+      </c>
+      <c r="AL233">
+        <v>1.38</v>
+      </c>
+      <c r="AM233">
+        <v>1.37</v>
+      </c>
+      <c r="AN233">
+        <v>1.18</v>
+      </c>
+      <c r="AO233">
+        <v>0.67</v>
+      </c>
+      <c r="AP233">
+        <v>1.17</v>
+      </c>
+      <c r="AQ233">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR233">
+        <v>0.95</v>
+      </c>
+      <c r="AS233">
+        <v>1.12</v>
+      </c>
+      <c r="AT233">
+        <v>2.07</v>
+      </c>
+      <c r="AU233">
+        <v>4</v>
+      </c>
+      <c r="AV233">
+        <v>8</v>
+      </c>
+      <c r="AW233">
+        <v>5</v>
+      </c>
+      <c r="AX233">
+        <v>9</v>
+      </c>
+      <c r="AY233">
+        <v>9</v>
+      </c>
+      <c r="AZ233">
+        <v>20</v>
+      </c>
+      <c r="BA233">
+        <v>3</v>
+      </c>
+      <c r="BB233">
+        <v>2</v>
+      </c>
+      <c r="BC233">
+        <v>5</v>
+      </c>
+      <c r="BD233">
+        <v>2.07</v>
+      </c>
+      <c r="BE233">
+        <v>6.1</v>
+      </c>
+      <c r="BF233">
+        <v>1.95</v>
+      </c>
+      <c r="BG233">
+        <v>1.49</v>
+      </c>
+      <c r="BH233">
+        <v>2.4</v>
+      </c>
+      <c r="BI233">
+        <v>1.83</v>
+      </c>
+      <c r="BJ233">
+        <v>1.85</v>
+      </c>
+      <c r="BK233">
+        <v>2.33</v>
+      </c>
+      <c r="BL233">
+        <v>1.52</v>
+      </c>
+      <c r="BM233">
+        <v>3.05</v>
+      </c>
+      <c r="BN233">
+        <v>1.3</v>
+      </c>
+      <c r="BO233">
+        <v>4.1</v>
+      </c>
+      <c r="BP233">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7465222</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45703.51041666666</v>
+      </c>
+      <c r="F234">
+        <v>24</v>
+      </c>
+      <c r="G234" t="s">
+        <v>74</v>
+      </c>
+      <c r="H234" t="s">
+        <v>84</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>1</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>1</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>221</v>
+      </c>
+      <c r="P234" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q234">
+        <v>5.5</v>
+      </c>
+      <c r="R234">
+        <v>2.4</v>
+      </c>
+      <c r="S234">
+        <v>2.1</v>
+      </c>
+      <c r="T234">
+        <v>1.3</v>
+      </c>
+      <c r="U234">
+        <v>3.4</v>
+      </c>
+      <c r="V234">
+        <v>2.5</v>
+      </c>
+      <c r="W234">
+        <v>1.5</v>
+      </c>
+      <c r="X234">
+        <v>6</v>
+      </c>
+      <c r="Y234">
+        <v>1.13</v>
+      </c>
+      <c r="Z234">
+        <v>5.75</v>
+      </c>
+      <c r="AA234">
+        <v>3.9</v>
+      </c>
+      <c r="AB234">
+        <v>1.57</v>
+      </c>
+      <c r="AC234">
+        <v>1.03</v>
+      </c>
+      <c r="AD234">
+        <v>15</v>
+      </c>
+      <c r="AE234">
+        <v>1.2</v>
+      </c>
+      <c r="AF234">
+        <v>4.5</v>
+      </c>
+      <c r="AG234">
+        <v>1.67</v>
+      </c>
+      <c r="AH234">
+        <v>2.2</v>
+      </c>
+      <c r="AI234">
+        <v>1.7</v>
+      </c>
+      <c r="AJ234">
+        <v>2.05</v>
+      </c>
+      <c r="AK234">
+        <v>2.37</v>
+      </c>
+      <c r="AL234">
+        <v>1.21</v>
+      </c>
+      <c r="AM234">
+        <v>1.15</v>
+      </c>
+      <c r="AN234">
+        <v>1.83</v>
+      </c>
+      <c r="AO234">
+        <v>1.83</v>
+      </c>
+      <c r="AP234">
+        <v>1.77</v>
+      </c>
+      <c r="AQ234">
+        <v>1.77</v>
+      </c>
+      <c r="AR234">
+        <v>1.47</v>
+      </c>
+      <c r="AS234">
+        <v>1.72</v>
+      </c>
+      <c r="AT234">
+        <v>3.19</v>
+      </c>
+      <c r="AU234">
+        <v>5</v>
+      </c>
+      <c r="AV234">
+        <v>6</v>
+      </c>
+      <c r="AW234">
+        <v>7</v>
+      </c>
+      <c r="AX234">
+        <v>12</v>
+      </c>
+      <c r="AY234">
+        <v>13</v>
+      </c>
+      <c r="AZ234">
+        <v>23</v>
+      </c>
+      <c r="BA234">
+        <v>6</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>8</v>
+      </c>
+      <c r="BD234">
+        <v>2.9</v>
+      </c>
+      <c r="BE234">
+        <v>7</v>
+      </c>
+      <c r="BF234">
+        <v>1.5</v>
+      </c>
+      <c r="BG234">
+        <v>1.27</v>
+      </c>
+      <c r="BH234">
+        <v>3.3</v>
+      </c>
+      <c r="BI234">
+        <v>1.48</v>
+      </c>
+      <c r="BJ234">
+        <v>2.43</v>
+      </c>
+      <c r="BK234">
+        <v>1.77</v>
+      </c>
+      <c r="BL234">
+        <v>1.92</v>
+      </c>
+      <c r="BM234">
+        <v>2.2</v>
+      </c>
+      <c r="BN234">
+        <v>1.58</v>
+      </c>
+      <c r="BO234">
+        <v>2.8</v>
+      </c>
+      <c r="BP234">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7465219</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45703.60416666666</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="s">
+        <v>87</v>
+      </c>
+      <c r="H235" t="s">
+        <v>72</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>1</v>
+      </c>
+      <c r="M235">
+        <v>1</v>
+      </c>
+      <c r="N235">
+        <v>2</v>
+      </c>
+      <c r="O235" t="s">
+        <v>148</v>
+      </c>
+      <c r="P235" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q235">
+        <v>1.95</v>
+      </c>
+      <c r="R235">
+        <v>2.3</v>
+      </c>
+      <c r="S235">
+        <v>7</v>
+      </c>
+      <c r="T235">
+        <v>1.36</v>
+      </c>
+      <c r="U235">
+        <v>3</v>
+      </c>
+      <c r="V235">
+        <v>2.75</v>
+      </c>
+      <c r="W235">
+        <v>1.4</v>
+      </c>
+      <c r="X235">
+        <v>7</v>
+      </c>
+      <c r="Y235">
+        <v>1.1</v>
+      </c>
+      <c r="Z235">
+        <v>1.42</v>
+      </c>
+      <c r="AA235">
+        <v>4.5</v>
+      </c>
+      <c r="AB235">
+        <v>7</v>
+      </c>
+      <c r="AC235">
+        <v>1.04</v>
+      </c>
+      <c r="AD235">
+        <v>13</v>
+      </c>
+      <c r="AE235">
+        <v>1.28</v>
+      </c>
+      <c r="AF235">
+        <v>3.75</v>
+      </c>
+      <c r="AG235">
+        <v>1.8</v>
+      </c>
+      <c r="AH235">
+        <v>2</v>
+      </c>
+      <c r="AI235">
+        <v>2.1</v>
+      </c>
+      <c r="AJ235">
+        <v>1.67</v>
+      </c>
+      <c r="AK235">
+        <v>1.1</v>
+      </c>
+      <c r="AL235">
+        <v>1.2</v>
+      </c>
+      <c r="AM235">
+        <v>2.75</v>
+      </c>
+      <c r="AN235">
+        <v>2.5</v>
+      </c>
+      <c r="AO235">
+        <v>0.45</v>
+      </c>
+      <c r="AP235">
+        <v>2.38</v>
+      </c>
+      <c r="AQ235">
+        <v>0.5</v>
+      </c>
+      <c r="AR235">
+        <v>1.76</v>
+      </c>
+      <c r="AS235">
+        <v>1.24</v>
+      </c>
+      <c r="AT235">
+        <v>3</v>
+      </c>
+      <c r="AU235">
+        <v>4</v>
+      </c>
+      <c r="AV235">
+        <v>5</v>
+      </c>
+      <c r="AW235">
+        <v>6</v>
+      </c>
+      <c r="AX235">
+        <v>7</v>
+      </c>
+      <c r="AY235">
+        <v>11</v>
+      </c>
+      <c r="AZ235">
+        <v>14</v>
+      </c>
+      <c r="BA235">
+        <v>2</v>
+      </c>
+      <c r="BB235">
+        <v>7</v>
+      </c>
+      <c r="BC235">
+        <v>9</v>
+      </c>
+      <c r="BD235">
+        <v>1.33</v>
+      </c>
+      <c r="BE235">
+        <v>6.75</v>
+      </c>
+      <c r="BF235">
+        <v>3.7</v>
+      </c>
+      <c r="BG235">
+        <v>1.46</v>
+      </c>
+      <c r="BH235">
+        <v>2.5</v>
+      </c>
+      <c r="BI235">
+        <v>1.77</v>
+      </c>
+      <c r="BJ235">
+        <v>1.92</v>
+      </c>
+      <c r="BK235">
+        <v>2.23</v>
+      </c>
+      <c r="BL235">
+        <v>1.57</v>
+      </c>
+      <c r="BM235">
+        <v>2.9</v>
+      </c>
+      <c r="BN235">
+        <v>1.35</v>
+      </c>
+      <c r="BO235">
+        <v>3.9</v>
+      </c>
+      <c r="BP235">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7465225</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45703.70833333334</v>
+      </c>
+      <c r="F236">
+        <v>24</v>
+      </c>
+      <c r="G236" t="s">
+        <v>79</v>
+      </c>
+      <c r="H236" t="s">
+        <v>75</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>1</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>2</v>
+      </c>
+      <c r="O236" t="s">
+        <v>246</v>
+      </c>
+      <c r="P236" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q236">
+        <v>2.05</v>
+      </c>
+      <c r="R236">
+        <v>2.4</v>
+      </c>
+      <c r="S236">
+        <v>6</v>
+      </c>
+      <c r="T236">
+        <v>1.33</v>
+      </c>
+      <c r="U236">
+        <v>3.25</v>
+      </c>
+      <c r="V236">
+        <v>2.5</v>
+      </c>
+      <c r="W236">
+        <v>1.5</v>
+      </c>
+      <c r="X236">
+        <v>6.5</v>
+      </c>
+      <c r="Y236">
+        <v>1.11</v>
+      </c>
+      <c r="Z236">
+        <v>1.5</v>
+      </c>
+      <c r="AA236">
+        <v>4.2</v>
+      </c>
+      <c r="AB236">
+        <v>6.25</v>
+      </c>
+      <c r="AC236">
+        <v>1.03</v>
+      </c>
+      <c r="AD236">
+        <v>15</v>
+      </c>
+      <c r="AE236">
+        <v>1.22</v>
+      </c>
+      <c r="AF236">
+        <v>4.33</v>
+      </c>
+      <c r="AG236">
+        <v>1.67</v>
+      </c>
+      <c r="AH236">
+        <v>2.2</v>
+      </c>
+      <c r="AI236">
+        <v>1.8</v>
+      </c>
+      <c r="AJ236">
+        <v>1.95</v>
+      </c>
+      <c r="AK236">
+        <v>1.13</v>
+      </c>
+      <c r="AL236">
+        <v>1.21</v>
+      </c>
+      <c r="AM236">
+        <v>2.5</v>
+      </c>
+      <c r="AN236">
+        <v>1.73</v>
+      </c>
+      <c r="AO236">
+        <v>0.36</v>
+      </c>
+      <c r="AP236">
+        <v>1.67</v>
+      </c>
+      <c r="AQ236">
+        <v>0.42</v>
+      </c>
+      <c r="AR236">
+        <v>1.64</v>
+      </c>
+      <c r="AS236">
+        <v>0.93</v>
+      </c>
+      <c r="AT236">
+        <v>2.57</v>
+      </c>
+      <c r="AU236">
+        <v>5</v>
+      </c>
+      <c r="AV236">
+        <v>4</v>
+      </c>
+      <c r="AW236">
+        <v>9</v>
+      </c>
+      <c r="AX236">
+        <v>9</v>
+      </c>
+      <c r="AY236">
+        <v>15</v>
+      </c>
+      <c r="AZ236">
+        <v>14</v>
+      </c>
+      <c r="BA236">
+        <v>4</v>
+      </c>
+      <c r="BB236">
+        <v>5</v>
+      </c>
+      <c r="BC236">
+        <v>9</v>
+      </c>
+      <c r="BD236">
+        <v>1.45</v>
+      </c>
+      <c r="BE236">
+        <v>7</v>
+      </c>
+      <c r="BF236">
+        <v>3.05</v>
+      </c>
+      <c r="BG236">
+        <v>1.33</v>
+      </c>
+      <c r="BH236">
+        <v>2.95</v>
+      </c>
+      <c r="BI236">
+        <v>1.56</v>
+      </c>
+      <c r="BJ236">
+        <v>2.23</v>
+      </c>
+      <c r="BK236">
+        <v>1.91</v>
+      </c>
+      <c r="BL236">
+        <v>1.78</v>
+      </c>
+      <c r="BM236">
+        <v>2.4</v>
+      </c>
+      <c r="BN236">
+        <v>1.49</v>
+      </c>
+      <c r="BO236">
+        <v>3.15</v>
+      </c>
+      <c r="BP236">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,15 @@
     <t>['32']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['7', '28', '35']</t>
+  </si>
+  <si>
+    <t>['51', '64', '69']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1022,6 +1031,12 @@
   </si>
   <si>
     <t>['25', '50', '68']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['5', '45+1', '67', '84']</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP236"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1639,7 +1654,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1923,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -2051,7 +2066,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2257,7 +2272,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2338,7 +2353,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ5">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2463,7 +2478,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2669,7 +2684,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2875,7 +2890,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3081,7 +3096,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3159,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9">
         <v>1.77</v>
@@ -3365,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>0.18</v>
@@ -3493,7 +3508,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3905,7 +3920,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4398,7 +4413,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ15">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4601,10 +4616,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ16">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5222,7 +5237,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ19">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5759,7 +5774,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6043,10 +6058,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ23">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR23">
         <v>1.51</v>
@@ -6171,7 +6186,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6661,7 +6676,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>0.83</v>
@@ -6995,7 +7010,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -8103,7 +8118,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ33">
         <v>1.42</v>
@@ -8231,7 +8246,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8724,7 +8739,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ36">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR36">
         <v>0.71</v>
@@ -8849,7 +8864,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9055,7 +9070,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9342,7 +9357,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR39">
         <v>1.12</v>
@@ -9751,7 +9766,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41">
         <v>0.83</v>
@@ -9879,7 +9894,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9957,7 +9972,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ42">
         <v>1.75</v>
@@ -10085,7 +10100,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10163,7 +10178,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ43">
         <v>0.6899999999999999</v>
@@ -10497,7 +10512,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10909,7 +10924,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11115,7 +11130,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11196,7 +11211,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ48">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11811,10 +11826,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ51">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR51">
         <v>1.4</v>
@@ -12017,7 +12032,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
         <v>1.17</v>
@@ -12145,7 +12160,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12226,7 +12241,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ53">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR53">
         <v>1.17</v>
@@ -12432,7 +12447,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ54">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR54">
         <v>1.07</v>
@@ -12635,10 +12650,10 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -12763,7 +12778,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12844,7 +12859,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ56">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -13793,7 +13808,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14205,7 +14220,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14283,7 +14298,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ63">
         <v>1.36</v>
@@ -14617,7 +14632,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14823,7 +14838,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15441,7 +15456,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15519,7 +15534,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ69">
         <v>1.75</v>
@@ -15647,7 +15662,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16059,7 +16074,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16137,7 +16152,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
         <v>1.36</v>
@@ -16883,7 +16898,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17376,7 +17391,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ78">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17579,7 +17594,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ79">
         <v>0.18</v>
@@ -17707,7 +17722,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17913,7 +17928,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -17994,7 +18009,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -18403,7 +18418,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ83">
         <v>1.36</v>
@@ -18943,7 +18958,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19021,7 +19036,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ86">
         <v>1.42</v>
@@ -19355,7 +19370,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19436,7 +19451,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ88">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19561,7 +19576,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19973,7 +19988,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20179,7 +20194,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20591,7 +20606,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20878,7 +20893,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ95">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -21003,7 +21018,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21287,7 +21302,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ97">
         <v>1.42</v>
@@ -21908,7 +21923,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ100">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22033,7 +22048,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22114,7 +22129,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ101">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR101">
         <v>1.21</v>
@@ -22239,7 +22254,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22317,10 +22332,10 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ102">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>1.07</v>
@@ -22445,7 +22460,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22523,7 +22538,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ103">
         <v>1.75</v>
@@ -23063,7 +23078,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23759,7 +23774,7 @@
         <v>1.8</v>
       </c>
       <c r="AP109">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109">
         <v>1.73</v>
@@ -23887,7 +23902,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24171,10 +24186,10 @@
         <v>1.5</v>
       </c>
       <c r="AP111">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ111">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR111">
         <v>1.44</v>
@@ -24711,7 +24726,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24998,7 +25013,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ115">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25123,7 +25138,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25329,7 +25344,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25410,7 +25425,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ117">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR117">
         <v>1.53</v>
@@ -25535,7 +25550,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25947,7 +25962,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26028,7 +26043,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ120">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR120">
         <v>1.55</v>
@@ -26646,7 +26661,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ123">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR123">
         <v>1.08</v>
@@ -26771,7 +26786,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26849,7 +26864,7 @@
         <v>0.6</v>
       </c>
       <c r="AP124">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ124">
         <v>0.5</v>
@@ -27055,7 +27070,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ125">
         <v>1.73</v>
@@ -27467,10 +27482,10 @@
         <v>1.4</v>
       </c>
       <c r="AP127">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -28007,7 +28022,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28419,7 +28434,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28831,7 +28846,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29037,7 +29052,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29449,7 +29464,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29736,7 +29751,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ138">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR138">
         <v>1.36</v>
@@ -29939,7 +29954,7 @@
         <v>0.33</v>
       </c>
       <c r="AP139">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ139">
         <v>0.42</v>
@@ -30067,7 +30082,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30148,7 +30163,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ140">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR140">
         <v>1.94</v>
@@ -30557,7 +30572,7 @@
         <v>0.67</v>
       </c>
       <c r="AP142">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ142">
         <v>0.5</v>
@@ -30685,7 +30700,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30763,7 +30778,7 @@
         <v>1.71</v>
       </c>
       <c r="AP143">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ143">
         <v>1.73</v>
@@ -30891,7 +30906,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31303,7 +31318,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31384,7 +31399,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ146">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR146">
         <v>1.72</v>
@@ -31921,7 +31936,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -31999,7 +32014,7 @@
         <v>2.11</v>
       </c>
       <c r="AP149">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ149">
         <v>2.08</v>
@@ -32127,7 +32142,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32745,7 +32760,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32823,7 +32838,7 @@
         <v>2.2</v>
       </c>
       <c r="AP153">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ153">
         <v>2.08</v>
@@ -33157,7 +33172,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33363,7 +33378,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33444,7 +33459,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ156">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR156">
         <v>0.98</v>
@@ -33775,7 +33790,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33981,7 +33996,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34062,7 +34077,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ159">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34471,7 +34486,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ161">
         <v>0.42</v>
@@ -34677,7 +34692,7 @@
         <v>0.86</v>
       </c>
       <c r="AP162">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ162">
         <v>0.82</v>
@@ -34883,7 +34898,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ163">
         <v>1</v>
@@ -35217,7 +35232,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35629,7 +35644,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35710,7 +35725,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ167">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR167">
         <v>1.17</v>
@@ -35916,7 +35931,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ168">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR168">
         <v>1.43</v>
@@ -36041,7 +36056,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36453,7 +36468,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36531,7 +36546,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ171">
         <v>0.42</v>
@@ -37358,7 +37373,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ175">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR175">
         <v>1.41</v>
@@ -37564,7 +37579,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ176">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37689,7 +37704,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37895,7 +37910,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38101,7 +38116,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38182,7 +38197,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ179">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR179">
         <v>1.81</v>
@@ -38307,7 +38322,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38797,7 +38812,7 @@
         <v>1.33</v>
       </c>
       <c r="AP182">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ182">
         <v>1.42</v>
@@ -38925,7 +38940,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39337,7 +39352,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39621,7 +39636,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ186">
         <v>1</v>
@@ -39827,7 +39842,7 @@
         <v>0.89</v>
       </c>
       <c r="AP187">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ187">
         <v>0.83</v>
@@ -40161,7 +40176,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40857,7 +40872,7 @@
         <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ192">
         <v>0.25</v>
@@ -40985,7 +41000,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41066,7 +41081,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ193">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR193">
         <v>1.37</v>
@@ -41397,7 +41412,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41475,7 +41490,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ195">
         <v>0.6899999999999999</v>
@@ -41809,7 +41824,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41890,7 +41905,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ197">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR197">
         <v>1.41</v>
@@ -42015,7 +42030,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42096,7 +42111,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ198">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR198">
         <v>1.8</v>
@@ -42508,7 +42523,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ200">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR200">
         <v>1.33</v>
@@ -43045,7 +43060,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43123,7 +43138,7 @@
         <v>0.9</v>
       </c>
       <c r="AP203">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ203">
         <v>1</v>
@@ -43251,7 +43266,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43457,7 +43472,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43663,7 +43678,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43741,7 +43756,7 @@
         <v>1.9</v>
       </c>
       <c r="AP206">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ206">
         <v>1.77</v>
@@ -44075,7 +44090,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44693,7 +44708,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44899,7 +44914,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45186,7 +45201,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ213">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR213">
         <v>1.36</v>
@@ -45801,7 +45816,7 @@
         <v>2</v>
       </c>
       <c r="AP216">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ216">
         <v>1.77</v>
@@ -46422,7 +46437,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ219">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR219">
         <v>1.48</v>
@@ -46547,7 +46562,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -46625,10 +46640,10 @@
         <v>1.8</v>
       </c>
       <c r="AP220">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ220">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR220">
         <v>1.72</v>
@@ -46834,7 +46849,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ221">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR221">
         <v>1.35</v>
@@ -47165,7 +47180,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47577,7 +47592,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48607,7 +48622,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -48891,7 +48906,7 @@
         <v>0.8</v>
       </c>
       <c r="AP231">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ231">
         <v>0.82</v>
@@ -49019,7 +49034,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49225,7 +49240,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49431,7 +49446,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50000,6 +50015,830 @@
       </c>
       <c r="BP236">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7469587</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45704.41666666666</v>
+      </c>
+      <c r="F237">
+        <v>24</v>
+      </c>
+      <c r="G237" t="s">
+        <v>82</v>
+      </c>
+      <c r="H237" t="s">
+        <v>70</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>2</v>
+      </c>
+      <c r="O237" t="s">
+        <v>247</v>
+      </c>
+      <c r="P237" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q237">
+        <v>5.5</v>
+      </c>
+      <c r="R237">
+        <v>2.05</v>
+      </c>
+      <c r="S237">
+        <v>2.4</v>
+      </c>
+      <c r="T237">
+        <v>1.5</v>
+      </c>
+      <c r="U237">
+        <v>2.5</v>
+      </c>
+      <c r="V237">
+        <v>3.5</v>
+      </c>
+      <c r="W237">
+        <v>1.29</v>
+      </c>
+      <c r="X237">
+        <v>11</v>
+      </c>
+      <c r="Y237">
+        <v>1.05</v>
+      </c>
+      <c r="Z237">
+        <v>4.75</v>
+      </c>
+      <c r="AA237">
+        <v>3.5</v>
+      </c>
+      <c r="AB237">
+        <v>1.75</v>
+      </c>
+      <c r="AC237">
+        <v>1.08</v>
+      </c>
+      <c r="AD237">
+        <v>8.5</v>
+      </c>
+      <c r="AE237">
+        <v>1.44</v>
+      </c>
+      <c r="AF237">
+        <v>2.85</v>
+      </c>
+      <c r="AG237">
+        <v>2.3</v>
+      </c>
+      <c r="AH237">
+        <v>1.62</v>
+      </c>
+      <c r="AI237">
+        <v>2.1</v>
+      </c>
+      <c r="AJ237">
+        <v>1.67</v>
+      </c>
+      <c r="AK237">
+        <v>2</v>
+      </c>
+      <c r="AL237">
+        <v>1.3</v>
+      </c>
+      <c r="AM237">
+        <v>1.18</v>
+      </c>
+      <c r="AN237">
+        <v>1.75</v>
+      </c>
+      <c r="AO237">
+        <v>1.73</v>
+      </c>
+      <c r="AP237">
+        <v>1.69</v>
+      </c>
+      <c r="AQ237">
+        <v>1.67</v>
+      </c>
+      <c r="AR237">
+        <v>1.14</v>
+      </c>
+      <c r="AS237">
+        <v>1.37</v>
+      </c>
+      <c r="AT237">
+        <v>2.51</v>
+      </c>
+      <c r="AU237">
+        <v>5</v>
+      </c>
+      <c r="AV237">
+        <v>6</v>
+      </c>
+      <c r="AW237">
+        <v>8</v>
+      </c>
+      <c r="AX237">
+        <v>9</v>
+      </c>
+      <c r="AY237">
+        <v>17</v>
+      </c>
+      <c r="AZ237">
+        <v>19</v>
+      </c>
+      <c r="BA237">
+        <v>2</v>
+      </c>
+      <c r="BB237">
+        <v>7</v>
+      </c>
+      <c r="BC237">
+        <v>9</v>
+      </c>
+      <c r="BD237">
+        <v>3.4</v>
+      </c>
+      <c r="BE237">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF237">
+        <v>1.46</v>
+      </c>
+      <c r="BG237">
+        <v>1.27</v>
+      </c>
+      <c r="BH237">
+        <v>3.14</v>
+      </c>
+      <c r="BI237">
+        <v>1.52</v>
+      </c>
+      <c r="BJ237">
+        <v>2.3</v>
+      </c>
+      <c r="BK237">
+        <v>1.9</v>
+      </c>
+      <c r="BL237">
+        <v>1.8</v>
+      </c>
+      <c r="BM237">
+        <v>2.48</v>
+      </c>
+      <c r="BN237">
+        <v>1.45</v>
+      </c>
+      <c r="BO237">
+        <v>3.34</v>
+      </c>
+      <c r="BP237">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7465224</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45704.51041666666</v>
+      </c>
+      <c r="F238">
+        <v>24</v>
+      </c>
+      <c r="G238" t="s">
+        <v>78</v>
+      </c>
+      <c r="H238" t="s">
+        <v>80</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>2</v>
+      </c>
+      <c r="K238">
+        <v>2</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>4</v>
+      </c>
+      <c r="N238">
+        <v>4</v>
+      </c>
+      <c r="O238" t="s">
+        <v>104</v>
+      </c>
+      <c r="P238" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q238">
+        <v>4.5</v>
+      </c>
+      <c r="R238">
+        <v>2.05</v>
+      </c>
+      <c r="S238">
+        <v>2.63</v>
+      </c>
+      <c r="T238">
+        <v>1.5</v>
+      </c>
+      <c r="U238">
+        <v>2.5</v>
+      </c>
+      <c r="V238">
+        <v>3.4</v>
+      </c>
+      <c r="W238">
+        <v>1.3</v>
+      </c>
+      <c r="X238">
+        <v>10</v>
+      </c>
+      <c r="Y238">
+        <v>1.06</v>
+      </c>
+      <c r="Z238">
+        <v>3.9</v>
+      </c>
+      <c r="AA238">
+        <v>3.4</v>
+      </c>
+      <c r="AB238">
+        <v>1.95</v>
+      </c>
+      <c r="AC238">
+        <v>1.08</v>
+      </c>
+      <c r="AD238">
+        <v>9</v>
+      </c>
+      <c r="AE238">
+        <v>1.4</v>
+      </c>
+      <c r="AF238">
+        <v>3</v>
+      </c>
+      <c r="AG238">
+        <v>2.2</v>
+      </c>
+      <c r="AH238">
+        <v>1.67</v>
+      </c>
+      <c r="AI238">
+        <v>1.95</v>
+      </c>
+      <c r="AJ238">
+        <v>1.8</v>
+      </c>
+      <c r="AK238">
+        <v>1.82</v>
+      </c>
+      <c r="AL238">
+        <v>1.32</v>
+      </c>
+      <c r="AM238">
+        <v>1.23</v>
+      </c>
+      <c r="AN238">
+        <v>1.09</v>
+      </c>
+      <c r="AO238">
+        <v>0.91</v>
+      </c>
+      <c r="AP238">
+        <v>1</v>
+      </c>
+      <c r="AQ238">
+        <v>1.08</v>
+      </c>
+      <c r="AR238">
+        <v>1</v>
+      </c>
+      <c r="AS238">
+        <v>1.2</v>
+      </c>
+      <c r="AT238">
+        <v>2.2</v>
+      </c>
+      <c r="AU238">
+        <v>3</v>
+      </c>
+      <c r="AV238">
+        <v>7</v>
+      </c>
+      <c r="AW238">
+        <v>5</v>
+      </c>
+      <c r="AX238">
+        <v>5</v>
+      </c>
+      <c r="AY238">
+        <v>11</v>
+      </c>
+      <c r="AZ238">
+        <v>12</v>
+      </c>
+      <c r="BA238">
+        <v>3</v>
+      </c>
+      <c r="BB238">
+        <v>2</v>
+      </c>
+      <c r="BC238">
+        <v>5</v>
+      </c>
+      <c r="BD238">
+        <v>2.91</v>
+      </c>
+      <c r="BE238">
+        <v>8.4</v>
+      </c>
+      <c r="BF238">
+        <v>1.6</v>
+      </c>
+      <c r="BG238">
+        <v>1.38</v>
+      </c>
+      <c r="BH238">
+        <v>2.71</v>
+      </c>
+      <c r="BI238">
+        <v>1.71</v>
+      </c>
+      <c r="BJ238">
+        <v>2.02</v>
+      </c>
+      <c r="BK238">
+        <v>2.17</v>
+      </c>
+      <c r="BL238">
+        <v>1.58</v>
+      </c>
+      <c r="BM238">
+        <v>2.88</v>
+      </c>
+      <c r="BN238">
+        <v>1.32</v>
+      </c>
+      <c r="BO238">
+        <v>4.1</v>
+      </c>
+      <c r="BP238">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7465226</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45704.60416666666</v>
+      </c>
+      <c r="F239">
+        <v>24</v>
+      </c>
+      <c r="G239" t="s">
+        <v>77</v>
+      </c>
+      <c r="H239" t="s">
+        <v>73</v>
+      </c>
+      <c r="I239">
+        <v>3</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>3</v>
+      </c>
+      <c r="L239">
+        <v>3</v>
+      </c>
+      <c r="M239">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>4</v>
+      </c>
+      <c r="O239" t="s">
+        <v>248</v>
+      </c>
+      <c r="P239" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q239">
+        <v>2.4</v>
+      </c>
+      <c r="R239">
+        <v>2</v>
+      </c>
+      <c r="S239">
+        <v>6</v>
+      </c>
+      <c r="T239">
+        <v>1.53</v>
+      </c>
+      <c r="U239">
+        <v>2.38</v>
+      </c>
+      <c r="V239">
+        <v>3.5</v>
+      </c>
+      <c r="W239">
+        <v>1.29</v>
+      </c>
+      <c r="X239">
+        <v>11</v>
+      </c>
+      <c r="Y239">
+        <v>1.05</v>
+      </c>
+      <c r="Z239">
+        <v>1.73</v>
+      </c>
+      <c r="AA239">
+        <v>3.4</v>
+      </c>
+      <c r="AB239">
+        <v>5.25</v>
+      </c>
+      <c r="AC239">
+        <v>1.1</v>
+      </c>
+      <c r="AD239">
+        <v>6.75</v>
+      </c>
+      <c r="AE239">
+        <v>1.5</v>
+      </c>
+      <c r="AF239">
+        <v>2.7</v>
+      </c>
+      <c r="AG239">
+        <v>2.5</v>
+      </c>
+      <c r="AH239">
+        <v>1.53</v>
+      </c>
+      <c r="AI239">
+        <v>2.2</v>
+      </c>
+      <c r="AJ239">
+        <v>1.62</v>
+      </c>
+      <c r="AK239">
+        <v>1.17</v>
+      </c>
+      <c r="AL239">
+        <v>1.3</v>
+      </c>
+      <c r="AM239">
+        <v>1.98</v>
+      </c>
+      <c r="AN239">
+        <v>1.33</v>
+      </c>
+      <c r="AO239">
+        <v>0.91</v>
+      </c>
+      <c r="AP239">
+        <v>1.46</v>
+      </c>
+      <c r="AQ239">
+        <v>0.83</v>
+      </c>
+      <c r="AR239">
+        <v>1.24</v>
+      </c>
+      <c r="AS239">
+        <v>1.04</v>
+      </c>
+      <c r="AT239">
+        <v>2.28</v>
+      </c>
+      <c r="AU239">
+        <v>6</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>9</v>
+      </c>
+      <c r="AX239">
+        <v>5</v>
+      </c>
+      <c r="AY239">
+        <v>18</v>
+      </c>
+      <c r="AZ239">
+        <v>11</v>
+      </c>
+      <c r="BA239">
+        <v>3</v>
+      </c>
+      <c r="BB239">
+        <v>5</v>
+      </c>
+      <c r="BC239">
+        <v>8</v>
+      </c>
+      <c r="BD239">
+        <v>1.59</v>
+      </c>
+      <c r="BE239">
+        <v>8.5</v>
+      </c>
+      <c r="BF239">
+        <v>2.93</v>
+      </c>
+      <c r="BG239">
+        <v>1.36</v>
+      </c>
+      <c r="BH239">
+        <v>2.79</v>
+      </c>
+      <c r="BI239">
+        <v>1.67</v>
+      </c>
+      <c r="BJ239">
+        <v>2.08</v>
+      </c>
+      <c r="BK239">
+        <v>2.11</v>
+      </c>
+      <c r="BL239">
+        <v>1.62</v>
+      </c>
+      <c r="BM239">
+        <v>2.78</v>
+      </c>
+      <c r="BN239">
+        <v>1.34</v>
+      </c>
+      <c r="BO239">
+        <v>3.92</v>
+      </c>
+      <c r="BP239">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7465221</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45704.70833333334</v>
+      </c>
+      <c r="F240">
+        <v>24</v>
+      </c>
+      <c r="G240" t="s">
+        <v>71</v>
+      </c>
+      <c r="H240" t="s">
+        <v>76</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>3</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>3</v>
+      </c>
+      <c r="O240" t="s">
+        <v>249</v>
+      </c>
+      <c r="P240" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q240">
+        <v>3.25</v>
+      </c>
+      <c r="R240">
+        <v>1.95</v>
+      </c>
+      <c r="S240">
+        <v>3.75</v>
+      </c>
+      <c r="T240">
+        <v>1.53</v>
+      </c>
+      <c r="U240">
+        <v>2.38</v>
+      </c>
+      <c r="V240">
+        <v>3.5</v>
+      </c>
+      <c r="W240">
+        <v>1.29</v>
+      </c>
+      <c r="X240">
+        <v>11</v>
+      </c>
+      <c r="Y240">
+        <v>1.05</v>
+      </c>
+      <c r="Z240">
+        <v>2.4</v>
+      </c>
+      <c r="AA240">
+        <v>3.1</v>
+      </c>
+      <c r="AB240">
+        <v>3.1</v>
+      </c>
+      <c r="AC240">
+        <v>1.07</v>
+      </c>
+      <c r="AD240">
+        <v>7.3</v>
+      </c>
+      <c r="AE240">
+        <v>1.47</v>
+      </c>
+      <c r="AF240">
+        <v>2.8</v>
+      </c>
+      <c r="AG240">
+        <v>2.38</v>
+      </c>
+      <c r="AH240">
+        <v>1.57</v>
+      </c>
+      <c r="AI240">
+        <v>2</v>
+      </c>
+      <c r="AJ240">
+        <v>1.75</v>
+      </c>
+      <c r="AK240">
+        <v>1.37</v>
+      </c>
+      <c r="AL240">
+        <v>1.36</v>
+      </c>
+      <c r="AM240">
+        <v>1.51</v>
+      </c>
+      <c r="AN240">
+        <v>1.55</v>
+      </c>
+      <c r="AO240">
+        <v>1.27</v>
+      </c>
+      <c r="AP240">
+        <v>1.67</v>
+      </c>
+      <c r="AQ240">
+        <v>1.17</v>
+      </c>
+      <c r="AR240">
+        <v>1.7</v>
+      </c>
+      <c r="AS240">
+        <v>1.13</v>
+      </c>
+      <c r="AT240">
+        <v>2.83</v>
+      </c>
+      <c r="AU240">
+        <v>9</v>
+      </c>
+      <c r="AV240">
+        <v>0</v>
+      </c>
+      <c r="AW240">
+        <v>16</v>
+      </c>
+      <c r="AX240">
+        <v>5</v>
+      </c>
+      <c r="AY240">
+        <v>33</v>
+      </c>
+      <c r="AZ240">
+        <v>5</v>
+      </c>
+      <c r="BA240">
+        <v>5</v>
+      </c>
+      <c r="BB240">
+        <v>5</v>
+      </c>
+      <c r="BC240">
+        <v>10</v>
+      </c>
+      <c r="BD240">
+        <v>1.74</v>
+      </c>
+      <c r="BE240">
+        <v>8.5</v>
+      </c>
+      <c r="BF240">
+        <v>2.53</v>
+      </c>
+      <c r="BG240">
+        <v>1.28</v>
+      </c>
+      <c r="BH240">
+        <v>3.08</v>
+      </c>
+      <c r="BI240">
+        <v>1.53</v>
+      </c>
+      <c r="BJ240">
+        <v>2.28</v>
+      </c>
+      <c r="BK240">
+        <v>1.94</v>
+      </c>
+      <c r="BL240">
+        <v>1.77</v>
+      </c>
+      <c r="BM240">
+        <v>2.51</v>
+      </c>
+      <c r="BN240">
+        <v>1.44</v>
+      </c>
+      <c r="BO240">
+        <v>3.42</v>
+      </c>
+      <c r="BP240">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1398,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2971,7 +2971,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ8">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4410,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ15">
         <v>1.67</v>
@@ -4825,7 +4825,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ31">
         <v>0.25</v>
@@ -8121,7 +8121,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ33">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -15125,7 +15125,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ67">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR67">
         <v>1.32</v>
@@ -15328,7 +15328,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ68">
         <v>1.17</v>
@@ -19039,7 +19039,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -21305,7 +21305,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ97">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR97">
         <v>1.35</v>
@@ -21920,7 +21920,7 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ100">
         <v>1.08</v>
@@ -25216,7 +25216,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ116">
         <v>0.18</v>
@@ -29339,7 +29339,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ136">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR136">
         <v>1.38</v>
@@ -30160,7 +30160,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ140">
         <v>0.83</v>
@@ -33047,7 +33047,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR154">
         <v>1.29</v>
@@ -36340,7 +36340,7 @@
         <v>0.63</v>
       </c>
       <c r="AP170">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ170">
         <v>0.83</v>
@@ -36755,7 +36755,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ172">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR172">
         <v>1.52</v>
@@ -37782,7 +37782,7 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ177">
         <v>1.73</v>
@@ -38815,7 +38815,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ182">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR182">
         <v>1.81</v>
@@ -42317,7 +42317,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ199">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -44580,7 +44580,7 @@
         <v>0.4</v>
       </c>
       <c r="AP210">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ210">
         <v>0.42</v>
@@ -44995,7 +44995,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ212">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR212">
         <v>0.97</v>
@@ -46022,7 +46022,7 @@
         <v>0.73</v>
       </c>
       <c r="AP217">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ217">
         <v>0.6899999999999999</v>
@@ -50839,6 +50839,212 @@
       </c>
       <c r="BP240">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7465220</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45705.70833333334</v>
+      </c>
+      <c r="F241">
+        <v>24</v>
+      </c>
+      <c r="G241" t="s">
+        <v>81</v>
+      </c>
+      <c r="H241" t="s">
+        <v>88</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>1</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>1</v>
+      </c>
+      <c r="O241" t="s">
+        <v>187</v>
+      </c>
+      <c r="P241" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q241">
+        <v>1.57</v>
+      </c>
+      <c r="R241">
+        <v>3.1</v>
+      </c>
+      <c r="S241">
+        <v>8.5</v>
+      </c>
+      <c r="T241">
+        <v>1.18</v>
+      </c>
+      <c r="U241">
+        <v>4.5</v>
+      </c>
+      <c r="V241">
+        <v>1.83</v>
+      </c>
+      <c r="W241">
+        <v>1.83</v>
+      </c>
+      <c r="X241">
+        <v>3.75</v>
+      </c>
+      <c r="Y241">
+        <v>1.25</v>
+      </c>
+      <c r="Z241">
+        <v>1.19</v>
+      </c>
+      <c r="AA241">
+        <v>7.51</v>
+      </c>
+      <c r="AB241">
+        <v>12.03</v>
+      </c>
+      <c r="AC241">
+        <v>1.01</v>
+      </c>
+      <c r="AD241">
+        <v>29</v>
+      </c>
+      <c r="AE241">
+        <v>1.08</v>
+      </c>
+      <c r="AF241">
+        <v>8</v>
+      </c>
+      <c r="AG241">
+        <v>1.3</v>
+      </c>
+      <c r="AH241">
+        <v>3.5</v>
+      </c>
+      <c r="AI241">
+        <v>1.75</v>
+      </c>
+      <c r="AJ241">
+        <v>2</v>
+      </c>
+      <c r="AK241">
+        <v>1.06</v>
+      </c>
+      <c r="AL241">
+        <v>1.1</v>
+      </c>
+      <c r="AM241">
+        <v>4.1</v>
+      </c>
+      <c r="AN241">
+        <v>2.1</v>
+      </c>
+      <c r="AO241">
+        <v>1.42</v>
+      </c>
+      <c r="AP241">
+        <v>2.18</v>
+      </c>
+      <c r="AQ241">
+        <v>1.31</v>
+      </c>
+      <c r="AR241">
+        <v>2.03</v>
+      </c>
+      <c r="AS241">
+        <v>1.13</v>
+      </c>
+      <c r="AT241">
+        <v>3.16</v>
+      </c>
+      <c r="AU241">
+        <v>6</v>
+      </c>
+      <c r="AV241">
+        <v>5</v>
+      </c>
+      <c r="AW241">
+        <v>9</v>
+      </c>
+      <c r="AX241">
+        <v>4</v>
+      </c>
+      <c r="AY241">
+        <v>17</v>
+      </c>
+      <c r="AZ241">
+        <v>9</v>
+      </c>
+      <c r="BA241">
+        <v>4</v>
+      </c>
+      <c r="BB241">
+        <v>5</v>
+      </c>
+      <c r="BC241">
+        <v>9</v>
+      </c>
+      <c r="BD241">
+        <v>1.22</v>
+      </c>
+      <c r="BE241">
+        <v>8.5</v>
+      </c>
+      <c r="BF241">
+        <v>4.6</v>
+      </c>
+      <c r="BG241">
+        <v>1.23</v>
+      </c>
+      <c r="BH241">
+        <v>3.65</v>
+      </c>
+      <c r="BI241">
+        <v>1.41</v>
+      </c>
+      <c r="BJ241">
+        <v>2.65</v>
+      </c>
+      <c r="BK241">
+        <v>1.65</v>
+      </c>
+      <c r="BL241">
+        <v>2.08</v>
+      </c>
+      <c r="BM241">
+        <v>1.98</v>
+      </c>
+      <c r="BN241">
+        <v>1.72</v>
+      </c>
+      <c r="BO241">
+        <v>2.48</v>
+      </c>
+      <c r="BP241">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1398,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0.6899999999999999</v>
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>0.42</v>
@@ -7297,7 +7297,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ29">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -10796,7 +10796,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.25</v>
@@ -11623,7 +11623,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ50">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR50">
         <v>1.14</v>
@@ -14507,7 +14507,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.24</v>
@@ -15946,7 +15946,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
         <v>1.73</v>
@@ -17182,7 +17182,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -18627,7 +18627,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ84">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR84">
         <v>1.3</v>
@@ -21096,7 +21096,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>1.77</v>
@@ -23983,7 +23983,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -25834,7 +25834,7 @@
         <v>0.4</v>
       </c>
       <c r="AP119">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
         <v>1.17</v>
@@ -26249,7 +26249,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ121">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR121">
         <v>1.83</v>
@@ -28924,7 +28924,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>2.08</v>
@@ -31811,7 +31811,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ148">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR148">
         <v>1.35</v>
@@ -32426,7 +32426,7 @@
         <v>1.71</v>
       </c>
       <c r="AP151">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
         <v>1.36</v>
@@ -34695,7 +34695,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ162">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -37370,7 +37370,7 @@
         <v>1.75</v>
       </c>
       <c r="AP175">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ175">
         <v>1.17</v>
@@ -40463,7 +40463,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ190">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -41902,7 +41902,7 @@
         <v>1.67</v>
       </c>
       <c r="AP197">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ197">
         <v>1.67</v>
@@ -42935,7 +42935,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ202">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR202">
         <v>1.36</v>
@@ -47258,7 +47258,7 @@
         <v>1.09</v>
       </c>
       <c r="AP223">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ223">
         <v>1</v>
@@ -48909,7 +48909,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ231">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR231">
         <v>1.25</v>
@@ -51045,6 +51045,212 @@
       </c>
       <c r="BP241">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7465229</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45709.70833333334</v>
+      </c>
+      <c r="F242">
+        <v>25</v>
+      </c>
+      <c r="G242" t="s">
+        <v>72</v>
+      </c>
+      <c r="H242" t="s">
+        <v>74</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>1</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>1</v>
+      </c>
+      <c r="O242" t="s">
+        <v>210</v>
+      </c>
+      <c r="P242" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q242">
+        <v>2.5</v>
+      </c>
+      <c r="R242">
+        <v>2.2</v>
+      </c>
+      <c r="S242">
+        <v>4.75</v>
+      </c>
+      <c r="T242">
+        <v>1.4</v>
+      </c>
+      <c r="U242">
+        <v>2.75</v>
+      </c>
+      <c r="V242">
+        <v>3</v>
+      </c>
+      <c r="W242">
+        <v>1.36</v>
+      </c>
+      <c r="X242">
+        <v>8</v>
+      </c>
+      <c r="Y242">
+        <v>1.08</v>
+      </c>
+      <c r="Z242">
+        <v>1.85</v>
+      </c>
+      <c r="AA242">
+        <v>3.6</v>
+      </c>
+      <c r="AB242">
+        <v>4.1</v>
+      </c>
+      <c r="AC242">
+        <v>1.05</v>
+      </c>
+      <c r="AD242">
+        <v>11</v>
+      </c>
+      <c r="AE242">
+        <v>1.33</v>
+      </c>
+      <c r="AF242">
+        <v>3.4</v>
+      </c>
+      <c r="AG242">
+        <v>2</v>
+      </c>
+      <c r="AH242">
+        <v>1.8</v>
+      </c>
+      <c r="AI242">
+        <v>1.91</v>
+      </c>
+      <c r="AJ242">
+        <v>1.91</v>
+      </c>
+      <c r="AK242">
+        <v>1.23</v>
+      </c>
+      <c r="AL242">
+        <v>1.29</v>
+      </c>
+      <c r="AM242">
+        <v>1.87</v>
+      </c>
+      <c r="AN242">
+        <v>1.92</v>
+      </c>
+      <c r="AO242">
+        <v>0.82</v>
+      </c>
+      <c r="AP242">
+        <v>2</v>
+      </c>
+      <c r="AQ242">
+        <v>0.75</v>
+      </c>
+      <c r="AR242">
+        <v>1.38</v>
+      </c>
+      <c r="AS242">
+        <v>0.95</v>
+      </c>
+      <c r="AT242">
+        <v>2.33</v>
+      </c>
+      <c r="AU242">
+        <v>6</v>
+      </c>
+      <c r="AV242">
+        <v>2</v>
+      </c>
+      <c r="AW242">
+        <v>7</v>
+      </c>
+      <c r="AX242">
+        <v>17</v>
+      </c>
+      <c r="AY242">
+        <v>13</v>
+      </c>
+      <c r="AZ242">
+        <v>23</v>
+      </c>
+      <c r="BA242">
+        <v>5</v>
+      </c>
+      <c r="BB242">
+        <v>4</v>
+      </c>
+      <c r="BC242">
+        <v>9</v>
+      </c>
+      <c r="BD242">
+        <v>1.61</v>
+      </c>
+      <c r="BE242">
+        <v>6.5</v>
+      </c>
+      <c r="BF242">
+        <v>2.55</v>
+      </c>
+      <c r="BG242">
+        <v>1.36</v>
+      </c>
+      <c r="BH242">
+        <v>2.85</v>
+      </c>
+      <c r="BI242">
+        <v>1.61</v>
+      </c>
+      <c r="BJ242">
+        <v>2.15</v>
+      </c>
+      <c r="BK242">
+        <v>2</v>
+      </c>
+      <c r="BL242">
+        <v>1.71</v>
+      </c>
+      <c r="BM242">
+        <v>2.55</v>
+      </c>
+      <c r="BN242">
+        <v>1.44</v>
+      </c>
+      <c r="BO242">
+        <v>3.3</v>
+      </c>
+      <c r="BP242">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1038,6 +1038,15 @@
   <si>
     <t>['5', '45+1', '67', '84']</t>
   </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['12', '30', '86']</t>
+  </si>
+  <si>
+    <t>['62', '90+5']</t>
+  </si>
 </sst>
 </file>
 
@@ -1398,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2350,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1.08</v>
@@ -2762,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3383,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="AQ10">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3589,7 +3598,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ11">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4001,7 +4010,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ13">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5440,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -6264,10 +6273,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6885,7 +6894,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ27">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR27">
         <v>1.31</v>
@@ -7500,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ30">
         <v>1.77</v>
@@ -7915,7 +7924,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ32">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -8324,10 +8333,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR34">
         <v>0.87</v>
@@ -8736,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ36">
         <v>0.83</v>
@@ -9975,7 +9984,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ42">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR42">
         <v>1.48</v>
@@ -11005,7 +11014,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ47">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR47">
         <v>1.41</v>
@@ -11208,7 +11217,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>1.67</v>
@@ -11620,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
         <v>0.75</v>
@@ -12444,7 +12453,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ54">
         <v>1.08</v>
@@ -13062,7 +13071,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13271,7 +13280,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ58">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR58">
         <v>2.01</v>
@@ -13889,7 +13898,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ61">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -14092,10 +14101,10 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR62">
         <v>1.49</v>
@@ -14504,7 +14513,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ64">
         <v>0.75</v>
@@ -15537,7 +15546,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ69">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR69">
         <v>1.13</v>
@@ -15740,7 +15749,7 @@
         <v>0.5</v>
       </c>
       <c r="AP70">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15949,7 +15958,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR71">
         <v>1.29</v>
@@ -16564,7 +16573,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74">
         <v>0.83</v>
@@ -16979,7 +16988,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ76">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR76">
         <v>1.49</v>
@@ -17597,7 +17606,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ79">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR79">
         <v>1.68</v>
@@ -18830,7 +18839,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
         <v>0.5</v>
@@ -19245,7 +19254,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ87">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR87">
         <v>2.14</v>
@@ -19654,10 +19663,10 @@
         <v>2.4</v>
       </c>
       <c r="AP89">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ89">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR89">
         <v>1.08</v>
@@ -20069,7 +20078,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ91">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR91">
         <v>1.21</v>
@@ -20272,7 +20281,7 @@
         <v>0</v>
       </c>
       <c r="AP92">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ92">
         <v>0.25</v>
@@ -20481,7 +20490,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ93">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -22126,7 +22135,7 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ101">
         <v>0.83</v>
@@ -22541,7 +22550,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR103">
         <v>1.21</v>
@@ -22744,7 +22753,7 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ104">
         <v>0.6899999999999999</v>
@@ -22950,7 +22959,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
         <v>1</v>
@@ -23159,7 +23168,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ106">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR106">
         <v>1.96</v>
@@ -23777,7 +23786,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ109">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR109">
         <v>1.79</v>
@@ -24392,7 +24401,7 @@
         <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ112">
         <v>1.36</v>
@@ -25219,7 +25228,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ116">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR116">
         <v>1.93</v>
@@ -26040,7 +26049,7 @@
         <v>0.5</v>
       </c>
       <c r="AP120">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
         <v>0.83</v>
@@ -27073,7 +27082,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ125">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR125">
         <v>1.29</v>
@@ -27691,7 +27700,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ128">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -28100,7 +28109,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28512,7 +28521,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
         <v>1.36</v>
@@ -28721,7 +28730,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ133">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR133">
         <v>1.36</v>
@@ -28927,7 +28936,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR134">
         <v>1.32</v>
@@ -29133,7 +29142,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ135">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -30366,7 +30375,7 @@
         <v>0.57</v>
       </c>
       <c r="AP141">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ141">
         <v>0.83</v>
@@ -30781,7 +30790,7 @@
         <v>1</v>
       </c>
       <c r="AQ143">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR143">
         <v>1.13</v>
@@ -31396,7 +31405,7 @@
         <v>1.33</v>
       </c>
       <c r="AP146">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ146">
         <v>1.67</v>
@@ -32017,7 +32026,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ149">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR149">
         <v>1.29</v>
@@ -32632,7 +32641,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ152">
         <v>0.25</v>
@@ -32841,7 +32850,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ153">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR153">
         <v>1.84</v>
@@ -33044,7 +33053,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ154">
         <v>1.31</v>
@@ -33665,7 +33674,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ157">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -34283,7 +34292,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR160">
         <v>1.3</v>
@@ -35310,7 +35319,7 @@
         <v>1.88</v>
       </c>
       <c r="AP165">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ165">
         <v>1.77</v>
@@ -35722,7 +35731,7 @@
         <v>1.57</v>
       </c>
       <c r="AP167">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ167">
         <v>1.67</v>
@@ -37785,7 +37794,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ177">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR177">
         <v>2</v>
@@ -37988,7 +37997,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ178">
         <v>0.6899999999999999</v>
@@ -38403,7 +38412,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ180">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR180">
         <v>0.99</v>
@@ -38606,10 +38615,10 @@
         <v>0.13</v>
       </c>
       <c r="AP181">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ181">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR181">
         <v>1.34</v>
@@ -39018,7 +39027,7 @@
         <v>1.78</v>
       </c>
       <c r="AP183">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ183">
         <v>1.77</v>
@@ -39224,7 +39233,7 @@
         <v>0.5</v>
       </c>
       <c r="AP184">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ184">
         <v>0.5</v>
@@ -39430,7 +39439,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -40254,7 +40263,7 @@
         <v>0.25</v>
       </c>
       <c r="AP189">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ189">
         <v>1.17</v>
@@ -40669,7 +40678,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ191">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR191">
         <v>1.44</v>
@@ -41287,7 +41296,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ194">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR194">
         <v>0.96</v>
@@ -41699,7 +41708,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ196">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR196">
         <v>1.38</v>
@@ -42520,7 +42529,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ200">
         <v>1.17</v>
@@ -42932,7 +42941,7 @@
         <v>0.78</v>
       </c>
       <c r="AP202">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ202">
         <v>0.75</v>
@@ -43347,7 +43356,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ204">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR204">
         <v>1.67</v>
@@ -43553,7 +43562,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ205">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR205">
         <v>1.35</v>
@@ -43962,7 +43971,7 @@
         <v>1.2</v>
       </c>
       <c r="AP207">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44786,7 +44795,7 @@
         <v>0.44</v>
       </c>
       <c r="AP211">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ211">
         <v>0.5</v>
@@ -46228,7 +46237,7 @@
         <v>0.5</v>
       </c>
       <c r="AP218">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ218">
         <v>0.5</v>
@@ -47052,7 +47061,7 @@
         <v>0.27</v>
       </c>
       <c r="AP222">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ222">
         <v>0.25</v>
@@ -47670,10 +47679,10 @@
         <v>1.64</v>
       </c>
       <c r="AP225">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ225">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AR225">
         <v>1.41</v>
@@ -47879,7 +47888,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ226">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR226">
         <v>1.93</v>
@@ -48082,7 +48091,7 @@
         <v>0.8</v>
       </c>
       <c r="AP227">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ227">
         <v>1.17</v>
@@ -48288,7 +48297,7 @@
         <v>0.91</v>
       </c>
       <c r="AP228">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ228">
         <v>0.83</v>
@@ -48497,7 +48506,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ229">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR229">
         <v>1.42</v>
@@ -48703,7 +48712,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ230">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR230">
         <v>1.46</v>
@@ -51251,6 +51260,830 @@
       </c>
       <c r="BP242">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7469684</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45710.41666666666</v>
+      </c>
+      <c r="F243">
+        <v>25</v>
+      </c>
+      <c r="G243" t="s">
+        <v>86</v>
+      </c>
+      <c r="H243" t="s">
+        <v>82</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>1</v>
+      </c>
+      <c r="N243">
+        <v>1</v>
+      </c>
+      <c r="O243" t="s">
+        <v>104</v>
+      </c>
+      <c r="P243" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q243">
+        <v>2.6</v>
+      </c>
+      <c r="R243">
+        <v>1.95</v>
+      </c>
+      <c r="S243">
+        <v>5.5</v>
+      </c>
+      <c r="T243">
+        <v>1.57</v>
+      </c>
+      <c r="U243">
+        <v>2.25</v>
+      </c>
+      <c r="V243">
+        <v>3.75</v>
+      </c>
+      <c r="W243">
+        <v>1.25</v>
+      </c>
+      <c r="X243">
+        <v>13</v>
+      </c>
+      <c r="Y243">
+        <v>1.04</v>
+      </c>
+      <c r="Z243">
+        <v>1.83</v>
+      </c>
+      <c r="AA243">
+        <v>3.25</v>
+      </c>
+      <c r="AB243">
+        <v>5</v>
+      </c>
+      <c r="AC243">
+        <v>1.11</v>
+      </c>
+      <c r="AD243">
+        <v>7</v>
+      </c>
+      <c r="AE243">
+        <v>1.5</v>
+      </c>
+      <c r="AF243">
+        <v>2.4</v>
+      </c>
+      <c r="AG243">
+        <v>2.63</v>
+      </c>
+      <c r="AH243">
+        <v>1.5</v>
+      </c>
+      <c r="AI243">
+        <v>2.25</v>
+      </c>
+      <c r="AJ243">
+        <v>1.57</v>
+      </c>
+      <c r="AK243">
+        <v>1.18</v>
+      </c>
+      <c r="AL243">
+        <v>1.32</v>
+      </c>
+      <c r="AM243">
+        <v>1.93</v>
+      </c>
+      <c r="AN243">
+        <v>1.18</v>
+      </c>
+      <c r="AO243">
+        <v>0.18</v>
+      </c>
+      <c r="AP243">
+        <v>1.08</v>
+      </c>
+      <c r="AQ243">
+        <v>0.42</v>
+      </c>
+      <c r="AR243">
+        <v>1.16</v>
+      </c>
+      <c r="AS243">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AT243">
+        <v>1.97</v>
+      </c>
+      <c r="AU243">
+        <v>5</v>
+      </c>
+      <c r="AV243">
+        <v>3</v>
+      </c>
+      <c r="AW243">
+        <v>9</v>
+      </c>
+      <c r="AX243">
+        <v>7</v>
+      </c>
+      <c r="AY243">
+        <v>17</v>
+      </c>
+      <c r="AZ243">
+        <v>11</v>
+      </c>
+      <c r="BA243">
+        <v>7</v>
+      </c>
+      <c r="BB243">
+        <v>0</v>
+      </c>
+      <c r="BC243">
+        <v>7</v>
+      </c>
+      <c r="BD243">
+        <v>1.38</v>
+      </c>
+      <c r="BE243">
+        <v>6.75</v>
+      </c>
+      <c r="BF243">
+        <v>3.4</v>
+      </c>
+      <c r="BG243">
+        <v>1.37</v>
+      </c>
+      <c r="BH243">
+        <v>2.8</v>
+      </c>
+      <c r="BI243">
+        <v>1.6</v>
+      </c>
+      <c r="BJ243">
+        <v>2.17</v>
+      </c>
+      <c r="BK243">
+        <v>1.98</v>
+      </c>
+      <c r="BL243">
+        <v>1.72</v>
+      </c>
+      <c r="BM243">
+        <v>2.55</v>
+      </c>
+      <c r="BN243">
+        <v>1.44</v>
+      </c>
+      <c r="BO243">
+        <v>3.3</v>
+      </c>
+      <c r="BP243">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7465230</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45710.51041666666</v>
+      </c>
+      <c r="F244">
+        <v>25</v>
+      </c>
+      <c r="G244" t="s">
+        <v>88</v>
+      </c>
+      <c r="H244" t="s">
+        <v>79</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>1</v>
+      </c>
+      <c r="O244" t="s">
+        <v>104</v>
+      </c>
+      <c r="P244" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q244">
+        <v>3.5</v>
+      </c>
+      <c r="R244">
+        <v>2.2</v>
+      </c>
+      <c r="S244">
+        <v>3</v>
+      </c>
+      <c r="T244">
+        <v>1.36</v>
+      </c>
+      <c r="U244">
+        <v>3</v>
+      </c>
+      <c r="V244">
+        <v>2.63</v>
+      </c>
+      <c r="W244">
+        <v>1.44</v>
+      </c>
+      <c r="X244">
+        <v>7</v>
+      </c>
+      <c r="Y244">
+        <v>1.1</v>
+      </c>
+      <c r="Z244">
+        <v>2.9</v>
+      </c>
+      <c r="AA244">
+        <v>3.5</v>
+      </c>
+      <c r="AB244">
+        <v>2.3</v>
+      </c>
+      <c r="AC244">
+        <v>1.05</v>
+      </c>
+      <c r="AD244">
+        <v>12</v>
+      </c>
+      <c r="AE244">
+        <v>1.26</v>
+      </c>
+      <c r="AF244">
+        <v>4</v>
+      </c>
+      <c r="AG244">
+        <v>1.8</v>
+      </c>
+      <c r="AH244">
+        <v>2</v>
+      </c>
+      <c r="AI244">
+        <v>1.67</v>
+      </c>
+      <c r="AJ244">
+        <v>2.1</v>
+      </c>
+      <c r="AK244">
+        <v>1.58</v>
+      </c>
+      <c r="AL244">
+        <v>1.28</v>
+      </c>
+      <c r="AM244">
+        <v>1.4</v>
+      </c>
+      <c r="AN244">
+        <v>1.64</v>
+      </c>
+      <c r="AO244">
+        <v>1.75</v>
+      </c>
+      <c r="AP244">
+        <v>1.5</v>
+      </c>
+      <c r="AQ244">
+        <v>1.85</v>
+      </c>
+      <c r="AR244">
+        <v>1.68</v>
+      </c>
+      <c r="AS244">
+        <v>1.49</v>
+      </c>
+      <c r="AT244">
+        <v>3.17</v>
+      </c>
+      <c r="AU244">
+        <v>6</v>
+      </c>
+      <c r="AV244">
+        <v>6</v>
+      </c>
+      <c r="AW244">
+        <v>5</v>
+      </c>
+      <c r="AX244">
+        <v>5</v>
+      </c>
+      <c r="AY244">
+        <v>11</v>
+      </c>
+      <c r="AZ244">
+        <v>13</v>
+      </c>
+      <c r="BA244">
+        <v>3</v>
+      </c>
+      <c r="BB244">
+        <v>5</v>
+      </c>
+      <c r="BC244">
+        <v>8</v>
+      </c>
+      <c r="BD244">
+        <v>1.92</v>
+      </c>
+      <c r="BE244">
+        <v>6.4</v>
+      </c>
+      <c r="BF244">
+        <v>2.08</v>
+      </c>
+      <c r="BG244">
+        <v>1.32</v>
+      </c>
+      <c r="BH244">
+        <v>3</v>
+      </c>
+      <c r="BI244">
+        <v>1.55</v>
+      </c>
+      <c r="BJ244">
+        <v>2.25</v>
+      </c>
+      <c r="BK244">
+        <v>1.9</v>
+      </c>
+      <c r="BL244">
+        <v>1.78</v>
+      </c>
+      <c r="BM244">
+        <v>2.4</v>
+      </c>
+      <c r="BN244">
+        <v>1.49</v>
+      </c>
+      <c r="BO244">
+        <v>3.15</v>
+      </c>
+      <c r="BP244">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7465231</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45710.60416666666</v>
+      </c>
+      <c r="F245">
+        <v>25</v>
+      </c>
+      <c r="G245" t="s">
+        <v>75</v>
+      </c>
+      <c r="H245" t="s">
+        <v>87</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>2</v>
+      </c>
+      <c r="K245">
+        <v>2</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>3</v>
+      </c>
+      <c r="N245">
+        <v>3</v>
+      </c>
+      <c r="O245" t="s">
+        <v>104</v>
+      </c>
+      <c r="P245" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q245">
+        <v>4.75</v>
+      </c>
+      <c r="R245">
+        <v>2.05</v>
+      </c>
+      <c r="S245">
+        <v>2.63</v>
+      </c>
+      <c r="T245">
+        <v>1.5</v>
+      </c>
+      <c r="U245">
+        <v>2.5</v>
+      </c>
+      <c r="V245">
+        <v>3.4</v>
+      </c>
+      <c r="W245">
+        <v>1.3</v>
+      </c>
+      <c r="X245">
+        <v>10</v>
+      </c>
+      <c r="Y245">
+        <v>1.06</v>
+      </c>
+      <c r="Z245">
+        <v>4.2</v>
+      </c>
+      <c r="AA245">
+        <v>3.4</v>
+      </c>
+      <c r="AB245">
+        <v>1.91</v>
+      </c>
+      <c r="AC245">
+        <v>1.08</v>
+      </c>
+      <c r="AD245">
+        <v>8.5</v>
+      </c>
+      <c r="AE245">
+        <v>1.42</v>
+      </c>
+      <c r="AF245">
+        <v>2.9</v>
+      </c>
+      <c r="AG245">
+        <v>2.2</v>
+      </c>
+      <c r="AH245">
+        <v>1.67</v>
+      </c>
+      <c r="AI245">
+        <v>2</v>
+      </c>
+      <c r="AJ245">
+        <v>1.75</v>
+      </c>
+      <c r="AK245">
+        <v>1.87</v>
+      </c>
+      <c r="AL245">
+        <v>1.31</v>
+      </c>
+      <c r="AM245">
+        <v>1.21</v>
+      </c>
+      <c r="AN245">
+        <v>1.5</v>
+      </c>
+      <c r="AO245">
+        <v>1.73</v>
+      </c>
+      <c r="AP245">
+        <v>1.38</v>
+      </c>
+      <c r="AQ245">
+        <v>1.83</v>
+      </c>
+      <c r="AR245">
+        <v>1.34</v>
+      </c>
+      <c r="AS245">
+        <v>1.16</v>
+      </c>
+      <c r="AT245">
+        <v>2.5</v>
+      </c>
+      <c r="AU245">
+        <v>3</v>
+      </c>
+      <c r="AV245">
+        <v>4</v>
+      </c>
+      <c r="AW245">
+        <v>16</v>
+      </c>
+      <c r="AX245">
+        <v>8</v>
+      </c>
+      <c r="AY245">
+        <v>22</v>
+      </c>
+      <c r="AZ245">
+        <v>16</v>
+      </c>
+      <c r="BA245">
+        <v>7</v>
+      </c>
+      <c r="BB245">
+        <v>0</v>
+      </c>
+      <c r="BC245">
+        <v>7</v>
+      </c>
+      <c r="BD245">
+        <v>2.38</v>
+      </c>
+      <c r="BE245">
+        <v>6.4</v>
+      </c>
+      <c r="BF245">
+        <v>1.73</v>
+      </c>
+      <c r="BG245">
+        <v>1.35</v>
+      </c>
+      <c r="BH245">
+        <v>2.9</v>
+      </c>
+      <c r="BI245">
+        <v>1.61</v>
+      </c>
+      <c r="BJ245">
+        <v>2.15</v>
+      </c>
+      <c r="BK245">
+        <v>2</v>
+      </c>
+      <c r="BL245">
+        <v>1.71</v>
+      </c>
+      <c r="BM245">
+        <v>2.55</v>
+      </c>
+      <c r="BN245">
+        <v>1.44</v>
+      </c>
+      <c r="BO245">
+        <v>3.3</v>
+      </c>
+      <c r="BP245">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7465232</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45710.70833333334</v>
+      </c>
+      <c r="F246">
+        <v>25</v>
+      </c>
+      <c r="G246" t="s">
+        <v>73</v>
+      </c>
+      <c r="H246" t="s">
+        <v>81</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>2</v>
+      </c>
+      <c r="N246">
+        <v>2</v>
+      </c>
+      <c r="O246" t="s">
+        <v>104</v>
+      </c>
+      <c r="P246" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q246">
+        <v>7.5</v>
+      </c>
+      <c r="R246">
+        <v>3</v>
+      </c>
+      <c r="S246">
+        <v>1.62</v>
+      </c>
+      <c r="T246">
+        <v>1.18</v>
+      </c>
+      <c r="U246">
+        <v>4.5</v>
+      </c>
+      <c r="V246">
+        <v>1.83</v>
+      </c>
+      <c r="W246">
+        <v>1.83</v>
+      </c>
+      <c r="X246">
+        <v>3.75</v>
+      </c>
+      <c r="Y246">
+        <v>1.25</v>
+      </c>
+      <c r="Z246">
+        <v>9.5</v>
+      </c>
+      <c r="AA246">
+        <v>6</v>
+      </c>
+      <c r="AB246">
+        <v>1.25</v>
+      </c>
+      <c r="AC246">
+        <v>1.01</v>
+      </c>
+      <c r="AD246">
+        <v>26</v>
+      </c>
+      <c r="AE246">
+        <v>1.08</v>
+      </c>
+      <c r="AF246">
+        <v>8</v>
+      </c>
+      <c r="AG246">
+        <v>1.33</v>
+      </c>
+      <c r="AH246">
+        <v>3.4</v>
+      </c>
+      <c r="AI246">
+        <v>1.67</v>
+      </c>
+      <c r="AJ246">
+        <v>2.1</v>
+      </c>
+      <c r="AK246">
+        <v>3.6</v>
+      </c>
+      <c r="AL246">
+        <v>1.12</v>
+      </c>
+      <c r="AM246">
+        <v>1.06</v>
+      </c>
+      <c r="AN246">
+        <v>1.08</v>
+      </c>
+      <c r="AO246">
+        <v>2.08</v>
+      </c>
+      <c r="AP246">
+        <v>1</v>
+      </c>
+      <c r="AQ246">
+        <v>2.14</v>
+      </c>
+      <c r="AR246">
+        <v>1.41</v>
+      </c>
+      <c r="AS246">
+        <v>1.69</v>
+      </c>
+      <c r="AT246">
+        <v>3.1</v>
+      </c>
+      <c r="AU246">
+        <v>3</v>
+      </c>
+      <c r="AV246">
+        <v>6</v>
+      </c>
+      <c r="AW246">
+        <v>8</v>
+      </c>
+      <c r="AX246">
+        <v>10</v>
+      </c>
+      <c r="AY246">
+        <v>14</v>
+      </c>
+      <c r="AZ246">
+        <v>17</v>
+      </c>
+      <c r="BA246">
+        <v>5</v>
+      </c>
+      <c r="BB246">
+        <v>3</v>
+      </c>
+      <c r="BC246">
+        <v>8</v>
+      </c>
+      <c r="BD246">
+        <v>3.9</v>
+      </c>
+      <c r="BE246">
+        <v>7.5</v>
+      </c>
+      <c r="BF246">
+        <v>1.3</v>
+      </c>
+      <c r="BG246">
+        <v>1.29</v>
+      </c>
+      <c r="BH246">
+        <v>3.15</v>
+      </c>
+      <c r="BI246">
+        <v>1.52</v>
+      </c>
+      <c r="BJ246">
+        <v>2.33</v>
+      </c>
+      <c r="BK246">
+        <v>1.83</v>
+      </c>
+      <c r="BL246">
+        <v>1.85</v>
+      </c>
+      <c r="BM246">
+        <v>2.3</v>
+      </c>
+      <c r="BN246">
+        <v>1.54</v>
+      </c>
+      <c r="BO246">
+        <v>2.9</v>
+      </c>
+      <c r="BP246">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="348">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,15 @@
     <t>['51', '64', '69']</t>
   </si>
   <si>
+    <t>['10', '35', '43', '45+2', '66', '69', '87']</t>
+  </si>
+  <si>
+    <t>['41', '83']</t>
+  </si>
+  <si>
+    <t>['12', '48', '80']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1046,6 +1055,9 @@
   </si>
   <si>
     <t>['62', '90+5']</t>
+  </si>
+  <si>
+    <t>['18', '77']</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP246"/>
+  <dimension ref="A1:BP250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1663,7 +1675,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1741,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ2">
         <v>1.17</v>
@@ -1950,7 +1962,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2075,7 +2087,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2281,7 +2293,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2487,7 +2499,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2568,7 +2580,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ6">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2693,7 +2705,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2899,7 +2911,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2977,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ8">
         <v>1.31</v>
@@ -3105,7 +3117,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3517,7 +3529,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3929,7 +3941,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4831,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ17">
         <v>1.31</v>
@@ -5037,10 +5049,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ18">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5452,7 +5464,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5658,7 +5670,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5783,7 +5795,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6195,7 +6207,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6479,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ25">
         <v>0.42</v>
@@ -6688,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -7019,7 +7031,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7097,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ28">
         <v>0.6899999999999999</v>
@@ -7718,7 +7730,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ31">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR31">
         <v>1.51</v>
@@ -7921,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ32">
         <v>1.83</v>
@@ -8255,7 +8267,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8873,7 +8885,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9079,7 +9091,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9160,7 +9172,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR38">
         <v>1.9</v>
@@ -9363,7 +9375,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ39">
         <v>1.17</v>
@@ -9569,10 +9581,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR40">
         <v>2.11</v>
@@ -9778,7 +9790,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ41">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR41">
         <v>1.59</v>
@@ -9903,7 +9915,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10109,7 +10121,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10521,7 +10533,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10599,7 +10611,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ45">
         <v>1.77</v>
@@ -10808,7 +10820,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR46">
         <v>1.11</v>
@@ -10933,7 +10945,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11139,7 +11151,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12169,7 +12181,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12787,7 +12799,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13074,7 +13086,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
         <v>1.38</v>
@@ -13277,7 +13289,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ58">
         <v>0.42</v>
@@ -13483,10 +13495,10 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ59">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR59">
         <v>1.14</v>
@@ -13689,7 +13701,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ60">
         <v>0.5</v>
@@ -13817,7 +13829,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14229,7 +14241,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14641,7 +14653,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14722,7 +14734,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14847,7 +14859,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14925,7 +14937,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ66">
         <v>0.6899999999999999</v>
@@ -15465,7 +15477,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15671,7 +15683,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15752,7 +15764,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR70">
         <v>1.36</v>
@@ -16083,7 +16095,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16367,7 +16379,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ73">
         <v>0.6899999999999999</v>
@@ -16576,7 +16588,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR74">
         <v>1.48</v>
@@ -16779,7 +16791,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ75">
         <v>0.42</v>
@@ -16907,7 +16919,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17194,7 +17206,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
         <v>1.31</v>
@@ -17397,7 +17409,7 @@
         <v>0.67</v>
       </c>
       <c r="AP78">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ78">
         <v>1.08</v>
@@ -17731,7 +17743,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17937,7 +17949,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18633,7 +18645,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ84">
         <v>0.75</v>
@@ -18967,7 +18979,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19251,7 +19263,7 @@
         <v>2.5</v>
       </c>
       <c r="AP87">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ87">
         <v>1.85</v>
@@ -19379,7 +19391,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19585,7 +19597,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19872,7 +19884,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR90">
         <v>1.55</v>
@@ -19997,7 +20009,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20075,7 +20087,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ91">
         <v>1.83</v>
@@ -20203,7 +20215,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20284,7 +20296,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ92">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR92">
         <v>1.06</v>
@@ -20487,7 +20499,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ93">
         <v>0.42</v>
@@ -20615,7 +20627,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20696,7 +20708,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -21027,7 +21039,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21520,7 +21532,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ98">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR98">
         <v>1.58</v>
@@ -22057,7 +22069,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22263,7 +22275,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22469,7 +22481,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22962,7 +22974,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR105">
         <v>1.4</v>
@@ -23087,7 +23099,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23165,7 +23177,7 @@
         <v>2.5</v>
       </c>
       <c r="AP106">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ106">
         <v>2.14</v>
@@ -23577,7 +23589,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ108">
         <v>0.42</v>
@@ -23911,7 +23923,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23989,7 +24001,7 @@
         <v>0.5</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ110">
         <v>0.75</v>
@@ -24610,7 +24622,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ113">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24735,7 +24747,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24816,7 +24828,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ114">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR114">
         <v>1.33</v>
@@ -25147,7 +25159,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25353,7 +25365,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25559,7 +25571,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25637,10 +25649,10 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25971,7 +25983,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26255,7 +26267,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ121">
         <v>0.75</v>
@@ -26795,7 +26807,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27285,10 +27297,10 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -27697,7 +27709,7 @@
         <v>2.57</v>
       </c>
       <c r="AP128">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ128">
         <v>2.14</v>
@@ -27903,10 +27915,10 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ129">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR129">
         <v>1.27</v>
@@ -28031,7 +28043,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28112,7 +28124,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR130">
         <v>1.31</v>
@@ -28443,7 +28455,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28855,7 +28867,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29061,7 +29073,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29473,7 +29485,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29757,7 +29769,7 @@
         <v>1.83</v>
       </c>
       <c r="AP138">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ138">
         <v>1.17</v>
@@ -30091,7 +30103,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30378,7 +30390,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ141">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR141">
         <v>1.08</v>
@@ -30709,7 +30721,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30915,7 +30927,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -30996,7 +31008,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR144">
         <v>1.51</v>
@@ -31199,7 +31211,7 @@
         <v>0.33</v>
       </c>
       <c r="AP145">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ145">
         <v>1.17</v>
@@ -31327,7 +31339,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31611,10 +31623,10 @@
         <v>0.86</v>
       </c>
       <c r="AP147">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR147">
         <v>1.56</v>
@@ -31945,7 +31957,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32151,7 +32163,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32229,7 +32241,7 @@
         <v>2</v>
       </c>
       <c r="AP150">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ150">
         <v>1.77</v>
@@ -32644,7 +32656,7 @@
         <v>1</v>
       </c>
       <c r="AQ152">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR152">
         <v>1.35</v>
@@ -32769,7 +32781,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33181,7 +33193,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33387,7 +33399,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33671,7 +33683,7 @@
         <v>2</v>
       </c>
       <c r="AP157">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ157">
         <v>1.85</v>
@@ -33799,7 +33811,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34005,7 +34017,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34289,7 +34301,7 @@
         <v>0.14</v>
       </c>
       <c r="AP160">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ160">
         <v>0.42</v>
@@ -34910,7 +34922,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR163">
         <v>1.23</v>
@@ -35241,7 +35253,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35653,7 +35665,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35937,7 +35949,7 @@
         <v>1.13</v>
       </c>
       <c r="AP168">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ168">
         <v>0.83</v>
@@ -36065,7 +36077,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36146,7 +36158,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ169">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36352,7 +36364,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ170">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR170">
         <v>1.98</v>
@@ -36477,7 +36489,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36970,7 +36982,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ173">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR173">
         <v>1.37</v>
@@ -37173,7 +37185,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ174">
         <v>1.36</v>
@@ -37713,7 +37725,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37919,7 +37931,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38125,7 +38137,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38203,7 +38215,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ179">
         <v>1.08</v>
@@ -38331,7 +38343,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38949,7 +38961,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39361,7 +39373,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39442,7 +39454,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR185">
         <v>1.15</v>
@@ -39648,7 +39660,7 @@
         <v>1</v>
       </c>
       <c r="AQ186">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR186">
         <v>1.03</v>
@@ -39854,7 +39866,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ187">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR187">
         <v>1.12</v>
@@ -40185,7 +40197,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40675,7 +40687,7 @@
         <v>1.89</v>
       </c>
       <c r="AP191">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ191">
         <v>1.85</v>
@@ -40884,7 +40896,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ192">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR192">
         <v>1.16</v>
@@ -41009,7 +41021,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41421,7 +41433,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41705,7 +41717,7 @@
         <v>2.09</v>
       </c>
       <c r="AP196">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ196">
         <v>2.14</v>
@@ -41833,7 +41845,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42039,7 +42051,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42117,7 +42129,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ198">
         <v>0.83</v>
@@ -43069,7 +43081,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43150,7 +43162,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ203">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR203">
         <v>1.2</v>
@@ -43275,7 +43287,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43481,7 +43493,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43687,7 +43699,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43974,7 +43986,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR207">
         <v>1.57</v>
@@ -44099,7 +44111,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44177,7 +44189,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP208">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ208">
         <v>1.17</v>
@@ -44383,10 +44395,10 @@
         <v>0.9</v>
       </c>
       <c r="AP209">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ209">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR209">
         <v>1.31</v>
@@ -44717,7 +44729,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44923,7 +44935,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45207,7 +45219,7 @@
         <v>0.9</v>
       </c>
       <c r="AP213">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ213">
         <v>1.08</v>
@@ -45416,7 +45428,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ214">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR214">
         <v>1.55</v>
@@ -46571,7 +46583,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47064,7 +47076,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ222">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AR222">
         <v>1.62</v>
@@ -47189,7 +47201,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47270,7 +47282,7 @@
         <v>2</v>
       </c>
       <c r="AQ223">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR223">
         <v>1.34</v>
@@ -47473,10 +47485,10 @@
         <v>1.09</v>
       </c>
       <c r="AP224">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ224">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR224">
         <v>1.44</v>
@@ -47601,7 +47613,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -47885,7 +47897,7 @@
         <v>1.8</v>
       </c>
       <c r="AP226">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ226">
         <v>1.83</v>
@@ -48300,7 +48312,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ228">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR228">
         <v>1.3</v>
@@ -48503,7 +48515,7 @@
         <v>0.2</v>
       </c>
       <c r="AP229">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ229">
         <v>0.42</v>
@@ -48631,7 +48643,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49043,7 +49055,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49249,7 +49261,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49455,7 +49467,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50073,7 +50085,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50279,7 +50291,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -51309,7 +51321,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51515,7 +51527,7 @@
         <v>104</v>
       </c>
       <c r="P244" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -51721,7 +51733,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51927,7 +51939,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52084,6 +52096,830 @@
       </c>
       <c r="BP246">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7465228</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45711.41666666666</v>
+      </c>
+      <c r="F247">
+        <v>25</v>
+      </c>
+      <c r="G247" t="s">
+        <v>70</v>
+      </c>
+      <c r="H247" t="s">
+        <v>78</v>
+      </c>
+      <c r="I247">
+        <v>4</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>4</v>
+      </c>
+      <c r="L247">
+        <v>7</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>8</v>
+      </c>
+      <c r="O247" t="s">
+        <v>250</v>
+      </c>
+      <c r="P247" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q247">
+        <v>1.62</v>
+      </c>
+      <c r="R247">
+        <v>2.63</v>
+      </c>
+      <c r="S247">
+        <v>13</v>
+      </c>
+      <c r="T247">
+        <v>1.3</v>
+      </c>
+      <c r="U247">
+        <v>3.4</v>
+      </c>
+      <c r="V247">
+        <v>2.5</v>
+      </c>
+      <c r="W247">
+        <v>1.5</v>
+      </c>
+      <c r="X247">
+        <v>6</v>
+      </c>
+      <c r="Y247">
+        <v>1.13</v>
+      </c>
+      <c r="Z247">
+        <v>1.18</v>
+      </c>
+      <c r="AA247">
+        <v>7</v>
+      </c>
+      <c r="AB247">
+        <v>12</v>
+      </c>
+      <c r="AC247">
+        <v>1.03</v>
+      </c>
+      <c r="AD247">
+        <v>17</v>
+      </c>
+      <c r="AE247">
+        <v>1.2</v>
+      </c>
+      <c r="AF247">
+        <v>4.5</v>
+      </c>
+      <c r="AG247">
+        <v>1.67</v>
+      </c>
+      <c r="AH247">
+        <v>2.2</v>
+      </c>
+      <c r="AI247">
+        <v>2.63</v>
+      </c>
+      <c r="AJ247">
+        <v>1.44</v>
+      </c>
+      <c r="AK247">
+        <v>1.02</v>
+      </c>
+      <c r="AL247">
+        <v>1.11</v>
+      </c>
+      <c r="AM247">
+        <v>4.5</v>
+      </c>
+      <c r="AN247">
+        <v>2.08</v>
+      </c>
+      <c r="AO247">
+        <v>0.25</v>
+      </c>
+      <c r="AP247">
+        <v>2.15</v>
+      </c>
+      <c r="AQ247">
+        <v>0.23</v>
+      </c>
+      <c r="AR247">
+        <v>1.54</v>
+      </c>
+      <c r="AS247">
+        <v>0.95</v>
+      </c>
+      <c r="AT247">
+        <v>2.49</v>
+      </c>
+      <c r="AU247">
+        <v>17</v>
+      </c>
+      <c r="AV247">
+        <v>4</v>
+      </c>
+      <c r="AW247">
+        <v>13</v>
+      </c>
+      <c r="AX247">
+        <v>2</v>
+      </c>
+      <c r="AY247">
+        <v>31</v>
+      </c>
+      <c r="AZ247">
+        <v>6</v>
+      </c>
+      <c r="BA247">
+        <v>4</v>
+      </c>
+      <c r="BB247">
+        <v>4</v>
+      </c>
+      <c r="BC247">
+        <v>8</v>
+      </c>
+      <c r="BD247">
+        <v>1.15</v>
+      </c>
+      <c r="BE247">
+        <v>9</v>
+      </c>
+      <c r="BF247">
+        <v>5.6</v>
+      </c>
+      <c r="BG247">
+        <v>1.33</v>
+      </c>
+      <c r="BH247">
+        <v>2.95</v>
+      </c>
+      <c r="BI247">
+        <v>1.55</v>
+      </c>
+      <c r="BJ247">
+        <v>2.25</v>
+      </c>
+      <c r="BK247">
+        <v>1.9</v>
+      </c>
+      <c r="BL247">
+        <v>1.79</v>
+      </c>
+      <c r="BM247">
+        <v>2.38</v>
+      </c>
+      <c r="BN247">
+        <v>1.5</v>
+      </c>
+      <c r="BO247">
+        <v>3.05</v>
+      </c>
+      <c r="BP247">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7465234</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45711.51041666666</v>
+      </c>
+      <c r="F248">
+        <v>25</v>
+      </c>
+      <c r="G248" t="s">
+        <v>84</v>
+      </c>
+      <c r="H248" t="s">
+        <v>89</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>2</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>2</v>
+      </c>
+      <c r="O248" t="s">
+        <v>251</v>
+      </c>
+      <c r="P248" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q248">
+        <v>1.73</v>
+      </c>
+      <c r="R248">
+        <v>2.88</v>
+      </c>
+      <c r="S248">
+        <v>7.5</v>
+      </c>
+      <c r="T248">
+        <v>1.22</v>
+      </c>
+      <c r="U248">
+        <v>4</v>
+      </c>
+      <c r="V248">
+        <v>2</v>
+      </c>
+      <c r="W248">
+        <v>1.73</v>
+      </c>
+      <c r="X248">
+        <v>4.33</v>
+      </c>
+      <c r="Y248">
+        <v>1.2</v>
+      </c>
+      <c r="Z248">
+        <v>1.3</v>
+      </c>
+      <c r="AA248">
+        <v>6</v>
+      </c>
+      <c r="AB248">
+        <v>8</v>
+      </c>
+      <c r="AC248">
+        <v>1.02</v>
+      </c>
+      <c r="AD248">
+        <v>21</v>
+      </c>
+      <c r="AE248">
+        <v>1.12</v>
+      </c>
+      <c r="AF248">
+        <v>6.5</v>
+      </c>
+      <c r="AG248">
+        <v>1.4</v>
+      </c>
+      <c r="AH248">
+        <v>3</v>
+      </c>
+      <c r="AI248">
+        <v>1.75</v>
+      </c>
+      <c r="AJ248">
+        <v>2</v>
+      </c>
+      <c r="AK248">
+        <v>1.07</v>
+      </c>
+      <c r="AL248">
+        <v>1.14</v>
+      </c>
+      <c r="AM248">
+        <v>3.4</v>
+      </c>
+      <c r="AN248">
+        <v>2.55</v>
+      </c>
+      <c r="AO248">
+        <v>1</v>
+      </c>
+      <c r="AP248">
+        <v>2.58</v>
+      </c>
+      <c r="AQ248">
+        <v>0.92</v>
+      </c>
+      <c r="AR248">
+        <v>2.01</v>
+      </c>
+      <c r="AS248">
+        <v>1.08</v>
+      </c>
+      <c r="AT248">
+        <v>3.09</v>
+      </c>
+      <c r="AU248">
+        <v>6</v>
+      </c>
+      <c r="AV248">
+        <v>3</v>
+      </c>
+      <c r="AW248">
+        <v>17</v>
+      </c>
+      <c r="AX248">
+        <v>4</v>
+      </c>
+      <c r="AY248">
+        <v>29</v>
+      </c>
+      <c r="AZ248">
+        <v>9</v>
+      </c>
+      <c r="BA248">
+        <v>11</v>
+      </c>
+      <c r="BB248">
+        <v>5</v>
+      </c>
+      <c r="BC248">
+        <v>16</v>
+      </c>
+      <c r="BD248">
+        <v>1.27</v>
+      </c>
+      <c r="BE248">
+        <v>7.5</v>
+      </c>
+      <c r="BF248">
+        <v>4.1</v>
+      </c>
+      <c r="BG248">
+        <v>1.29</v>
+      </c>
+      <c r="BH248">
+        <v>3.15</v>
+      </c>
+      <c r="BI248">
+        <v>1.5</v>
+      </c>
+      <c r="BJ248">
+        <v>2.35</v>
+      </c>
+      <c r="BK248">
+        <v>1.82</v>
+      </c>
+      <c r="BL248">
+        <v>1.86</v>
+      </c>
+      <c r="BM248">
+        <v>2.3</v>
+      </c>
+      <c r="BN248">
+        <v>1.54</v>
+      </c>
+      <c r="BO248">
+        <v>2.9</v>
+      </c>
+      <c r="BP248">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7465233</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45711.60416666666</v>
+      </c>
+      <c r="F249">
+        <v>25</v>
+      </c>
+      <c r="G249" t="s">
+        <v>83</v>
+      </c>
+      <c r="H249" t="s">
+        <v>71</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>2</v>
+      </c>
+      <c r="N249">
+        <v>3</v>
+      </c>
+      <c r="O249" t="s">
+        <v>178</v>
+      </c>
+      <c r="P249" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q249">
+        <v>3.5</v>
+      </c>
+      <c r="R249">
+        <v>1.91</v>
+      </c>
+      <c r="S249">
+        <v>3.75</v>
+      </c>
+      <c r="T249">
+        <v>1.57</v>
+      </c>
+      <c r="U249">
+        <v>2.25</v>
+      </c>
+      <c r="V249">
+        <v>3.75</v>
+      </c>
+      <c r="W249">
+        <v>1.25</v>
+      </c>
+      <c r="X249">
+        <v>13</v>
+      </c>
+      <c r="Y249">
+        <v>1.04</v>
+      </c>
+      <c r="Z249">
+        <v>2.5</v>
+      </c>
+      <c r="AA249">
+        <v>3.25</v>
+      </c>
+      <c r="AB249">
+        <v>2.8</v>
+      </c>
+      <c r="AC249">
+        <v>1.11</v>
+      </c>
+      <c r="AD249">
+        <v>7</v>
+      </c>
+      <c r="AE249">
+        <v>1.5</v>
+      </c>
+      <c r="AF249">
+        <v>2.45</v>
+      </c>
+      <c r="AG249">
+        <v>2.63</v>
+      </c>
+      <c r="AH249">
+        <v>1.5</v>
+      </c>
+      <c r="AI249">
+        <v>2.2</v>
+      </c>
+      <c r="AJ249">
+        <v>1.62</v>
+      </c>
+      <c r="AK249">
+        <v>1.37</v>
+      </c>
+      <c r="AL249">
+        <v>1.36</v>
+      </c>
+      <c r="AM249">
+        <v>1.5</v>
+      </c>
+      <c r="AN249">
+        <v>1.33</v>
+      </c>
+      <c r="AO249">
+        <v>1</v>
+      </c>
+      <c r="AP249">
+        <v>1.23</v>
+      </c>
+      <c r="AQ249">
+        <v>1.15</v>
+      </c>
+      <c r="AR249">
+        <v>1.32</v>
+      </c>
+      <c r="AS249">
+        <v>1.25</v>
+      </c>
+      <c r="AT249">
+        <v>2.57</v>
+      </c>
+      <c r="AU249">
+        <v>5</v>
+      </c>
+      <c r="AV249">
+        <v>7</v>
+      </c>
+      <c r="AW249">
+        <v>6</v>
+      </c>
+      <c r="AX249">
+        <v>7</v>
+      </c>
+      <c r="AY249">
+        <v>13</v>
+      </c>
+      <c r="AZ249">
+        <v>15</v>
+      </c>
+      <c r="BA249">
+        <v>2</v>
+      </c>
+      <c r="BB249">
+        <v>5</v>
+      </c>
+      <c r="BC249">
+        <v>7</v>
+      </c>
+      <c r="BD249">
+        <v>1.84</v>
+      </c>
+      <c r="BE249">
+        <v>6.4</v>
+      </c>
+      <c r="BF249">
+        <v>2.17</v>
+      </c>
+      <c r="BG249">
+        <v>1.43</v>
+      </c>
+      <c r="BH249">
+        <v>2.55</v>
+      </c>
+      <c r="BI249">
+        <v>1.72</v>
+      </c>
+      <c r="BJ249">
+        <v>1.98</v>
+      </c>
+      <c r="BK249">
+        <v>2.17</v>
+      </c>
+      <c r="BL249">
+        <v>1.6</v>
+      </c>
+      <c r="BM249">
+        <v>2.8</v>
+      </c>
+      <c r="BN249">
+        <v>1.37</v>
+      </c>
+      <c r="BO249">
+        <v>3.7</v>
+      </c>
+      <c r="BP249">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7465236</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45711.70833333334</v>
+      </c>
+      <c r="F250">
+        <v>25</v>
+      </c>
+      <c r="G250" t="s">
+        <v>76</v>
+      </c>
+      <c r="H250" t="s">
+        <v>85</v>
+      </c>
+      <c r="I250">
+        <v>1</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <v>3</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>3</v>
+      </c>
+      <c r="O250" t="s">
+        <v>252</v>
+      </c>
+      <c r="P250" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q250">
+        <v>2.2</v>
+      </c>
+      <c r="R250">
+        <v>2.05</v>
+      </c>
+      <c r="S250">
+        <v>7.5</v>
+      </c>
+      <c r="T250">
+        <v>1.53</v>
+      </c>
+      <c r="U250">
+        <v>2.38</v>
+      </c>
+      <c r="V250">
+        <v>3.75</v>
+      </c>
+      <c r="W250">
+        <v>1.25</v>
+      </c>
+      <c r="X250">
+        <v>11</v>
+      </c>
+      <c r="Y250">
+        <v>1.05</v>
+      </c>
+      <c r="Z250">
+        <v>1.53</v>
+      </c>
+      <c r="AA250">
+        <v>3.75</v>
+      </c>
+      <c r="AB250">
+        <v>7.5</v>
+      </c>
+      <c r="AC250">
+        <v>1.09</v>
+      </c>
+      <c r="AD250">
+        <v>8</v>
+      </c>
+      <c r="AE250">
+        <v>1.48</v>
+      </c>
+      <c r="AF250">
+        <v>2.65</v>
+      </c>
+      <c r="AG250">
+        <v>2.5</v>
+      </c>
+      <c r="AH250">
+        <v>1.53</v>
+      </c>
+      <c r="AI250">
+        <v>2.5</v>
+      </c>
+      <c r="AJ250">
+        <v>1.5</v>
+      </c>
+      <c r="AK250">
+        <v>1.11</v>
+      </c>
+      <c r="AL250">
+        <v>1.26</v>
+      </c>
+      <c r="AM250">
+        <v>2.37</v>
+      </c>
+      <c r="AN250">
+        <v>1.42</v>
+      </c>
+      <c r="AO250">
+        <v>0.83</v>
+      </c>
+      <c r="AP250">
+        <v>1.54</v>
+      </c>
+      <c r="AQ250">
+        <v>0.77</v>
+      </c>
+      <c r="AR250">
+        <v>1.44</v>
+      </c>
+      <c r="AS250">
+        <v>0.93</v>
+      </c>
+      <c r="AT250">
+        <v>2.37</v>
+      </c>
+      <c r="AU250">
+        <v>6</v>
+      </c>
+      <c r="AV250">
+        <v>3</v>
+      </c>
+      <c r="AW250">
+        <v>7</v>
+      </c>
+      <c r="AX250">
+        <v>6</v>
+      </c>
+      <c r="AY250">
+        <v>13</v>
+      </c>
+      <c r="AZ250">
+        <v>10</v>
+      </c>
+      <c r="BA250">
+        <v>3</v>
+      </c>
+      <c r="BB250">
+        <v>3</v>
+      </c>
+      <c r="BC250">
+        <v>6</v>
+      </c>
+      <c r="BD250">
+        <v>1.25</v>
+      </c>
+      <c r="BE250">
+        <v>8</v>
+      </c>
+      <c r="BF250">
+        <v>4.1</v>
+      </c>
+      <c r="BG250">
+        <v>1.27</v>
+      </c>
+      <c r="BH250">
+        <v>3.3</v>
+      </c>
+      <c r="BI250">
+        <v>1.47</v>
+      </c>
+      <c r="BJ250">
+        <v>2.48</v>
+      </c>
+      <c r="BK250">
+        <v>1.75</v>
+      </c>
+      <c r="BL250">
+        <v>1.95</v>
+      </c>
+      <c r="BM250">
+        <v>2.17</v>
+      </c>
+      <c r="BN250">
+        <v>1.6</v>
+      </c>
+      <c r="BO250">
+        <v>2.7</v>
+      </c>
+      <c r="BP250">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -775,6 +775,9 @@
     <t>['12', '48', '80']</t>
   </si>
   <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1419,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP250"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1675,7 +1678,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2087,7 +2090,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2293,7 +2296,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2499,7 +2502,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2705,7 +2708,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2911,7 +2914,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3117,7 +3120,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3529,7 +3532,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3941,7 +3944,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4019,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ13">
         <v>1.85</v>
@@ -4228,7 +4231,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
         <v>1.83</v>
@@ -5795,7 +5798,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6207,7 +6210,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -7031,7 +7034,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -8267,7 +8270,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8554,7 +8557,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ35">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8885,7 +8888,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9091,7 +9094,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9169,7 +9172,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ38">
         <v>0.92</v>
@@ -9915,7 +9918,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10121,7 +10124,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10405,7 +10408,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ44">
         <v>1.17</v>
@@ -10533,7 +10536,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10945,7 +10948,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11151,7 +11154,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12181,7 +12184,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12799,7 +12802,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13829,7 +13832,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14241,7 +14244,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14322,7 +14325,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR63">
         <v>1.68</v>
@@ -14653,7 +14656,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14731,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ65">
         <v>0.23</v>
@@ -14859,7 +14862,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15477,7 +15480,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15683,7 +15686,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16095,7 +16098,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16176,7 +16179,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR72">
         <v>1.16</v>
@@ -16919,7 +16922,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17743,7 +17746,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17949,7 +17952,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18442,7 +18445,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.07</v>
@@ -18979,7 +18982,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19391,7 +19394,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19597,7 +19600,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19881,7 +19884,7 @@
         <v>0.67</v>
       </c>
       <c r="AP90">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ90">
         <v>1.15</v>
@@ -20009,7 +20012,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20215,7 +20218,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20627,7 +20630,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21039,7 +21042,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -22069,7 +22072,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22275,7 +22278,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22481,7 +22484,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23099,7 +23102,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23923,7 +23926,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24416,7 +24419,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR112">
         <v>1.08</v>
@@ -24747,7 +24750,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25159,7 +25162,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -25365,7 +25368,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25443,7 +25446,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ117">
         <v>1.17</v>
@@ -25571,7 +25574,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25983,7 +25986,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26807,7 +26810,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -28043,7 +28046,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28455,7 +28458,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28536,7 +28539,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28867,7 +28870,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29073,7 +29076,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29357,7 +29360,7 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ136">
         <v>1.31</v>
@@ -29485,7 +29488,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -30103,7 +30106,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30721,7 +30724,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30927,7 +30930,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31339,7 +31342,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31829,7 +31832,7 @@
         <v>0.83</v>
       </c>
       <c r="AP148">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ148">
         <v>0.75</v>
@@ -31957,7 +31960,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32163,7 +32166,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32450,7 +32453,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
         <v>1.39</v>
@@ -32781,7 +32784,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33193,7 +33196,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33399,7 +33402,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33811,7 +33814,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34017,7 +34020,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -35125,7 +35128,7 @@
         <v>0.57</v>
       </c>
       <c r="AP164">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ164">
         <v>0.5</v>
@@ -35253,7 +35256,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35665,7 +35668,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36077,7 +36080,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36489,7 +36492,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37188,7 +37191,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ174">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR174">
         <v>1.33</v>
@@ -37725,7 +37728,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37931,7 +37934,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38137,7 +38140,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38343,7 +38346,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38961,7 +38964,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39373,7 +39376,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40069,7 +40072,7 @@
         <v>0.33</v>
       </c>
       <c r="AP188">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ188">
         <v>0.42</v>
@@ -40197,7 +40200,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -41021,7 +41024,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41433,7 +41436,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41845,7 +41848,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42051,7 +42054,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42750,7 +42753,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ201">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR201">
         <v>1.52</v>
@@ -43081,7 +43084,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43287,7 +43290,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43493,7 +43496,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43571,7 +43574,7 @@
         <v>0.11</v>
       </c>
       <c r="AP205">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ205">
         <v>0.42</v>
@@ -43699,7 +43702,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44111,7 +44114,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44729,7 +44732,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44935,7 +44938,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45634,7 +45637,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ215">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR215">
         <v>1.74</v>
@@ -46583,7 +46586,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47201,7 +47204,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47613,7 +47616,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48643,7 +48646,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -48721,7 +48724,7 @@
         <v>2</v>
       </c>
       <c r="AP230">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ230">
         <v>2.14</v>
@@ -49055,7 +49058,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49261,7 +49264,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49467,7 +49470,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50085,7 +50088,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50291,7 +50294,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -51321,7 +51324,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51527,7 +51530,7 @@
         <v>104</v>
       </c>
       <c r="P244" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -51733,7 +51736,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51939,7 +51942,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52145,7 +52148,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52557,7 +52560,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52920,6 +52923,212 @@
       </c>
       <c r="BP250">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7465235</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45712.70833333334</v>
+      </c>
+      <c r="F251">
+        <v>25</v>
+      </c>
+      <c r="G251" t="s">
+        <v>80</v>
+      </c>
+      <c r="H251" t="s">
+        <v>77</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>1</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>2</v>
+      </c>
+      <c r="O251" t="s">
+        <v>253</v>
+      </c>
+      <c r="P251" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q251">
+        <v>2.88</v>
+      </c>
+      <c r="R251">
+        <v>1.95</v>
+      </c>
+      <c r="S251">
+        <v>4.5</v>
+      </c>
+      <c r="T251">
+        <v>1.57</v>
+      </c>
+      <c r="U251">
+        <v>2.25</v>
+      </c>
+      <c r="V251">
+        <v>3.75</v>
+      </c>
+      <c r="W251">
+        <v>1.25</v>
+      </c>
+      <c r="X251">
+        <v>13</v>
+      </c>
+      <c r="Y251">
+        <v>1.04</v>
+      </c>
+      <c r="Z251">
+        <v>2.05</v>
+      </c>
+      <c r="AA251">
+        <v>3.2</v>
+      </c>
+      <c r="AB251">
+        <v>3.8</v>
+      </c>
+      <c r="AC251">
+        <v>1.1</v>
+      </c>
+      <c r="AD251">
+        <v>7.5</v>
+      </c>
+      <c r="AE251">
+        <v>1.52</v>
+      </c>
+      <c r="AF251">
+        <v>2.6</v>
+      </c>
+      <c r="AG251">
+        <v>2.63</v>
+      </c>
+      <c r="AH251">
+        <v>1.5</v>
+      </c>
+      <c r="AI251">
+        <v>2.1</v>
+      </c>
+      <c r="AJ251">
+        <v>1.67</v>
+      </c>
+      <c r="AK251">
+        <v>1.25</v>
+      </c>
+      <c r="AL251">
+        <v>1.34</v>
+      </c>
+      <c r="AM251">
+        <v>1.75</v>
+      </c>
+      <c r="AN251">
+        <v>1.5</v>
+      </c>
+      <c r="AO251">
+        <v>1.36</v>
+      </c>
+      <c r="AP251">
+        <v>1.46</v>
+      </c>
+      <c r="AQ251">
+        <v>1.33</v>
+      </c>
+      <c r="AR251">
+        <v>1.43</v>
+      </c>
+      <c r="AS251">
+        <v>1.18</v>
+      </c>
+      <c r="AT251">
+        <v>2.61</v>
+      </c>
+      <c r="AU251">
+        <v>5</v>
+      </c>
+      <c r="AV251">
+        <v>3</v>
+      </c>
+      <c r="AW251">
+        <v>15</v>
+      </c>
+      <c r="AX251">
+        <v>11</v>
+      </c>
+      <c r="AY251">
+        <v>20</v>
+      </c>
+      <c r="AZ251">
+        <v>14</v>
+      </c>
+      <c r="BA251">
+        <v>4</v>
+      </c>
+      <c r="BB251">
+        <v>4</v>
+      </c>
+      <c r="BC251">
+        <v>8</v>
+      </c>
+      <c r="BD251">
+        <v>1.49</v>
+      </c>
+      <c r="BE251">
+        <v>6.75</v>
+      </c>
+      <c r="BF251">
+        <v>2.95</v>
+      </c>
+      <c r="BG251">
+        <v>1.4</v>
+      </c>
+      <c r="BH251">
+        <v>2.65</v>
+      </c>
+      <c r="BI251">
+        <v>1.68</v>
+      </c>
+      <c r="BJ251">
+        <v>2.04</v>
+      </c>
+      <c r="BK251">
+        <v>2.08</v>
+      </c>
+      <c r="BL251">
+        <v>1.65</v>
+      </c>
+      <c r="BM251">
+        <v>2.65</v>
+      </c>
+      <c r="BN251">
+        <v>1.41</v>
+      </c>
+      <c r="BO251">
+        <v>3.55</v>
+      </c>
+      <c r="BP251">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -778,6 +778,9 @@
     <t>['45+2']</t>
   </si>
   <si>
+    <t>['63']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -905,9 +908,6 @@
   </si>
   <si>
     <t>['25', '41', '77']</t>
-  </si>
-  <si>
-    <t>['63']</t>
   </si>
   <si>
     <t>['34', '68']</t>
@@ -1422,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1678,7 +1678,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2090,7 +2090,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2296,7 +2296,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2502,7 +2502,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2708,7 +2708,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2914,7 +2914,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3120,7 +3120,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3532,7 +3532,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3944,7 +3944,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -5261,7 +5261,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ19">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5798,7 +5798,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6210,7 +6210,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -7034,7 +7034,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -8270,7 +8270,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8763,7 +8763,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ36">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR36">
         <v>0.71</v>
@@ -8888,7 +8888,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9094,7 +9094,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9918,7 +9918,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10124,7 +10124,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10536,7 +10536,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10948,7 +10948,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11154,7 +11154,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12184,7 +12184,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12802,7 +12802,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12883,7 +12883,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ56">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -13832,7 +13832,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14244,7 +14244,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14656,7 +14656,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14862,7 +14862,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15480,7 +15480,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15686,7 +15686,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16098,7 +16098,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16922,7 +16922,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17746,7 +17746,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17952,7 +17952,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18033,7 +18033,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -18982,7 +18982,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19394,7 +19394,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19600,7 +19600,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -20012,7 +20012,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20218,7 +20218,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20630,7 +20630,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21042,7 +21042,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -22072,7 +22072,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22153,7 +22153,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ101">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR101">
         <v>1.21</v>
@@ -22278,7 +22278,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22484,7 +22484,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23102,7 +23102,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23926,7 +23926,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24750,7 +24750,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25037,7 +25037,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ115">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25162,7 +25162,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>1.4</v>
@@ -26067,7 +26067,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR120">
         <v>1.55</v>
@@ -30187,7 +30187,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ140">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR140">
         <v>1.94</v>
@@ -35955,7 +35955,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ168">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR168">
         <v>1.43</v>
@@ -36492,7 +36492,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -42054,7 +42054,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42135,7 +42135,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ198">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR198">
         <v>1.8</v>
@@ -46873,7 +46873,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ221">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR221">
         <v>1.35</v>
@@ -50581,7 +50581,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ239">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR239">
         <v>1.24</v>
@@ -52148,7 +52148,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -53129,6 +53129,212 @@
       </c>
       <c r="BP251">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7465244</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45716.70833333334</v>
+      </c>
+      <c r="F252">
+        <v>26</v>
+      </c>
+      <c r="G252" t="s">
+        <v>78</v>
+      </c>
+      <c r="H252" t="s">
+        <v>73</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>1</v>
+      </c>
+      <c r="M252">
+        <v>1</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>254</v>
+      </c>
+      <c r="P252" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q252">
+        <v>3.75</v>
+      </c>
+      <c r="R252">
+        <v>2.05</v>
+      </c>
+      <c r="S252">
+        <v>3.2</v>
+      </c>
+      <c r="T252">
+        <v>1.5</v>
+      </c>
+      <c r="U252">
+        <v>2.5</v>
+      </c>
+      <c r="V252">
+        <v>3.4</v>
+      </c>
+      <c r="W252">
+        <v>1.3</v>
+      </c>
+      <c r="X252">
+        <v>10</v>
+      </c>
+      <c r="Y252">
+        <v>1.06</v>
+      </c>
+      <c r="Z252">
+        <v>3</v>
+      </c>
+      <c r="AA252">
+        <v>3.2</v>
+      </c>
+      <c r="AB252">
+        <v>2.4</v>
+      </c>
+      <c r="AC252">
+        <v>1.08</v>
+      </c>
+      <c r="AD252">
+        <v>9</v>
+      </c>
+      <c r="AE252">
+        <v>1.4</v>
+      </c>
+      <c r="AF252">
+        <v>3</v>
+      </c>
+      <c r="AG252">
+        <v>2.2</v>
+      </c>
+      <c r="AH252">
+        <v>1.67</v>
+      </c>
+      <c r="AI252">
+        <v>1.95</v>
+      </c>
+      <c r="AJ252">
+        <v>1.8</v>
+      </c>
+      <c r="AK252">
+        <v>1.51</v>
+      </c>
+      <c r="AL252">
+        <v>1.33</v>
+      </c>
+      <c r="AM252">
+        <v>1.4</v>
+      </c>
+      <c r="AN252">
+        <v>1</v>
+      </c>
+      <c r="AO252">
+        <v>0.83</v>
+      </c>
+      <c r="AP252">
+        <v>1</v>
+      </c>
+      <c r="AQ252">
+        <v>0.85</v>
+      </c>
+      <c r="AR252">
+        <v>0.99</v>
+      </c>
+      <c r="AS252">
+        <v>1.07</v>
+      </c>
+      <c r="AT252">
+        <v>2.06</v>
+      </c>
+      <c r="AU252">
+        <v>8</v>
+      </c>
+      <c r="AV252">
+        <v>4</v>
+      </c>
+      <c r="AW252">
+        <v>15</v>
+      </c>
+      <c r="AX252">
+        <v>1</v>
+      </c>
+      <c r="AY252">
+        <v>25</v>
+      </c>
+      <c r="AZ252">
+        <v>5</v>
+      </c>
+      <c r="BA252">
+        <v>13</v>
+      </c>
+      <c r="BB252">
+        <v>4</v>
+      </c>
+      <c r="BC252">
+        <v>17</v>
+      </c>
+      <c r="BD252">
+        <v>2.1</v>
+      </c>
+      <c r="BE252">
+        <v>6.1</v>
+      </c>
+      <c r="BF252">
+        <v>1.91</v>
+      </c>
+      <c r="BG252">
+        <v>1.49</v>
+      </c>
+      <c r="BH252">
+        <v>2.4</v>
+      </c>
+      <c r="BI252">
+        <v>1.82</v>
+      </c>
+      <c r="BJ252">
+        <v>1.86</v>
+      </c>
+      <c r="BK252">
+        <v>2.32</v>
+      </c>
+      <c r="BL252">
+        <v>1.53</v>
+      </c>
+      <c r="BM252">
+        <v>3.05</v>
+      </c>
+      <c r="BN252">
+        <v>1.32</v>
+      </c>
+      <c r="BO252">
+        <v>4.1</v>
+      </c>
+      <c r="BP252">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="352">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -781,6 +781,15 @@
     <t>['63']</t>
   </si>
   <si>
+    <t>['21', '68']</t>
+  </si>
+  <si>
+    <t>['34', '54']</t>
+  </si>
+  <si>
+    <t>['66']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1024,9 +1033,6 @@
     <t>['72', '74', '85']</t>
   </si>
   <si>
-    <t>['66']</t>
-  </si>
-  <si>
     <t>['33', '69']</t>
   </si>
   <si>
@@ -1061,6 +1067,9 @@
   </si>
   <si>
     <t>['18', '77']</t>
+  </si>
+  <si>
+    <t>['36', '51']</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP252"/>
+  <dimension ref="A1:BP256"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1678,7 +1687,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1962,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ3">
         <v>0.92</v>
@@ -2090,7 +2099,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2296,7 +2305,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2502,7 +2511,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2708,7 +2717,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2914,7 +2923,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3120,7 +3129,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3201,7 +3210,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ9">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3532,7 +3541,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3944,7 +3953,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4437,7 +4446,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ15">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5670,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ21">
         <v>0.92</v>
@@ -5798,7 +5807,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -5879,7 +5888,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR22">
         <v>1.08</v>
@@ -6210,7 +6219,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6288,7 +6297,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ24">
         <v>2.14</v>
@@ -6906,7 +6915,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ27">
         <v>0.42</v>
@@ -7034,7 +7043,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7318,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ29">
         <v>0.75</v>
@@ -7527,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="AQ30">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR30">
         <v>1.44</v>
@@ -8270,7 +8279,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8888,7 +8897,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8969,7 +8978,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -9094,7 +9103,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9790,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ41">
         <v>0.77</v>
@@ -9918,7 +9927,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10124,7 +10133,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10536,7 +10545,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10617,7 +10626,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ45">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR45">
         <v>1.14</v>
@@ -10948,7 +10957,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11026,7 +11035,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ47">
         <v>2.14</v>
@@ -11154,7 +11163,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11235,7 +11244,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11438,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ49">
         <v>0.42</v>
@@ -11644,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ50">
         <v>0.75</v>
@@ -12056,7 +12065,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ52">
         <v>1.17</v>
@@ -12184,7 +12193,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12265,7 +12274,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ53">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR53">
         <v>1.17</v>
@@ -12802,7 +12811,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13707,7 +13716,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ60">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -13832,7 +13841,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14116,7 +14125,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ62">
         <v>1.83</v>
@@ -14244,7 +14253,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14322,7 +14331,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ63">
         <v>1.33</v>
@@ -14656,7 +14665,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14862,7 +14871,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15146,7 +15155,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ67">
         <v>1.31</v>
@@ -15480,7 +15489,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15686,7 +15695,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16098,7 +16107,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16588,7 +16597,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
         <v>0.77</v>
@@ -16922,7 +16931,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17618,7 +17627,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ79">
         <v>0.42</v>
@@ -17746,7 +17755,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17824,10 +17833,10 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ80">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR80">
         <v>1.69</v>
@@ -17952,7 +17961,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18857,7 +18866,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR85">
         <v>1.24</v>
@@ -18982,7 +18991,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19394,7 +19403,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19472,10 +19481,10 @@
         <v>2</v>
       </c>
       <c r="AP88">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19600,7 +19609,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -20012,7 +20021,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20218,7 +20227,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20630,7 +20639,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20914,7 +20923,7 @@
         <v>1.25</v>
       </c>
       <c r="AP95">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ95">
         <v>1.17</v>
@@ -21042,7 +21051,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21123,7 +21132,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -21532,7 +21541,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ98">
         <v>0.77</v>
@@ -22072,7 +22081,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22278,7 +22287,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22484,7 +22493,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22768,7 +22777,7 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ104">
         <v>0.6899999999999999</v>
@@ -23102,7 +23111,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23389,7 +23398,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR107">
         <v>1.1</v>
@@ -23798,7 +23807,7 @@
         <v>1.8</v>
       </c>
       <c r="AP109">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109">
         <v>1.83</v>
@@ -23926,7 +23935,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24213,7 +24222,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ111">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR111">
         <v>1.44</v>
@@ -24750,7 +24759,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24828,7 +24837,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ114">
         <v>0.77</v>
@@ -25034,7 +25043,7 @@
         <v>0.6</v>
       </c>
       <c r="AP115">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ115">
         <v>0.85</v>
@@ -25368,7 +25377,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25574,7 +25583,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25986,7 +25995,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26064,7 +26073,7 @@
         <v>0.5</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ120">
         <v>0.85</v>
@@ -26810,7 +26819,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26888,10 +26897,10 @@
         <v>0.6</v>
       </c>
       <c r="AP124">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ124">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR124">
         <v>1.82</v>
@@ -27509,7 +27518,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -28046,7 +28055,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28330,7 +28339,7 @@
         <v>0.43</v>
       </c>
       <c r="AP131">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ131">
         <v>0.6899999999999999</v>
@@ -28458,7 +28467,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28742,7 +28751,7 @@
         <v>0.17</v>
       </c>
       <c r="AP133">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ133">
         <v>0.42</v>
@@ -28870,7 +28879,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29076,7 +29085,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29488,7 +29497,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29569,7 +29578,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ137">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -30106,7 +30115,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30599,7 +30608,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ142">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR142">
         <v>1.12</v>
@@ -30724,7 +30733,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30930,7 +30939,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31342,7 +31351,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31420,10 +31429,10 @@
         <v>1.33</v>
       </c>
       <c r="AP146">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ146">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR146">
         <v>1.72</v>
@@ -31960,7 +31969,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32166,7 +32175,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32247,7 +32256,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ150">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32784,7 +32793,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32862,7 +32871,7 @@
         <v>2.2</v>
       </c>
       <c r="AP153">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ153">
         <v>2.14</v>
@@ -33196,7 +33205,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33274,10 +33283,10 @@
         <v>1.71</v>
       </c>
       <c r="AP155">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ155">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR155">
         <v>1.38</v>
@@ -33402,7 +33411,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33814,7 +33823,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34020,7 +34029,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34098,7 +34107,7 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ159">
         <v>1.08</v>
@@ -35131,7 +35140,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ164">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR164">
         <v>1.37</v>
@@ -35256,7 +35265,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35334,10 +35343,10 @@
         <v>1.88</v>
       </c>
       <c r="AP165">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ165">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR165">
         <v>1.64</v>
@@ -35540,7 +35549,7 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ166">
         <v>1.17</v>
@@ -35668,7 +35677,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35749,7 +35758,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ167">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR167">
         <v>1.17</v>
@@ -36080,7 +36089,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36492,7 +36501,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36982,7 +36991,7 @@
         <v>0.38</v>
       </c>
       <c r="AP173">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ173">
         <v>0.23</v>
@@ -37603,7 +37612,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ176">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37728,7 +37737,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37934,7 +37943,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38140,7 +38149,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38346,7 +38355,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38836,7 +38845,7 @@
         <v>1.33</v>
       </c>
       <c r="AP182">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ182">
         <v>1.31</v>
@@ -38964,7 +38973,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39045,7 +39054,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ183">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR183">
         <v>1.35</v>
@@ -39248,10 +39257,10 @@
         <v>0.5</v>
       </c>
       <c r="AP184">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ184">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR184">
         <v>1.61</v>
@@ -39376,7 +39385,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40200,7 +40209,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40484,7 +40493,7 @@
         <v>0.88</v>
       </c>
       <c r="AP190">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ190">
         <v>0.75</v>
@@ -41024,7 +41033,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41102,7 +41111,7 @@
         <v>0.67</v>
       </c>
       <c r="AP193">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ193">
         <v>1.08</v>
@@ -41436,7 +41445,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41514,7 +41523,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ195">
         <v>0.6899999999999999</v>
@@ -41848,7 +41857,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41929,7 +41938,7 @@
         <v>2</v>
       </c>
       <c r="AQ197">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR197">
         <v>1.41</v>
@@ -42054,7 +42063,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -43084,7 +43093,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43290,7 +43299,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43368,7 +43377,7 @@
         <v>1.7</v>
       </c>
       <c r="AP204">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ204">
         <v>1.85</v>
@@ -43496,7 +43505,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43702,7 +43711,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43783,7 +43792,7 @@
         <v>1</v>
       </c>
       <c r="AQ206">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR206">
         <v>1.01</v>
@@ -43986,7 +43995,7 @@
         <v>1.2</v>
       </c>
       <c r="AP207">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ207">
         <v>0.92</v>
@@ -44114,7 +44123,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44732,7 +44741,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="Q211">
         <v>3.4</v>
@@ -44813,7 +44822,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ211">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR211">
         <v>1.16</v>
@@ -44938,7 +44947,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45634,7 +45643,7 @@
         <v>1.5</v>
       </c>
       <c r="AP215">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ215">
         <v>1.33</v>
@@ -45843,7 +45852,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ216">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR216">
         <v>1.18</v>
@@ -46255,7 +46264,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ218">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR218">
         <v>1.3</v>
@@ -46586,7 +46595,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -46664,10 +46673,10 @@
         <v>1.8</v>
       </c>
       <c r="AP220">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ220">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR220">
         <v>1.72</v>
@@ -46870,7 +46879,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ221">
         <v>0.85</v>
@@ -47076,7 +47085,7 @@
         <v>0.27</v>
       </c>
       <c r="AP222">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ222">
         <v>0.23</v>
@@ -47204,7 +47213,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47616,7 +47625,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48646,7 +48655,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49058,7 +49067,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49136,7 +49145,7 @@
         <v>1</v>
       </c>
       <c r="AP232">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ232">
         <v>1.17</v>
@@ -49264,7 +49273,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49470,7 +49479,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -49551,7 +49560,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ234">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR234">
         <v>1.47</v>
@@ -49754,10 +49763,10 @@
         <v>0.45</v>
       </c>
       <c r="AP235">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ235">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR235">
         <v>1.76</v>
@@ -50088,7 +50097,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50169,7 +50178,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ237">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR237">
         <v>1.14</v>
@@ -50294,7 +50303,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -50784,7 +50793,7 @@
         <v>1.27</v>
       </c>
       <c r="AP240">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ240">
         <v>1.17</v>
@@ -51324,7 +51333,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51530,7 +51539,7 @@
         <v>104</v>
       </c>
       <c r="P244" t="s">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -51608,7 +51617,7 @@
         <v>1.75</v>
       </c>
       <c r="AP244">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ244">
         <v>1.85</v>
@@ -51736,7 +51745,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51942,7 +51951,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52148,7 +52157,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52560,7 +52569,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52972,7 +52981,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53178,7 +53187,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53335,6 +53344,830 @@
       </c>
       <c r="BP252">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7465242</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45717.41666666666</v>
+      </c>
+      <c r="F253">
+        <v>26</v>
+      </c>
+      <c r="G253" t="s">
+        <v>89</v>
+      </c>
+      <c r="H253" t="s">
+        <v>72</v>
+      </c>
+      <c r="I253">
+        <v>1</v>
+      </c>
+      <c r="J253">
+        <v>1</v>
+      </c>
+      <c r="K253">
+        <v>2</v>
+      </c>
+      <c r="L253">
+        <v>2</v>
+      </c>
+      <c r="M253">
+        <v>2</v>
+      </c>
+      <c r="N253">
+        <v>4</v>
+      </c>
+      <c r="O253" t="s">
+        <v>255</v>
+      </c>
+      <c r="P253" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q253">
+        <v>2.75</v>
+      </c>
+      <c r="R253">
+        <v>2.2</v>
+      </c>
+      <c r="S253">
+        <v>3.75</v>
+      </c>
+      <c r="T253">
+        <v>1.36</v>
+      </c>
+      <c r="U253">
+        <v>3</v>
+      </c>
+      <c r="V253">
+        <v>2.75</v>
+      </c>
+      <c r="W253">
+        <v>1.4</v>
+      </c>
+      <c r="X253">
+        <v>7</v>
+      </c>
+      <c r="Y253">
+        <v>1.1</v>
+      </c>
+      <c r="Z253">
+        <v>2.1</v>
+      </c>
+      <c r="AA253">
+        <v>3.5</v>
+      </c>
+      <c r="AB253">
+        <v>3.4</v>
+      </c>
+      <c r="AC253">
+        <v>1.05</v>
+      </c>
+      <c r="AD253">
+        <v>11</v>
+      </c>
+      <c r="AE253">
+        <v>1.3</v>
+      </c>
+      <c r="AF253">
+        <v>3.6</v>
+      </c>
+      <c r="AG253">
+        <v>1.91</v>
+      </c>
+      <c r="AH253">
+        <v>1.91</v>
+      </c>
+      <c r="AI253">
+        <v>1.7</v>
+      </c>
+      <c r="AJ253">
+        <v>2.05</v>
+      </c>
+      <c r="AK253">
+        <v>1.31</v>
+      </c>
+      <c r="AL253">
+        <v>1.3</v>
+      </c>
+      <c r="AM253">
+        <v>1.7</v>
+      </c>
+      <c r="AN253">
+        <v>1.58</v>
+      </c>
+      <c r="AO253">
+        <v>0.5</v>
+      </c>
+      <c r="AP253">
+        <v>1.54</v>
+      </c>
+      <c r="AQ253">
+        <v>0.54</v>
+      </c>
+      <c r="AR253">
+        <v>1.4</v>
+      </c>
+      <c r="AS253">
+        <v>1.27</v>
+      </c>
+      <c r="AT253">
+        <v>2.67</v>
+      </c>
+      <c r="AU253">
+        <v>7</v>
+      </c>
+      <c r="AV253">
+        <v>7</v>
+      </c>
+      <c r="AW253">
+        <v>3</v>
+      </c>
+      <c r="AX253">
+        <v>4</v>
+      </c>
+      <c r="AY253">
+        <v>11</v>
+      </c>
+      <c r="AZ253">
+        <v>13</v>
+      </c>
+      <c r="BA253">
+        <v>4</v>
+      </c>
+      <c r="BB253">
+        <v>2</v>
+      </c>
+      <c r="BC253">
+        <v>6</v>
+      </c>
+      <c r="BD253">
+        <v>1.55</v>
+      </c>
+      <c r="BE253">
+        <v>6.5</v>
+      </c>
+      <c r="BF253">
+        <v>2.7</v>
+      </c>
+      <c r="BG253">
+        <v>1.41</v>
+      </c>
+      <c r="BH253">
+        <v>2.65</v>
+      </c>
+      <c r="BI253">
+        <v>1.68</v>
+      </c>
+      <c r="BJ253">
+        <v>2.02</v>
+      </c>
+      <c r="BK253">
+        <v>2.08</v>
+      </c>
+      <c r="BL253">
+        <v>1.65</v>
+      </c>
+      <c r="BM253">
+        <v>2.7</v>
+      </c>
+      <c r="BN253">
+        <v>1.4</v>
+      </c>
+      <c r="BO253">
+        <v>3.55</v>
+      </c>
+      <c r="BP253">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7465240</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45717.51041666666</v>
+      </c>
+      <c r="F254">
+        <v>26</v>
+      </c>
+      <c r="G254" t="s">
+        <v>88</v>
+      </c>
+      <c r="H254" t="s">
+        <v>80</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+      <c r="L254">
+        <v>1</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254">
+        <v>2</v>
+      </c>
+      <c r="O254" t="s">
+        <v>102</v>
+      </c>
+      <c r="P254" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q254">
+        <v>3</v>
+      </c>
+      <c r="R254">
+        <v>2.05</v>
+      </c>
+      <c r="S254">
+        <v>3.75</v>
+      </c>
+      <c r="T254">
+        <v>1.5</v>
+      </c>
+      <c r="U254">
+        <v>2.5</v>
+      </c>
+      <c r="V254">
+        <v>3.4</v>
+      </c>
+      <c r="W254">
+        <v>1.3</v>
+      </c>
+      <c r="X254">
+        <v>10</v>
+      </c>
+      <c r="Y254">
+        <v>1.06</v>
+      </c>
+      <c r="Z254">
+        <v>2.2</v>
+      </c>
+      <c r="AA254">
+        <v>3.25</v>
+      </c>
+      <c r="AB254">
+        <v>3.3</v>
+      </c>
+      <c r="AC254">
+        <v>1.08</v>
+      </c>
+      <c r="AD254">
+        <v>8.5</v>
+      </c>
+      <c r="AE254">
+        <v>1.42</v>
+      </c>
+      <c r="AF254">
+        <v>2.9</v>
+      </c>
+      <c r="AG254">
+        <v>2.1</v>
+      </c>
+      <c r="AH254">
+        <v>1.65</v>
+      </c>
+      <c r="AI254">
+        <v>1.91</v>
+      </c>
+      <c r="AJ254">
+        <v>1.91</v>
+      </c>
+      <c r="AK254">
+        <v>1.32</v>
+      </c>
+      <c r="AL254">
+        <v>1.33</v>
+      </c>
+      <c r="AM254">
+        <v>1.63</v>
+      </c>
+      <c r="AN254">
+        <v>1.5</v>
+      </c>
+      <c r="AO254">
+        <v>1.08</v>
+      </c>
+      <c r="AP254">
+        <v>1.46</v>
+      </c>
+      <c r="AQ254">
+        <v>1.08</v>
+      </c>
+      <c r="AR254">
+        <v>1.67</v>
+      </c>
+      <c r="AS254">
+        <v>1.22</v>
+      </c>
+      <c r="AT254">
+        <v>2.89</v>
+      </c>
+      <c r="AU254">
+        <v>9</v>
+      </c>
+      <c r="AV254">
+        <v>6</v>
+      </c>
+      <c r="AW254">
+        <v>12</v>
+      </c>
+      <c r="AX254">
+        <v>5</v>
+      </c>
+      <c r="AY254">
+        <v>25</v>
+      </c>
+      <c r="AZ254">
+        <v>13</v>
+      </c>
+      <c r="BA254">
+        <v>6</v>
+      </c>
+      <c r="BB254">
+        <v>6</v>
+      </c>
+      <c r="BC254">
+        <v>12</v>
+      </c>
+      <c r="BD254">
+        <v>1.8</v>
+      </c>
+      <c r="BE254">
+        <v>6.5</v>
+      </c>
+      <c r="BF254">
+        <v>2.2</v>
+      </c>
+      <c r="BG254">
+        <v>1.32</v>
+      </c>
+      <c r="BH254">
+        <v>3</v>
+      </c>
+      <c r="BI254">
+        <v>1.56</v>
+      </c>
+      <c r="BJ254">
+        <v>2.23</v>
+      </c>
+      <c r="BK254">
+        <v>1.92</v>
+      </c>
+      <c r="BL254">
+        <v>1.77</v>
+      </c>
+      <c r="BM254">
+        <v>2.43</v>
+      </c>
+      <c r="BN254">
+        <v>1.48</v>
+      </c>
+      <c r="BO254">
+        <v>3.15</v>
+      </c>
+      <c r="BP254">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7465238</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45717.60416666666</v>
+      </c>
+      <c r="F255">
+        <v>26</v>
+      </c>
+      <c r="G255" t="s">
+        <v>71</v>
+      </c>
+      <c r="H255" t="s">
+        <v>84</v>
+      </c>
+      <c r="I255">
+        <v>1</v>
+      </c>
+      <c r="J255">
+        <v>1</v>
+      </c>
+      <c r="K255">
+        <v>2</v>
+      </c>
+      <c r="L255">
+        <v>2</v>
+      </c>
+      <c r="M255">
+        <v>1</v>
+      </c>
+      <c r="N255">
+        <v>3</v>
+      </c>
+      <c r="O255" t="s">
+        <v>256</v>
+      </c>
+      <c r="P255" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q255">
+        <v>4.33</v>
+      </c>
+      <c r="R255">
+        <v>2.5</v>
+      </c>
+      <c r="S255">
+        <v>2.25</v>
+      </c>
+      <c r="T255">
+        <v>1.29</v>
+      </c>
+      <c r="U255">
+        <v>3.5</v>
+      </c>
+      <c r="V255">
+        <v>2.25</v>
+      </c>
+      <c r="W255">
+        <v>1.57</v>
+      </c>
+      <c r="X255">
+        <v>5.5</v>
+      </c>
+      <c r="Y255">
+        <v>1.14</v>
+      </c>
+      <c r="Z255">
+        <v>4.5</v>
+      </c>
+      <c r="AA255">
+        <v>3.9</v>
+      </c>
+      <c r="AB255">
+        <v>1.7</v>
+      </c>
+      <c r="AC255">
+        <v>1.02</v>
+      </c>
+      <c r="AD255">
+        <v>19</v>
+      </c>
+      <c r="AE255">
+        <v>1.18</v>
+      </c>
+      <c r="AF255">
+        <v>5</v>
+      </c>
+      <c r="AG255">
+        <v>1.53</v>
+      </c>
+      <c r="AH255">
+        <v>2.5</v>
+      </c>
+      <c r="AI255">
+        <v>1.53</v>
+      </c>
+      <c r="AJ255">
+        <v>2.38</v>
+      </c>
+      <c r="AK255">
+        <v>2.05</v>
+      </c>
+      <c r="AL255">
+        <v>1.23</v>
+      </c>
+      <c r="AM255">
+        <v>1.21</v>
+      </c>
+      <c r="AN255">
+        <v>1.67</v>
+      </c>
+      <c r="AO255">
+        <v>1.77</v>
+      </c>
+      <c r="AP255">
+        <v>1.77</v>
+      </c>
+      <c r="AQ255">
+        <v>1.64</v>
+      </c>
+      <c r="AR255">
+        <v>1.79</v>
+      </c>
+      <c r="AS255">
+        <v>1.74</v>
+      </c>
+      <c r="AT255">
+        <v>3.53</v>
+      </c>
+      <c r="AU255">
+        <v>4</v>
+      </c>
+      <c r="AV255">
+        <v>3</v>
+      </c>
+      <c r="AW255">
+        <v>15</v>
+      </c>
+      <c r="AX255">
+        <v>7</v>
+      </c>
+      <c r="AY255">
+        <v>26</v>
+      </c>
+      <c r="AZ255">
+        <v>14</v>
+      </c>
+      <c r="BA255">
+        <v>9</v>
+      </c>
+      <c r="BB255">
+        <v>2</v>
+      </c>
+      <c r="BC255">
+        <v>11</v>
+      </c>
+      <c r="BD255">
+        <v>2.48</v>
+      </c>
+      <c r="BE255">
+        <v>6.75</v>
+      </c>
+      <c r="BF255">
+        <v>1.65</v>
+      </c>
+      <c r="BG255">
+        <v>1.27</v>
+      </c>
+      <c r="BH255">
+        <v>3.3</v>
+      </c>
+      <c r="BI255">
+        <v>1.46</v>
+      </c>
+      <c r="BJ255">
+        <v>2.48</v>
+      </c>
+      <c r="BK255">
+        <v>1.76</v>
+      </c>
+      <c r="BL255">
+        <v>1.94</v>
+      </c>
+      <c r="BM255">
+        <v>2.18</v>
+      </c>
+      <c r="BN255">
+        <v>1.58</v>
+      </c>
+      <c r="BO255">
+        <v>2.8</v>
+      </c>
+      <c r="BP255">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7465241</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45717.70833333334</v>
+      </c>
+      <c r="F256">
+        <v>26</v>
+      </c>
+      <c r="G256" t="s">
+        <v>87</v>
+      </c>
+      <c r="H256" t="s">
+        <v>70</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>0</v>
+      </c>
+      <c r="L256">
+        <v>1</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
+      </c>
+      <c r="N256">
+        <v>1</v>
+      </c>
+      <c r="O256" t="s">
+        <v>257</v>
+      </c>
+      <c r="P256" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q256">
+        <v>2.75</v>
+      </c>
+      <c r="R256">
+        <v>2.05</v>
+      </c>
+      <c r="S256">
+        <v>4.33</v>
+      </c>
+      <c r="T256">
+        <v>1.44</v>
+      </c>
+      <c r="U256">
+        <v>2.63</v>
+      </c>
+      <c r="V256">
+        <v>3.4</v>
+      </c>
+      <c r="W256">
+        <v>1.3</v>
+      </c>
+      <c r="X256">
+        <v>10</v>
+      </c>
+      <c r="Y256">
+        <v>1.06</v>
+      </c>
+      <c r="Z256">
+        <v>2.05</v>
+      </c>
+      <c r="AA256">
+        <v>3.4</v>
+      </c>
+      <c r="AB256">
+        <v>3.6</v>
+      </c>
+      <c r="AC256">
+        <v>1.07</v>
+      </c>
+      <c r="AD256">
+        <v>9.5</v>
+      </c>
+      <c r="AE256">
+        <v>1.4</v>
+      </c>
+      <c r="AF256">
+        <v>3</v>
+      </c>
+      <c r="AG256">
+        <v>2.1</v>
+      </c>
+      <c r="AH256">
+        <v>1.65</v>
+      </c>
+      <c r="AI256">
+        <v>1.95</v>
+      </c>
+      <c r="AJ256">
+        <v>1.8</v>
+      </c>
+      <c r="AK256">
+        <v>1.28</v>
+      </c>
+      <c r="AL256">
+        <v>1.31</v>
+      </c>
+      <c r="AM256">
+        <v>1.75</v>
+      </c>
+      <c r="AN256">
+        <v>2.38</v>
+      </c>
+      <c r="AO256">
+        <v>1.67</v>
+      </c>
+      <c r="AP256">
+        <v>2.43</v>
+      </c>
+      <c r="AQ256">
+        <v>1.54</v>
+      </c>
+      <c r="AR256">
+        <v>1.71</v>
+      </c>
+      <c r="AS256">
+        <v>1.41</v>
+      </c>
+      <c r="AT256">
+        <v>3.12</v>
+      </c>
+      <c r="AU256">
+        <v>5</v>
+      </c>
+      <c r="AV256">
+        <v>4</v>
+      </c>
+      <c r="AW256">
+        <v>8</v>
+      </c>
+      <c r="AX256">
+        <v>12</v>
+      </c>
+      <c r="AY256">
+        <v>13</v>
+      </c>
+      <c r="AZ256">
+        <v>18</v>
+      </c>
+      <c r="BA256">
+        <v>6</v>
+      </c>
+      <c r="BB256">
+        <v>2</v>
+      </c>
+      <c r="BC256">
+        <v>8</v>
+      </c>
+      <c r="BD256">
+        <v>1.74</v>
+      </c>
+      <c r="BE256">
+        <v>6.4</v>
+      </c>
+      <c r="BF256">
+        <v>2.33</v>
+      </c>
+      <c r="BG256">
+        <v>1.34</v>
+      </c>
+      <c r="BH256">
+        <v>2.9</v>
+      </c>
+      <c r="BI256">
+        <v>1.58</v>
+      </c>
+      <c r="BJ256">
+        <v>2.18</v>
+      </c>
+      <c r="BK256">
+        <v>1.95</v>
+      </c>
+      <c r="BL256">
+        <v>1.74</v>
+      </c>
+      <c r="BM256">
+        <v>2.48</v>
+      </c>
+      <c r="BN256">
+        <v>1.47</v>
+      </c>
+      <c r="BO256">
+        <v>3.3</v>
+      </c>
+      <c r="BP256">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="352">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1431,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP256"/>
+  <dimension ref="A1:BP257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1768,7 +1768,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ2">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ19">
         <v>0.85</v>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ35">
         <v>1.33</v>
@@ -10420,7 +10420,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ44">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -12068,7 +12068,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ52">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12271,7 +12271,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ53">
         <v>1.54</v>
@@ -15364,7 +15364,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ68">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR68">
         <v>1.97</v>
@@ -18245,7 +18245,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ82">
         <v>0.42</v>
@@ -21750,7 +21750,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR99">
         <v>1.66</v>
@@ -23395,7 +23395,7 @@
         <v>0.75</v>
       </c>
       <c r="AP107">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ107">
         <v>0.54</v>
@@ -25870,7 +25870,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -26691,7 +26691,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ123">
         <v>1.08</v>
@@ -29575,7 +29575,7 @@
         <v>1.8</v>
       </c>
       <c r="AP137">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ137">
         <v>1.64</v>
@@ -31226,7 +31226,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ145">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR145">
         <v>1.86</v>
@@ -33489,7 +33489,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ156">
         <v>1.17</v>
@@ -35552,7 +35552,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ166">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR166">
         <v>1.77</v>
@@ -38433,7 +38433,7 @@
         <v>1.75</v>
       </c>
       <c r="AP180">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ180">
         <v>1.85</v>
@@ -40290,7 +40290,7 @@
         <v>1</v>
       </c>
       <c r="AQ189">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -41317,7 +41317,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ194">
         <v>1.83</v>
@@ -44204,7 +44204,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ208">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR208">
         <v>1.41</v>
@@ -45025,7 +45025,7 @@
         <v>1.27</v>
       </c>
       <c r="AP212">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ212">
         <v>1.31</v>
@@ -48118,7 +48118,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ227">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR227">
         <v>1.1</v>
@@ -49148,7 +49148,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ232">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR232">
         <v>1.36</v>
@@ -49351,7 +49351,7 @@
         <v>0.67</v>
       </c>
       <c r="AP233">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ233">
         <v>0.6899999999999999</v>
@@ -54168,6 +54168,212 @@
       </c>
       <c r="BP256">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7465243</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45718.41666666666</v>
+      </c>
+      <c r="F257">
+        <v>26</v>
+      </c>
+      <c r="G257" t="s">
+        <v>85</v>
+      </c>
+      <c r="H257" t="s">
+        <v>83</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>1</v>
+      </c>
+      <c r="O257" t="s">
+        <v>175</v>
+      </c>
+      <c r="P257" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q257">
+        <v>4</v>
+      </c>
+      <c r="R257">
+        <v>1.8</v>
+      </c>
+      <c r="S257">
+        <v>3.6</v>
+      </c>
+      <c r="T257">
+        <v>1.73</v>
+      </c>
+      <c r="U257">
+        <v>2</v>
+      </c>
+      <c r="V257">
+        <v>5</v>
+      </c>
+      <c r="W257">
+        <v>1.17</v>
+      </c>
+      <c r="X257">
+        <v>17</v>
+      </c>
+      <c r="Y257">
+        <v>1.03</v>
+      </c>
+      <c r="Z257">
+        <v>3.2</v>
+      </c>
+      <c r="AA257">
+        <v>2.7</v>
+      </c>
+      <c r="AB257">
+        <v>2.6</v>
+      </c>
+      <c r="AC257">
+        <v>1.17</v>
+      </c>
+      <c r="AD257">
+        <v>5.5</v>
+      </c>
+      <c r="AE257">
+        <v>1.7</v>
+      </c>
+      <c r="AF257">
+        <v>2.05</v>
+      </c>
+      <c r="AG257">
+        <v>3.4</v>
+      </c>
+      <c r="AH257">
+        <v>1.33</v>
+      </c>
+      <c r="AI257">
+        <v>2.5</v>
+      </c>
+      <c r="AJ257">
+        <v>1.5</v>
+      </c>
+      <c r="AK257">
+        <v>1.47</v>
+      </c>
+      <c r="AL257">
+        <v>1.44</v>
+      </c>
+      <c r="AM257">
+        <v>1.33</v>
+      </c>
+      <c r="AN257">
+        <v>1.17</v>
+      </c>
+      <c r="AO257">
+        <v>1.17</v>
+      </c>
+      <c r="AP257">
+        <v>1.31</v>
+      </c>
+      <c r="AQ257">
+        <v>1.08</v>
+      </c>
+      <c r="AR257">
+        <v>0.96</v>
+      </c>
+      <c r="AS257">
+        <v>1.1</v>
+      </c>
+      <c r="AT257">
+        <v>2.06</v>
+      </c>
+      <c r="AU257">
+        <v>-1</v>
+      </c>
+      <c r="AV257">
+        <v>-1</v>
+      </c>
+      <c r="AW257">
+        <v>-1</v>
+      </c>
+      <c r="AX257">
+        <v>-1</v>
+      </c>
+      <c r="AY257">
+        <v>-1</v>
+      </c>
+      <c r="AZ257">
+        <v>-1</v>
+      </c>
+      <c r="BA257">
+        <v>-1</v>
+      </c>
+      <c r="BB257">
+        <v>-1</v>
+      </c>
+      <c r="BC257">
+        <v>-1</v>
+      </c>
+      <c r="BD257">
+        <v>2.14</v>
+      </c>
+      <c r="BE257">
+        <v>6.2</v>
+      </c>
+      <c r="BF257">
+        <v>2.18</v>
+      </c>
+      <c r="BG257">
+        <v>1.49</v>
+      </c>
+      <c r="BH257">
+        <v>2.38</v>
+      </c>
+      <c r="BI257">
+        <v>1.88</v>
+      </c>
+      <c r="BJ257">
+        <v>1.82</v>
+      </c>
+      <c r="BK257">
+        <v>2.48</v>
+      </c>
+      <c r="BL257">
+        <v>1.45</v>
+      </c>
+      <c r="BM257">
+        <v>3.42</v>
+      </c>
+      <c r="BN257">
+        <v>1.23</v>
+      </c>
+      <c r="BO257">
+        <v>4.95</v>
+      </c>
+      <c r="BP257">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -790,6 +790,9 @@
     <t>['66']</t>
   </si>
   <si>
+    <t>['25', '29', '56', '60']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1431,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP257"/>
+  <dimension ref="A1:BP258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1687,7 +1690,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2099,7 +2102,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2305,7 +2308,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2511,7 +2514,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2717,7 +2720,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2923,7 +2926,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3129,7 +3132,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3541,7 +3544,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3953,7 +3956,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4443,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15">
         <v>1.54</v>
@@ -4652,7 +4655,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ16">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5807,7 +5810,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6219,7 +6222,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -7043,7 +7046,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7739,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ31">
         <v>0.23</v>
@@ -8279,7 +8282,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8897,7 +8900,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9103,7 +9106,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9390,7 +9393,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ39">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR39">
         <v>1.12</v>
@@ -9927,7 +9930,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10133,7 +10136,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10545,7 +10548,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10957,7 +10960,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11163,7 +11166,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11862,7 +11865,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ51">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR51">
         <v>1.4</v>
@@ -12193,7 +12196,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12686,7 +12689,7 @@
         <v>1</v>
       </c>
       <c r="AQ55">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -12811,7 +12814,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13841,7 +13844,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14253,7 +14256,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14665,7 +14668,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14871,7 +14874,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15361,7 +15364,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ68">
         <v>1.08</v>
@@ -15489,7 +15492,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15695,7 +15698,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16107,7 +16110,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16931,7 +16934,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17755,7 +17758,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17961,7 +17964,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18991,7 +18994,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19403,7 +19406,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19609,7 +19612,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -20021,7 +20024,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20227,7 +20230,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20639,7 +20642,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20926,7 +20929,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ95">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -21051,7 +21054,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21953,7 +21956,7 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ100">
         <v>1.08</v>
@@ -22081,7 +22084,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22287,7 +22290,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22493,7 +22496,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23111,7 +23114,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23935,7 +23938,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24759,7 +24762,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25249,7 +25252,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ116">
         <v>0.42</v>
@@ -25377,7 +25380,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25458,7 +25461,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ117">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR117">
         <v>1.53</v>
@@ -25583,7 +25586,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25995,7 +25998,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26819,7 +26822,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -28055,7 +28058,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28467,7 +28470,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28879,7 +28882,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29085,7 +29088,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29497,7 +29500,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29784,7 +29787,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ138">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR138">
         <v>1.36</v>
@@ -30115,7 +30118,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30193,7 +30196,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ140">
         <v>0.85</v>
@@ -30733,7 +30736,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30939,7 +30942,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31351,7 +31354,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31969,7 +31972,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32175,7 +32178,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32793,7 +32796,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33205,7 +33208,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33411,7 +33414,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33492,7 +33495,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ156">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR156">
         <v>0.98</v>
@@ -33823,7 +33826,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34029,7 +34032,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -35265,7 +35268,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35677,7 +35680,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36089,7 +36092,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36373,7 +36376,7 @@
         <v>0.63</v>
       </c>
       <c r="AP170">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ170">
         <v>0.77</v>
@@ -36501,7 +36504,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37406,7 +37409,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR175">
         <v>1.41</v>
@@ -37737,7 +37740,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37815,7 +37818,7 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ177">
         <v>1.83</v>
@@ -37943,7 +37946,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38149,7 +38152,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38355,7 +38358,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38973,7 +38976,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39385,7 +39388,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40209,7 +40212,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -41033,7 +41036,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41445,7 +41448,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41857,7 +41860,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42063,7 +42066,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42556,7 +42559,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ200">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR200">
         <v>1.33</v>
@@ -43093,7 +43096,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43299,7 +43302,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43505,7 +43508,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43711,7 +43714,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44123,7 +44126,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44613,7 +44616,7 @@
         <v>0.4</v>
       </c>
       <c r="AP210">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ210">
         <v>0.42</v>
@@ -44947,7 +44950,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -46055,7 +46058,7 @@
         <v>0.73</v>
       </c>
       <c r="AP217">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ217">
         <v>0.6899999999999999</v>
@@ -46470,7 +46473,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ219">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR219">
         <v>1.48</v>
@@ -46595,7 +46598,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47213,7 +47216,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47625,7 +47628,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48655,7 +48658,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49067,7 +49070,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49273,7 +49276,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49479,7 +49482,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50097,7 +50100,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50303,7 +50306,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -50796,7 +50799,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ240">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR240">
         <v>1.7</v>
@@ -50999,7 +51002,7 @@
         <v>1.42</v>
       </c>
       <c r="AP241">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ241">
         <v>1.31</v>
@@ -51333,7 +51336,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51745,7 +51748,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51951,7 +51954,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52157,7 +52160,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52569,7 +52572,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52981,7 +52984,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53187,7 +53190,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53393,7 +53396,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53805,7 +53808,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -54310,31 +54313,31 @@
         <v>2.06</v>
       </c>
       <c r="AU257">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV257">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW257">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX257">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AY257">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AZ257">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA257">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB257">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC257">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD257">
         <v>2.14</v>
@@ -54374,6 +54377,212 @@
       </c>
       <c r="BP257">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7465237</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45718.51041666666</v>
+      </c>
+      <c r="F258">
+        <v>26</v>
+      </c>
+      <c r="G258" t="s">
+        <v>81</v>
+      </c>
+      <c r="H258" t="s">
+        <v>76</v>
+      </c>
+      <c r="I258">
+        <v>2</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>2</v>
+      </c>
+      <c r="L258">
+        <v>4</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>4</v>
+      </c>
+      <c r="O258" t="s">
+        <v>258</v>
+      </c>
+      <c r="P258" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q258">
+        <v>1.67</v>
+      </c>
+      <c r="R258">
+        <v>2.63</v>
+      </c>
+      <c r="S258">
+        <v>9</v>
+      </c>
+      <c r="T258">
+        <v>1.29</v>
+      </c>
+      <c r="U258">
+        <v>3.5</v>
+      </c>
+      <c r="V258">
+        <v>2.38</v>
+      </c>
+      <c r="W258">
+        <v>1.53</v>
+      </c>
+      <c r="X258">
+        <v>5.5</v>
+      </c>
+      <c r="Y258">
+        <v>1.14</v>
+      </c>
+      <c r="Z258">
+        <v>1.25</v>
+      </c>
+      <c r="AA258">
+        <v>5.5</v>
+      </c>
+      <c r="AB258">
+        <v>11</v>
+      </c>
+      <c r="AC258">
+        <v>1.03</v>
+      </c>
+      <c r="AD258">
+        <v>15</v>
+      </c>
+      <c r="AE258">
+        <v>1.19</v>
+      </c>
+      <c r="AF258">
+        <v>4.75</v>
+      </c>
+      <c r="AG258">
+        <v>1.57</v>
+      </c>
+      <c r="AH258">
+        <v>2.38</v>
+      </c>
+      <c r="AI258">
+        <v>2.05</v>
+      </c>
+      <c r="AJ258">
+        <v>1.7</v>
+      </c>
+      <c r="AK258">
+        <v>1.01</v>
+      </c>
+      <c r="AL258">
+        <v>1.12</v>
+      </c>
+      <c r="AM258">
+        <v>3.75</v>
+      </c>
+      <c r="AN258">
+        <v>2.18</v>
+      </c>
+      <c r="AO258">
+        <v>1.17</v>
+      </c>
+      <c r="AP258">
+        <v>2.25</v>
+      </c>
+      <c r="AQ258">
+        <v>1.08</v>
+      </c>
+      <c r="AR258">
+        <v>2</v>
+      </c>
+      <c r="AS258">
+        <v>1.08</v>
+      </c>
+      <c r="AT258">
+        <v>3.08</v>
+      </c>
+      <c r="AU258">
+        <v>11</v>
+      </c>
+      <c r="AV258">
+        <v>0</v>
+      </c>
+      <c r="AW258">
+        <v>23</v>
+      </c>
+      <c r="AX258">
+        <v>0</v>
+      </c>
+      <c r="AY258">
+        <v>44</v>
+      </c>
+      <c r="AZ258">
+        <v>0</v>
+      </c>
+      <c r="BA258">
+        <v>12</v>
+      </c>
+      <c r="BB258">
+        <v>0</v>
+      </c>
+      <c r="BC258">
+        <v>12</v>
+      </c>
+      <c r="BD258">
+        <v>1.19</v>
+      </c>
+      <c r="BE258">
+        <v>9</v>
+      </c>
+      <c r="BF258">
+        <v>4.9</v>
+      </c>
+      <c r="BG258">
+        <v>1.26</v>
+      </c>
+      <c r="BH258">
+        <v>3.4</v>
+      </c>
+      <c r="BI258">
+        <v>1.46</v>
+      </c>
+      <c r="BJ258">
+        <v>2.5</v>
+      </c>
+      <c r="BK258">
+        <v>1.72</v>
+      </c>
+      <c r="BL258">
+        <v>1.98</v>
+      </c>
+      <c r="BM258">
+        <v>2.12</v>
+      </c>
+      <c r="BN258">
+        <v>1.63</v>
+      </c>
+      <c r="BO258">
+        <v>2.65</v>
+      </c>
+      <c r="BP258">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="355">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,9 @@
     <t>['25', '29', '56', '60']</t>
   </si>
   <si>
+    <t>['26', '39', '45']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1073,6 +1076,9 @@
   </si>
   <si>
     <t>['36', '51']</t>
+  </si>
+  <si>
+    <t>['14', '32', '87']</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP258"/>
+  <dimension ref="A1:BP260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1690,7 +1696,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2102,7 +2108,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2183,7 +2189,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2308,7 +2314,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2514,7 +2520,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2592,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ6">
         <v>0.77</v>
@@ -2720,7 +2726,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2926,7 +2932,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3132,7 +3138,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3210,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ9">
         <v>1.64</v>
@@ -3544,7 +3550,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3831,7 +3837,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR12">
         <v>1.07</v>
@@ -3956,7 +3962,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4240,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ14">
         <v>1.33</v>
@@ -5810,7 +5816,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6094,7 +6100,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ23">
         <v>1.08</v>
@@ -6222,7 +6228,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6509,7 +6515,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ25">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR25">
         <v>0.96</v>
@@ -7046,7 +7052,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7127,7 +7133,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ28">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -8282,7 +8288,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8900,7 +8906,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -8978,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ37">
         <v>0.54</v>
@@ -9106,7 +9112,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9930,7 +9936,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10008,7 +10014,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ42">
         <v>1.85</v>
@@ -10136,7 +10142,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10217,7 +10223,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ43">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR43">
         <v>1.17</v>
@@ -10548,7 +10554,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10960,7 +10966,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11166,7 +11172,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11453,7 +11459,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ49">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR49">
         <v>1.74</v>
@@ -11862,7 +11868,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ51">
         <v>1.08</v>
@@ -12196,7 +12202,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12814,7 +12820,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12892,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ56">
         <v>0.85</v>
@@ -13844,7 +13850,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14256,7 +14262,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14668,7 +14674,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14874,7 +14880,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14955,7 +14961,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ66">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR66">
         <v>2.43</v>
@@ -15492,7 +15498,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15698,7 +15704,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16110,7 +16116,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16397,7 +16403,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ73">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16809,7 +16815,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ75">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR75">
         <v>1.11</v>
@@ -16934,7 +16940,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17012,7 +17018,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ76">
         <v>2.14</v>
@@ -17758,7 +17764,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17964,7 +17970,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18251,7 +18257,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ82">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR82">
         <v>1.25</v>
@@ -18994,7 +19000,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19406,7 +19412,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19612,7 +19618,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -20024,7 +20030,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20230,7 +20236,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20642,7 +20648,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20720,7 +20726,7 @@
         <v>0.5</v>
       </c>
       <c r="AP94">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ94">
         <v>1.15</v>
@@ -21054,7 +21060,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21338,7 +21344,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ97">
         <v>1.31</v>
@@ -22084,7 +22090,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22290,7 +22296,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22496,7 +22502,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22783,7 +22789,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ104">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR104">
         <v>1.49</v>
@@ -23114,7 +23120,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23607,7 +23613,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -23938,7 +23944,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24222,7 +24228,7 @@
         <v>1.5</v>
       </c>
       <c r="AP111">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ111">
         <v>1.54</v>
@@ -24634,7 +24640,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ113">
         <v>0.23</v>
@@ -24762,7 +24768,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25380,7 +25386,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25586,7 +25592,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25998,7 +26004,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26491,7 +26497,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ122">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR122">
         <v>1.57</v>
@@ -26822,7 +26828,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27106,7 +27112,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ125">
         <v>1.83</v>
@@ -28058,7 +28064,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28345,7 +28351,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ131">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28470,7 +28476,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28882,7 +28888,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29088,7 +29094,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29166,7 +29172,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ135">
         <v>1.85</v>
@@ -29500,7 +29506,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29990,10 +29996,10 @@
         <v>0.33</v>
       </c>
       <c r="AP139">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ139">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR139">
         <v>1.33</v>
@@ -30118,7 +30124,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30736,7 +30742,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30942,7 +30948,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31354,7 +31360,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31972,7 +31978,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32050,7 +32056,7 @@
         <v>2.11</v>
       </c>
       <c r="AP149">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ149">
         <v>2.14</v>
@@ -32178,7 +32184,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32796,7 +32802,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33208,7 +33214,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33414,7 +33420,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33826,7 +33832,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33904,10 +33910,10 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ158">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR158">
         <v>1.47</v>
@@ -34032,7 +34038,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34525,7 +34531,7 @@
         <v>1</v>
       </c>
       <c r="AQ161">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR161">
         <v>1.1</v>
@@ -34934,7 +34940,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ163">
         <v>0.92</v>
@@ -35268,7 +35274,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35680,7 +35686,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36092,7 +36098,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36504,7 +36510,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36585,7 +36591,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ171">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR171">
         <v>1.12</v>
@@ -37612,7 +37618,7 @@
         <v>1.5</v>
       </c>
       <c r="AP176">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ176">
         <v>1.54</v>
@@ -37740,7 +37746,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37946,7 +37952,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38027,7 +38033,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ178">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR178">
         <v>1.38</v>
@@ -38152,7 +38158,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38358,7 +38364,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38976,7 +38982,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39388,7 +39394,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40087,7 +40093,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ188">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR188">
         <v>1.34</v>
@@ -40212,7 +40218,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -41036,7 +41042,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41448,7 +41454,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41529,7 +41535,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ195">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR195">
         <v>1.78</v>
@@ -41860,7 +41866,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42066,7 +42072,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42350,7 +42356,7 @@
         <v>1.3</v>
       </c>
       <c r="AP199">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ199">
         <v>1.31</v>
@@ -43096,7 +43102,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43174,7 +43180,7 @@
         <v>0.9</v>
       </c>
       <c r="AP203">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ203">
         <v>1.15</v>
@@ -43302,7 +43308,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43508,7 +43514,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43714,7 +43720,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44126,7 +44132,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44619,7 +44625,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ210">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR210">
         <v>2.02</v>
@@ -44950,7 +44956,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -46061,7 +46067,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ217">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR217">
         <v>2.09</v>
@@ -46470,7 +46476,7 @@
         <v>1.4</v>
       </c>
       <c r="AP219">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ219">
         <v>1.08</v>
@@ -46598,7 +46604,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47216,7 +47222,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47628,7 +47634,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48658,7 +48664,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -48942,7 +48948,7 @@
         <v>0.8</v>
       </c>
       <c r="AP231">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ231">
         <v>0.75</v>
@@ -49070,7 +49076,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49276,7 +49282,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49357,7 +49363,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ233">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR233">
         <v>0.95</v>
@@ -49482,7 +49488,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -49560,7 +49566,7 @@
         <v>1.83</v>
       </c>
       <c r="AP234">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ234">
         <v>1.64</v>
@@ -49975,7 +49981,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ236">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR236">
         <v>1.64</v>
@@ -50100,7 +50106,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50306,7 +50312,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -50590,7 +50596,7 @@
         <v>0.91</v>
       </c>
       <c r="AP239">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ239">
         <v>0.85</v>
@@ -51336,7 +51342,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51748,7 +51754,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51954,7 +51960,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52160,7 +52166,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52572,7 +52578,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52984,7 +52990,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53190,7 +53196,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53396,7 +53402,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53808,7 +53814,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -54583,6 +54589,418 @@
       </c>
       <c r="BP258">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7465245</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45718.60416666666</v>
+      </c>
+      <c r="F259">
+        <v>26</v>
+      </c>
+      <c r="G259" t="s">
+        <v>77</v>
+      </c>
+      <c r="H259" t="s">
+        <v>86</v>
+      </c>
+      <c r="I259">
+        <v>1</v>
+      </c>
+      <c r="J259">
+        <v>0</v>
+      </c>
+      <c r="K259">
+        <v>1</v>
+      </c>
+      <c r="L259">
+        <v>1</v>
+      </c>
+      <c r="M259">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>2</v>
+      </c>
+      <c r="O259" t="s">
+        <v>109</v>
+      </c>
+      <c r="P259" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q259">
+        <v>3.1</v>
+      </c>
+      <c r="R259">
+        <v>1.83</v>
+      </c>
+      <c r="S259">
+        <v>4.5</v>
+      </c>
+      <c r="T259">
+        <v>1.62</v>
+      </c>
+      <c r="U259">
+        <v>2.2</v>
+      </c>
+      <c r="V259">
+        <v>4</v>
+      </c>
+      <c r="W259">
+        <v>1.22</v>
+      </c>
+      <c r="X259">
+        <v>13</v>
+      </c>
+      <c r="Y259">
+        <v>1.04</v>
+      </c>
+      <c r="Z259">
+        <v>2.2</v>
+      </c>
+      <c r="AA259">
+        <v>3.1</v>
+      </c>
+      <c r="AB259">
+        <v>3.6</v>
+      </c>
+      <c r="AC259">
+        <v>1.12</v>
+      </c>
+      <c r="AD259">
+        <v>7</v>
+      </c>
+      <c r="AE259">
+        <v>1.55</v>
+      </c>
+      <c r="AF259">
+        <v>2.3</v>
+      </c>
+      <c r="AG259">
+        <v>2.75</v>
+      </c>
+      <c r="AH259">
+        <v>1.44</v>
+      </c>
+      <c r="AI259">
+        <v>2.25</v>
+      </c>
+      <c r="AJ259">
+        <v>1.57</v>
+      </c>
+      <c r="AK259">
+        <v>1.28</v>
+      </c>
+      <c r="AL259">
+        <v>1.36</v>
+      </c>
+      <c r="AM259">
+        <v>1.65</v>
+      </c>
+      <c r="AN259">
+        <v>1.46</v>
+      </c>
+      <c r="AO259">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP259">
+        <v>1.43</v>
+      </c>
+      <c r="AQ259">
+        <v>0.71</v>
+      </c>
+      <c r="AR259">
+        <v>1.28</v>
+      </c>
+      <c r="AS259">
+        <v>1.18</v>
+      </c>
+      <c r="AT259">
+        <v>2.46</v>
+      </c>
+      <c r="AU259">
+        <v>5</v>
+      </c>
+      <c r="AV259">
+        <v>7</v>
+      </c>
+      <c r="AW259">
+        <v>11</v>
+      </c>
+      <c r="AX259">
+        <v>12</v>
+      </c>
+      <c r="AY259">
+        <v>18</v>
+      </c>
+      <c r="AZ259">
+        <v>23</v>
+      </c>
+      <c r="BA259">
+        <v>3</v>
+      </c>
+      <c r="BB259">
+        <v>9</v>
+      </c>
+      <c r="BC259">
+        <v>12</v>
+      </c>
+      <c r="BD259">
+        <v>1.79</v>
+      </c>
+      <c r="BE259">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF259">
+        <v>2.46</v>
+      </c>
+      <c r="BG259">
+        <v>1.39</v>
+      </c>
+      <c r="BH259">
+        <v>2.67</v>
+      </c>
+      <c r="BI259">
+        <v>1.73</v>
+      </c>
+      <c r="BJ259">
+        <v>1.99</v>
+      </c>
+      <c r="BK259">
+        <v>2.21</v>
+      </c>
+      <c r="BL259">
+        <v>1.56</v>
+      </c>
+      <c r="BM259">
+        <v>2.92</v>
+      </c>
+      <c r="BN259">
+        <v>1.31</v>
+      </c>
+      <c r="BO259">
+        <v>4.2</v>
+      </c>
+      <c r="BP259">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7465239</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45718.70833333334</v>
+      </c>
+      <c r="F260">
+        <v>26</v>
+      </c>
+      <c r="G260" t="s">
+        <v>74</v>
+      </c>
+      <c r="H260" t="s">
+        <v>75</v>
+      </c>
+      <c r="I260">
+        <v>3</v>
+      </c>
+      <c r="J260">
+        <v>2</v>
+      </c>
+      <c r="K260">
+        <v>5</v>
+      </c>
+      <c r="L260">
+        <v>3</v>
+      </c>
+      <c r="M260">
+        <v>3</v>
+      </c>
+      <c r="N260">
+        <v>6</v>
+      </c>
+      <c r="O260" t="s">
+        <v>259</v>
+      </c>
+      <c r="P260" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q260">
+        <v>3.1</v>
+      </c>
+      <c r="R260">
+        <v>2</v>
+      </c>
+      <c r="S260">
+        <v>4</v>
+      </c>
+      <c r="T260">
+        <v>1.5</v>
+      </c>
+      <c r="U260">
+        <v>2.5</v>
+      </c>
+      <c r="V260">
+        <v>3.5</v>
+      </c>
+      <c r="W260">
+        <v>1.29</v>
+      </c>
+      <c r="X260">
+        <v>11</v>
+      </c>
+      <c r="Y260">
+        <v>1.05</v>
+      </c>
+      <c r="Z260">
+        <v>2.25</v>
+      </c>
+      <c r="AA260">
+        <v>3.1</v>
+      </c>
+      <c r="AB260">
+        <v>3.3</v>
+      </c>
+      <c r="AC260">
+        <v>1.09</v>
+      </c>
+      <c r="AD260">
+        <v>8</v>
+      </c>
+      <c r="AE260">
+        <v>1.45</v>
+      </c>
+      <c r="AF260">
+        <v>2.8</v>
+      </c>
+      <c r="AG260">
+        <v>2.3</v>
+      </c>
+      <c r="AH260">
+        <v>1.55</v>
+      </c>
+      <c r="AI260">
+        <v>2</v>
+      </c>
+      <c r="AJ260">
+        <v>1.75</v>
+      </c>
+      <c r="AK260">
+        <v>1.31</v>
+      </c>
+      <c r="AL260">
+        <v>1.35</v>
+      </c>
+      <c r="AM260">
+        <v>1.61</v>
+      </c>
+      <c r="AN260">
+        <v>1.77</v>
+      </c>
+      <c r="AO260">
+        <v>0.42</v>
+      </c>
+      <c r="AP260">
+        <v>1.71</v>
+      </c>
+      <c r="AQ260">
+        <v>0.46</v>
+      </c>
+      <c r="AR260">
+        <v>1.48</v>
+      </c>
+      <c r="AS260">
+        <v>0.97</v>
+      </c>
+      <c r="AT260">
+        <v>2.45</v>
+      </c>
+      <c r="AU260">
+        <v>-1</v>
+      </c>
+      <c r="AV260">
+        <v>-1</v>
+      </c>
+      <c r="AW260">
+        <v>-1</v>
+      </c>
+      <c r="AX260">
+        <v>-1</v>
+      </c>
+      <c r="AY260">
+        <v>-1</v>
+      </c>
+      <c r="AZ260">
+        <v>-1</v>
+      </c>
+      <c r="BA260">
+        <v>-1</v>
+      </c>
+      <c r="BB260">
+        <v>-1</v>
+      </c>
+      <c r="BC260">
+        <v>-1</v>
+      </c>
+      <c r="BD260">
+        <v>1.68</v>
+      </c>
+      <c r="BE260">
+        <v>8.6</v>
+      </c>
+      <c r="BF260">
+        <v>2.66</v>
+      </c>
+      <c r="BG260">
+        <v>1.27</v>
+      </c>
+      <c r="BH260">
+        <v>3.14</v>
+      </c>
+      <c r="BI260">
+        <v>1.53</v>
+      </c>
+      <c r="BJ260">
+        <v>2.28</v>
+      </c>
+      <c r="BK260">
+        <v>1.93</v>
+      </c>
+      <c r="BL260">
+        <v>1.78</v>
+      </c>
+      <c r="BM260">
+        <v>2.51</v>
+      </c>
+      <c r="BN260">
+        <v>1.44</v>
+      </c>
+      <c r="BO260">
+        <v>3.34</v>
+      </c>
+      <c r="BP260">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -54937,31 +54937,31 @@
         <v>2.45</v>
       </c>
       <c r="AU260">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV260">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW260">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX260">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY260">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AZ260">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA260">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB260">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC260">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD260">
         <v>1.68</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="359">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -796,6 +796,15 @@
     <t>['26', '39', '45']</t>
   </si>
   <si>
+    <t>['26', '45+1']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['7', '58']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1079,6 +1088,9 @@
   </si>
   <si>
     <t>['14', '32', '87']</t>
+  </si>
+  <si>
+    <t>['40']</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP260"/>
+  <dimension ref="A1:BP263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1696,7 +1708,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2108,7 +2120,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2186,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ4">
         <v>0.71</v>
@@ -2314,7 +2326,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2520,7 +2532,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2601,7 +2613,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ6">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2726,7 +2738,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2804,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>2.14</v>
@@ -2932,7 +2944,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3138,7 +3150,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3550,7 +3562,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3834,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ12">
         <v>0.46</v>
@@ -3962,7 +3974,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4043,7 +4055,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ13">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5073,7 +5085,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ18">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5482,7 +5494,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ20">
         <v>1.15</v>
@@ -5816,7 +5828,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6228,7 +6240,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6721,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -7052,7 +7064,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7751,7 +7763,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ31">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR31">
         <v>1.51</v>
@@ -8288,7 +8300,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8366,10 +8378,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR34">
         <v>0.87</v>
@@ -8778,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ36">
         <v>0.85</v>
@@ -8906,7 +8918,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9112,7 +9124,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9811,7 +9823,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ41">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR41">
         <v>1.59</v>
@@ -9936,7 +9948,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10017,7 +10029,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ42">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR42">
         <v>1.48</v>
@@ -10142,7 +10154,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10554,7 +10566,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10838,10 +10850,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ46">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR46">
         <v>1.11</v>
@@ -10966,7 +10978,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11172,7 +11184,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12202,7 +12214,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12486,7 +12498,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ54">
         <v>1.08</v>
@@ -12820,7 +12832,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13104,7 +13116,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57">
         <v>0.92</v>
@@ -13519,7 +13531,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ59">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR59">
         <v>1.14</v>
@@ -13850,7 +13862,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14262,7 +14274,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14546,7 +14558,7 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
         <v>0.75</v>
@@ -14674,7 +14686,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14755,7 +14767,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ65">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14880,7 +14892,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15498,7 +15510,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15579,7 +15591,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ69">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR69">
         <v>1.13</v>
@@ -15704,7 +15716,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15988,7 +16000,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ71">
         <v>1.83</v>
@@ -16116,7 +16128,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16609,7 +16621,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR74">
         <v>1.48</v>
@@ -16940,7 +16952,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17224,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ77">
         <v>0.92</v>
@@ -17764,7 +17776,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17970,7 +17982,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -19000,7 +19012,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19287,7 +19299,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ87">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR87">
         <v>2.14</v>
@@ -19412,7 +19424,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19618,7 +19630,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19696,7 +19708,7 @@
         <v>2.4</v>
       </c>
       <c r="AP89">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ89">
         <v>2.14</v>
@@ -20030,7 +20042,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20236,7 +20248,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20314,10 +20326,10 @@
         <v>0</v>
       </c>
       <c r="AP92">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ92">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR92">
         <v>1.06</v>
@@ -20648,7 +20660,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21060,7 +21072,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21138,7 +21150,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ96">
         <v>1.64</v>
@@ -21553,7 +21565,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ98">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR98">
         <v>1.58</v>
@@ -22090,7 +22102,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22168,7 +22180,7 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101">
         <v>0.85</v>
@@ -22296,7 +22308,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22502,7 +22514,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22583,7 +22595,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR103">
         <v>1.21</v>
@@ -23120,7 +23132,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23944,7 +23956,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24434,7 +24446,7 @@
         <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ112">
         <v>1.33</v>
@@ -24643,7 +24655,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ113">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24768,7 +24780,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24849,7 +24861,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ114">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR114">
         <v>1.33</v>
@@ -25386,7 +25398,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25592,7 +25604,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25876,7 +25888,7 @@
         <v>0.4</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ119">
         <v>1.08</v>
@@ -26004,7 +26016,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26828,7 +26840,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27939,7 +27951,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ129">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR129">
         <v>1.27</v>
@@ -28064,7 +28076,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28142,7 +28154,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ130">
         <v>1.15</v>
@@ -28476,7 +28488,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28888,7 +28900,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -28966,7 +28978,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ134">
         <v>2.14</v>
@@ -29094,7 +29106,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29175,7 +29187,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ135">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -29506,7 +29518,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -30124,7 +30136,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30408,10 +30420,10 @@
         <v>0.57</v>
       </c>
       <c r="AP141">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ141">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR141">
         <v>1.08</v>
@@ -30742,7 +30754,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30948,7 +30960,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31360,7 +31372,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31978,7 +31990,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32184,7 +32196,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32468,7 +32480,7 @@
         <v>1.71</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ151">
         <v>1.33</v>
@@ -32677,7 +32689,7 @@
         <v>1</v>
       </c>
       <c r="AQ152">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR152">
         <v>1.35</v>
@@ -32802,7 +32814,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33086,7 +33098,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154">
         <v>1.31</v>
@@ -33214,7 +33226,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33420,7 +33432,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33707,7 +33719,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ157">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -33832,7 +33844,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34038,7 +34050,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -35274,7 +35286,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35686,7 +35698,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35764,7 +35776,7 @@
         <v>1.57</v>
       </c>
       <c r="AP167">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ167">
         <v>1.54</v>
@@ -36098,7 +36110,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36385,7 +36397,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ170">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR170">
         <v>1.98</v>
@@ -36510,7 +36522,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37003,7 +37015,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ173">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR173">
         <v>1.37</v>
@@ -37412,7 +37424,7 @@
         <v>1.75</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ175">
         <v>1.08</v>
@@ -37746,7 +37758,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37952,7 +37964,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38030,7 +38042,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ178">
         <v>0.71</v>
@@ -38158,7 +38170,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38364,7 +38376,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38445,7 +38457,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ180">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR180">
         <v>0.99</v>
@@ -38982,7 +38994,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39060,7 +39072,7 @@
         <v>1.78</v>
       </c>
       <c r="AP183">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ183">
         <v>1.64</v>
@@ -39394,7 +39406,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39472,7 +39484,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ185">
         <v>0.92</v>
@@ -39887,7 +39899,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ187">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR187">
         <v>1.12</v>
@@ -40218,7 +40230,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40711,7 +40723,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ191">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR191">
         <v>1.44</v>
@@ -40917,7 +40929,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ192">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR192">
         <v>1.16</v>
@@ -41042,7 +41054,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41454,7 +41466,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41866,7 +41878,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41944,7 +41956,7 @@
         <v>1.67</v>
       </c>
       <c r="AP197">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ197">
         <v>1.54</v>
@@ -42072,7 +42084,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42562,7 +42574,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ200">
         <v>1.08</v>
@@ -43102,7 +43114,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43308,7 +43320,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43389,7 +43401,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ204">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR204">
         <v>1.67</v>
@@ -43514,7 +43526,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43720,7 +43732,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44132,7 +44144,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44419,7 +44431,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ209">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR209">
         <v>1.31</v>
@@ -44828,7 +44840,7 @@
         <v>0.44</v>
       </c>
       <c r="AP211">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ211">
         <v>0.54</v>
@@ -44956,7 +44968,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45449,7 +45461,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ214">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR214">
         <v>1.55</v>
@@ -46270,7 +46282,7 @@
         <v>0.5</v>
       </c>
       <c r="AP218">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ218">
         <v>0.54</v>
@@ -46604,7 +46616,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47097,7 +47109,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ222">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR222">
         <v>1.62</v>
@@ -47222,7 +47234,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47300,7 +47312,7 @@
         <v>1.09</v>
       </c>
       <c r="AP223">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ223">
         <v>1.15</v>
@@ -47634,7 +47646,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -47715,7 +47727,7 @@
         <v>1</v>
       </c>
       <c r="AQ225">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR225">
         <v>1.41</v>
@@ -48124,7 +48136,7 @@
         <v>0.8</v>
       </c>
       <c r="AP227">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ227">
         <v>1.08</v>
@@ -48330,10 +48342,10 @@
         <v>0.91</v>
       </c>
       <c r="AP228">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ228">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR228">
         <v>1.3</v>
@@ -48664,7 +48676,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49076,7 +49088,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49282,7 +49294,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49488,7 +49500,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50106,7 +50118,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50312,7 +50324,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -51214,7 +51226,7 @@
         <v>0.82</v>
       </c>
       <c r="AP242">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ242">
         <v>0.75</v>
@@ -51342,7 +51354,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51420,7 +51432,7 @@
         <v>0.18</v>
       </c>
       <c r="AP243">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ243">
         <v>0.42</v>
@@ -51629,7 +51641,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ244">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR244">
         <v>1.68</v>
@@ -51754,7 +51766,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51832,7 +51844,7 @@
         <v>1.73</v>
       </c>
       <c r="AP245">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ245">
         <v>1.83</v>
@@ -51960,7 +51972,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52166,7 +52178,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52247,7 +52259,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ247">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52578,7 +52590,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52865,7 +52877,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ250">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR250">
         <v>1.44</v>
@@ -52990,7 +53002,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53196,7 +53208,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53402,7 +53414,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53814,7 +53826,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -54844,7 +54856,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55001,6 +55013,624 @@
       </c>
       <c r="BP260">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7465249</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45724.41666666666</v>
+      </c>
+      <c r="F261">
+        <v>27</v>
+      </c>
+      <c r="G261" t="s">
+        <v>72</v>
+      </c>
+      <c r="H261" t="s">
+        <v>85</v>
+      </c>
+      <c r="I261">
+        <v>2</v>
+      </c>
+      <c r="J261">
+        <v>1</v>
+      </c>
+      <c r="K261">
+        <v>3</v>
+      </c>
+      <c r="L261">
+        <v>2</v>
+      </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
+      <c r="N261">
+        <v>3</v>
+      </c>
+      <c r="O261" t="s">
+        <v>260</v>
+      </c>
+      <c r="P261" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q261">
+        <v>2.2</v>
+      </c>
+      <c r="R261">
+        <v>2.2</v>
+      </c>
+      <c r="S261">
+        <v>6</v>
+      </c>
+      <c r="T261">
+        <v>1.44</v>
+      </c>
+      <c r="U261">
+        <v>2.63</v>
+      </c>
+      <c r="V261">
+        <v>3</v>
+      </c>
+      <c r="W261">
+        <v>1.36</v>
+      </c>
+      <c r="X261">
+        <v>9</v>
+      </c>
+      <c r="Y261">
+        <v>1.07</v>
+      </c>
+      <c r="Z261">
+        <v>1.57</v>
+      </c>
+      <c r="AA261">
+        <v>3.8</v>
+      </c>
+      <c r="AB261">
+        <v>6</v>
+      </c>
+      <c r="AC261">
+        <v>1.05</v>
+      </c>
+      <c r="AD261">
+        <v>10</v>
+      </c>
+      <c r="AE261">
+        <v>1.33</v>
+      </c>
+      <c r="AF261">
+        <v>3.4</v>
+      </c>
+      <c r="AG261">
+        <v>2</v>
+      </c>
+      <c r="AH261">
+        <v>1.8</v>
+      </c>
+      <c r="AI261">
+        <v>2.05</v>
+      </c>
+      <c r="AJ261">
+        <v>1.7</v>
+      </c>
+      <c r="AK261">
+        <v>1.13</v>
+      </c>
+      <c r="AL261">
+        <v>1.24</v>
+      </c>
+      <c r="AM261">
+        <v>2.35</v>
+      </c>
+      <c r="AN261">
+        <v>2</v>
+      </c>
+      <c r="AO261">
+        <v>0.77</v>
+      </c>
+      <c r="AP261">
+        <v>2.07</v>
+      </c>
+      <c r="AQ261">
+        <v>0.71</v>
+      </c>
+      <c r="AR261">
+        <v>1.39</v>
+      </c>
+      <c r="AS261">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT261">
+        <v>2.33</v>
+      </c>
+      <c r="AU261">
+        <v>5</v>
+      </c>
+      <c r="AV261">
+        <v>7</v>
+      </c>
+      <c r="AW261">
+        <v>3</v>
+      </c>
+      <c r="AX261">
+        <v>6</v>
+      </c>
+      <c r="AY261">
+        <v>9</v>
+      </c>
+      <c r="AZ261">
+        <v>14</v>
+      </c>
+      <c r="BA261">
+        <v>2</v>
+      </c>
+      <c r="BB261">
+        <v>5</v>
+      </c>
+      <c r="BC261">
+        <v>7</v>
+      </c>
+      <c r="BD261">
+        <v>1.37</v>
+      </c>
+      <c r="BE261">
+        <v>7</v>
+      </c>
+      <c r="BF261">
+        <v>3.45</v>
+      </c>
+      <c r="BG261">
+        <v>1.41</v>
+      </c>
+      <c r="BH261">
+        <v>2.65</v>
+      </c>
+      <c r="BI261">
+        <v>1.7</v>
+      </c>
+      <c r="BJ261">
+        <v>2.02</v>
+      </c>
+      <c r="BK261">
+        <v>2.1</v>
+      </c>
+      <c r="BL261">
+        <v>1.64</v>
+      </c>
+      <c r="BM261">
+        <v>2.7</v>
+      </c>
+      <c r="BN261">
+        <v>1.4</v>
+      </c>
+      <c r="BO261">
+        <v>3.55</v>
+      </c>
+      <c r="BP261">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7465252</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45724.51041666666</v>
+      </c>
+      <c r="F262">
+        <v>27</v>
+      </c>
+      <c r="G262" t="s">
+        <v>86</v>
+      </c>
+      <c r="H262" t="s">
+        <v>79</v>
+      </c>
+      <c r="I262">
+        <v>1</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>1</v>
+      </c>
+      <c r="L262">
+        <v>1</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>1</v>
+      </c>
+      <c r="O262" t="s">
+        <v>261</v>
+      </c>
+      <c r="P262" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q262">
+        <v>3.6</v>
+      </c>
+      <c r="R262">
+        <v>2.1</v>
+      </c>
+      <c r="S262">
+        <v>3.1</v>
+      </c>
+      <c r="T262">
+        <v>1.44</v>
+      </c>
+      <c r="U262">
+        <v>2.63</v>
+      </c>
+      <c r="V262">
+        <v>3.25</v>
+      </c>
+      <c r="W262">
+        <v>1.33</v>
+      </c>
+      <c r="X262">
+        <v>9</v>
+      </c>
+      <c r="Y262">
+        <v>1.07</v>
+      </c>
+      <c r="Z262">
+        <v>3.1</v>
+      </c>
+      <c r="AA262">
+        <v>3.2</v>
+      </c>
+      <c r="AB262">
+        <v>2.38</v>
+      </c>
+      <c r="AC262">
+        <v>1.07</v>
+      </c>
+      <c r="AD262">
+        <v>9.5</v>
+      </c>
+      <c r="AE262">
+        <v>1.36</v>
+      </c>
+      <c r="AF262">
+        <v>3.2</v>
+      </c>
+      <c r="AG262">
+        <v>2.1</v>
+      </c>
+      <c r="AH262">
+        <v>1.73</v>
+      </c>
+      <c r="AI262">
+        <v>1.8</v>
+      </c>
+      <c r="AJ262">
+        <v>1.95</v>
+      </c>
+      <c r="AK262">
+        <v>1.55</v>
+      </c>
+      <c r="AL262">
+        <v>1.32</v>
+      </c>
+      <c r="AM262">
+        <v>1.37</v>
+      </c>
+      <c r="AN262">
+        <v>1.08</v>
+      </c>
+      <c r="AO262">
+        <v>1.85</v>
+      </c>
+      <c r="AP262">
+        <v>1.23</v>
+      </c>
+      <c r="AQ262">
+        <v>1.71</v>
+      </c>
+      <c r="AR262">
+        <v>1.2</v>
+      </c>
+      <c r="AS262">
+        <v>1.48</v>
+      </c>
+      <c r="AT262">
+        <v>2.68</v>
+      </c>
+      <c r="AU262">
+        <v>4</v>
+      </c>
+      <c r="AV262">
+        <v>3</v>
+      </c>
+      <c r="AW262">
+        <v>2</v>
+      </c>
+      <c r="AX262">
+        <v>21</v>
+      </c>
+      <c r="AY262">
+        <v>7</v>
+      </c>
+      <c r="AZ262">
+        <v>26</v>
+      </c>
+      <c r="BA262">
+        <v>1</v>
+      </c>
+      <c r="BB262">
+        <v>6</v>
+      </c>
+      <c r="BC262">
+        <v>7</v>
+      </c>
+      <c r="BD262">
+        <v>1.86</v>
+      </c>
+      <c r="BE262">
+        <v>6.4</v>
+      </c>
+      <c r="BF262">
+        <v>2.15</v>
+      </c>
+      <c r="BG262">
+        <v>1.4</v>
+      </c>
+      <c r="BH262">
+        <v>2.65</v>
+      </c>
+      <c r="BI262">
+        <v>1.68</v>
+      </c>
+      <c r="BJ262">
+        <v>2.02</v>
+      </c>
+      <c r="BK262">
+        <v>2.1</v>
+      </c>
+      <c r="BL262">
+        <v>1.64</v>
+      </c>
+      <c r="BM262">
+        <v>2.7</v>
+      </c>
+      <c r="BN262">
+        <v>1.38</v>
+      </c>
+      <c r="BO262">
+        <v>3.55</v>
+      </c>
+      <c r="BP262">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7465251</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45724.60416666666</v>
+      </c>
+      <c r="F263">
+        <v>27</v>
+      </c>
+      <c r="G263" t="s">
+        <v>75</v>
+      </c>
+      <c r="H263" t="s">
+        <v>78</v>
+      </c>
+      <c r="I263">
+        <v>1</v>
+      </c>
+      <c r="J263">
+        <v>1</v>
+      </c>
+      <c r="K263">
+        <v>2</v>
+      </c>
+      <c r="L263">
+        <v>2</v>
+      </c>
+      <c r="M263">
+        <v>1</v>
+      </c>
+      <c r="N263">
+        <v>3</v>
+      </c>
+      <c r="O263" t="s">
+        <v>262</v>
+      </c>
+      <c r="P263" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q263">
+        <v>1.95</v>
+      </c>
+      <c r="R263">
+        <v>2.25</v>
+      </c>
+      <c r="S263">
+        <v>9</v>
+      </c>
+      <c r="T263">
+        <v>1.44</v>
+      </c>
+      <c r="U263">
+        <v>2.63</v>
+      </c>
+      <c r="V263">
+        <v>3.25</v>
+      </c>
+      <c r="W263">
+        <v>1.33</v>
+      </c>
+      <c r="X263">
+        <v>9</v>
+      </c>
+      <c r="Y263">
+        <v>1.07</v>
+      </c>
+      <c r="Z263">
+        <v>1.36</v>
+      </c>
+      <c r="AA263">
+        <v>4.5</v>
+      </c>
+      <c r="AB263">
+        <v>9</v>
+      </c>
+      <c r="AC263">
+        <v>1.07</v>
+      </c>
+      <c r="AD263">
+        <v>8.5</v>
+      </c>
+      <c r="AE263">
+        <v>1.42</v>
+      </c>
+      <c r="AF263">
+        <v>2.9</v>
+      </c>
+      <c r="AG263">
+        <v>2.1</v>
+      </c>
+      <c r="AH263">
+        <v>1.73</v>
+      </c>
+      <c r="AI263">
+        <v>2.5</v>
+      </c>
+      <c r="AJ263">
+        <v>1.5</v>
+      </c>
+      <c r="AK263">
+        <v>1.07</v>
+      </c>
+      <c r="AL263">
+        <v>1.2</v>
+      </c>
+      <c r="AM263">
+        <v>2.87</v>
+      </c>
+      <c r="AN263">
+        <v>1.38</v>
+      </c>
+      <c r="AO263">
+        <v>0.23</v>
+      </c>
+      <c r="AP263">
+        <v>1.5</v>
+      </c>
+      <c r="AQ263">
+        <v>0.21</v>
+      </c>
+      <c r="AR263">
+        <v>1.39</v>
+      </c>
+      <c r="AS263">
+        <v>0.93</v>
+      </c>
+      <c r="AT263">
+        <v>2.32</v>
+      </c>
+      <c r="AU263">
+        <v>5</v>
+      </c>
+      <c r="AV263">
+        <v>5</v>
+      </c>
+      <c r="AW263">
+        <v>13</v>
+      </c>
+      <c r="AX263">
+        <v>7</v>
+      </c>
+      <c r="AY263">
+        <v>21</v>
+      </c>
+      <c r="AZ263">
+        <v>13</v>
+      </c>
+      <c r="BA263">
+        <v>0</v>
+      </c>
+      <c r="BB263">
+        <v>6</v>
+      </c>
+      <c r="BC263">
+        <v>6</v>
+      </c>
+      <c r="BD263">
+        <v>1.26</v>
+      </c>
+      <c r="BE263">
+        <v>7.5</v>
+      </c>
+      <c r="BF263">
+        <v>4.3</v>
+      </c>
+      <c r="BG263">
+        <v>1.37</v>
+      </c>
+      <c r="BH263">
+        <v>2.8</v>
+      </c>
+      <c r="BI263">
+        <v>1.64</v>
+      </c>
+      <c r="BJ263">
+        <v>2.1</v>
+      </c>
+      <c r="BK263">
+        <v>2.02</v>
+      </c>
+      <c r="BL263">
+        <v>1.7</v>
+      </c>
+      <c r="BM263">
+        <v>2.55</v>
+      </c>
+      <c r="BN263">
+        <v>1.43</v>
+      </c>
+      <c r="BO263">
+        <v>3.3</v>
+      </c>
+      <c r="BP263">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -55585,13 +55585,13 @@
         <v>13</v>
       </c>
       <c r="BA263">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB263">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC263">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD263">
         <v>1.26</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="363">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -805,6 +805,12 @@
     <t>['7', '58']</t>
   </si>
   <si>
+    <t>['88', '90+2']</t>
+  </si>
+  <si>
+    <t>['30', '34']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1091,6 +1097,12 @@
   </si>
   <si>
     <t>['40']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['46']</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP263"/>
+  <dimension ref="A1:BP268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1708,7 +1720,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1786,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ2">
         <v>1.08</v>
@@ -1992,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
         <v>0.92</v>
@@ -2120,7 +2132,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2326,7 +2338,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2407,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2532,7 +2544,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2738,7 +2750,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2944,7 +2956,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3022,10 +3034,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ8">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3150,7 +3162,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3562,7 +3574,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3643,7 +3655,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ11">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3974,7 +3986,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4261,7 +4273,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR14">
         <v>1.83</v>
@@ -4876,10 +4888,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ17">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5082,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ18">
         <v>0.21</v>
@@ -5291,7 +5303,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ19">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5828,7 +5840,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6115,7 +6127,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ23">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR23">
         <v>1.51</v>
@@ -6240,7 +6252,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6524,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ25">
         <v>0.46</v>
@@ -7064,7 +7076,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7142,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ28">
         <v>0.71</v>
@@ -7966,10 +7978,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ32">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -8175,7 +8187,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ33">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -8300,7 +8312,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8587,7 +8599,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8793,7 +8805,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ36">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR36">
         <v>0.71</v>
@@ -8918,7 +8930,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9124,7 +9136,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9408,7 +9420,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ39">
         <v>1.08</v>
@@ -9614,7 +9626,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ40">
         <v>1.15</v>
@@ -9820,7 +9832,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ41">
         <v>0.71</v>
@@ -9948,7 +9960,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10154,7 +10166,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10566,7 +10578,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10644,7 +10656,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ45">
         <v>1.64</v>
@@ -10978,7 +10990,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11184,7 +11196,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12086,7 +12098,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52">
         <v>1.08</v>
@@ -12214,7 +12226,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12501,7 +12513,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ54">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR54">
         <v>1.07</v>
@@ -12832,7 +12844,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12913,7 +12925,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ56">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -13322,7 +13334,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ58">
         <v>0.42</v>
@@ -13528,7 +13540,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>0.71</v>
@@ -13734,7 +13746,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ60">
         <v>0.54</v>
@@ -13862,7 +13874,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14149,7 +14161,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ62">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR62">
         <v>1.49</v>
@@ -14274,7 +14286,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14352,10 +14364,10 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR63">
         <v>1.68</v>
@@ -14686,7 +14698,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14892,7 +14904,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14970,7 +14982,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ66">
         <v>0.71</v>
@@ -15179,7 +15191,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ67">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR67">
         <v>1.32</v>
@@ -15510,7 +15522,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15716,7 +15728,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16003,7 +16015,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ71">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR71">
         <v>1.29</v>
@@ -16128,7 +16140,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16209,7 +16221,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR72">
         <v>1.16</v>
@@ -16412,7 +16424,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ73">
         <v>0.71</v>
@@ -16824,7 +16836,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ75">
         <v>0.46</v>
@@ -16952,7 +16964,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17442,10 +17454,10 @@
         <v>0.67</v>
       </c>
       <c r="AP78">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ78">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17648,7 +17660,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ79">
         <v>0.42</v>
@@ -17776,7 +17788,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17982,7 +17994,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18063,7 +18075,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ81">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -18475,7 +18487,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR83">
         <v>1.07</v>
@@ -18678,7 +18690,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ84">
         <v>0.75</v>
@@ -19012,7 +19024,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19093,7 +19105,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -19296,7 +19308,7 @@
         <v>2.5</v>
       </c>
       <c r="AP87">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ87">
         <v>1.71</v>
@@ -19424,7 +19436,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19630,7 +19642,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -20042,7 +20054,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20120,10 +20132,10 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ91">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR91">
         <v>1.21</v>
@@ -20248,7 +20260,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20532,7 +20544,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ93">
         <v>0.42</v>
@@ -20660,7 +20672,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21072,7 +21084,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21359,7 +21371,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ97">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR97">
         <v>1.35</v>
@@ -21977,7 +21989,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ100">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22102,7 +22114,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22183,7 +22195,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ101">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR101">
         <v>1.21</v>
@@ -22308,7 +22320,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22389,7 +22401,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ102">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR102">
         <v>1.07</v>
@@ -22514,7 +22526,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23132,7 +23144,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23210,7 +23222,7 @@
         <v>2.5</v>
       </c>
       <c r="AP106">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ106">
         <v>2.14</v>
@@ -23622,7 +23634,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ108">
         <v>0.46</v>
@@ -23828,10 +23840,10 @@
         <v>1.8</v>
       </c>
       <c r="AP109">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR109">
         <v>1.79</v>
@@ -23956,7 +23968,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24034,7 +24046,7 @@
         <v>0.5</v>
       </c>
       <c r="AP110">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ110">
         <v>0.75</v>
@@ -24449,7 +24461,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ112">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR112">
         <v>1.08</v>
@@ -24780,7 +24792,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25067,7 +25079,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ115">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25398,7 +25410,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25604,7 +25616,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25682,7 +25694,7 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ118">
         <v>1.15</v>
@@ -26016,7 +26028,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26097,7 +26109,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ120">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR120">
         <v>1.55</v>
@@ -26300,7 +26312,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ121">
         <v>0.75</v>
@@ -26715,7 +26727,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ123">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR123">
         <v>1.08</v>
@@ -26840,7 +26852,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26918,7 +26930,7 @@
         <v>0.6</v>
       </c>
       <c r="AP124">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ124">
         <v>0.54</v>
@@ -27127,7 +27139,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ125">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR125">
         <v>1.29</v>
@@ -27330,7 +27342,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126">
         <v>0.92</v>
@@ -27742,7 +27754,7 @@
         <v>2.57</v>
       </c>
       <c r="AP128">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ128">
         <v>2.14</v>
@@ -27948,7 +27960,7 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ129">
         <v>0.21</v>
@@ -28076,7 +28088,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28488,7 +28500,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28569,7 +28581,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28900,7 +28912,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29106,7 +29118,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29393,7 +29405,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ136">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR136">
         <v>1.38</v>
@@ -29518,7 +29530,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29802,7 +29814,7 @@
         <v>1.83</v>
       </c>
       <c r="AP138">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ138">
         <v>1.08</v>
@@ -30136,7 +30148,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30217,7 +30229,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ140">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR140">
         <v>1.94</v>
@@ -30754,7 +30766,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30835,7 +30847,7 @@
         <v>1</v>
       </c>
       <c r="AQ143">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR143">
         <v>1.13</v>
@@ -30960,7 +30972,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31244,7 +31256,7 @@
         <v>0.33</v>
       </c>
       <c r="AP145">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ145">
         <v>1.08</v>
@@ -31372,7 +31384,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31656,7 +31668,7 @@
         <v>0.86</v>
       </c>
       <c r="AP147">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ147">
         <v>1.15</v>
@@ -31990,7 +32002,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32196,7 +32208,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32274,7 +32286,7 @@
         <v>2</v>
       </c>
       <c r="AP150">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ150">
         <v>1.64</v>
@@ -32483,7 +32495,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR151">
         <v>1.39</v>
@@ -32814,7 +32826,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32892,7 +32904,7 @@
         <v>2.2</v>
       </c>
       <c r="AP153">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ153">
         <v>2.14</v>
@@ -33101,7 +33113,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR154">
         <v>1.29</v>
@@ -33226,7 +33238,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33432,7 +33444,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33716,7 +33728,7 @@
         <v>2</v>
       </c>
       <c r="AP157">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ157">
         <v>1.71</v>
@@ -33844,7 +33856,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34050,7 +34062,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34131,7 +34143,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ159">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34334,7 +34346,7 @@
         <v>0.14</v>
       </c>
       <c r="AP160">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ160">
         <v>0.42</v>
@@ -35286,7 +35298,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35698,7 +35710,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35982,10 +35994,10 @@
         <v>1.13</v>
       </c>
       <c r="AP168">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ168">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR168">
         <v>1.43</v>
@@ -36110,7 +36122,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36522,7 +36534,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36809,7 +36821,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ172">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR172">
         <v>1.52</v>
@@ -37218,10 +37230,10 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ174">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR174">
         <v>1.33</v>
@@ -37758,7 +37770,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37839,7 +37851,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ177">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR177">
         <v>2</v>
@@ -37964,7 +37976,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38170,7 +38182,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38248,10 +38260,10 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ179">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR179">
         <v>1.81</v>
@@ -38376,7 +38388,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38866,10 +38878,10 @@
         <v>1.33</v>
       </c>
       <c r="AP182">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ182">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR182">
         <v>1.81</v>
@@ -38994,7 +39006,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39406,7 +39418,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40230,7 +40242,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40720,7 +40732,7 @@
         <v>1.89</v>
       </c>
       <c r="AP191">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ191">
         <v>1.71</v>
@@ -41054,7 +41066,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41135,7 +41147,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ193">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR193">
         <v>1.37</v>
@@ -41341,7 +41353,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ194">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR194">
         <v>0.96</v>
@@ -41466,7 +41478,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41544,7 +41556,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ195">
         <v>0.71</v>
@@ -41750,7 +41762,7 @@
         <v>2.09</v>
       </c>
       <c r="AP196">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ196">
         <v>2.14</v>
@@ -41878,7 +41890,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42084,7 +42096,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42162,10 +42174,10 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ198">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR198">
         <v>1.8</v>
@@ -42371,7 +42383,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ199">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -42783,7 +42795,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ201">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR201">
         <v>1.52</v>
@@ -43114,7 +43126,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43320,7 +43332,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43526,7 +43538,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43732,7 +43744,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44144,7 +44156,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44222,7 +44234,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP208">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ208">
         <v>1.08</v>
@@ -44428,7 +44440,7 @@
         <v>0.9</v>
       </c>
       <c r="AP209">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ209">
         <v>0.71</v>
@@ -44968,7 +44980,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45049,7 +45061,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ212">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR212">
         <v>0.97</v>
@@ -45252,10 +45264,10 @@
         <v>0.9</v>
       </c>
       <c r="AP213">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ213">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR213">
         <v>1.36</v>
@@ -45667,7 +45679,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ215">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR215">
         <v>1.74</v>
@@ -46616,7 +46628,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -46694,7 +46706,7 @@
         <v>1.8</v>
       </c>
       <c r="AP220">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ220">
         <v>1.54</v>
@@ -46903,7 +46915,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ221">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR221">
         <v>1.35</v>
@@ -47234,7 +47246,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47518,7 +47530,7 @@
         <v>1.09</v>
       </c>
       <c r="AP224">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ224">
         <v>0.92</v>
@@ -47646,7 +47658,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -47930,10 +47942,10 @@
         <v>1.8</v>
       </c>
       <c r="AP226">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ226">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR226">
         <v>1.93</v>
@@ -48548,7 +48560,7 @@
         <v>0.2</v>
       </c>
       <c r="AP229">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ229">
         <v>0.42</v>
@@ -48676,7 +48688,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49088,7 +49100,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49294,7 +49306,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49500,7 +49512,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50118,7 +50130,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50324,7 +50336,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -50405,7 +50417,7 @@
         <v>1</v>
       </c>
       <c r="AQ238">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR238">
         <v>1</v>
@@ -50611,7 +50623,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ239">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR239">
         <v>1.24</v>
@@ -50814,7 +50826,7 @@
         <v>1.27</v>
       </c>
       <c r="AP240">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ240">
         <v>1.08</v>
@@ -51023,7 +51035,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ241">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR241">
         <v>2.03</v>
@@ -51354,7 +51366,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51766,7 +51778,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51847,7 +51859,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ245">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AR245">
         <v>1.34</v>
@@ -51972,7 +51984,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52178,7 +52190,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52256,7 +52268,7 @@
         <v>0.25</v>
       </c>
       <c r="AP247">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ247">
         <v>0.21</v>
@@ -52462,7 +52474,7 @@
         <v>1</v>
       </c>
       <c r="AP248">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ248">
         <v>0.92</v>
@@ -52590,7 +52602,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52668,7 +52680,7 @@
         <v>1</v>
       </c>
       <c r="AP249">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ249">
         <v>1.15</v>
@@ -52874,7 +52886,7 @@
         <v>0.83</v>
       </c>
       <c r="AP250">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ250">
         <v>0.71</v>
@@ -53002,7 +53014,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53083,7 +53095,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ251">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR251">
         <v>1.43</v>
@@ -53208,7 +53220,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53289,7 +53301,7 @@
         <v>1</v>
       </c>
       <c r="AQ252">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR252">
         <v>0.99</v>
@@ -53414,7 +53426,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53701,7 +53713,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ254">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR254">
         <v>1.67</v>
@@ -53826,7 +53838,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -53904,7 +53916,7 @@
         <v>1.77</v>
       </c>
       <c r="AP255">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ255">
         <v>1.64</v>
@@ -54856,7 +54868,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55474,7 +55486,7 @@
         <v>262</v>
       </c>
       <c r="P263" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q263">
         <v>1.95</v>
@@ -55631,6 +55643,1036 @@
       </c>
       <c r="BP263">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7465253</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45725.41666666666</v>
+      </c>
+      <c r="F264">
+        <v>27</v>
+      </c>
+      <c r="G264" t="s">
+        <v>83</v>
+      </c>
+      <c r="H264" t="s">
+        <v>87</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>2</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+      <c r="N264">
+        <v>3</v>
+      </c>
+      <c r="O264" t="s">
+        <v>263</v>
+      </c>
+      <c r="P264" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q264">
+        <v>5</v>
+      </c>
+      <c r="R264">
+        <v>1.91</v>
+      </c>
+      <c r="S264">
+        <v>2.88</v>
+      </c>
+      <c r="T264">
+        <v>1.62</v>
+      </c>
+      <c r="U264">
+        <v>2.2</v>
+      </c>
+      <c r="V264">
+        <v>4</v>
+      </c>
+      <c r="W264">
+        <v>1.22</v>
+      </c>
+      <c r="X264">
+        <v>13</v>
+      </c>
+      <c r="Y264">
+        <v>1.04</v>
+      </c>
+      <c r="Z264">
+        <v>4.33</v>
+      </c>
+      <c r="AA264">
+        <v>3.1</v>
+      </c>
+      <c r="AB264">
+        <v>2</v>
+      </c>
+      <c r="AC264">
+        <v>1.12</v>
+      </c>
+      <c r="AD264">
+        <v>6.5</v>
+      </c>
+      <c r="AE264">
+        <v>1.55</v>
+      </c>
+      <c r="AF264">
+        <v>2.3</v>
+      </c>
+      <c r="AG264">
+        <v>2.75</v>
+      </c>
+      <c r="AH264">
+        <v>1.44</v>
+      </c>
+      <c r="AI264">
+        <v>2.25</v>
+      </c>
+      <c r="AJ264">
+        <v>1.57</v>
+      </c>
+      <c r="AK264">
+        <v>1.75</v>
+      </c>
+      <c r="AL264">
+        <v>1.36</v>
+      </c>
+      <c r="AM264">
+        <v>1.22</v>
+      </c>
+      <c r="AN264">
+        <v>1.23</v>
+      </c>
+      <c r="AO264">
+        <v>1.83</v>
+      </c>
+      <c r="AP264">
+        <v>1.36</v>
+      </c>
+      <c r="AQ264">
+        <v>1.69</v>
+      </c>
+      <c r="AR264">
+        <v>1.32</v>
+      </c>
+      <c r="AS264">
+        <v>1.19</v>
+      </c>
+      <c r="AT264">
+        <v>2.51</v>
+      </c>
+      <c r="AU264">
+        <v>4</v>
+      </c>
+      <c r="AV264">
+        <v>3</v>
+      </c>
+      <c r="AW264">
+        <v>8</v>
+      </c>
+      <c r="AX264">
+        <v>2</v>
+      </c>
+      <c r="AY264">
+        <v>15</v>
+      </c>
+      <c r="AZ264">
+        <v>6</v>
+      </c>
+      <c r="BA264">
+        <v>4</v>
+      </c>
+      <c r="BB264">
+        <v>4</v>
+      </c>
+      <c r="BC264">
+        <v>8</v>
+      </c>
+      <c r="BD264">
+        <v>2.3</v>
+      </c>
+      <c r="BE264">
+        <v>6.1</v>
+      </c>
+      <c r="BF264">
+        <v>1.79</v>
+      </c>
+      <c r="BG264">
+        <v>1.54</v>
+      </c>
+      <c r="BH264">
+        <v>2.3</v>
+      </c>
+      <c r="BI264">
+        <v>1.91</v>
+      </c>
+      <c r="BJ264">
+        <v>1.77</v>
+      </c>
+      <c r="BK264">
+        <v>2.45</v>
+      </c>
+      <c r="BL264">
+        <v>1.48</v>
+      </c>
+      <c r="BM264">
+        <v>3.2</v>
+      </c>
+      <c r="BN264">
+        <v>1.28</v>
+      </c>
+      <c r="BO264">
+        <v>4.35</v>
+      </c>
+      <c r="BP264">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7465254</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45725.51041666666</v>
+      </c>
+      <c r="F265">
+        <v>27</v>
+      </c>
+      <c r="G265" t="s">
+        <v>84</v>
+      </c>
+      <c r="H265" t="s">
+        <v>88</v>
+      </c>
+      <c r="I265">
+        <v>2</v>
+      </c>
+      <c r="J265">
+        <v>1</v>
+      </c>
+      <c r="K265">
+        <v>3</v>
+      </c>
+      <c r="L265">
+        <v>2</v>
+      </c>
+      <c r="M265">
+        <v>1</v>
+      </c>
+      <c r="N265">
+        <v>3</v>
+      </c>
+      <c r="O265" t="s">
+        <v>264</v>
+      </c>
+      <c r="P265" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q265">
+        <v>1.73</v>
+      </c>
+      <c r="R265">
+        <v>2.63</v>
+      </c>
+      <c r="S265">
+        <v>8</v>
+      </c>
+      <c r="T265">
+        <v>1.29</v>
+      </c>
+      <c r="U265">
+        <v>3.5</v>
+      </c>
+      <c r="V265">
+        <v>2.25</v>
+      </c>
+      <c r="W265">
+        <v>1.57</v>
+      </c>
+      <c r="X265">
+        <v>5.5</v>
+      </c>
+      <c r="Y265">
+        <v>1.14</v>
+      </c>
+      <c r="Z265">
+        <v>1.29</v>
+      </c>
+      <c r="AA265">
+        <v>5.75</v>
+      </c>
+      <c r="AB265">
+        <v>9</v>
+      </c>
+      <c r="AC265">
+        <v>1.01</v>
+      </c>
+      <c r="AD265">
+        <v>21</v>
+      </c>
+      <c r="AE265">
+        <v>1.17</v>
+      </c>
+      <c r="AF265">
+        <v>5</v>
+      </c>
+      <c r="AG265">
+        <v>1.53</v>
+      </c>
+      <c r="AH265">
+        <v>2.5</v>
+      </c>
+      <c r="AI265">
+        <v>1.95</v>
+      </c>
+      <c r="AJ265">
+        <v>1.8</v>
+      </c>
+      <c r="AK265">
+        <v>1.06</v>
+      </c>
+      <c r="AL265">
+        <v>1.14</v>
+      </c>
+      <c r="AM265">
+        <v>3.6</v>
+      </c>
+      <c r="AN265">
+        <v>2.58</v>
+      </c>
+      <c r="AO265">
+        <v>1.31</v>
+      </c>
+      <c r="AP265">
+        <v>2.62</v>
+      </c>
+      <c r="AQ265">
+        <v>1.21</v>
+      </c>
+      <c r="AR265">
+        <v>2.04</v>
+      </c>
+      <c r="AS265">
+        <v>1.14</v>
+      </c>
+      <c r="AT265">
+        <v>3.18</v>
+      </c>
+      <c r="AU265">
+        <v>6</v>
+      </c>
+      <c r="AV265">
+        <v>7</v>
+      </c>
+      <c r="AW265">
+        <v>5</v>
+      </c>
+      <c r="AX265">
+        <v>14</v>
+      </c>
+      <c r="AY265">
+        <v>13</v>
+      </c>
+      <c r="AZ265">
+        <v>25</v>
+      </c>
+      <c r="BA265">
+        <v>4</v>
+      </c>
+      <c r="BB265">
+        <v>6</v>
+      </c>
+      <c r="BC265">
+        <v>10</v>
+      </c>
+      <c r="BD265">
+        <v>1.21</v>
+      </c>
+      <c r="BE265">
+        <v>8.5</v>
+      </c>
+      <c r="BF265">
+        <v>4.8</v>
+      </c>
+      <c r="BG265">
+        <v>1.24</v>
+      </c>
+      <c r="BH265">
+        <v>3.55</v>
+      </c>
+      <c r="BI265">
+        <v>1.41</v>
+      </c>
+      <c r="BJ265">
+        <v>2.65</v>
+      </c>
+      <c r="BK265">
+        <v>1.67</v>
+      </c>
+      <c r="BL265">
+        <v>2.05</v>
+      </c>
+      <c r="BM265">
+        <v>2.05</v>
+      </c>
+      <c r="BN265">
+        <v>1.67</v>
+      </c>
+      <c r="BO265">
+        <v>2.55</v>
+      </c>
+      <c r="BP265">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7465248</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45725.60416666666</v>
+      </c>
+      <c r="F266">
+        <v>27</v>
+      </c>
+      <c r="G266" t="s">
+        <v>71</v>
+      </c>
+      <c r="H266" t="s">
+        <v>73</v>
+      </c>
+      <c r="I266">
+        <v>0</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>0</v>
+      </c>
+      <c r="L266">
+        <v>1</v>
+      </c>
+      <c r="M266">
+        <v>0</v>
+      </c>
+      <c r="N266">
+        <v>1</v>
+      </c>
+      <c r="O266" t="s">
+        <v>208</v>
+      </c>
+      <c r="P266" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q266">
+        <v>1.91</v>
+      </c>
+      <c r="R266">
+        <v>2.4</v>
+      </c>
+      <c r="S266">
+        <v>7</v>
+      </c>
+      <c r="T266">
+        <v>1.33</v>
+      </c>
+      <c r="U266">
+        <v>3.25</v>
+      </c>
+      <c r="V266">
+        <v>2.63</v>
+      </c>
+      <c r="W266">
+        <v>1.44</v>
+      </c>
+      <c r="X266">
+        <v>6.5</v>
+      </c>
+      <c r="Y266">
+        <v>1.11</v>
+      </c>
+      <c r="Z266">
+        <v>1.42</v>
+      </c>
+      <c r="AA266">
+        <v>4.75</v>
+      </c>
+      <c r="AB266">
+        <v>7</v>
+      </c>
+      <c r="AC266">
+        <v>1.04</v>
+      </c>
+      <c r="AD266">
+        <v>13</v>
+      </c>
+      <c r="AE266">
+        <v>1.26</v>
+      </c>
+      <c r="AF266">
+        <v>4</v>
+      </c>
+      <c r="AG266">
+        <v>1.73</v>
+      </c>
+      <c r="AH266">
+        <v>2.1</v>
+      </c>
+      <c r="AI266">
+        <v>1.95</v>
+      </c>
+      <c r="AJ266">
+        <v>1.8</v>
+      </c>
+      <c r="AK266">
+        <v>1.11</v>
+      </c>
+      <c r="AL266">
+        <v>1.19</v>
+      </c>
+      <c r="AM266">
+        <v>2.7</v>
+      </c>
+      <c r="AN266">
+        <v>1.77</v>
+      </c>
+      <c r="AO266">
+        <v>0.85</v>
+      </c>
+      <c r="AP266">
+        <v>1.86</v>
+      </c>
+      <c r="AQ266">
+        <v>0.79</v>
+      </c>
+      <c r="AR266">
+        <v>1.79</v>
+      </c>
+      <c r="AS266">
+        <v>1.06</v>
+      </c>
+      <c r="AT266">
+        <v>2.85</v>
+      </c>
+      <c r="AU266">
+        <v>7</v>
+      </c>
+      <c r="AV266">
+        <v>2</v>
+      </c>
+      <c r="AW266">
+        <v>8</v>
+      </c>
+      <c r="AX266">
+        <v>7</v>
+      </c>
+      <c r="AY266">
+        <v>18</v>
+      </c>
+      <c r="AZ266">
+        <v>10</v>
+      </c>
+      <c r="BA266">
+        <v>11</v>
+      </c>
+      <c r="BB266">
+        <v>1</v>
+      </c>
+      <c r="BC266">
+        <v>12</v>
+      </c>
+      <c r="BD266">
+        <v>1.28</v>
+      </c>
+      <c r="BE266">
+        <v>7.5</v>
+      </c>
+      <c r="BF266">
+        <v>3.95</v>
+      </c>
+      <c r="BG266">
+        <v>1.29</v>
+      </c>
+      <c r="BH266">
+        <v>3.15</v>
+      </c>
+      <c r="BI266">
+        <v>1.5</v>
+      </c>
+      <c r="BJ266">
+        <v>2.38</v>
+      </c>
+      <c r="BK266">
+        <v>1.81</v>
+      </c>
+      <c r="BL266">
+        <v>1.88</v>
+      </c>
+      <c r="BM266">
+        <v>2.25</v>
+      </c>
+      <c r="BN266">
+        <v>1.55</v>
+      </c>
+      <c r="BO266">
+        <v>2.9</v>
+      </c>
+      <c r="BP266">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7465246</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45725.60416666666</v>
+      </c>
+      <c r="F267">
+        <v>27</v>
+      </c>
+      <c r="G267" t="s">
+        <v>70</v>
+      </c>
+      <c r="H267" t="s">
+        <v>77</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>0</v>
+      </c>
+      <c r="L267">
+        <v>1</v>
+      </c>
+      <c r="M267">
+        <v>1</v>
+      </c>
+      <c r="N267">
+        <v>2</v>
+      </c>
+      <c r="O267" t="s">
+        <v>221</v>
+      </c>
+      <c r="P267" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q267">
+        <v>2.25</v>
+      </c>
+      <c r="R267">
+        <v>2.1</v>
+      </c>
+      <c r="S267">
+        <v>6.5</v>
+      </c>
+      <c r="T267">
+        <v>1.44</v>
+      </c>
+      <c r="U267">
+        <v>2.63</v>
+      </c>
+      <c r="V267">
+        <v>3.25</v>
+      </c>
+      <c r="W267">
+        <v>1.33</v>
+      </c>
+      <c r="X267">
+        <v>10</v>
+      </c>
+      <c r="Y267">
+        <v>1.06</v>
+      </c>
+      <c r="Z267">
+        <v>1.6</v>
+      </c>
+      <c r="AA267">
+        <v>3.75</v>
+      </c>
+      <c r="AB267">
+        <v>6</v>
+      </c>
+      <c r="AC267">
+        <v>1.05</v>
+      </c>
+      <c r="AD267">
+        <v>10</v>
+      </c>
+      <c r="AE267">
+        <v>1.33</v>
+      </c>
+      <c r="AF267">
+        <v>3.4</v>
+      </c>
+      <c r="AG267">
+        <v>2.2</v>
+      </c>
+      <c r="AH267">
+        <v>1.67</v>
+      </c>
+      <c r="AI267">
+        <v>2.1</v>
+      </c>
+      <c r="AJ267">
+        <v>1.67</v>
+      </c>
+      <c r="AK267">
+        <v>1.13</v>
+      </c>
+      <c r="AL267">
+        <v>1.25</v>
+      </c>
+      <c r="AM267">
+        <v>2.3</v>
+      </c>
+      <c r="AN267">
+        <v>2.15</v>
+      </c>
+      <c r="AO267">
+        <v>1.33</v>
+      </c>
+      <c r="AP267">
+        <v>2.07</v>
+      </c>
+      <c r="AQ267">
+        <v>1.31</v>
+      </c>
+      <c r="AR267">
+        <v>1.69</v>
+      </c>
+      <c r="AS267">
+        <v>1.2</v>
+      </c>
+      <c r="AT267">
+        <v>2.89</v>
+      </c>
+      <c r="AU267">
+        <v>3</v>
+      </c>
+      <c r="AV267">
+        <v>3</v>
+      </c>
+      <c r="AW267">
+        <v>6</v>
+      </c>
+      <c r="AX267">
+        <v>7</v>
+      </c>
+      <c r="AY267">
+        <v>10</v>
+      </c>
+      <c r="AZ267">
+        <v>10</v>
+      </c>
+      <c r="BA267">
+        <v>3</v>
+      </c>
+      <c r="BB267">
+        <v>3</v>
+      </c>
+      <c r="BC267">
+        <v>6</v>
+      </c>
+      <c r="BD267">
+        <v>1.34</v>
+      </c>
+      <c r="BE267">
+        <v>7</v>
+      </c>
+      <c r="BF267">
+        <v>3.55</v>
+      </c>
+      <c r="BG267">
+        <v>1.35</v>
+      </c>
+      <c r="BH267">
+        <v>2.9</v>
+      </c>
+      <c r="BI267">
+        <v>1.6</v>
+      </c>
+      <c r="BJ267">
+        <v>2.17</v>
+      </c>
+      <c r="BK267">
+        <v>1.97</v>
+      </c>
+      <c r="BL267">
+        <v>1.73</v>
+      </c>
+      <c r="BM267">
+        <v>2.48</v>
+      </c>
+      <c r="BN267">
+        <v>1.47</v>
+      </c>
+      <c r="BO267">
+        <v>3.25</v>
+      </c>
+      <c r="BP267">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7465250</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45725.70833333334</v>
+      </c>
+      <c r="F268">
+        <v>27</v>
+      </c>
+      <c r="G268" t="s">
+        <v>76</v>
+      </c>
+      <c r="H268" t="s">
+        <v>80</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>0</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+      <c r="M268">
+        <v>1</v>
+      </c>
+      <c r="N268">
+        <v>1</v>
+      </c>
+      <c r="O268" t="s">
+        <v>104</v>
+      </c>
+      <c r="P268" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q268">
+        <v>2.88</v>
+      </c>
+      <c r="R268">
+        <v>2</v>
+      </c>
+      <c r="S268">
+        <v>4.33</v>
+      </c>
+      <c r="T268">
+        <v>1.5</v>
+      </c>
+      <c r="U268">
+        <v>2.5</v>
+      </c>
+      <c r="V268">
+        <v>3.5</v>
+      </c>
+      <c r="W268">
+        <v>1.29</v>
+      </c>
+      <c r="X268">
+        <v>11</v>
+      </c>
+      <c r="Y268">
+        <v>1.05</v>
+      </c>
+      <c r="Z268">
+        <v>2.1</v>
+      </c>
+      <c r="AA268">
+        <v>3.2</v>
+      </c>
+      <c r="AB268">
+        <v>3.7</v>
+      </c>
+      <c r="AC268">
+        <v>1.07</v>
+      </c>
+      <c r="AD268">
+        <v>9</v>
+      </c>
+      <c r="AE268">
+        <v>1.4</v>
+      </c>
+      <c r="AF268">
+        <v>3</v>
+      </c>
+      <c r="AG268">
+        <v>2.3</v>
+      </c>
+      <c r="AH268">
+        <v>1.62</v>
+      </c>
+      <c r="AI268">
+        <v>2</v>
+      </c>
+      <c r="AJ268">
+        <v>1.75</v>
+      </c>
+      <c r="AK268">
+        <v>1.26</v>
+      </c>
+      <c r="AL268">
+        <v>1.33</v>
+      </c>
+      <c r="AM268">
+        <v>1.73</v>
+      </c>
+      <c r="AN268">
+        <v>1.54</v>
+      </c>
+      <c r="AO268">
+        <v>1.08</v>
+      </c>
+      <c r="AP268">
+        <v>1.43</v>
+      </c>
+      <c r="AQ268">
+        <v>1.21</v>
+      </c>
+      <c r="AR268">
+        <v>1.45</v>
+      </c>
+      <c r="AS268">
+        <v>1.23</v>
+      </c>
+      <c r="AT268">
+        <v>2.68</v>
+      </c>
+      <c r="AU268">
+        <v>3</v>
+      </c>
+      <c r="AV268">
+        <v>5</v>
+      </c>
+      <c r="AW268">
+        <v>5</v>
+      </c>
+      <c r="AX268">
+        <v>5</v>
+      </c>
+      <c r="AY268">
+        <v>8</v>
+      </c>
+      <c r="AZ268">
+        <v>11</v>
+      </c>
+      <c r="BA268">
+        <v>6</v>
+      </c>
+      <c r="BB268">
+        <v>3</v>
+      </c>
+      <c r="BC268">
+        <v>9</v>
+      </c>
+      <c r="BD268">
+        <v>1.68</v>
+      </c>
+      <c r="BE268">
+        <v>6.5</v>
+      </c>
+      <c r="BF268">
+        <v>2.4</v>
+      </c>
+      <c r="BG268">
+        <v>1.29</v>
+      </c>
+      <c r="BH268">
+        <v>3.15</v>
+      </c>
+      <c r="BI268">
+        <v>1.5</v>
+      </c>
+      <c r="BJ268">
+        <v>2.35</v>
+      </c>
+      <c r="BK268">
+        <v>1.83</v>
+      </c>
+      <c r="BL268">
+        <v>1.85</v>
+      </c>
+      <c r="BM268">
+        <v>2.3</v>
+      </c>
+      <c r="BN268">
+        <v>1.54</v>
+      </c>
+      <c r="BO268">
+        <v>2.9</v>
+      </c>
+      <c r="BP268">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="363">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1464,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP268"/>
+  <dimension ref="A1:BP269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2007,7 +2007,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ16">
         <v>1.08</v>
@@ -5715,7 +5715,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ21">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -8184,7 +8184,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ33">
         <v>1.21</v>
@@ -9217,7 +9217,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ38">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR38">
         <v>1.9</v>
@@ -10244,7 +10244,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43">
         <v>0.71</v>
@@ -13131,7 +13131,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR57">
         <v>1.38</v>
@@ -15600,7 +15600,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ69">
         <v>1.71</v>
@@ -17251,7 +17251,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ77">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR77">
         <v>1.31</v>
@@ -18484,7 +18484,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83">
         <v>1.31</v>
@@ -22398,7 +22398,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ102">
         <v>1.21</v>
@@ -23019,7 +23019,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR105">
         <v>1.4</v>
@@ -27345,7 +27345,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ126">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -30638,7 +30638,7 @@
         <v>0.67</v>
       </c>
       <c r="AP142">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ142">
         <v>0.54</v>
@@ -31053,7 +31053,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ144">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR144">
         <v>1.51</v>
@@ -34758,7 +34758,7 @@
         <v>0.86</v>
       </c>
       <c r="AP162">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ162">
         <v>0.75</v>
@@ -34967,7 +34967,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ163">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR163">
         <v>1.23</v>
@@ -36612,7 +36612,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ171">
         <v>0.46</v>
@@ -39499,7 +39499,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ185">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR185">
         <v>1.15</v>
@@ -39908,7 +39908,7 @@
         <v>0.89</v>
       </c>
       <c r="AP187">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ187">
         <v>0.71</v>
@@ -40938,7 +40938,7 @@
         <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ192">
         <v>0.21</v>
@@ -44031,7 +44031,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ207">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR207">
         <v>1.57</v>
@@ -45882,7 +45882,7 @@
         <v>2</v>
       </c>
       <c r="AP216">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ216">
         <v>1.64</v>
@@ -47533,7 +47533,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ224">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR224">
         <v>1.44</v>
@@ -50208,7 +50208,7 @@
         <v>1.73</v>
       </c>
       <c r="AP237">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ237">
         <v>1.54</v>
@@ -52477,7 +52477,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ248">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR248">
         <v>2.01</v>
@@ -56673,6 +56673,212 @@
       </c>
       <c r="BP268">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7469588</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45726.70833333334</v>
+      </c>
+      <c r="F269">
+        <v>27</v>
+      </c>
+      <c r="G269" t="s">
+        <v>82</v>
+      </c>
+      <c r="H269" t="s">
+        <v>89</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>0</v>
+      </c>
+      <c r="L269">
+        <v>1</v>
+      </c>
+      <c r="M269">
+        <v>1</v>
+      </c>
+      <c r="N269">
+        <v>2</v>
+      </c>
+      <c r="O269" t="s">
+        <v>226</v>
+      </c>
+      <c r="P269" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q269">
+        <v>3.75</v>
+      </c>
+      <c r="R269">
+        <v>2.05</v>
+      </c>
+      <c r="S269">
+        <v>3.1</v>
+      </c>
+      <c r="T269">
+        <v>1.5</v>
+      </c>
+      <c r="U269">
+        <v>2.5</v>
+      </c>
+      <c r="V269">
+        <v>3.4</v>
+      </c>
+      <c r="W269">
+        <v>1.3</v>
+      </c>
+      <c r="X269">
+        <v>10</v>
+      </c>
+      <c r="Y269">
+        <v>1.06</v>
+      </c>
+      <c r="Z269">
+        <v>3.1</v>
+      </c>
+      <c r="AA269">
+        <v>3.2</v>
+      </c>
+      <c r="AB269">
+        <v>2.35</v>
+      </c>
+      <c r="AC269">
+        <v>1.07</v>
+      </c>
+      <c r="AD269">
+        <v>10</v>
+      </c>
+      <c r="AE269">
+        <v>1.33</v>
+      </c>
+      <c r="AF269">
+        <v>3.3</v>
+      </c>
+      <c r="AG269">
+        <v>2.2</v>
+      </c>
+      <c r="AH269">
+        <v>1.67</v>
+      </c>
+      <c r="AI269">
+        <v>1.91</v>
+      </c>
+      <c r="AJ269">
+        <v>1.91</v>
+      </c>
+      <c r="AK269">
+        <v>1.6</v>
+      </c>
+      <c r="AL269">
+        <v>1.32</v>
+      </c>
+      <c r="AM269">
+        <v>1.35</v>
+      </c>
+      <c r="AN269">
+        <v>1.69</v>
+      </c>
+      <c r="AO269">
+        <v>0.92</v>
+      </c>
+      <c r="AP269">
+        <v>1.64</v>
+      </c>
+      <c r="AQ269">
+        <v>0.93</v>
+      </c>
+      <c r="AR269">
+        <v>1.16</v>
+      </c>
+      <c r="AS269">
+        <v>1.07</v>
+      </c>
+      <c r="AT269">
+        <v>2.23</v>
+      </c>
+      <c r="AU269">
+        <v>5</v>
+      </c>
+      <c r="AV269">
+        <v>5</v>
+      </c>
+      <c r="AW269">
+        <v>3</v>
+      </c>
+      <c r="AX269">
+        <v>14</v>
+      </c>
+      <c r="AY269">
+        <v>9</v>
+      </c>
+      <c r="AZ269">
+        <v>21</v>
+      </c>
+      <c r="BA269">
+        <v>4</v>
+      </c>
+      <c r="BB269">
+        <v>9</v>
+      </c>
+      <c r="BC269">
+        <v>13</v>
+      </c>
+      <c r="BD269">
+        <v>2.33</v>
+      </c>
+      <c r="BE269">
+        <v>6.25</v>
+      </c>
+      <c r="BF269">
+        <v>1.74</v>
+      </c>
+      <c r="BG269">
+        <v>1.43</v>
+      </c>
+      <c r="BH269">
+        <v>2.55</v>
+      </c>
+      <c r="BI269">
+        <v>1.72</v>
+      </c>
+      <c r="BJ269">
+        <v>1.98</v>
+      </c>
+      <c r="BK269">
+        <v>2.17</v>
+      </c>
+      <c r="BL269">
+        <v>1.6</v>
+      </c>
+      <c r="BM269">
+        <v>2.8</v>
+      </c>
+      <c r="BN269">
+        <v>1.37</v>
+      </c>
+      <c r="BO269">
+        <v>3.65</v>
+      </c>
+      <c r="BP269">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -811,6 +811,12 @@
     <t>['30', '34']</t>
   </si>
   <si>
+    <t>['90', '90+5']</t>
+  </si>
+  <si>
+    <t>['65', '90+7']</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
@@ -1103,6 +1109,12 @@
   </si>
   <si>
     <t>['46']</t>
+  </si>
+  <si>
+    <t>['7', '63']</t>
+  </si>
+  <si>
+    <t>['17', '23']</t>
   </si>
 </sst>
 </file>
@@ -1464,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP269"/>
+  <dimension ref="A1:BP273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1720,7 +1732,7 @@
         <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2132,7 +2144,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2213,7 +2225,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ4">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2338,7 +2350,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2544,7 +2556,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2750,7 +2762,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2956,7 +2968,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3162,7 +3174,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3240,10 +3252,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ9">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3446,10 +3458,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ10">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3574,7 +3586,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3652,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11">
         <v>1.69</v>
@@ -3986,7 +3998,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -5840,7 +5852,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -5918,10 +5930,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ22">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR22">
         <v>1.08</v>
@@ -6124,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ23">
         <v>1.21</v>
@@ -6252,7 +6264,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6742,7 +6754,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ26">
         <v>0.71</v>
@@ -6951,7 +6963,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ27">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR27">
         <v>1.31</v>
@@ -7076,7 +7088,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7157,7 +7169,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ28">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -7569,7 +7581,7 @@
         <v>1</v>
       </c>
       <c r="AQ30">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR30">
         <v>1.44</v>
@@ -8312,7 +8324,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8930,7 +8942,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9011,7 +9023,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ37">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -9136,7 +9148,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9960,7 +9972,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10038,7 +10050,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ42">
         <v>1.71</v>
@@ -10166,7 +10178,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10247,7 +10259,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ43">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR43">
         <v>1.17</v>
@@ -10578,7 +10590,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10659,7 +10671,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ45">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR45">
         <v>1.14</v>
@@ -10990,7 +11002,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11196,7 +11208,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11892,7 +11904,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ51">
         <v>1.08</v>
@@ -12226,7 +12238,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12716,7 +12728,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ55">
         <v>1.08</v>
@@ -12844,7 +12856,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13337,7 +13349,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ58">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR58">
         <v>2.01</v>
@@ -13749,7 +13761,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ60">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -13874,7 +13886,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13952,7 +13964,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ61">
         <v>2.14</v>
@@ -14286,7 +14298,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14698,7 +14710,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14904,7 +14916,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -14985,7 +14997,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ66">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR66">
         <v>2.43</v>
@@ -15522,7 +15534,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15728,7 +15740,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16140,7 +16152,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16218,7 +16230,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ72">
         <v>1.31</v>
@@ -16427,7 +16439,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ73">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16964,7 +16976,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17663,7 +17675,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ79">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR79">
         <v>1.68</v>
@@ -17788,7 +17800,7 @@
         <v>150</v>
       </c>
       <c r="P80" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q80">
         <v>3.25</v>
@@ -17869,7 +17881,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ80">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR80">
         <v>1.69</v>
@@ -17994,7 +18006,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18072,7 +18084,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ81">
         <v>0.79</v>
@@ -18899,7 +18911,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR85">
         <v>1.24</v>
@@ -19024,7 +19036,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19102,7 +19114,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ86">
         <v>1.21</v>
@@ -19436,7 +19448,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19642,7 +19654,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -20054,7 +20066,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20260,7 +20272,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20547,7 +20559,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ93">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -20672,7 +20684,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21084,7 +21096,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21165,7 +21177,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ96">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -21368,7 +21380,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ97">
         <v>1.21</v>
@@ -21780,7 +21792,7 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ99">
         <v>1.08</v>
@@ -22114,7 +22126,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22320,7 +22332,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22526,7 +22538,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22604,7 +22616,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ103">
         <v>1.71</v>
@@ -22813,7 +22825,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ104">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
         <v>1.49</v>
@@ -23144,7 +23156,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23431,7 +23443,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ107">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR107">
         <v>1.1</v>
@@ -23968,7 +23980,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24252,7 +24264,7 @@
         <v>1.5</v>
       </c>
       <c r="AP111">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ111">
         <v>1.54</v>
@@ -24792,7 +24804,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25285,7 +25297,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ116">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR116">
         <v>1.93</v>
@@ -25410,7 +25422,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25616,7 +25628,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -26028,7 +26040,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26518,10 +26530,10 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ122">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR122">
         <v>1.57</v>
@@ -26852,7 +26864,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26933,7 +26945,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ124">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR124">
         <v>1.82</v>
@@ -27136,7 +27148,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ125">
         <v>1.69</v>
@@ -27548,7 +27560,7 @@
         <v>1.4</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ127">
         <v>1.54</v>
@@ -28088,7 +28100,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28375,7 +28387,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ131">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28500,7 +28512,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28787,7 +28799,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ133">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR133">
         <v>1.36</v>
@@ -28912,7 +28924,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29118,7 +29130,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29530,7 +29542,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29611,7 +29623,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ137">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR137">
         <v>1.07</v>
@@ -30020,7 +30032,7 @@
         <v>0.33</v>
       </c>
       <c r="AP139">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ139">
         <v>0.46</v>
@@ -30148,7 +30160,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30641,7 +30653,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ142">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR142">
         <v>1.12</v>
@@ -30766,7 +30778,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30844,7 +30856,7 @@
         <v>1.71</v>
       </c>
       <c r="AP143">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ143">
         <v>1.69</v>
@@ -30972,7 +30984,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31050,7 +31062,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ144">
         <v>0.93</v>
@@ -31384,7 +31396,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -32002,7 +32014,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32080,7 +32092,7 @@
         <v>2.11</v>
       </c>
       <c r="AP149">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ149">
         <v>2.14</v>
@@ -32208,7 +32220,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32289,7 +32301,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ150">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32826,7 +32838,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33238,7 +33250,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33319,7 +33331,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ155">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR155">
         <v>1.38</v>
@@ -33444,7 +33456,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33856,7 +33868,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33937,7 +33949,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ158">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR158">
         <v>1.47</v>
@@ -34062,7 +34074,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34349,7 +34361,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ160">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR160">
         <v>1.3</v>
@@ -34552,7 +34564,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ161">
         <v>0.46</v>
@@ -34964,7 +34976,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ163">
         <v>0.93</v>
@@ -35173,7 +35185,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ164">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR164">
         <v>1.37</v>
@@ -35298,7 +35310,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35379,7 +35391,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ165">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR165">
         <v>1.64</v>
@@ -35710,7 +35722,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36122,7 +36134,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36200,7 +36212,7 @@
         <v>0.75</v>
       </c>
       <c r="AP169">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ169">
         <v>1.15</v>
@@ -36534,7 +36546,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36818,7 +36830,7 @@
         <v>1.38</v>
       </c>
       <c r="AP172">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ172">
         <v>1.21</v>
@@ -37770,7 +37782,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37976,7 +37988,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38057,7 +38069,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ178">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR178">
         <v>1.38</v>
@@ -38182,7 +38194,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38388,7 +38400,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38675,7 +38687,7 @@
         <v>1</v>
       </c>
       <c r="AQ181">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR181">
         <v>1.34</v>
@@ -39006,7 +39018,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39087,7 +39099,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ183">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR183">
         <v>1.35</v>
@@ -39293,7 +39305,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ184">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR184">
         <v>1.61</v>
@@ -39418,7 +39430,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39702,7 +39714,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ186">
         <v>1.15</v>
@@ -40242,7 +40254,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -41066,7 +41078,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41478,7 +41490,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41559,7 +41571,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ195">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR195">
         <v>1.78</v>
@@ -41890,7 +41902,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42096,7 +42108,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42792,7 +42804,7 @@
         <v>1.67</v>
       </c>
       <c r="AP201">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ201">
         <v>1.31</v>
@@ -43126,7 +43138,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43204,7 +43216,7 @@
         <v>0.9</v>
       </c>
       <c r="AP203">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ203">
         <v>1.15</v>
@@ -43332,7 +43344,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43538,7 +43550,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43619,7 +43631,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ205">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR205">
         <v>1.35</v>
@@ -43744,7 +43756,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -43822,10 +43834,10 @@
         <v>1.9</v>
       </c>
       <c r="AP206">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ206">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR206">
         <v>1.01</v>
@@ -44156,7 +44168,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44855,7 +44867,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ211">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR211">
         <v>1.16</v>
@@ -44980,7 +44992,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45470,7 +45482,7 @@
         <v>0.3</v>
       </c>
       <c r="AP214">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ214">
         <v>0.21</v>
@@ -45885,7 +45897,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ216">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR216">
         <v>1.18</v>
@@ -46091,7 +46103,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ217">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR217">
         <v>2.09</v>
@@ -46297,7 +46309,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ218">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR218">
         <v>1.3</v>
@@ -46628,7 +46640,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47246,7 +47258,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47658,7 +47670,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48563,7 +48575,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ229">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR229">
         <v>1.42</v>
@@ -48688,7 +48700,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -48972,7 +48984,7 @@
         <v>0.8</v>
       </c>
       <c r="AP231">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ231">
         <v>0.75</v>
@@ -49100,7 +49112,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49306,7 +49318,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49387,7 +49399,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ233">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR233">
         <v>0.95</v>
@@ -49512,7 +49524,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -49593,7 +49605,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ234">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR234">
         <v>1.47</v>
@@ -49799,7 +49811,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ235">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR235">
         <v>1.76</v>
@@ -50002,7 +50014,7 @@
         <v>0.36</v>
       </c>
       <c r="AP236">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ236">
         <v>0.46</v>
@@ -50130,7 +50142,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50336,7 +50348,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -50414,7 +50426,7 @@
         <v>0.91</v>
       </c>
       <c r="AP238">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ238">
         <v>1.21</v>
@@ -50620,7 +50632,7 @@
         <v>0.91</v>
       </c>
       <c r="AP239">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ239">
         <v>0.79</v>
@@ -51366,7 +51378,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51447,7 +51459,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ243">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR243">
         <v>1.16</v>
@@ -51778,7 +51790,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51984,7 +51996,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52190,7 +52202,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52602,7 +52614,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53014,7 +53026,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53220,7 +53232,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53298,7 +53310,7 @@
         <v>0.83</v>
       </c>
       <c r="AP252">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ252">
         <v>0.79</v>
@@ -53426,7 +53438,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53507,7 +53519,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ253">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="AR253">
         <v>1.4</v>
@@ -53838,7 +53850,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -53919,7 +53931,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ255">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR255">
         <v>1.79</v>
@@ -54740,10 +54752,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP259">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ259">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR259">
         <v>1.28</v>
@@ -54868,7 +54880,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55486,7 +55498,7 @@
         <v>262</v>
       </c>
       <c r="P263" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q263">
         <v>1.95</v>
@@ -55692,7 +55704,7 @@
         <v>263</v>
       </c>
       <c r="P264" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q264">
         <v>5</v>
@@ -56310,7 +56322,7 @@
         <v>221</v>
       </c>
       <c r="P267" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q267">
         <v>2.25</v>
@@ -56516,7 +56528,7 @@
         <v>104</v>
       </c>
       <c r="P268" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q268">
         <v>2.88</v>
@@ -56879,6 +56891,830 @@
       </c>
       <c r="BP269">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7465263</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45730.70833333334</v>
+      </c>
+      <c r="F270">
+        <v>28</v>
+      </c>
+      <c r="G270" t="s">
+        <v>73</v>
+      </c>
+      <c r="H270" t="s">
+        <v>86</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>1</v>
+      </c>
+      <c r="K270">
+        <v>1</v>
+      </c>
+      <c r="L270">
+        <v>2</v>
+      </c>
+      <c r="M270">
+        <v>2</v>
+      </c>
+      <c r="N270">
+        <v>4</v>
+      </c>
+      <c r="O270" t="s">
+        <v>265</v>
+      </c>
+      <c r="P270" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q270">
+        <v>3.75</v>
+      </c>
+      <c r="R270">
+        <v>1.91</v>
+      </c>
+      <c r="S270">
+        <v>3.5</v>
+      </c>
+      <c r="T270">
+        <v>1.57</v>
+      </c>
+      <c r="U270">
+        <v>2.25</v>
+      </c>
+      <c r="V270">
+        <v>3.75</v>
+      </c>
+      <c r="W270">
+        <v>1.25</v>
+      </c>
+      <c r="X270">
+        <v>13</v>
+      </c>
+      <c r="Y270">
+        <v>1.04</v>
+      </c>
+      <c r="Z270">
+        <v>2.8</v>
+      </c>
+      <c r="AA270">
+        <v>3</v>
+      </c>
+      <c r="AB270">
+        <v>2.62</v>
+      </c>
+      <c r="AC270">
+        <v>1.1</v>
+      </c>
+      <c r="AD270">
+        <v>6.5</v>
+      </c>
+      <c r="AE270">
+        <v>1.5</v>
+      </c>
+      <c r="AF270">
+        <v>2.4</v>
+      </c>
+      <c r="AG270">
+        <v>2.63</v>
+      </c>
+      <c r="AH270">
+        <v>1.5</v>
+      </c>
+      <c r="AI270">
+        <v>2.1</v>
+      </c>
+      <c r="AJ270">
+        <v>1.67</v>
+      </c>
+      <c r="AK270">
+        <v>1.46</v>
+      </c>
+      <c r="AL270">
+        <v>1.36</v>
+      </c>
+      <c r="AM270">
+        <v>1.42</v>
+      </c>
+      <c r="AN270">
+        <v>1</v>
+      </c>
+      <c r="AO270">
+        <v>0.71</v>
+      </c>
+      <c r="AP270">
+        <v>1</v>
+      </c>
+      <c r="AQ270">
+        <v>0.73</v>
+      </c>
+      <c r="AR270">
+        <v>1.38</v>
+      </c>
+      <c r="AS270">
+        <v>1.24</v>
+      </c>
+      <c r="AT270">
+        <v>2.62</v>
+      </c>
+      <c r="AU270">
+        <v>8</v>
+      </c>
+      <c r="AV270">
+        <v>4</v>
+      </c>
+      <c r="AW270">
+        <v>7</v>
+      </c>
+      <c r="AX270">
+        <v>6</v>
+      </c>
+      <c r="AY270">
+        <v>17</v>
+      </c>
+      <c r="AZ270">
+        <v>11</v>
+      </c>
+      <c r="BA270">
+        <v>4</v>
+      </c>
+      <c r="BB270">
+        <v>5</v>
+      </c>
+      <c r="BC270">
+        <v>9</v>
+      </c>
+      <c r="BD270">
+        <v>2</v>
+      </c>
+      <c r="BE270">
+        <v>6.4</v>
+      </c>
+      <c r="BF270">
+        <v>1.98</v>
+      </c>
+      <c r="BG270">
+        <v>1.48</v>
+      </c>
+      <c r="BH270">
+        <v>2.45</v>
+      </c>
+      <c r="BI270">
+        <v>1.79</v>
+      </c>
+      <c r="BJ270">
+        <v>1.9</v>
+      </c>
+      <c r="BK270">
+        <v>2.28</v>
+      </c>
+      <c r="BL270">
+        <v>1.54</v>
+      </c>
+      <c r="BM270">
+        <v>2.95</v>
+      </c>
+      <c r="BN270">
+        <v>1.33</v>
+      </c>
+      <c r="BO270">
+        <v>3.95</v>
+      </c>
+      <c r="BP270">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7465260</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45731.41666666666</v>
+      </c>
+      <c r="F271">
+        <v>28</v>
+      </c>
+      <c r="G271" t="s">
+        <v>78</v>
+      </c>
+      <c r="H271" t="s">
+        <v>72</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>0</v>
+      </c>
+      <c r="L271">
+        <v>0</v>
+      </c>
+      <c r="M271">
+        <v>1</v>
+      </c>
+      <c r="N271">
+        <v>1</v>
+      </c>
+      <c r="O271" t="s">
+        <v>104</v>
+      </c>
+      <c r="P271" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q271">
+        <v>5.5</v>
+      </c>
+      <c r="R271">
+        <v>2.2</v>
+      </c>
+      <c r="S271">
+        <v>2.3</v>
+      </c>
+      <c r="T271">
+        <v>1.4</v>
+      </c>
+      <c r="U271">
+        <v>2.75</v>
+      </c>
+      <c r="V271">
+        <v>3</v>
+      </c>
+      <c r="W271">
+        <v>1.36</v>
+      </c>
+      <c r="X271">
+        <v>8</v>
+      </c>
+      <c r="Y271">
+        <v>1.08</v>
+      </c>
+      <c r="Z271">
+        <v>4.8</v>
+      </c>
+      <c r="AA271">
+        <v>3.75</v>
+      </c>
+      <c r="AB271">
+        <v>1.7</v>
+      </c>
+      <c r="AC271">
+        <v>1.05</v>
+      </c>
+      <c r="AD271">
+        <v>9.5</v>
+      </c>
+      <c r="AE271">
+        <v>1.3</v>
+      </c>
+      <c r="AF271">
+        <v>3.45</v>
+      </c>
+      <c r="AG271">
+        <v>1.91</v>
+      </c>
+      <c r="AH271">
+        <v>1.83</v>
+      </c>
+      <c r="AI271">
+        <v>1.91</v>
+      </c>
+      <c r="AJ271">
+        <v>1.91</v>
+      </c>
+      <c r="AK271">
+        <v>2.1</v>
+      </c>
+      <c r="AL271">
+        <v>1.26</v>
+      </c>
+      <c r="AM271">
+        <v>1.18</v>
+      </c>
+      <c r="AN271">
+        <v>1</v>
+      </c>
+      <c r="AO271">
+        <v>0.54</v>
+      </c>
+      <c r="AP271">
+        <v>0.93</v>
+      </c>
+      <c r="AQ271">
+        <v>0.71</v>
+      </c>
+      <c r="AR271">
+        <v>1.11</v>
+      </c>
+      <c r="AS271">
+        <v>1.28</v>
+      </c>
+      <c r="AT271">
+        <v>2.39</v>
+      </c>
+      <c r="AU271">
+        <v>3</v>
+      </c>
+      <c r="AV271">
+        <v>2</v>
+      </c>
+      <c r="AW271">
+        <v>3</v>
+      </c>
+      <c r="AX271">
+        <v>9</v>
+      </c>
+      <c r="AY271">
+        <v>6</v>
+      </c>
+      <c r="AZ271">
+        <v>16</v>
+      </c>
+      <c r="BA271">
+        <v>3</v>
+      </c>
+      <c r="BB271">
+        <v>4</v>
+      </c>
+      <c r="BC271">
+        <v>7</v>
+      </c>
+      <c r="BD271">
+        <v>2.91</v>
+      </c>
+      <c r="BE271">
+        <v>8.4</v>
+      </c>
+      <c r="BF271">
+        <v>1.6</v>
+      </c>
+      <c r="BG271">
+        <v>1.39</v>
+      </c>
+      <c r="BH271">
+        <v>2.67</v>
+      </c>
+      <c r="BI271">
+        <v>1.67</v>
+      </c>
+      <c r="BJ271">
+        <v>2.1</v>
+      </c>
+      <c r="BK271">
+        <v>2.19</v>
+      </c>
+      <c r="BL271">
+        <v>1.57</v>
+      </c>
+      <c r="BM271">
+        <v>2.92</v>
+      </c>
+      <c r="BN271">
+        <v>1.31</v>
+      </c>
+      <c r="BO271">
+        <v>4.2</v>
+      </c>
+      <c r="BP271">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7469686</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45731.51041666666</v>
+      </c>
+      <c r="F272">
+        <v>28</v>
+      </c>
+      <c r="G272" t="s">
+        <v>77</v>
+      </c>
+      <c r="H272" t="s">
+        <v>82</v>
+      </c>
+      <c r="I272">
+        <v>0</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>0</v>
+      </c>
+      <c r="L272">
+        <v>2</v>
+      </c>
+      <c r="M272">
+        <v>1</v>
+      </c>
+      <c r="N272">
+        <v>3</v>
+      </c>
+      <c r="O272" t="s">
+        <v>266</v>
+      </c>
+      <c r="P272" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q272">
+        <v>2.6</v>
+      </c>
+      <c r="R272">
+        <v>1.95</v>
+      </c>
+      <c r="S272">
+        <v>5.5</v>
+      </c>
+      <c r="T272">
+        <v>1.57</v>
+      </c>
+      <c r="U272">
+        <v>2.25</v>
+      </c>
+      <c r="V272">
+        <v>3.75</v>
+      </c>
+      <c r="W272">
+        <v>1.25</v>
+      </c>
+      <c r="X272">
+        <v>11</v>
+      </c>
+      <c r="Y272">
+        <v>1.05</v>
+      </c>
+      <c r="Z272">
+        <v>1.8</v>
+      </c>
+      <c r="AA272">
+        <v>3.4</v>
+      </c>
+      <c r="AB272">
+        <v>4.6</v>
+      </c>
+      <c r="AC272">
+        <v>1.09</v>
+      </c>
+      <c r="AD272">
+        <v>7</v>
+      </c>
+      <c r="AE272">
+        <v>1.48</v>
+      </c>
+      <c r="AF272">
+        <v>2.6</v>
+      </c>
+      <c r="AG272">
+        <v>2.37</v>
+      </c>
+      <c r="AH272">
+        <v>1.53</v>
+      </c>
+      <c r="AI272">
+        <v>2.2</v>
+      </c>
+      <c r="AJ272">
+        <v>1.62</v>
+      </c>
+      <c r="AK272">
+        <v>1.19</v>
+      </c>
+      <c r="AL272">
+        <v>1.31</v>
+      </c>
+      <c r="AM272">
+        <v>1.95</v>
+      </c>
+      <c r="AN272">
+        <v>1.43</v>
+      </c>
+      <c r="AO272">
+        <v>0.42</v>
+      </c>
+      <c r="AP272">
+        <v>1.53</v>
+      </c>
+      <c r="AQ272">
+        <v>0.38</v>
+      </c>
+      <c r="AR272">
+        <v>1.3</v>
+      </c>
+      <c r="AS272">
+        <v>0.83</v>
+      </c>
+      <c r="AT272">
+        <v>2.13</v>
+      </c>
+      <c r="AU272">
+        <v>8</v>
+      </c>
+      <c r="AV272">
+        <v>0</v>
+      </c>
+      <c r="AW272">
+        <v>6</v>
+      </c>
+      <c r="AX272">
+        <v>3</v>
+      </c>
+      <c r="AY272">
+        <v>21</v>
+      </c>
+      <c r="AZ272">
+        <v>3</v>
+      </c>
+      <c r="BA272">
+        <v>6</v>
+      </c>
+      <c r="BB272">
+        <v>2</v>
+      </c>
+      <c r="BC272">
+        <v>8</v>
+      </c>
+      <c r="BD272">
+        <v>1.48</v>
+      </c>
+      <c r="BE272">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF272">
+        <v>3.35</v>
+      </c>
+      <c r="BG272">
+        <v>1.36</v>
+      </c>
+      <c r="BH272">
+        <v>2.79</v>
+      </c>
+      <c r="BI272">
+        <v>1.68</v>
+      </c>
+      <c r="BJ272">
+        <v>2.06</v>
+      </c>
+      <c r="BK272">
+        <v>2.12</v>
+      </c>
+      <c r="BL272">
+        <v>1.61</v>
+      </c>
+      <c r="BM272">
+        <v>2.81</v>
+      </c>
+      <c r="BN272">
+        <v>1.33</v>
+      </c>
+      <c r="BO272">
+        <v>3.94</v>
+      </c>
+      <c r="BP272">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7465262</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45731.60416666666</v>
+      </c>
+      <c r="F273">
+        <v>28</v>
+      </c>
+      <c r="G273" t="s">
+        <v>79</v>
+      </c>
+      <c r="H273" t="s">
+        <v>84</v>
+      </c>
+      <c r="I273">
+        <v>1</v>
+      </c>
+      <c r="J273">
+        <v>2</v>
+      </c>
+      <c r="K273">
+        <v>3</v>
+      </c>
+      <c r="L273">
+        <v>1</v>
+      </c>
+      <c r="M273">
+        <v>2</v>
+      </c>
+      <c r="N273">
+        <v>3</v>
+      </c>
+      <c r="O273" t="s">
+        <v>138</v>
+      </c>
+      <c r="P273" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q273">
+        <v>3.6</v>
+      </c>
+      <c r="R273">
+        <v>2.5</v>
+      </c>
+      <c r="S273">
+        <v>2.5</v>
+      </c>
+      <c r="T273">
+        <v>1.25</v>
+      </c>
+      <c r="U273">
+        <v>3.75</v>
+      </c>
+      <c r="V273">
+        <v>2.2</v>
+      </c>
+      <c r="W273">
+        <v>1.62</v>
+      </c>
+      <c r="X273">
+        <v>5</v>
+      </c>
+      <c r="Y273">
+        <v>1.17</v>
+      </c>
+      <c r="Z273">
+        <v>3.25</v>
+      </c>
+      <c r="AA273">
+        <v>3.9</v>
+      </c>
+      <c r="AB273">
+        <v>2</v>
+      </c>
+      <c r="AC273">
+        <v>1.01</v>
+      </c>
+      <c r="AD273">
+        <v>13</v>
+      </c>
+      <c r="AE273">
+        <v>1.15</v>
+      </c>
+      <c r="AF273">
+        <v>5.25</v>
+      </c>
+      <c r="AG273">
+        <v>1.5</v>
+      </c>
+      <c r="AH273">
+        <v>2.63</v>
+      </c>
+      <c r="AI273">
+        <v>1.44</v>
+      </c>
+      <c r="AJ273">
+        <v>2.63</v>
+      </c>
+      <c r="AK273">
+        <v>1.78</v>
+      </c>
+      <c r="AL273">
+        <v>1.24</v>
+      </c>
+      <c r="AM273">
+        <v>1.32</v>
+      </c>
+      <c r="AN273">
+        <v>1.67</v>
+      </c>
+      <c r="AO273">
+        <v>1.64</v>
+      </c>
+      <c r="AP273">
+        <v>1.54</v>
+      </c>
+      <c r="AQ273">
+        <v>1.73</v>
+      </c>
+      <c r="AR273">
+        <v>1.64</v>
+      </c>
+      <c r="AS273">
+        <v>1.7</v>
+      </c>
+      <c r="AT273">
+        <v>3.34</v>
+      </c>
+      <c r="AU273">
+        <v>11</v>
+      </c>
+      <c r="AV273">
+        <v>6</v>
+      </c>
+      <c r="AW273">
+        <v>13</v>
+      </c>
+      <c r="AX273">
+        <v>4</v>
+      </c>
+      <c r="AY273">
+        <v>25</v>
+      </c>
+      <c r="AZ273">
+        <v>11</v>
+      </c>
+      <c r="BA273">
+        <v>11</v>
+      </c>
+      <c r="BB273">
+        <v>4</v>
+      </c>
+      <c r="BC273">
+        <v>15</v>
+      </c>
+      <c r="BD273">
+        <v>2.25</v>
+      </c>
+      <c r="BE273">
+        <v>6.55</v>
+      </c>
+      <c r="BF273">
+        <v>2.04</v>
+      </c>
+      <c r="BG273">
+        <v>1.22</v>
+      </c>
+      <c r="BH273">
+        <v>3.48</v>
+      </c>
+      <c r="BI273">
+        <v>1.45</v>
+      </c>
+      <c r="BJ273">
+        <v>2.48</v>
+      </c>
+      <c r="BK273">
+        <v>1.81</v>
+      </c>
+      <c r="BL273">
+        <v>1.89</v>
+      </c>
+      <c r="BM273">
+        <v>2.3</v>
+      </c>
+      <c r="BN273">
+        <v>1.52</v>
+      </c>
+      <c r="BO273">
+        <v>3.05</v>
+      </c>
+      <c r="BP273">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1476,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP273"/>
+  <dimension ref="A1:BP274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3873,7 +3873,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ12">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>1.07</v>
@@ -6551,7 +6551,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ25">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>0.96</v>
@@ -7372,7 +7372,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>0.75</v>
@@ -11080,7 +11080,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>2.14</v>
@@ -11495,7 +11495,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ49">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR49">
         <v>1.74</v>
@@ -15200,7 +15200,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ67">
         <v>1.21</v>
@@ -16851,7 +16851,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ75">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.11</v>
@@ -18293,7 +18293,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ82">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR82">
         <v>1.25</v>
@@ -19526,7 +19526,7 @@
         <v>2</v>
       </c>
       <c r="AP88">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ88">
         <v>1.54</v>
@@ -20968,7 +20968,7 @@
         <v>1.25</v>
       </c>
       <c r="AP95">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ95">
         <v>1.08</v>
@@ -23649,7 +23649,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ108">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -24882,7 +24882,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ114">
         <v>0.71</v>
@@ -28796,7 +28796,7 @@
         <v>0.17</v>
       </c>
       <c r="AP133">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
         <v>0.38</v>
@@ -30035,7 +30035,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ139">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR139">
         <v>1.33</v>
@@ -33328,7 +33328,7 @@
         <v>1.71</v>
       </c>
       <c r="AP155">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ155">
         <v>1.73</v>
@@ -34567,7 +34567,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ161">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR161">
         <v>1.1</v>
@@ -36627,7 +36627,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ171">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR171">
         <v>1.12</v>
@@ -37036,7 +37036,7 @@
         <v>0.38</v>
       </c>
       <c r="AP173">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ173">
         <v>0.21</v>
@@ -40129,7 +40129,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ188">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR188">
         <v>1.34</v>
@@ -41156,7 +41156,7 @@
         <v>0.67</v>
       </c>
       <c r="AP193">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ193">
         <v>1.21</v>
@@ -44661,7 +44661,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ210">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR210">
         <v>2.02</v>
@@ -46924,7 +46924,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ221">
         <v>0.79</v>
@@ -49190,7 +49190,7 @@
         <v>1</v>
       </c>
       <c r="AP232">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ232">
         <v>1.08</v>
@@ -50017,7 +50017,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ236">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR236">
         <v>1.64</v>
@@ -53516,7 +53516,7 @@
         <v>0.5</v>
       </c>
       <c r="AP253">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ253">
         <v>0.71</v>
@@ -54961,7 +54961,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ260">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR260">
         <v>1.48</v>
@@ -57715,6 +57715,212 @@
       </c>
       <c r="BP273">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="274" spans="1:68">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>7465256</v>
+      </c>
+      <c r="C274" t="s">
+        <v>68</v>
+      </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274" s="2">
+        <v>45731.70833333334</v>
+      </c>
+      <c r="F274">
+        <v>28</v>
+      </c>
+      <c r="G274" t="s">
+        <v>89</v>
+      </c>
+      <c r="H274" t="s">
+        <v>75</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>0</v>
+      </c>
+      <c r="L274">
+        <v>1</v>
+      </c>
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>2</v>
+      </c>
+      <c r="O274" t="s">
+        <v>267</v>
+      </c>
+      <c r="P274" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q274">
+        <v>2.63</v>
+      </c>
+      <c r="R274">
+        <v>2.1</v>
+      </c>
+      <c r="S274">
+        <v>4.33</v>
+      </c>
+      <c r="T274">
+        <v>1.44</v>
+      </c>
+      <c r="U274">
+        <v>2.63</v>
+      </c>
+      <c r="V274">
+        <v>3.25</v>
+      </c>
+      <c r="W274">
+        <v>1.33</v>
+      </c>
+      <c r="X274">
+        <v>9</v>
+      </c>
+      <c r="Y274">
+        <v>1.07</v>
+      </c>
+      <c r="Z274">
+        <v>2</v>
+      </c>
+      <c r="AA274">
+        <v>3.4</v>
+      </c>
+      <c r="AB274">
+        <v>3.7</v>
+      </c>
+      <c r="AC274">
+        <v>1.06</v>
+      </c>
+      <c r="AD274">
+        <v>8.5</v>
+      </c>
+      <c r="AE274">
+        <v>1.35</v>
+      </c>
+      <c r="AF274">
+        <v>3.1</v>
+      </c>
+      <c r="AG274">
+        <v>2</v>
+      </c>
+      <c r="AH274">
+        <v>1.7</v>
+      </c>
+      <c r="AI274">
+        <v>1.91</v>
+      </c>
+      <c r="AJ274">
+        <v>1.91</v>
+      </c>
+      <c r="AK274">
+        <v>1.26</v>
+      </c>
+      <c r="AL274">
+        <v>1.31</v>
+      </c>
+      <c r="AM274">
+        <v>1.77</v>
+      </c>
+      <c r="AN274">
+        <v>1.54</v>
+      </c>
+      <c r="AO274">
+        <v>0.46</v>
+      </c>
+      <c r="AP274">
+        <v>1.5</v>
+      </c>
+      <c r="AQ274">
+        <v>0.5</v>
+      </c>
+      <c r="AR274">
+        <v>1.4</v>
+      </c>
+      <c r="AS274">
+        <v>1.01</v>
+      </c>
+      <c r="AT274">
+        <v>2.41</v>
+      </c>
+      <c r="AU274">
+        <v>5</v>
+      </c>
+      <c r="AV274">
+        <v>3</v>
+      </c>
+      <c r="AW274">
+        <v>10</v>
+      </c>
+      <c r="AX274">
+        <v>10</v>
+      </c>
+      <c r="AY274">
+        <v>18</v>
+      </c>
+      <c r="AZ274">
+        <v>15</v>
+      </c>
+      <c r="BA274">
+        <v>9</v>
+      </c>
+      <c r="BB274">
+        <v>4</v>
+      </c>
+      <c r="BC274">
+        <v>13</v>
+      </c>
+      <c r="BD274">
+        <v>1.52</v>
+      </c>
+      <c r="BE274">
+        <v>9</v>
+      </c>
+      <c r="BF274">
+        <v>3.14</v>
+      </c>
+      <c r="BG274">
+        <v>1.27</v>
+      </c>
+      <c r="BH274">
+        <v>3.14</v>
+      </c>
+      <c r="BI274">
+        <v>1.52</v>
+      </c>
+      <c r="BJ274">
+        <v>2.3</v>
+      </c>
+      <c r="BK274">
+        <v>1.92</v>
+      </c>
+      <c r="BL274">
+        <v>1.79</v>
+      </c>
+      <c r="BM274">
+        <v>2.48</v>
+      </c>
+      <c r="BN274">
+        <v>1.45</v>
+      </c>
+      <c r="BO274">
+        <v>3.34</v>
+      </c>
+      <c r="BP274">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="374">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -820,6 +820,15 @@
     <t>['64']</t>
   </si>
   <si>
+    <t>['29', '44']</t>
+  </si>
+  <si>
+    <t>['58', '72']</t>
+  </si>
+  <si>
+    <t>['45', '70']</t>
+  </si>
+  <si>
     <t>['17']</t>
   </si>
   <si>
@@ -1115,6 +1124,18 @@
   </si>
   <si>
     <t>['17', '23']</t>
+  </si>
+  <si>
+    <t>['64', '78', '82']</t>
+  </si>
+  <si>
+    <t>['55', '71']</t>
+  </si>
+  <si>
+    <t>['20', '80']</t>
+  </si>
+  <si>
+    <t>['72', '78', '90+2', '90+8']</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP274"/>
+  <dimension ref="A1:BP279"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1813,7 +1834,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ2">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2144,7 +2165,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2350,7 +2371,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2556,7 +2577,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2634,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6">
         <v>0.71</v>
@@ -2762,7 +2783,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2843,7 +2864,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2968,7 +2989,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3174,7 +3195,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3586,7 +3607,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3998,7 +4019,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4076,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ13">
         <v>1.71</v>
@@ -4282,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14">
         <v>1.31</v>
@@ -4491,7 +4512,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ15">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4697,7 +4718,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5312,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ19">
         <v>0.79</v>
@@ -5521,7 +5542,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ20">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5724,7 +5745,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ21">
         <v>0.93</v>
@@ -5852,7 +5873,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6264,7 +6285,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6342,10 +6363,10 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ24">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6960,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ27">
         <v>0.38</v>
@@ -7088,7 +7109,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -8324,7 +8345,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8608,7 +8629,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ35">
         <v>1.31</v>
@@ -8942,7 +8963,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9020,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ37">
         <v>0.71</v>
@@ -9148,7 +9169,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9226,7 +9247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ38">
         <v>0.93</v>
@@ -9435,7 +9456,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR39">
         <v>1.12</v>
@@ -9641,7 +9662,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ40">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR40">
         <v>2.11</v>
@@ -9972,7 +9993,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10178,7 +10199,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10462,10 +10483,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ44">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10590,7 +10611,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -11002,7 +11023,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11083,7 +11104,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR47">
         <v>1.41</v>
@@ -11208,7 +11229,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11289,7 +11310,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11492,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ49">
         <v>0.5</v>
@@ -11698,7 +11719,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ50">
         <v>0.75</v>
@@ -11907,7 +11928,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ51">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR51">
         <v>1.4</v>
@@ -12113,7 +12134,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ52">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12238,7 +12259,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12316,10 +12337,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ53">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR53">
         <v>1.17</v>
@@ -12731,7 +12752,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -12856,7 +12877,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -12934,7 +12955,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56">
         <v>0.79</v>
@@ -13886,7 +13907,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -13967,7 +13988,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ61">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR61">
         <v>1.71</v>
@@ -14170,7 +14191,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ62">
         <v>1.69</v>
@@ -14298,7 +14319,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14710,7 +14731,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14788,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ65">
         <v>0.21</v>
@@ -14916,7 +14937,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15409,7 +15430,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ68">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR68">
         <v>1.97</v>
@@ -15534,7 +15555,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15740,7 +15761,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15821,7 +15842,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR70">
         <v>1.36</v>
@@ -16152,7 +16173,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16642,7 +16663,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ74">
         <v>0.71</v>
@@ -16976,7 +16997,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17054,10 +17075,10 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ76">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR76">
         <v>1.49</v>
@@ -17878,7 +17899,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ80">
         <v>1.73</v>
@@ -18006,7 +18027,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18290,7 +18311,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ82">
         <v>0.5</v>
@@ -19036,7 +19057,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19448,7 +19469,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19529,7 +19550,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ88">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19654,7 +19675,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19735,7 +19756,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ89">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR89">
         <v>1.08</v>
@@ -19938,10 +19959,10 @@
         <v>0.67</v>
       </c>
       <c r="AP90">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ90">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR90">
         <v>1.55</v>
@@ -20066,7 +20087,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20272,7 +20293,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20684,7 +20705,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -20762,10 +20783,10 @@
         <v>0.5</v>
       </c>
       <c r="AP94">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -20971,7 +20992,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ95">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -21096,7 +21117,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21586,7 +21607,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ98">
         <v>0.71</v>
@@ -21795,7 +21816,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ99">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR99">
         <v>1.66</v>
@@ -22126,7 +22147,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22332,7 +22353,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22538,7 +22559,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22822,7 +22843,7 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ104">
         <v>0.73</v>
@@ -23156,7 +23177,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23237,7 +23258,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ106">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR106">
         <v>1.96</v>
@@ -23440,7 +23461,7 @@
         <v>0.75</v>
       </c>
       <c r="AP107">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ107">
         <v>0.71</v>
@@ -23980,7 +24001,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24267,7 +24288,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ111">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR111">
         <v>1.44</v>
@@ -24676,7 +24697,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ113">
         <v>0.21</v>
@@ -24804,7 +24825,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25088,7 +25109,7 @@
         <v>0.6</v>
       </c>
       <c r="AP115">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ115">
         <v>0.79</v>
@@ -25422,7 +25443,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25500,10 +25521,10 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ117">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR117">
         <v>1.53</v>
@@ -25628,7 +25649,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25709,7 +25730,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ118">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -25915,7 +25936,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ119">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -26040,7 +26061,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26118,7 +26139,7 @@
         <v>0.5</v>
       </c>
       <c r="AP120">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120">
         <v>0.79</v>
@@ -26736,7 +26757,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ123">
         <v>1.21</v>
@@ -26864,7 +26885,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27563,7 +27584,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ127">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -27769,7 +27790,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ128">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR128">
         <v>1.58</v>
@@ -28100,7 +28121,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28181,7 +28202,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ130">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR130">
         <v>1.31</v>
@@ -28384,7 +28405,7 @@
         <v>0.43</v>
       </c>
       <c r="AP131">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ131">
         <v>0.73</v>
@@ -28512,7 +28533,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28924,7 +28945,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29005,7 +29026,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ134">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR134">
         <v>1.32</v>
@@ -29130,7 +29151,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29208,7 +29229,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ135">
         <v>1.71</v>
@@ -29414,7 +29435,7 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ136">
         <v>1.21</v>
@@ -29542,7 +29563,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29620,7 +29641,7 @@
         <v>1.8</v>
       </c>
       <c r="AP137">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ137">
         <v>1.73</v>
@@ -29829,7 +29850,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ138">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR138">
         <v>1.36</v>
@@ -30160,7 +30181,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30778,7 +30799,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30984,7 +31005,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31271,7 +31292,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ145">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR145">
         <v>1.86</v>
@@ -31396,7 +31417,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31474,10 +31495,10 @@
         <v>1.33</v>
       </c>
       <c r="AP146">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ146">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR146">
         <v>1.72</v>
@@ -31683,7 +31704,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ147">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR147">
         <v>1.56</v>
@@ -31886,7 +31907,7 @@
         <v>0.83</v>
       </c>
       <c r="AP148">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ148">
         <v>0.75</v>
@@ -32014,7 +32035,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32095,7 +32116,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ149">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR149">
         <v>1.29</v>
@@ -32220,7 +32241,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32838,7 +32859,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32919,7 +32940,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ153">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR153">
         <v>1.84</v>
@@ -33250,7 +33271,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33456,7 +33477,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33534,10 +33555,10 @@
         <v>1.57</v>
       </c>
       <c r="AP156">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ156">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR156">
         <v>0.98</v>
@@ -33868,7 +33889,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -33946,7 +33967,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ158">
         <v>0.73</v>
@@ -34074,7 +34095,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34152,7 +34173,7 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ159">
         <v>1.21</v>
@@ -35182,7 +35203,7 @@
         <v>0.57</v>
       </c>
       <c r="AP164">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ164">
         <v>0.71</v>
@@ -35310,7 +35331,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35388,7 +35409,7 @@
         <v>1.88</v>
       </c>
       <c r="AP165">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ165">
         <v>1.73</v>
@@ -35594,10 +35615,10 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ166">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR166">
         <v>1.77</v>
@@ -35722,7 +35743,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35803,7 +35824,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ167">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR167">
         <v>1.17</v>
@@ -36134,7 +36155,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36215,7 +36236,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ169">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36546,7 +36567,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37451,7 +37472,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ175">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR175">
         <v>1.41</v>
@@ -37654,10 +37675,10 @@
         <v>1.5</v>
       </c>
       <c r="AP176">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ176">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37782,7 +37803,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37988,7 +38009,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38194,7 +38215,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38400,7 +38421,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38478,7 +38499,7 @@
         <v>1.75</v>
       </c>
       <c r="AP180">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ180">
         <v>1.71</v>
@@ -39018,7 +39039,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39302,7 +39323,7 @@
         <v>0.5</v>
       </c>
       <c r="AP184">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ184">
         <v>0.71</v>
@@ -39430,7 +39451,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39717,7 +39738,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ186">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR186">
         <v>1.03</v>
@@ -40126,7 +40147,7 @@
         <v>0.33</v>
       </c>
       <c r="AP188">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ188">
         <v>0.5</v>
@@ -40254,7 +40275,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40335,7 +40356,7 @@
         <v>1</v>
       </c>
       <c r="AQ189">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -40538,7 +40559,7 @@
         <v>0.88</v>
       </c>
       <c r="AP190">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ190">
         <v>0.75</v>
@@ -41078,7 +41099,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41362,7 +41383,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ194">
         <v>1.69</v>
@@ -41490,7 +41511,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41777,7 +41798,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ196">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR196">
         <v>1.38</v>
@@ -41902,7 +41923,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -41983,7 +42004,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ197">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR197">
         <v>1.41</v>
@@ -42108,7 +42129,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42392,7 +42413,7 @@
         <v>1.3</v>
       </c>
       <c r="AP199">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ199">
         <v>1.21</v>
@@ -42601,7 +42622,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ200">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR200">
         <v>1.33</v>
@@ -43138,7 +43159,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43219,7 +43240,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ203">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR203">
         <v>1.2</v>
@@ -43344,7 +43365,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43422,7 +43443,7 @@
         <v>1.7</v>
       </c>
       <c r="AP204">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ204">
         <v>1.71</v>
@@ -43550,7 +43571,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43628,7 +43649,7 @@
         <v>0.11</v>
       </c>
       <c r="AP205">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ205">
         <v>0.38</v>
@@ -43756,7 +43777,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44040,7 +44061,7 @@
         <v>1.2</v>
       </c>
       <c r="AP207">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ207">
         <v>0.93</v>
@@ -44168,7 +44189,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44249,7 +44270,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ208">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR208">
         <v>1.41</v>
@@ -44992,7 +45013,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45070,7 +45091,7 @@
         <v>1.27</v>
       </c>
       <c r="AP212">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ212">
         <v>1.21</v>
@@ -45688,7 +45709,7 @@
         <v>1.5</v>
       </c>
       <c r="AP215">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ215">
         <v>1.31</v>
@@ -46512,10 +46533,10 @@
         <v>1.4</v>
       </c>
       <c r="AP219">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ219">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR219">
         <v>1.48</v>
@@ -46640,7 +46661,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -46721,7 +46742,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ220">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR220">
         <v>1.72</v>
@@ -47130,7 +47151,7 @@
         <v>0.27</v>
       </c>
       <c r="AP222">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ222">
         <v>0.21</v>
@@ -47258,7 +47279,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47339,7 +47360,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ223">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR223">
         <v>1.34</v>
@@ -47670,7 +47691,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48163,7 +48184,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ227">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR227">
         <v>1.1</v>
@@ -48700,7 +48721,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -48778,10 +48799,10 @@
         <v>2</v>
       </c>
       <c r="AP230">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ230">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR230">
         <v>1.46</v>
@@ -49112,7 +49133,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49193,7 +49214,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ232">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR232">
         <v>1.36</v>
@@ -49318,7 +49339,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49396,7 +49417,7 @@
         <v>0.67</v>
       </c>
       <c r="AP233">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ233">
         <v>0.73</v>
@@ -49524,7 +49545,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -49602,7 +49623,7 @@
         <v>1.83</v>
       </c>
       <c r="AP234">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ234">
         <v>1.73</v>
@@ -49808,7 +49829,7 @@
         <v>0.45</v>
       </c>
       <c r="AP235">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ235">
         <v>0.71</v>
@@ -50142,7 +50163,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50223,7 +50244,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ237">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR237">
         <v>1.14</v>
@@ -50348,7 +50369,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -50841,7 +50862,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ240">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR240">
         <v>1.7</v>
@@ -51378,7 +51399,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51662,7 +51683,7 @@
         <v>1.75</v>
       </c>
       <c r="AP244">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ244">
         <v>1.71</v>
@@ -51790,7 +51811,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51996,7 +52017,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52077,7 +52098,7 @@
         <v>1</v>
       </c>
       <c r="AQ246">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR246">
         <v>1.41</v>
@@ -52202,7 +52223,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52614,7 +52635,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52695,7 +52716,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ249">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR249">
         <v>1.32</v>
@@ -53026,7 +53047,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53104,7 +53125,7 @@
         <v>1.36</v>
       </c>
       <c r="AP251">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ251">
         <v>1.31</v>
@@ -53232,7 +53253,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53438,7 +53459,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53722,7 +53743,7 @@
         <v>1.08</v>
       </c>
       <c r="AP254">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ254">
         <v>1.21</v>
@@ -53850,7 +53871,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -54134,10 +54155,10 @@
         <v>1.67</v>
       </c>
       <c r="AP256">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AQ256">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR256">
         <v>1.71</v>
@@ -54340,10 +54361,10 @@
         <v>1.17</v>
       </c>
       <c r="AP257">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ257">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR257">
         <v>0.96</v>
@@ -54549,7 +54570,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ258">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR258">
         <v>2</v>
@@ -54880,7 +54901,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -54958,7 +54979,7 @@
         <v>0.42</v>
       </c>
       <c r="AP260">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ260">
         <v>0.5</v>
@@ -55498,7 +55519,7 @@
         <v>262</v>
       </c>
       <c r="P263" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q263">
         <v>1.95</v>
@@ -55704,7 +55725,7 @@
         <v>263</v>
       </c>
       <c r="P264" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q264">
         <v>5</v>
@@ -56074,7 +56095,7 @@
         <v>265</v>
       </c>
       <c r="B266">
-        <v>7465248</v>
+        <v>7465246</v>
       </c>
       <c r="C266" t="s">
         <v>68</v>
@@ -56089,10 +56110,10 @@
         <v>27</v>
       </c>
       <c r="G266" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H266" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I266">
         <v>0</v>
@@ -56107,172 +56128,172 @@
         <v>1</v>
       </c>
       <c r="M266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N266">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O266" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="P266" t="s">
-        <v>104</v>
+        <v>294</v>
       </c>
       <c r="Q266">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R266">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S266">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="T266">
+        <v>1.44</v>
+      </c>
+      <c r="U266">
+        <v>2.63</v>
+      </c>
+      <c r="V266">
+        <v>3.25</v>
+      </c>
+      <c r="W266">
         <v>1.33</v>
       </c>
-      <c r="U266">
-        <v>3.25</v>
-      </c>
-      <c r="V266">
-        <v>2.63</v>
-      </c>
-      <c r="W266">
-        <v>1.44</v>
-      </c>
       <c r="X266">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="Y266">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z266">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AA266">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="AB266">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC266">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD266">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE266">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AF266">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AG266">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AH266">
+        <v>1.67</v>
+      </c>
+      <c r="AI266">
         <v>2.1</v>
       </c>
-      <c r="AI266">
-        <v>1.95</v>
-      </c>
       <c r="AJ266">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AK266">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AL266">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AM266">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AN266">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AO266">
-        <v>0.85</v>
+        <v>1.33</v>
       </c>
       <c r="AP266">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AQ266">
-        <v>0.79</v>
+        <v>1.31</v>
       </c>
       <c r="AR266">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AS266">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AT266">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AU266">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV266">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW266">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX266">
         <v>7</v>
       </c>
       <c r="AY266">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ266">
         <v>10</v>
       </c>
       <c r="BA266">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BB266">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC266">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BD266">
+        <v>1.34</v>
+      </c>
+      <c r="BE266">
+        <v>7</v>
+      </c>
+      <c r="BF266">
+        <v>3.55</v>
+      </c>
+      <c r="BG266">
+        <v>1.35</v>
+      </c>
+      <c r="BH266">
+        <v>2.9</v>
+      </c>
+      <c r="BI266">
+        <v>1.6</v>
+      </c>
+      <c r="BJ266">
+        <v>2.17</v>
+      </c>
+      <c r="BK266">
+        <v>1.97</v>
+      </c>
+      <c r="BL266">
+        <v>1.73</v>
+      </c>
+      <c r="BM266">
+        <v>2.48</v>
+      </c>
+      <c r="BN266">
+        <v>1.47</v>
+      </c>
+      <c r="BO266">
+        <v>3.25</v>
+      </c>
+      <c r="BP266">
         <v>1.28</v>
-      </c>
-      <c r="BE266">
-        <v>7.5</v>
-      </c>
-      <c r="BF266">
-        <v>3.95</v>
-      </c>
-      <c r="BG266">
-        <v>1.29</v>
-      </c>
-      <c r="BH266">
-        <v>3.15</v>
-      </c>
-      <c r="BI266">
-        <v>1.5</v>
-      </c>
-      <c r="BJ266">
-        <v>2.38</v>
-      </c>
-      <c r="BK266">
-        <v>1.81</v>
-      </c>
-      <c r="BL266">
-        <v>1.88</v>
-      </c>
-      <c r="BM266">
-        <v>2.25</v>
-      </c>
-      <c r="BN266">
-        <v>1.55</v>
-      </c>
-      <c r="BO266">
-        <v>2.9</v>
-      </c>
-      <c r="BP266">
-        <v>1.34</v>
       </c>
     </row>
     <row r="267" spans="1:68">
@@ -56280,7 +56301,7 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>7465246</v>
+        <v>7465248</v>
       </c>
       <c r="C267" t="s">
         <v>68</v>
@@ -56295,10 +56316,10 @@
         <v>27</v>
       </c>
       <c r="G267" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H267" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I267">
         <v>0</v>
@@ -56313,172 +56334,172 @@
         <v>1</v>
       </c>
       <c r="M267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N267">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O267" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="P267" t="s">
-        <v>291</v>
+        <v>104</v>
       </c>
       <c r="Q267">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="R267">
+        <v>2.4</v>
+      </c>
+      <c r="S267">
+        <v>7</v>
+      </c>
+      <c r="T267">
+        <v>1.33</v>
+      </c>
+      <c r="U267">
+        <v>3.25</v>
+      </c>
+      <c r="V267">
+        <v>2.63</v>
+      </c>
+      <c r="W267">
+        <v>1.44</v>
+      </c>
+      <c r="X267">
+        <v>6.5</v>
+      </c>
+      <c r="Y267">
+        <v>1.11</v>
+      </c>
+      <c r="Z267">
+        <v>1.42</v>
+      </c>
+      <c r="AA267">
+        <v>4.75</v>
+      </c>
+      <c r="AB267">
+        <v>7</v>
+      </c>
+      <c r="AC267">
+        <v>1.04</v>
+      </c>
+      <c r="AD267">
+        <v>13</v>
+      </c>
+      <c r="AE267">
+        <v>1.26</v>
+      </c>
+      <c r="AF267">
+        <v>4</v>
+      </c>
+      <c r="AG267">
+        <v>1.73</v>
+      </c>
+      <c r="AH267">
         <v>2.1</v>
       </c>
-      <c r="S267">
-        <v>6.5</v>
-      </c>
-      <c r="T267">
-        <v>1.44</v>
-      </c>
-      <c r="U267">
-        <v>2.63</v>
-      </c>
-      <c r="V267">
-        <v>3.25</v>
-      </c>
-      <c r="W267">
-        <v>1.33</v>
-      </c>
-      <c r="X267">
-        <v>10</v>
-      </c>
-      <c r="Y267">
+      <c r="AI267">
+        <v>1.95</v>
+      </c>
+      <c r="AJ267">
+        <v>1.8</v>
+      </c>
+      <c r="AK267">
+        <v>1.11</v>
+      </c>
+      <c r="AL267">
+        <v>1.19</v>
+      </c>
+      <c r="AM267">
+        <v>2.7</v>
+      </c>
+      <c r="AN267">
+        <v>1.77</v>
+      </c>
+      <c r="AO267">
+        <v>0.85</v>
+      </c>
+      <c r="AP267">
+        <v>1.86</v>
+      </c>
+      <c r="AQ267">
+        <v>0.79</v>
+      </c>
+      <c r="AR267">
+        <v>1.79</v>
+      </c>
+      <c r="AS267">
         <v>1.06</v>
       </c>
-      <c r="Z267">
-        <v>1.6</v>
-      </c>
-      <c r="AA267">
-        <v>3.75</v>
-      </c>
-      <c r="AB267">
-        <v>6</v>
-      </c>
-      <c r="AC267">
-        <v>1.05</v>
-      </c>
-      <c r="AD267">
-        <v>10</v>
-      </c>
-      <c r="AE267">
-        <v>1.33</v>
-      </c>
-      <c r="AF267">
-        <v>3.4</v>
-      </c>
-      <c r="AG267">
-        <v>2.2</v>
-      </c>
-      <c r="AH267">
-        <v>1.67</v>
-      </c>
-      <c r="AI267">
-        <v>2.1</v>
-      </c>
-      <c r="AJ267">
-        <v>1.67</v>
-      </c>
-      <c r="AK267">
-        <v>1.13</v>
-      </c>
-      <c r="AL267">
-        <v>1.25</v>
-      </c>
-      <c r="AM267">
-        <v>2.3</v>
-      </c>
-      <c r="AN267">
-        <v>2.15</v>
-      </c>
-      <c r="AO267">
-        <v>1.33</v>
-      </c>
-      <c r="AP267">
-        <v>2.07</v>
-      </c>
-      <c r="AQ267">
-        <v>1.31</v>
-      </c>
-      <c r="AR267">
-        <v>1.69</v>
-      </c>
-      <c r="AS267">
-        <v>1.2</v>
-      </c>
       <c r="AT267">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AU267">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV267">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW267">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX267">
         <v>7</v>
       </c>
       <c r="AY267">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ267">
         <v>10</v>
       </c>
       <c r="BA267">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="BB267">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC267">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BD267">
+        <v>1.28</v>
+      </c>
+      <c r="BE267">
+        <v>7.5</v>
+      </c>
+      <c r="BF267">
+        <v>3.95</v>
+      </c>
+      <c r="BG267">
+        <v>1.29</v>
+      </c>
+      <c r="BH267">
+        <v>3.15</v>
+      </c>
+      <c r="BI267">
+        <v>1.5</v>
+      </c>
+      <c r="BJ267">
+        <v>2.38</v>
+      </c>
+      <c r="BK267">
+        <v>1.81</v>
+      </c>
+      <c r="BL267">
+        <v>1.88</v>
+      </c>
+      <c r="BM267">
+        <v>2.25</v>
+      </c>
+      <c r="BN267">
+        <v>1.55</v>
+      </c>
+      <c r="BO267">
+        <v>2.9</v>
+      </c>
+      <c r="BP267">
         <v>1.34</v>
-      </c>
-      <c r="BE267">
-        <v>7</v>
-      </c>
-      <c r="BF267">
-        <v>3.55</v>
-      </c>
-      <c r="BG267">
-        <v>1.35</v>
-      </c>
-      <c r="BH267">
-        <v>2.9</v>
-      </c>
-      <c r="BI267">
-        <v>1.6</v>
-      </c>
-      <c r="BJ267">
-        <v>2.17</v>
-      </c>
-      <c r="BK267">
-        <v>1.97</v>
-      </c>
-      <c r="BL267">
-        <v>1.73</v>
-      </c>
-      <c r="BM267">
-        <v>2.48</v>
-      </c>
-      <c r="BN267">
-        <v>1.47</v>
-      </c>
-      <c r="BO267">
-        <v>3.25</v>
-      </c>
-      <c r="BP267">
-        <v>1.28</v>
       </c>
     </row>
     <row r="268" spans="1:68">
@@ -56528,7 +56549,7 @@
         <v>104</v>
       </c>
       <c r="P268" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q268">
         <v>2.88</v>
@@ -56940,7 +56961,7 @@
         <v>265</v>
       </c>
       <c r="P270" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q270">
         <v>3.75</v>
@@ -57558,7 +57579,7 @@
         <v>138</v>
       </c>
       <c r="P273" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q273">
         <v>3.6</v>
@@ -57921,6 +57942,1036 @@
       </c>
       <c r="BP274">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7465259</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45732.41666666666</v>
+      </c>
+      <c r="F275">
+        <v>28</v>
+      </c>
+      <c r="G275" t="s">
+        <v>85</v>
+      </c>
+      <c r="H275" t="s">
+        <v>71</v>
+      </c>
+      <c r="I275">
+        <v>2</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>2</v>
+      </c>
+      <c r="L275">
+        <v>2</v>
+      </c>
+      <c r="M275">
+        <v>3</v>
+      </c>
+      <c r="N275">
+        <v>5</v>
+      </c>
+      <c r="O275" t="s">
+        <v>268</v>
+      </c>
+      <c r="P275" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q275">
+        <v>4.33</v>
+      </c>
+      <c r="R275">
+        <v>2.05</v>
+      </c>
+      <c r="S275">
+        <v>2.75</v>
+      </c>
+      <c r="T275">
+        <v>1.5</v>
+      </c>
+      <c r="U275">
+        <v>2.5</v>
+      </c>
+      <c r="V275">
+        <v>3.4</v>
+      </c>
+      <c r="W275">
+        <v>1.3</v>
+      </c>
+      <c r="X275">
+        <v>10</v>
+      </c>
+      <c r="Y275">
+        <v>1.06</v>
+      </c>
+      <c r="Z275">
+        <v>3.9</v>
+      </c>
+      <c r="AA275">
+        <v>3.3</v>
+      </c>
+      <c r="AB275">
+        <v>2</v>
+      </c>
+      <c r="AC275">
+        <v>1.07</v>
+      </c>
+      <c r="AD275">
+        <v>8</v>
+      </c>
+      <c r="AE275">
+        <v>1.4</v>
+      </c>
+      <c r="AF275">
+        <v>2.9</v>
+      </c>
+      <c r="AG275">
+        <v>2.1</v>
+      </c>
+      <c r="AH275">
+        <v>1.67</v>
+      </c>
+      <c r="AI275">
+        <v>1.95</v>
+      </c>
+      <c r="AJ275">
+        <v>1.8</v>
+      </c>
+      <c r="AK275">
+        <v>1.78</v>
+      </c>
+      <c r="AL275">
+        <v>1.31</v>
+      </c>
+      <c r="AM275">
+        <v>1.25</v>
+      </c>
+      <c r="AN275">
+        <v>1.31</v>
+      </c>
+      <c r="AO275">
+        <v>1.15</v>
+      </c>
+      <c r="AP275">
+        <v>1.21</v>
+      </c>
+      <c r="AQ275">
+        <v>1.29</v>
+      </c>
+      <c r="AR275">
+        <v>0.95</v>
+      </c>
+      <c r="AS275">
+        <v>1.28</v>
+      </c>
+      <c r="AT275">
+        <v>2.23</v>
+      </c>
+      <c r="AU275">
+        <v>5</v>
+      </c>
+      <c r="AV275">
+        <v>7</v>
+      </c>
+      <c r="AW275">
+        <v>6</v>
+      </c>
+      <c r="AX275">
+        <v>15</v>
+      </c>
+      <c r="AY275">
+        <v>11</v>
+      </c>
+      <c r="AZ275">
+        <v>22</v>
+      </c>
+      <c r="BA275">
+        <v>3</v>
+      </c>
+      <c r="BB275">
+        <v>7</v>
+      </c>
+      <c r="BC275">
+        <v>10</v>
+      </c>
+      <c r="BD275">
+        <v>2.83</v>
+      </c>
+      <c r="BE275">
+        <v>8.6</v>
+      </c>
+      <c r="BF275">
+        <v>1.62</v>
+      </c>
+      <c r="BG275">
+        <v>1.32</v>
+      </c>
+      <c r="BH275">
+        <v>2.88</v>
+      </c>
+      <c r="BI275">
+        <v>1.61</v>
+      </c>
+      <c r="BJ275">
+        <v>2.12</v>
+      </c>
+      <c r="BK275">
+        <v>2.06</v>
+      </c>
+      <c r="BL275">
+        <v>1.68</v>
+      </c>
+      <c r="BM275">
+        <v>2.71</v>
+      </c>
+      <c r="BN275">
+        <v>1.38</v>
+      </c>
+      <c r="BO275">
+        <v>3.72</v>
+      </c>
+      <c r="BP275">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7465258</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45732.51041666666</v>
+      </c>
+      <c r="F276">
+        <v>28</v>
+      </c>
+      <c r="G276" t="s">
+        <v>80</v>
+      </c>
+      <c r="H276" t="s">
+        <v>70</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+      <c r="M276">
+        <v>1</v>
+      </c>
+      <c r="N276">
+        <v>1</v>
+      </c>
+      <c r="O276" t="s">
+        <v>104</v>
+      </c>
+      <c r="P276" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q276">
+        <v>3.75</v>
+      </c>
+      <c r="R276">
+        <v>2</v>
+      </c>
+      <c r="S276">
+        <v>3.2</v>
+      </c>
+      <c r="T276">
+        <v>1.5</v>
+      </c>
+      <c r="U276">
+        <v>2.5</v>
+      </c>
+      <c r="V276">
+        <v>3.5</v>
+      </c>
+      <c r="W276">
+        <v>1.29</v>
+      </c>
+      <c r="X276">
+        <v>11</v>
+      </c>
+      <c r="Y276">
+        <v>1.05</v>
+      </c>
+      <c r="Z276">
+        <v>2.9</v>
+      </c>
+      <c r="AA276">
+        <v>3.2</v>
+      </c>
+      <c r="AB276">
+        <v>2.45</v>
+      </c>
+      <c r="AC276">
+        <v>1.08</v>
+      </c>
+      <c r="AD276">
+        <v>7.5</v>
+      </c>
+      <c r="AE276">
+        <v>1.44</v>
+      </c>
+      <c r="AF276">
+        <v>2.75</v>
+      </c>
+      <c r="AG276">
+        <v>2.25</v>
+      </c>
+      <c r="AH276">
+        <v>1.57</v>
+      </c>
+      <c r="AI276">
+        <v>1.95</v>
+      </c>
+      <c r="AJ276">
+        <v>1.8</v>
+      </c>
+      <c r="AK276">
+        <v>1.52</v>
+      </c>
+      <c r="AL276">
+        <v>1.34</v>
+      </c>
+      <c r="AM276">
+        <v>1.38</v>
+      </c>
+      <c r="AN276">
+        <v>1.46</v>
+      </c>
+      <c r="AO276">
+        <v>1.54</v>
+      </c>
+      <c r="AP276">
+        <v>1.36</v>
+      </c>
+      <c r="AQ276">
+        <v>1.64</v>
+      </c>
+      <c r="AR276">
+        <v>1.47</v>
+      </c>
+      <c r="AS276">
+        <v>1.42</v>
+      </c>
+      <c r="AT276">
+        <v>2.89</v>
+      </c>
+      <c r="AU276">
+        <v>5</v>
+      </c>
+      <c r="AV276">
+        <v>5</v>
+      </c>
+      <c r="AW276">
+        <v>7</v>
+      </c>
+      <c r="AX276">
+        <v>5</v>
+      </c>
+      <c r="AY276">
+        <v>14</v>
+      </c>
+      <c r="AZ276">
+        <v>11</v>
+      </c>
+      <c r="BA276">
+        <v>4</v>
+      </c>
+      <c r="BB276">
+        <v>6</v>
+      </c>
+      <c r="BC276">
+        <v>10</v>
+      </c>
+      <c r="BD276">
+        <v>2.14</v>
+      </c>
+      <c r="BE276">
+        <v>6.45</v>
+      </c>
+      <c r="BF276">
+        <v>2.15</v>
+      </c>
+      <c r="BG276">
+        <v>1.28</v>
+      </c>
+      <c r="BH276">
+        <v>3.08</v>
+      </c>
+      <c r="BI276">
+        <v>1.54</v>
+      </c>
+      <c r="BJ276">
+        <v>2.25</v>
+      </c>
+      <c r="BK276">
+        <v>1.95</v>
+      </c>
+      <c r="BL276">
+        <v>1.76</v>
+      </c>
+      <c r="BM276">
+        <v>2.54</v>
+      </c>
+      <c r="BN276">
+        <v>1.43</v>
+      </c>
+      <c r="BO276">
+        <v>3.42</v>
+      </c>
+      <c r="BP276">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7465261</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F277">
+        <v>28</v>
+      </c>
+      <c r="G277" t="s">
+        <v>74</v>
+      </c>
+      <c r="H277" t="s">
+        <v>83</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>1</v>
+      </c>
+      <c r="L277">
+        <v>1</v>
+      </c>
+      <c r="M277">
+        <v>2</v>
+      </c>
+      <c r="N277">
+        <v>3</v>
+      </c>
+      <c r="O277" t="s">
+        <v>110</v>
+      </c>
+      <c r="P277" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q277">
+        <v>3.2</v>
+      </c>
+      <c r="R277">
+        <v>1.8</v>
+      </c>
+      <c r="S277">
+        <v>4.75</v>
+      </c>
+      <c r="T277">
+        <v>1.67</v>
+      </c>
+      <c r="U277">
+        <v>2.1</v>
+      </c>
+      <c r="V277">
+        <v>4.33</v>
+      </c>
+      <c r="W277">
+        <v>1.2</v>
+      </c>
+      <c r="X277">
+        <v>15</v>
+      </c>
+      <c r="Y277">
+        <v>1.03</v>
+      </c>
+      <c r="Z277">
+        <v>2.3</v>
+      </c>
+      <c r="AA277">
+        <v>2.87</v>
+      </c>
+      <c r="AB277">
+        <v>3.5</v>
+      </c>
+      <c r="AC277">
+        <v>1.14</v>
+      </c>
+      <c r="AD277">
+        <v>5.5</v>
+      </c>
+      <c r="AE277">
+        <v>1.67</v>
+      </c>
+      <c r="AF277">
+        <v>2.1</v>
+      </c>
+      <c r="AG277">
+        <v>3.2</v>
+      </c>
+      <c r="AH277">
+        <v>1.36</v>
+      </c>
+      <c r="AI277">
+        <v>2.38</v>
+      </c>
+      <c r="AJ277">
+        <v>1.53</v>
+      </c>
+      <c r="AK277">
+        <v>1.29</v>
+      </c>
+      <c r="AL277">
+        <v>1.4</v>
+      </c>
+      <c r="AM277">
+        <v>1.58</v>
+      </c>
+      <c r="AN277">
+        <v>1.71</v>
+      </c>
+      <c r="AO277">
+        <v>1.08</v>
+      </c>
+      <c r="AP277">
+        <v>1.6</v>
+      </c>
+      <c r="AQ277">
+        <v>1.21</v>
+      </c>
+      <c r="AR277">
+        <v>1.48</v>
+      </c>
+      <c r="AS277">
+        <v>1.1</v>
+      </c>
+      <c r="AT277">
+        <v>2.58</v>
+      </c>
+      <c r="AU277">
+        <v>5</v>
+      </c>
+      <c r="AV277">
+        <v>5</v>
+      </c>
+      <c r="AW277">
+        <v>7</v>
+      </c>
+      <c r="AX277">
+        <v>3</v>
+      </c>
+      <c r="AY277">
+        <v>15</v>
+      </c>
+      <c r="AZ277">
+        <v>10</v>
+      </c>
+      <c r="BA277">
+        <v>3</v>
+      </c>
+      <c r="BB277">
+        <v>2</v>
+      </c>
+      <c r="BC277">
+        <v>5</v>
+      </c>
+      <c r="BD277">
+        <v>1.67</v>
+      </c>
+      <c r="BE277">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF277">
+        <v>2.73</v>
+      </c>
+      <c r="BG277">
+        <v>1.45</v>
+      </c>
+      <c r="BH277">
+        <v>2.48</v>
+      </c>
+      <c r="BI277">
+        <v>1.83</v>
+      </c>
+      <c r="BJ277">
+        <v>1.87</v>
+      </c>
+      <c r="BK277">
+        <v>2.38</v>
+      </c>
+      <c r="BL277">
+        <v>1.49</v>
+      </c>
+      <c r="BM277">
+        <v>3.2</v>
+      </c>
+      <c r="BN277">
+        <v>1.26</v>
+      </c>
+      <c r="BO277">
+        <v>4.65</v>
+      </c>
+      <c r="BP277">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7465257</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F278">
+        <v>28</v>
+      </c>
+      <c r="G278" t="s">
+        <v>88</v>
+      </c>
+      <c r="H278" t="s">
+        <v>76</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278">
+        <v>1</v>
+      </c>
+      <c r="L278">
+        <v>2</v>
+      </c>
+      <c r="M278">
+        <v>2</v>
+      </c>
+      <c r="N278">
+        <v>4</v>
+      </c>
+      <c r="O278" t="s">
+        <v>269</v>
+      </c>
+      <c r="P278" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q278">
+        <v>3.4</v>
+      </c>
+      <c r="R278">
+        <v>1.91</v>
+      </c>
+      <c r="S278">
+        <v>4</v>
+      </c>
+      <c r="T278">
+        <v>1.62</v>
+      </c>
+      <c r="U278">
+        <v>2.2</v>
+      </c>
+      <c r="V278">
+        <v>4</v>
+      </c>
+      <c r="W278">
+        <v>1.22</v>
+      </c>
+      <c r="X278">
+        <v>13</v>
+      </c>
+      <c r="Y278">
+        <v>1.04</v>
+      </c>
+      <c r="Z278">
+        <v>2.5</v>
+      </c>
+      <c r="AA278">
+        <v>3</v>
+      </c>
+      <c r="AB278">
+        <v>3</v>
+      </c>
+      <c r="AC278">
+        <v>1.11</v>
+      </c>
+      <c r="AD278">
+        <v>6.25</v>
+      </c>
+      <c r="AE278">
+        <v>1.55</v>
+      </c>
+      <c r="AF278">
+        <v>2.3</v>
+      </c>
+      <c r="AG278">
+        <v>2.75</v>
+      </c>
+      <c r="AH278">
+        <v>1.44</v>
+      </c>
+      <c r="AI278">
+        <v>2.2</v>
+      </c>
+      <c r="AJ278">
+        <v>1.62</v>
+      </c>
+      <c r="AK278">
+        <v>1.37</v>
+      </c>
+      <c r="AL278">
+        <v>1.38</v>
+      </c>
+      <c r="AM278">
+        <v>1.49</v>
+      </c>
+      <c r="AN278">
+        <v>1.46</v>
+      </c>
+      <c r="AO278">
+        <v>1.08</v>
+      </c>
+      <c r="AP278">
+        <v>1.43</v>
+      </c>
+      <c r="AQ278">
+        <v>1.07</v>
+      </c>
+      <c r="AR278">
+        <v>1.72</v>
+      </c>
+      <c r="AS278">
+        <v>1</v>
+      </c>
+      <c r="AT278">
+        <v>2.72</v>
+      </c>
+      <c r="AU278">
+        <v>6</v>
+      </c>
+      <c r="AV278">
+        <v>5</v>
+      </c>
+      <c r="AW278">
+        <v>3</v>
+      </c>
+      <c r="AX278">
+        <v>1</v>
+      </c>
+      <c r="AY278">
+        <v>11</v>
+      </c>
+      <c r="AZ278">
+        <v>9</v>
+      </c>
+      <c r="BA278">
+        <v>4</v>
+      </c>
+      <c r="BB278">
+        <v>4</v>
+      </c>
+      <c r="BC278">
+        <v>8</v>
+      </c>
+      <c r="BD278">
+        <v>1.77</v>
+      </c>
+      <c r="BE278">
+        <v>8.4</v>
+      </c>
+      <c r="BF278">
+        <v>2.48</v>
+      </c>
+      <c r="BG278">
+        <v>1.28</v>
+      </c>
+      <c r="BH278">
+        <v>3.08</v>
+      </c>
+      <c r="BI278">
+        <v>1.55</v>
+      </c>
+      <c r="BJ278">
+        <v>2.23</v>
+      </c>
+      <c r="BK278">
+        <v>1.96</v>
+      </c>
+      <c r="BL278">
+        <v>1.75</v>
+      </c>
+      <c r="BM278">
+        <v>2.54</v>
+      </c>
+      <c r="BN278">
+        <v>1.43</v>
+      </c>
+      <c r="BO278">
+        <v>3.42</v>
+      </c>
+      <c r="BP278">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7465255</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45732.70833333334</v>
+      </c>
+      <c r="F279">
+        <v>28</v>
+      </c>
+      <c r="G279" t="s">
+        <v>87</v>
+      </c>
+      <c r="H279" t="s">
+        <v>81</v>
+      </c>
+      <c r="I279">
+        <v>1</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <v>2</v>
+      </c>
+      <c r="M279">
+        <v>4</v>
+      </c>
+      <c r="N279">
+        <v>6</v>
+      </c>
+      <c r="O279" t="s">
+        <v>270</v>
+      </c>
+      <c r="P279" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q279">
+        <v>3.4</v>
+      </c>
+      <c r="R279">
+        <v>2.38</v>
+      </c>
+      <c r="S279">
+        <v>2.75</v>
+      </c>
+      <c r="T279">
+        <v>1.29</v>
+      </c>
+      <c r="U279">
+        <v>3.5</v>
+      </c>
+      <c r="V279">
+        <v>2.38</v>
+      </c>
+      <c r="W279">
+        <v>1.53</v>
+      </c>
+      <c r="X279">
+        <v>5.5</v>
+      </c>
+      <c r="Y279">
+        <v>1.14</v>
+      </c>
+      <c r="Z279">
+        <v>2.87</v>
+      </c>
+      <c r="AA279">
+        <v>3.6</v>
+      </c>
+      <c r="AB279">
+        <v>2.25</v>
+      </c>
+      <c r="AC279">
+        <v>1.04</v>
+      </c>
+      <c r="AD279">
+        <v>10</v>
+      </c>
+      <c r="AE279">
+        <v>1.2</v>
+      </c>
+      <c r="AF279">
+        <v>4.5</v>
+      </c>
+      <c r="AG279">
+        <v>1.55</v>
+      </c>
+      <c r="AH279">
+        <v>2.3</v>
+      </c>
+      <c r="AI279">
+        <v>1.5</v>
+      </c>
+      <c r="AJ279">
+        <v>2.5</v>
+      </c>
+      <c r="AK279">
+        <v>1.6</v>
+      </c>
+      <c r="AL279">
+        <v>1.27</v>
+      </c>
+      <c r="AM279">
+        <v>1.4</v>
+      </c>
+      <c r="AN279">
+        <v>2.43</v>
+      </c>
+      <c r="AO279">
+        <v>2.14</v>
+      </c>
+      <c r="AP279">
+        <v>2.27</v>
+      </c>
+      <c r="AQ279">
+        <v>2.2</v>
+      </c>
+      <c r="AR279">
+        <v>1.69</v>
+      </c>
+      <c r="AS279">
+        <v>1.71</v>
+      </c>
+      <c r="AT279">
+        <v>3.4</v>
+      </c>
+      <c r="AU279">
+        <v>3</v>
+      </c>
+      <c r="AV279">
+        <v>7</v>
+      </c>
+      <c r="AW279">
+        <v>5</v>
+      </c>
+      <c r="AX279">
+        <v>7</v>
+      </c>
+      <c r="AY279">
+        <v>8</v>
+      </c>
+      <c r="AZ279">
+        <v>14</v>
+      </c>
+      <c r="BA279">
+        <v>6</v>
+      </c>
+      <c r="BB279">
+        <v>6</v>
+      </c>
+      <c r="BC279">
+        <v>12</v>
+      </c>
+      <c r="BD279">
+        <v>2.27</v>
+      </c>
+      <c r="BE279">
+        <v>6.5</v>
+      </c>
+      <c r="BF279">
+        <v>2.03</v>
+      </c>
+      <c r="BG279">
+        <v>1.24</v>
+      </c>
+      <c r="BH279">
+        <v>3.34</v>
+      </c>
+      <c r="BI279">
+        <v>1.47</v>
+      </c>
+      <c r="BJ279">
+        <v>2.42</v>
+      </c>
+      <c r="BK279">
+        <v>1.85</v>
+      </c>
+      <c r="BL279">
+        <v>1.85</v>
+      </c>
+      <c r="BM279">
+        <v>2.34</v>
+      </c>
+      <c r="BN279">
+        <v>1.5</v>
+      </c>
+      <c r="BO279">
+        <v>3.14</v>
+      </c>
+      <c r="BP279">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -1129,10 +1129,10 @@
     <t>['64', '78', '82']</t>
   </si>
   <si>
-    <t>['55', '71']</t>
+    <t>['20', '80']</t>
   </si>
   <si>
-    <t>['20', '80']</t>
+    <t>['55', '71']</t>
   </si>
   <si>
     <t>['72', '78', '90+2', '90+8']</t>
@@ -58361,7 +58361,7 @@
         <v>276</v>
       </c>
       <c r="B277">
-        <v>7465261</v>
+        <v>7465257</v>
       </c>
       <c r="C277" t="s">
         <v>68</v>
@@ -58376,190 +58376,190 @@
         <v>28</v>
       </c>
       <c r="G277" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H277" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K277">
         <v>1</v>
       </c>
       <c r="L277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M277">
         <v>2</v>
       </c>
       <c r="N277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O277" t="s">
-        <v>110</v>
+        <v>269</v>
       </c>
       <c r="P277" t="s">
         <v>371</v>
       </c>
       <c r="Q277">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R277">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S277">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="T277">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="U277">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V277">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="W277">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X277">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y277">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z277">
+        <v>2.5</v>
+      </c>
+      <c r="AA277">
+        <v>3</v>
+      </c>
+      <c r="AB277">
+        <v>3</v>
+      </c>
+      <c r="AC277">
+        <v>1.11</v>
+      </c>
+      <c r="AD277">
+        <v>6.25</v>
+      </c>
+      <c r="AE277">
+        <v>1.55</v>
+      </c>
+      <c r="AF277">
         <v>2.3</v>
       </c>
-      <c r="AA277">
-        <v>2.87</v>
-      </c>
-      <c r="AB277">
-        <v>3.5</v>
-      </c>
-      <c r="AC277">
-        <v>1.14</v>
-      </c>
-      <c r="AD277">
-        <v>5.5</v>
-      </c>
-      <c r="AE277">
-        <v>1.67</v>
-      </c>
-      <c r="AF277">
-        <v>2.1</v>
-      </c>
       <c r="AG277">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AH277">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AI277">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AJ277">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AK277">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AL277">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AM277">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AN277">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AO277">
         <v>1.08</v>
       </c>
       <c r="AP277">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AQ277">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AR277">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AS277">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AT277">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="AU277">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV277">
         <v>5</v>
       </c>
       <c r="AW277">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX277">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY277">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ277">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB277">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC277">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD277">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BE277">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF277">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="BG277">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="BH277">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="BI277">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="BJ277">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="BK277">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="BL277">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="BM277">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="BN277">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="BO277">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="BP277">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="278" spans="1:68">
@@ -58567,7 +58567,7 @@
         <v>277</v>
       </c>
       <c r="B278">
-        <v>7465257</v>
+        <v>7465261</v>
       </c>
       <c r="C278" t="s">
         <v>68</v>
@@ -58582,190 +58582,190 @@
         <v>28</v>
       </c>
       <c r="G278" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H278" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I278">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K278">
         <v>1</v>
       </c>
       <c r="L278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M278">
         <v>2</v>
       </c>
       <c r="N278">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O278" t="s">
-        <v>269</v>
+        <v>110</v>
       </c>
       <c r="P278" t="s">
         <v>372</v>
       </c>
       <c r="Q278">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R278">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S278">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="T278">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U278">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V278">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="W278">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X278">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y278">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z278">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA278">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AB278">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AC278">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AD278">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="AE278">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF278">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG278">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH278">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AI278">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AJ278">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AK278">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AL278">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AM278">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AN278">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AO278">
         <v>1.08</v>
       </c>
       <c r="AP278">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AQ278">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AR278">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AS278">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AT278">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="AU278">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV278">
         <v>5</v>
       </c>
       <c r="AW278">
+        <v>7</v>
+      </c>
+      <c r="AX278">
         <v>3</v>
       </c>
-      <c r="AX278">
-        <v>1</v>
-      </c>
       <c r="AY278">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ278">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA278">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB278">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC278">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BD278">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="BE278">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF278">
+        <v>2.73</v>
+      </c>
+      <c r="BG278">
+        <v>1.45</v>
+      </c>
+      <c r="BH278">
         <v>2.48</v>
       </c>
-      <c r="BG278">
-        <v>1.28</v>
-      </c>
-      <c r="BH278">
-        <v>3.08</v>
-      </c>
       <c r="BI278">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="BJ278">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="BK278">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="BL278">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="BM278">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="BN278">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="BO278">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
       <c r="BP278">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="279" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="381">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -832,6 +832,18 @@
     <t>['11', '21', '77']</t>
   </si>
   <si>
+    <t>['23', '68']</t>
+  </si>
+  <si>
+    <t>['32', '47', '76']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['43', '61', '77', '86']</t>
+  </si>
+  <si>
     <t>['17']</t>
   </si>
   <si>
@@ -1060,9 +1072,6 @@
     <t>['90+6']</t>
   </si>
   <si>
-    <t>['29']</t>
-  </si>
-  <si>
     <t>['15']</t>
   </si>
   <si>
@@ -1139,6 +1148,15 @@
   </si>
   <si>
     <t>['72', '78', '90+2', '90+8']</t>
+  </si>
+  <si>
+    <t>['2', '58']</t>
+  </si>
+  <si>
+    <t>['33', '41']</t>
+  </si>
+  <si>
+    <t>['15', '33']</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP280"/>
+  <dimension ref="A1:BP286"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2043,7 +2061,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2168,7 +2186,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2374,7 +2392,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2580,7 +2598,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2661,7 +2679,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ6">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2786,7 +2804,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2992,7 +3010,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3070,10 +3088,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ8">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3198,7 +3216,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3610,7 +3628,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3691,7 +3709,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ11">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4022,7 +4040,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4103,7 +4121,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ13">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4512,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ15">
         <v>1.64</v>
@@ -4718,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ16">
         <v>1.07</v>
@@ -4924,10 +4942,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5130,10 +5148,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ18">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5542,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20">
         <v>1.29</v>
@@ -5751,7 +5769,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ21">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5876,7 +5894,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6288,7 +6306,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6781,7 +6799,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ26">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -7112,7 +7130,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7190,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ28">
         <v>0.73</v>
@@ -7808,10 +7826,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ31">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR31">
         <v>1.51</v>
@@ -8017,7 +8035,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ32">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -8220,10 +8238,10 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ33">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR33">
         <v>1.22</v>
@@ -8348,7 +8366,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8429,7 +8447,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR34">
         <v>0.87</v>
@@ -8838,7 +8856,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ36">
         <v>0.79</v>
@@ -8966,7 +8984,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9172,7 +9190,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9253,7 +9271,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ38">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR38">
         <v>1.9</v>
@@ -9456,7 +9474,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ39">
         <v>1.07</v>
@@ -9662,7 +9680,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ40">
         <v>1.29</v>
@@ -9871,7 +9889,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ41">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR41">
         <v>1.59</v>
@@ -9996,7 +10014,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10077,7 +10095,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ42">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR42">
         <v>1.48</v>
@@ -10202,7 +10220,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10280,7 +10298,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ43">
         <v>0.73</v>
@@ -10614,7 +10632,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10692,7 +10710,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ45">
         <v>1.73</v>
@@ -10901,7 +10919,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ46">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR46">
         <v>1.11</v>
@@ -11026,7 +11044,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11232,7 +11250,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -12262,7 +12280,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12546,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ54">
         <v>1.21</v>
@@ -12880,7 +12898,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13167,7 +13185,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR57">
         <v>1.38</v>
@@ -13370,7 +13388,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ58">
         <v>0.38</v>
@@ -13576,10 +13594,10 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ59">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR59">
         <v>1.14</v>
@@ -13910,7 +13928,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14197,7 +14215,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ62">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR62">
         <v>1.49</v>
@@ -14322,7 +14340,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14734,7 +14752,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14815,7 +14833,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ65">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -14940,7 +14958,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15018,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ66">
         <v>0.73</v>
@@ -15227,7 +15245,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ67">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR67">
         <v>1.32</v>
@@ -15430,7 +15448,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ68">
         <v>1.21</v>
@@ -15558,7 +15576,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15636,10 +15654,10 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ69">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR69">
         <v>1.13</v>
@@ -15764,7 +15782,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16051,7 +16069,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ71">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR71">
         <v>1.29</v>
@@ -16176,7 +16194,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16460,7 +16478,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ73">
         <v>0.73</v>
@@ -16669,7 +16687,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ74">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR74">
         <v>1.48</v>
@@ -16872,7 +16890,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -17000,7 +17018,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17287,7 +17305,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ77">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR77">
         <v>1.31</v>
@@ -18030,7 +18048,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18520,7 +18538,7 @@
         <v>2.25</v>
       </c>
       <c r="AP83">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ83">
         <v>1.31</v>
@@ -18726,7 +18744,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ84">
         <v>0.6899999999999999</v>
@@ -19060,7 +19078,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19141,7 +19159,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ86">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -19344,10 +19362,10 @@
         <v>2.5</v>
       </c>
       <c r="AP87">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ87">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR87">
         <v>2.14</v>
@@ -19472,7 +19490,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19678,7 +19696,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -19756,7 +19774,7 @@
         <v>2.4</v>
       </c>
       <c r="AP89">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ89">
         <v>2.2</v>
@@ -20090,7 +20108,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20168,10 +20186,10 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ91">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR91">
         <v>1.21</v>
@@ -20296,7 +20314,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20374,10 +20392,10 @@
         <v>0</v>
       </c>
       <c r="AP92">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR92">
         <v>1.06</v>
@@ -20708,7 +20726,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21120,7 +21138,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -21407,7 +21425,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ97">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR97">
         <v>1.35</v>
@@ -21613,7 +21631,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ98">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR98">
         <v>1.58</v>
@@ -22022,7 +22040,7 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ100">
         <v>1.21</v>
@@ -22150,7 +22168,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22356,7 +22374,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22434,7 +22452,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ102">
         <v>1.21</v>
@@ -22562,7 +22580,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22643,7 +22661,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ103">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR103">
         <v>1.21</v>
@@ -23055,7 +23073,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR105">
         <v>1.4</v>
@@ -23180,7 +23198,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23258,7 +23276,7 @@
         <v>2.5</v>
       </c>
       <c r="AP106">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ106">
         <v>2.2</v>
@@ -23670,7 +23688,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ108">
         <v>0.5</v>
@@ -23879,7 +23897,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR109">
         <v>1.79</v>
@@ -24004,7 +24022,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24082,7 +24100,7 @@
         <v>0.5</v>
       </c>
       <c r="AP110">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ110">
         <v>0.6899999999999999</v>
@@ -24494,7 +24512,7 @@
         <v>1.8</v>
       </c>
       <c r="AP112">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ112">
         <v>1.31</v>
@@ -24703,7 +24721,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ113">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24828,7 +24846,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24909,7 +24927,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ114">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR114">
         <v>1.33</v>
@@ -25318,7 +25336,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ116">
         <v>0.38</v>
@@ -25446,7 +25464,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25652,7 +25670,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -26064,7 +26082,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26348,7 +26366,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ121">
         <v>0.6899999999999999</v>
@@ -26888,7 +26906,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -27175,7 +27193,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ125">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR125">
         <v>1.29</v>
@@ -27378,10 +27396,10 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ126">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR126">
         <v>1.32</v>
@@ -27790,7 +27808,7 @@
         <v>2.57</v>
       </c>
       <c r="AP128">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ128">
         <v>2.2</v>
@@ -27996,10 +28014,10 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR129">
         <v>1.27</v>
@@ -28124,7 +28142,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28536,7 +28554,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28948,7 +28966,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29154,7 +29172,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29235,7 +29253,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ135">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -29441,7 +29459,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ136">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR136">
         <v>1.38</v>
@@ -29566,7 +29584,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -30184,7 +30202,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30262,7 +30280,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ140">
         <v>0.79</v>
@@ -30468,10 +30486,10 @@
         <v>0.57</v>
       </c>
       <c r="AP141">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ141">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR141">
         <v>1.08</v>
@@ -30674,7 +30692,7 @@
         <v>0.67</v>
       </c>
       <c r="AP142">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ142">
         <v>0.71</v>
@@ -30802,7 +30820,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -30883,7 +30901,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ143">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR143">
         <v>1.13</v>
@@ -31008,7 +31026,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31089,7 +31107,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ144">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR144">
         <v>1.51</v>
@@ -31292,7 +31310,7 @@
         <v>0.33</v>
       </c>
       <c r="AP145">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ145">
         <v>1.21</v>
@@ -31420,7 +31438,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31704,7 +31722,7 @@
         <v>0.86</v>
       </c>
       <c r="AP147">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ147">
         <v>1.29</v>
@@ -32038,7 +32056,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32244,7 +32262,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32737,7 +32755,7 @@
         <v>1</v>
       </c>
       <c r="AQ152">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR152">
         <v>1.35</v>
@@ -32862,7 +32880,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -33149,7 +33167,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR154">
         <v>1.29</v>
@@ -33274,7 +33292,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33480,7 +33498,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33767,7 +33785,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ157">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR157">
         <v>1.3</v>
@@ -33892,7 +33910,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34098,7 +34116,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34382,7 +34400,7 @@
         <v>0.14</v>
       </c>
       <c r="AP160">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ160">
         <v>0.38</v>
@@ -34794,7 +34812,7 @@
         <v>0.86</v>
       </c>
       <c r="AP162">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ162">
         <v>0.6899999999999999</v>
@@ -35003,7 +35021,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ163">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR163">
         <v>1.23</v>
@@ -35334,7 +35352,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35746,7 +35764,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -35824,7 +35842,7 @@
         <v>1.57</v>
       </c>
       <c r="AP167">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ167">
         <v>1.64</v>
@@ -36030,7 +36048,7 @@
         <v>1.13</v>
       </c>
       <c r="AP168">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ168">
         <v>0.79</v>
@@ -36158,7 +36176,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36442,10 +36460,10 @@
         <v>0.63</v>
       </c>
       <c r="AP170">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ170">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR170">
         <v>1.98</v>
@@ -36570,7 +36588,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -36648,7 +36666,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ171">
         <v>0.5</v>
@@ -36857,7 +36875,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ172">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR172">
         <v>1.52</v>
@@ -37063,7 +37081,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ173">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR173">
         <v>1.37</v>
@@ -37266,7 +37284,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ174">
         <v>1.31</v>
@@ -37806,7 +37824,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -37884,10 +37902,10 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ177">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR177">
         <v>2</v>
@@ -38012,7 +38030,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38218,7 +38236,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38296,7 +38314,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ179">
         <v>1.21</v>
@@ -38424,7 +38442,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38505,7 +38523,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ180">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR180">
         <v>0.99</v>
@@ -38917,7 +38935,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ182">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR182">
         <v>1.81</v>
@@ -39042,7 +39060,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39454,7 +39472,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39532,10 +39550,10 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ185">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR185">
         <v>1.15</v>
@@ -39944,10 +39962,10 @@
         <v>0.89</v>
       </c>
       <c r="AP187">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ187">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR187">
         <v>1.12</v>
@@ -40278,7 +40296,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40768,10 +40786,10 @@
         <v>1.89</v>
       </c>
       <c r="AP191">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ191">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR191">
         <v>1.44</v>
@@ -40974,10 +40992,10 @@
         <v>0.33</v>
       </c>
       <c r="AP192">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ192">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR192">
         <v>1.16</v>
@@ -41102,7 +41120,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41389,7 +41407,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ194">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR194">
         <v>0.96</v>
@@ -41514,7 +41532,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41798,7 +41816,7 @@
         <v>2.09</v>
       </c>
       <c r="AP196">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ196">
         <v>2.2</v>
@@ -41926,7 +41944,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42132,7 +42150,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42210,7 +42228,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ198">
         <v>0.79</v>
@@ -42419,7 +42437,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ199">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -43162,7 +43180,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43368,7 +43386,7 @@
         <v>221</v>
       </c>
       <c r="P204" t="s">
-        <v>348</v>
+        <v>274</v>
       </c>
       <c r="Q204">
         <v>2.2</v>
@@ -43449,7 +43467,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ204">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR204">
         <v>1.67</v>
@@ -43574,7 +43592,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43780,7 +43798,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44067,7 +44085,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ207">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR207">
         <v>1.57</v>
@@ -44192,7 +44210,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44270,7 +44288,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP208">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ208">
         <v>1.21</v>
@@ -44479,7 +44497,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ209">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR209">
         <v>1.31</v>
@@ -44682,7 +44700,7 @@
         <v>0.4</v>
       </c>
       <c r="AP210">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ210">
         <v>0.5</v>
@@ -44888,7 +44906,7 @@
         <v>0.44</v>
       </c>
       <c r="AP211">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ211">
         <v>0.71</v>
@@ -45016,7 +45034,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45097,7 +45115,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ212">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR212">
         <v>0.97</v>
@@ -45300,7 +45318,7 @@
         <v>0.9</v>
       </c>
       <c r="AP213">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ213">
         <v>1.21</v>
@@ -45509,7 +45527,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ214">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR214">
         <v>1.55</v>
@@ -45918,7 +45936,7 @@
         <v>2</v>
       </c>
       <c r="AP216">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ216">
         <v>1.73</v>
@@ -46124,7 +46142,7 @@
         <v>0.73</v>
       </c>
       <c r="AP217">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ217">
         <v>0.73</v>
@@ -46664,7 +46682,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -47157,7 +47175,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ222">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR222">
         <v>1.62</v>
@@ -47282,7 +47300,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47569,7 +47587,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ224">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR224">
         <v>1.44</v>
@@ -47694,7 +47712,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -47775,7 +47793,7 @@
         <v>1</v>
       </c>
       <c r="AQ225">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR225">
         <v>1.41</v>
@@ -47978,10 +47996,10 @@
         <v>1.8</v>
       </c>
       <c r="AP226">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ226">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR226">
         <v>1.93</v>
@@ -48184,7 +48202,7 @@
         <v>0.8</v>
       </c>
       <c r="AP227">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ227">
         <v>1.21</v>
@@ -48393,7 +48411,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ228">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR228">
         <v>1.3</v>
@@ -48596,7 +48614,7 @@
         <v>0.2</v>
       </c>
       <c r="AP229">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ229">
         <v>0.38</v>
@@ -48724,7 +48742,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49136,7 +49154,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49342,7 +49360,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49548,7 +49566,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50166,7 +50184,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50244,7 +50262,7 @@
         <v>1.73</v>
       </c>
       <c r="AP237">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ237">
         <v>1.64</v>
@@ -50372,7 +50390,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -51068,10 +51086,10 @@
         <v>1.42</v>
       </c>
       <c r="AP241">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ241">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR241">
         <v>2.03</v>
@@ -51402,7 +51420,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51480,7 +51498,7 @@
         <v>0.18</v>
       </c>
       <c r="AP243">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ243">
         <v>0.38</v>
@@ -51689,7 +51707,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ244">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR244">
         <v>1.68</v>
@@ -51814,7 +51832,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51895,7 +51913,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ245">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR245">
         <v>1.34</v>
@@ -52020,7 +52038,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52226,7 +52244,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52307,7 +52325,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ247">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52510,10 +52528,10 @@
         <v>1</v>
       </c>
       <c r="AP248">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ248">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR248">
         <v>2.01</v>
@@ -52638,7 +52656,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52716,7 +52734,7 @@
         <v>1</v>
       </c>
       <c r="AP249">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ249">
         <v>1.29</v>
@@ -52922,10 +52940,10 @@
         <v>0.83</v>
       </c>
       <c r="AP250">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ250">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR250">
         <v>1.44</v>
@@ -53050,7 +53068,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53256,7 +53274,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53462,7 +53480,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53874,7 +53892,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -54570,7 +54588,7 @@
         <v>1.17</v>
       </c>
       <c r="AP258">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ258">
         <v>1.07</v>
@@ -54904,7 +54922,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55191,7 +55209,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ261">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR261">
         <v>1.39</v>
@@ -55394,10 +55412,10 @@
         <v>1.85</v>
       </c>
       <c r="AP262">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ262">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR262">
         <v>1.2</v>
@@ -55522,7 +55540,7 @@
         <v>262</v>
       </c>
       <c r="P263" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q263">
         <v>1.95</v>
@@ -55603,7 +55621,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ263">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AR263">
         <v>1.39</v>
@@ -55728,7 +55746,7 @@
         <v>263</v>
       </c>
       <c r="P264" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q264">
         <v>5</v>
@@ -55806,10 +55824,10 @@
         <v>1.83</v>
       </c>
       <c r="AP264">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ264">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR264">
         <v>1.32</v>
@@ -56012,10 +56030,10 @@
         <v>1.31</v>
       </c>
       <c r="AP265">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ265">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR265">
         <v>2.04</v>
@@ -56346,7 +56364,7 @@
         <v>221</v>
       </c>
       <c r="P267" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q267">
         <v>2.25</v>
@@ -56552,7 +56570,7 @@
         <v>104</v>
       </c>
       <c r="P268" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q268">
         <v>2.88</v>
@@ -56630,7 +56648,7 @@
         <v>1.08</v>
       </c>
       <c r="AP268">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ268">
         <v>1.21</v>
@@ -56836,10 +56854,10 @@
         <v>0.92</v>
       </c>
       <c r="AP269">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ269">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR269">
         <v>1.16</v>
@@ -56964,7 +56982,7 @@
         <v>265</v>
       </c>
       <c r="P270" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q270">
         <v>3.75</v>
@@ -57582,7 +57600,7 @@
         <v>138</v>
       </c>
       <c r="P273" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q273">
         <v>3.6</v>
@@ -57994,7 +58012,7 @@
         <v>268</v>
       </c>
       <c r="P275" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q275">
         <v>4.33</v>
@@ -58406,7 +58424,7 @@
         <v>110</v>
       </c>
       <c r="P277" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58612,7 +58630,7 @@
         <v>269</v>
       </c>
       <c r="P278" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q278">
         <v>3.4</v>
@@ -58818,7 +58836,7 @@
         <v>270</v>
       </c>
       <c r="P279" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q279">
         <v>3.4</v>
@@ -59102,7 +59120,7 @@
         <v>0.75</v>
       </c>
       <c r="AP280">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ280">
         <v>0.6899999999999999</v>
@@ -59181,6 +59199,1242 @@
       </c>
       <c r="BP280">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7465269</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45745.41666666666</v>
+      </c>
+      <c r="F281">
+        <v>29</v>
+      </c>
+      <c r="G281" t="s">
+        <v>76</v>
+      </c>
+      <c r="H281" t="s">
+        <v>78</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>1</v>
+      </c>
+      <c r="L281">
+        <v>2</v>
+      </c>
+      <c r="M281">
+        <v>1</v>
+      </c>
+      <c r="N281">
+        <v>3</v>
+      </c>
+      <c r="O281" t="s">
+        <v>272</v>
+      </c>
+      <c r="P281" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q281">
+        <v>1.83</v>
+      </c>
+      <c r="R281">
+        <v>2.3</v>
+      </c>
+      <c r="S281">
+        <v>9.5</v>
+      </c>
+      <c r="T281">
+        <v>1.44</v>
+      </c>
+      <c r="U281">
+        <v>2.63</v>
+      </c>
+      <c r="V281">
+        <v>3</v>
+      </c>
+      <c r="W281">
+        <v>1.36</v>
+      </c>
+      <c r="X281">
+        <v>9</v>
+      </c>
+      <c r="Y281">
+        <v>1.07</v>
+      </c>
+      <c r="Z281">
+        <v>1.33</v>
+      </c>
+      <c r="AA281">
+        <v>4.5</v>
+      </c>
+      <c r="AB281">
+        <v>11</v>
+      </c>
+      <c r="AC281">
+        <v>1.01</v>
+      </c>
+      <c r="AD281">
+        <v>9.6</v>
+      </c>
+      <c r="AE281">
+        <v>1.31</v>
+      </c>
+      <c r="AF281">
+        <v>3.22</v>
+      </c>
+      <c r="AG281">
+        <v>2</v>
+      </c>
+      <c r="AH281">
+        <v>1.8</v>
+      </c>
+      <c r="AI281">
+        <v>2.5</v>
+      </c>
+      <c r="AJ281">
+        <v>1.5</v>
+      </c>
+      <c r="AK281">
+        <v>1.06</v>
+      </c>
+      <c r="AL281">
+        <v>1.18</v>
+      </c>
+      <c r="AM281">
+        <v>3.1</v>
+      </c>
+      <c r="AN281">
+        <v>1.43</v>
+      </c>
+      <c r="AO281">
+        <v>0.21</v>
+      </c>
+      <c r="AP281">
+        <v>1.53</v>
+      </c>
+      <c r="AQ281">
+        <v>0.2</v>
+      </c>
+      <c r="AR281">
+        <v>1.43</v>
+      </c>
+      <c r="AS281">
+        <v>0.96</v>
+      </c>
+      <c r="AT281">
+        <v>2.39</v>
+      </c>
+      <c r="AU281">
+        <v>3</v>
+      </c>
+      <c r="AV281">
+        <v>6</v>
+      </c>
+      <c r="AW281">
+        <v>10</v>
+      </c>
+      <c r="AX281">
+        <v>7</v>
+      </c>
+      <c r="AY281">
+        <v>16</v>
+      </c>
+      <c r="AZ281">
+        <v>13</v>
+      </c>
+      <c r="BA281">
+        <v>3</v>
+      </c>
+      <c r="BB281">
+        <v>6</v>
+      </c>
+      <c r="BC281">
+        <v>9</v>
+      </c>
+      <c r="BD281">
+        <v>1.2</v>
+      </c>
+      <c r="BE281">
+        <v>8.5</v>
+      </c>
+      <c r="BF281">
+        <v>4.9</v>
+      </c>
+      <c r="BG281">
+        <v>1.33</v>
+      </c>
+      <c r="BH281">
+        <v>2.95</v>
+      </c>
+      <c r="BI281">
+        <v>1.56</v>
+      </c>
+      <c r="BJ281">
+        <v>2.23</v>
+      </c>
+      <c r="BK281">
+        <v>1.9</v>
+      </c>
+      <c r="BL281">
+        <v>1.79</v>
+      </c>
+      <c r="BM281">
+        <v>2.38</v>
+      </c>
+      <c r="BN281">
+        <v>1.5</v>
+      </c>
+      <c r="BO281">
+        <v>3.05</v>
+      </c>
+      <c r="BP281">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7469589</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45745.51041666666</v>
+      </c>
+      <c r="F282">
+        <v>29</v>
+      </c>
+      <c r="G282" t="s">
+        <v>82</v>
+      </c>
+      <c r="H282" t="s">
+        <v>87</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>1</v>
+      </c>
+      <c r="K282">
+        <v>1</v>
+      </c>
+      <c r="L282">
+        <v>1</v>
+      </c>
+      <c r="M282">
+        <v>1</v>
+      </c>
+      <c r="N282">
+        <v>2</v>
+      </c>
+      <c r="O282" t="s">
+        <v>239</v>
+      </c>
+      <c r="P282" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q282">
+        <v>6.5</v>
+      </c>
+      <c r="R282">
+        <v>2.1</v>
+      </c>
+      <c r="S282">
+        <v>2.2</v>
+      </c>
+      <c r="T282">
+        <v>1.44</v>
+      </c>
+      <c r="U282">
+        <v>2.63</v>
+      </c>
+      <c r="V282">
+        <v>3.25</v>
+      </c>
+      <c r="W282">
+        <v>1.33</v>
+      </c>
+      <c r="X282">
+        <v>10</v>
+      </c>
+      <c r="Y282">
+        <v>1.06</v>
+      </c>
+      <c r="Z282">
+        <v>6.25</v>
+      </c>
+      <c r="AA282">
+        <v>3.9</v>
+      </c>
+      <c r="AB282">
+        <v>1.55</v>
+      </c>
+      <c r="AC282">
+        <v>1.06</v>
+      </c>
+      <c r="AD282">
+        <v>8.5</v>
+      </c>
+      <c r="AE282">
+        <v>1.36</v>
+      </c>
+      <c r="AF282">
+        <v>3.1</v>
+      </c>
+      <c r="AG282">
+        <v>2.1</v>
+      </c>
+      <c r="AH282">
+        <v>1.73</v>
+      </c>
+      <c r="AI282">
+        <v>2.2</v>
+      </c>
+      <c r="AJ282">
+        <v>1.62</v>
+      </c>
+      <c r="AK282">
+        <v>2.45</v>
+      </c>
+      <c r="AL282">
+        <v>1.24</v>
+      </c>
+      <c r="AM282">
+        <v>1.11</v>
+      </c>
+      <c r="AN282">
+        <v>1.64</v>
+      </c>
+      <c r="AO282">
+        <v>1.69</v>
+      </c>
+      <c r="AP282">
+        <v>1.6</v>
+      </c>
+      <c r="AQ282">
+        <v>1.64</v>
+      </c>
+      <c r="AR282">
+        <v>1.15</v>
+      </c>
+      <c r="AS282">
+        <v>1.16</v>
+      </c>
+      <c r="AT282">
+        <v>2.31</v>
+      </c>
+      <c r="AU282">
+        <v>2</v>
+      </c>
+      <c r="AV282">
+        <v>3</v>
+      </c>
+      <c r="AW282">
+        <v>7</v>
+      </c>
+      <c r="AX282">
+        <v>11</v>
+      </c>
+      <c r="AY282">
+        <v>11</v>
+      </c>
+      <c r="AZ282">
+        <v>18</v>
+      </c>
+      <c r="BA282">
+        <v>4</v>
+      </c>
+      <c r="BB282">
+        <v>3</v>
+      </c>
+      <c r="BC282">
+        <v>7</v>
+      </c>
+      <c r="BD282">
+        <v>3.2</v>
+      </c>
+      <c r="BE282">
+        <v>6.75</v>
+      </c>
+      <c r="BF282">
+        <v>1.42</v>
+      </c>
+      <c r="BG282">
+        <v>1.38</v>
+      </c>
+      <c r="BH282">
+        <v>2.7</v>
+      </c>
+      <c r="BI282">
+        <v>1.65</v>
+      </c>
+      <c r="BJ282">
+        <v>2.08</v>
+      </c>
+      <c r="BK282">
+        <v>2.06</v>
+      </c>
+      <c r="BL282">
+        <v>1.66</v>
+      </c>
+      <c r="BM282">
+        <v>2.6</v>
+      </c>
+      <c r="BN282">
+        <v>1.43</v>
+      </c>
+      <c r="BO282">
+        <v>3.4</v>
+      </c>
+      <c r="BP282">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7465270</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45745.60416666666</v>
+      </c>
+      <c r="F283">
+        <v>29</v>
+      </c>
+      <c r="G283" t="s">
+        <v>86</v>
+      </c>
+      <c r="H283" t="s">
+        <v>88</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>0</v>
+      </c>
+      <c r="M283">
+        <v>2</v>
+      </c>
+      <c r="N283">
+        <v>2</v>
+      </c>
+      <c r="O283" t="s">
+        <v>104</v>
+      </c>
+      <c r="P283" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q283">
+        <v>3.1</v>
+      </c>
+      <c r="R283">
+        <v>1.91</v>
+      </c>
+      <c r="S283">
+        <v>4.33</v>
+      </c>
+      <c r="T283">
+        <v>1.62</v>
+      </c>
+      <c r="U283">
+        <v>2.2</v>
+      </c>
+      <c r="V283">
+        <v>4</v>
+      </c>
+      <c r="W283">
+        <v>1.22</v>
+      </c>
+      <c r="X283">
+        <v>13</v>
+      </c>
+      <c r="Y283">
+        <v>1.04</v>
+      </c>
+      <c r="Z283">
+        <v>2.25</v>
+      </c>
+      <c r="AA283">
+        <v>2.9</v>
+      </c>
+      <c r="AB283">
+        <v>3.6</v>
+      </c>
+      <c r="AC283">
+        <v>1.11</v>
+      </c>
+      <c r="AD283">
+        <v>6.25</v>
+      </c>
+      <c r="AE283">
+        <v>1.51</v>
+      </c>
+      <c r="AF283">
+        <v>2.37</v>
+      </c>
+      <c r="AG283">
+        <v>2.75</v>
+      </c>
+      <c r="AH283">
+        <v>1.44</v>
+      </c>
+      <c r="AI283">
+        <v>2.2</v>
+      </c>
+      <c r="AJ283">
+        <v>1.62</v>
+      </c>
+      <c r="AK283">
+        <v>1.3</v>
+      </c>
+      <c r="AL283">
+        <v>1.36</v>
+      </c>
+      <c r="AM283">
+        <v>1.61</v>
+      </c>
+      <c r="AN283">
+        <v>1.23</v>
+      </c>
+      <c r="AO283">
+        <v>1.21</v>
+      </c>
+      <c r="AP283">
+        <v>1.14</v>
+      </c>
+      <c r="AQ283">
+        <v>1.33</v>
+      </c>
+      <c r="AR283">
+        <v>1.18</v>
+      </c>
+      <c r="AS283">
+        <v>1.2</v>
+      </c>
+      <c r="AT283">
+        <v>2.38</v>
+      </c>
+      <c r="AU283">
+        <v>5</v>
+      </c>
+      <c r="AV283">
+        <v>6</v>
+      </c>
+      <c r="AW283">
+        <v>8</v>
+      </c>
+      <c r="AX283">
+        <v>6</v>
+      </c>
+      <c r="AY283">
+        <v>14</v>
+      </c>
+      <c r="AZ283">
+        <v>14</v>
+      </c>
+      <c r="BA283">
+        <v>8</v>
+      </c>
+      <c r="BB283">
+        <v>5</v>
+      </c>
+      <c r="BC283">
+        <v>13</v>
+      </c>
+      <c r="BD283">
+        <v>1.58</v>
+      </c>
+      <c r="BE283">
+        <v>6.5</v>
+      </c>
+      <c r="BF283">
+        <v>2.65</v>
+      </c>
+      <c r="BG283">
+        <v>1.4</v>
+      </c>
+      <c r="BH283">
+        <v>2.7</v>
+      </c>
+      <c r="BI283">
+        <v>1.66</v>
+      </c>
+      <c r="BJ283">
+        <v>2.06</v>
+      </c>
+      <c r="BK283">
+        <v>2.06</v>
+      </c>
+      <c r="BL283">
+        <v>1.66</v>
+      </c>
+      <c r="BM283">
+        <v>2.65</v>
+      </c>
+      <c r="BN283">
+        <v>1.41</v>
+      </c>
+      <c r="BO283">
+        <v>3.4</v>
+      </c>
+      <c r="BP283">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7465272</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45745.70833333334</v>
+      </c>
+      <c r="F284">
+        <v>29</v>
+      </c>
+      <c r="G284" t="s">
+        <v>84</v>
+      </c>
+      <c r="H284" t="s">
+        <v>85</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+      <c r="J284">
+        <v>2</v>
+      </c>
+      <c r="K284">
+        <v>3</v>
+      </c>
+      <c r="L284">
+        <v>3</v>
+      </c>
+      <c r="M284">
+        <v>2</v>
+      </c>
+      <c r="N284">
+        <v>5</v>
+      </c>
+      <c r="O284" t="s">
+        <v>273</v>
+      </c>
+      <c r="P284" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q284">
+        <v>1.5</v>
+      </c>
+      <c r="R284">
+        <v>3.1</v>
+      </c>
+      <c r="S284">
+        <v>11</v>
+      </c>
+      <c r="T284">
+        <v>1.2</v>
+      </c>
+      <c r="U284">
+        <v>4.33</v>
+      </c>
+      <c r="V284">
+        <v>2</v>
+      </c>
+      <c r="W284">
+        <v>1.73</v>
+      </c>
+      <c r="X284">
+        <v>4</v>
+      </c>
+      <c r="Y284">
+        <v>1.22</v>
+      </c>
+      <c r="Z284">
+        <v>1.14</v>
+      </c>
+      <c r="AA284">
+        <v>7.5</v>
+      </c>
+      <c r="AB284">
+        <v>15</v>
+      </c>
+      <c r="AC284">
+        <v>1.01</v>
+      </c>
+      <c r="AD284">
+        <v>26</v>
+      </c>
+      <c r="AE284">
+        <v>1.11</v>
+      </c>
+      <c r="AF284">
+        <v>6.25</v>
+      </c>
+      <c r="AG284">
+        <v>1.36</v>
+      </c>
+      <c r="AH284">
+        <v>3.2</v>
+      </c>
+      <c r="AI284">
+        <v>2</v>
+      </c>
+      <c r="AJ284">
+        <v>1.75</v>
+      </c>
+      <c r="AK284">
+        <v>1.02</v>
+      </c>
+      <c r="AL284">
+        <v>1.08</v>
+      </c>
+      <c r="AM284">
+        <v>5</v>
+      </c>
+      <c r="AN284">
+        <v>2.62</v>
+      </c>
+      <c r="AO284">
+        <v>0.71</v>
+      </c>
+      <c r="AP284">
+        <v>2.64</v>
+      </c>
+      <c r="AQ284">
+        <v>0.67</v>
+      </c>
+      <c r="AR284">
+        <v>1.99</v>
+      </c>
+      <c r="AS284">
+        <v>0.99</v>
+      </c>
+      <c r="AT284">
+        <v>2.98</v>
+      </c>
+      <c r="AU284">
+        <v>11</v>
+      </c>
+      <c r="AV284">
+        <v>5</v>
+      </c>
+      <c r="AW284">
+        <v>14</v>
+      </c>
+      <c r="AX284">
+        <v>6</v>
+      </c>
+      <c r="AY284">
+        <v>30</v>
+      </c>
+      <c r="AZ284">
+        <v>12</v>
+      </c>
+      <c r="BA284">
+        <v>8</v>
+      </c>
+      <c r="BB284">
+        <v>3</v>
+      </c>
+      <c r="BC284">
+        <v>11</v>
+      </c>
+      <c r="BD284">
+        <v>1.13</v>
+      </c>
+      <c r="BE284">
+        <v>10</v>
+      </c>
+      <c r="BF284">
+        <v>6.5</v>
+      </c>
+      <c r="BG284">
+        <v>1.28</v>
+      </c>
+      <c r="BH284">
+        <v>3.3</v>
+      </c>
+      <c r="BI284">
+        <v>1.47</v>
+      </c>
+      <c r="BJ284">
+        <v>2.43</v>
+      </c>
+      <c r="BK284">
+        <v>1.77</v>
+      </c>
+      <c r="BL284">
+        <v>1.92</v>
+      </c>
+      <c r="BM284">
+        <v>2.18</v>
+      </c>
+      <c r="BN284">
+        <v>1.58</v>
+      </c>
+      <c r="BO284">
+        <v>2.8</v>
+      </c>
+      <c r="BP284">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7465268</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45746.375</v>
+      </c>
+      <c r="F285">
+        <v>29</v>
+      </c>
+      <c r="G285" t="s">
+        <v>83</v>
+      </c>
+      <c r="H285" t="s">
+        <v>79</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285">
+        <v>2</v>
+      </c>
+      <c r="K285">
+        <v>3</v>
+      </c>
+      <c r="L285">
+        <v>1</v>
+      </c>
+      <c r="M285">
+        <v>2</v>
+      </c>
+      <c r="N285">
+        <v>3</v>
+      </c>
+      <c r="O285" t="s">
+        <v>274</v>
+      </c>
+      <c r="P285" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q285">
+        <v>4</v>
+      </c>
+      <c r="R285">
+        <v>2</v>
+      </c>
+      <c r="S285">
+        <v>3.1</v>
+      </c>
+      <c r="T285">
+        <v>1.5</v>
+      </c>
+      <c r="U285">
+        <v>2.5</v>
+      </c>
+      <c r="V285">
+        <v>3.5</v>
+      </c>
+      <c r="W285">
+        <v>1.29</v>
+      </c>
+      <c r="X285">
+        <v>11</v>
+      </c>
+      <c r="Y285">
+        <v>1.05</v>
+      </c>
+      <c r="Z285">
+        <v>3.1</v>
+      </c>
+      <c r="AA285">
+        <v>3.2</v>
+      </c>
+      <c r="AB285">
+        <v>2.35</v>
+      </c>
+      <c r="AC285">
+        <v>1.09</v>
+      </c>
+      <c r="AD285">
+        <v>7</v>
+      </c>
+      <c r="AE285">
+        <v>1.45</v>
+      </c>
+      <c r="AF285">
+        <v>2.7</v>
+      </c>
+      <c r="AG285">
+        <v>2.3</v>
+      </c>
+      <c r="AH285">
+        <v>1.62</v>
+      </c>
+      <c r="AI285">
+        <v>1.95</v>
+      </c>
+      <c r="AJ285">
+        <v>1.8</v>
+      </c>
+      <c r="AK285">
+        <v>1.57</v>
+      </c>
+      <c r="AL285">
+        <v>1.35</v>
+      </c>
+      <c r="AM285">
+        <v>1.35</v>
+      </c>
+      <c r="AN285">
+        <v>1.36</v>
+      </c>
+      <c r="AO285">
+        <v>1.71</v>
+      </c>
+      <c r="AP285">
+        <v>1.27</v>
+      </c>
+      <c r="AQ285">
+        <v>1.8</v>
+      </c>
+      <c r="AR285">
+        <v>1.33</v>
+      </c>
+      <c r="AS285">
+        <v>1.55</v>
+      </c>
+      <c r="AT285">
+        <v>2.88</v>
+      </c>
+      <c r="AU285">
+        <v>5</v>
+      </c>
+      <c r="AV285">
+        <v>4</v>
+      </c>
+      <c r="AW285">
+        <v>7</v>
+      </c>
+      <c r="AX285">
+        <v>6</v>
+      </c>
+      <c r="AY285">
+        <v>12</v>
+      </c>
+      <c r="AZ285">
+        <v>12</v>
+      </c>
+      <c r="BA285">
+        <v>3</v>
+      </c>
+      <c r="BB285">
+        <v>1</v>
+      </c>
+      <c r="BC285">
+        <v>4</v>
+      </c>
+      <c r="BD285">
+        <v>2.02</v>
+      </c>
+      <c r="BE285">
+        <v>5.8</v>
+      </c>
+      <c r="BF285">
+        <v>1.98</v>
+      </c>
+      <c r="BG285">
+        <v>1.54</v>
+      </c>
+      <c r="BH285">
+        <v>2.3</v>
+      </c>
+      <c r="BI285">
+        <v>1.91</v>
+      </c>
+      <c r="BJ285">
+        <v>1.77</v>
+      </c>
+      <c r="BK285">
+        <v>2.43</v>
+      </c>
+      <c r="BL285">
+        <v>1.48</v>
+      </c>
+      <c r="BM285">
+        <v>3.2</v>
+      </c>
+      <c r="BN285">
+        <v>1.28</v>
+      </c>
+      <c r="BO285">
+        <v>4.35</v>
+      </c>
+      <c r="BP285">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="286" spans="1:68">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>7465265</v>
+      </c>
+      <c r="C286" t="s">
+        <v>68</v>
+      </c>
+      <c r="D286" t="s">
+        <v>69</v>
+      </c>
+      <c r="E286" s="2">
+        <v>45746.46875</v>
+      </c>
+      <c r="F286">
+        <v>29</v>
+      </c>
+      <c r="G286" t="s">
+        <v>81</v>
+      </c>
+      <c r="H286" t="s">
+        <v>89</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>1</v>
+      </c>
+      <c r="L286">
+        <v>4</v>
+      </c>
+      <c r="M286">
+        <v>1</v>
+      </c>
+      <c r="N286">
+        <v>5</v>
+      </c>
+      <c r="O286" t="s">
+        <v>275</v>
+      </c>
+      <c r="P286" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q286">
+        <v>1.67</v>
+      </c>
+      <c r="R286">
+        <v>3</v>
+      </c>
+      <c r="S286">
+        <v>7</v>
+      </c>
+      <c r="T286">
+        <v>1.2</v>
+      </c>
+      <c r="U286">
+        <v>4.33</v>
+      </c>
+      <c r="V286">
+        <v>1.91</v>
+      </c>
+      <c r="W286">
+        <v>1.8</v>
+      </c>
+      <c r="X286">
+        <v>4</v>
+      </c>
+      <c r="Y286">
+        <v>1.22</v>
+      </c>
+      <c r="Z286">
+        <v>1.27</v>
+      </c>
+      <c r="AA286">
+        <v>6</v>
+      </c>
+      <c r="AB286">
+        <v>9</v>
+      </c>
+      <c r="AC286">
+        <v>1.01</v>
+      </c>
+      <c r="AD286">
+        <v>26</v>
+      </c>
+      <c r="AE286">
+        <v>1.09</v>
+      </c>
+      <c r="AF286">
+        <v>7</v>
+      </c>
+      <c r="AG286">
+        <v>1.33</v>
+      </c>
+      <c r="AH286">
+        <v>3.4</v>
+      </c>
+      <c r="AI286">
+        <v>1.67</v>
+      </c>
+      <c r="AJ286">
+        <v>2.1</v>
+      </c>
+      <c r="AK286">
+        <v>1.07</v>
+      </c>
+      <c r="AL286">
+        <v>1.12</v>
+      </c>
+      <c r="AM286">
+        <v>3.6</v>
+      </c>
+      <c r="AN286">
+        <v>2.31</v>
+      </c>
+      <c r="AO286">
+        <v>0.93</v>
+      </c>
+      <c r="AP286">
+        <v>2.36</v>
+      </c>
+      <c r="AQ286">
+        <v>0.87</v>
+      </c>
+      <c r="AR286">
+        <v>2.13</v>
+      </c>
+      <c r="AS286">
+        <v>1.14</v>
+      </c>
+      <c r="AT286">
+        <v>3.27</v>
+      </c>
+      <c r="AU286">
+        <v>10</v>
+      </c>
+      <c r="AV286">
+        <v>3</v>
+      </c>
+      <c r="AW286">
+        <v>12</v>
+      </c>
+      <c r="AX286">
+        <v>2</v>
+      </c>
+      <c r="AY286">
+        <v>25</v>
+      </c>
+      <c r="AZ286">
+        <v>6</v>
+      </c>
+      <c r="BA286">
+        <v>10</v>
+      </c>
+      <c r="BB286">
+        <v>2</v>
+      </c>
+      <c r="BC286">
+        <v>12</v>
+      </c>
+      <c r="BD286">
+        <v>1.25</v>
+      </c>
+      <c r="BE286">
+        <v>7.5</v>
+      </c>
+      <c r="BF286">
+        <v>4.35</v>
+      </c>
+      <c r="BG286">
+        <v>1.28</v>
+      </c>
+      <c r="BH286">
+        <v>3.3</v>
+      </c>
+      <c r="BI286">
+        <v>1.47</v>
+      </c>
+      <c r="BJ286">
+        <v>2.43</v>
+      </c>
+      <c r="BK286">
+        <v>1.77</v>
+      </c>
+      <c r="BL286">
+        <v>1.92</v>
+      </c>
+      <c r="BM286">
+        <v>2.18</v>
+      </c>
+      <c r="BN286">
+        <v>1.58</v>
+      </c>
+      <c r="BO286">
+        <v>2.8</v>
+      </c>
+      <c r="BP286">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="382">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -844,6 +844,9 @@
     <t>['43', '61', '77', '86']</t>
   </si>
   <si>
+    <t>['25', '45+3']</t>
+  </si>
+  <si>
     <t>['17']</t>
   </si>
   <si>
@@ -1153,7 +1156,7 @@
     <t>['2', '58']</t>
   </si>
   <si>
-    <t>['33', '41']</t>
+    <t>['34', '41']</t>
   </si>
   <si>
     <t>['15', '33']</t>
@@ -1518,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP286"/>
+  <dimension ref="A1:BP289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1852,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1.21</v>
@@ -2058,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ3">
         <v>0.87</v>
@@ -2186,7 +2189,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2392,7 +2395,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -2473,7 +2476,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2598,7 +2601,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
@@ -2804,7 +2807,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q7">
         <v>4.75</v>
@@ -2882,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7">
         <v>2.2</v>
@@ -3010,7 +3013,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3216,7 +3219,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3628,7 +3631,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -4040,7 +4043,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4327,7 +4330,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ14">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR14">
         <v>1.83</v>
@@ -5894,7 +5897,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q22">
         <v>2.48</v>
@@ -6181,7 +6184,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ23">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR23">
         <v>1.51</v>
@@ -6306,7 +6309,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q24">
         <v>4.75</v>
@@ -6590,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>0.5</v>
@@ -7130,7 +7133,7 @@
         <v>111</v>
       </c>
       <c r="P28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7417,7 +7420,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -8032,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>1.64</v>
@@ -8366,7 +8369,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q34">
         <v>3.22</v>
@@ -8444,7 +8447,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
         <v>1.8</v>
@@ -8653,7 +8656,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ35">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8984,7 +8987,7 @@
         <v>118</v>
       </c>
       <c r="P37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -9190,7 +9193,7 @@
         <v>104</v>
       </c>
       <c r="P38" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q38">
         <v>2.79</v>
@@ -9886,7 +9889,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ41">
         <v>0.67</v>
@@ -10014,7 +10017,7 @@
         <v>121</v>
       </c>
       <c r="P42" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -10220,7 +10223,7 @@
         <v>122</v>
       </c>
       <c r="P43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -10632,7 +10635,7 @@
         <v>104</v>
       </c>
       <c r="P45" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -11044,7 +11047,7 @@
         <v>124</v>
       </c>
       <c r="P47" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -11250,7 +11253,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q48">
         <v>4.33</v>
@@ -11743,7 +11746,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ50">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR50">
         <v>1.14</v>
@@ -12152,7 +12155,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
         <v>1.21</v>
@@ -12280,7 +12283,7 @@
         <v>104</v>
       </c>
       <c r="P53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12567,7 +12570,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ54">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR54">
         <v>1.07</v>
@@ -12898,7 +12901,7 @@
         <v>131</v>
       </c>
       <c r="P56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
@@ -13182,7 +13185,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57">
         <v>0.87</v>
@@ -13800,7 +13803,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>0.71</v>
@@ -13928,7 +13931,7 @@
         <v>136</v>
       </c>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q61">
         <v>4</v>
@@ -14340,7 +14343,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -14418,10 +14421,10 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ63">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR63">
         <v>1.68</v>
@@ -14624,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ64">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR64">
         <v>1.24</v>
@@ -14752,7 +14755,7 @@
         <v>139</v>
       </c>
       <c r="P65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14958,7 +14961,7 @@
         <v>140</v>
       </c>
       <c r="P66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q66">
         <v>1.62</v>
@@ -15576,7 +15579,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15782,7 +15785,7 @@
         <v>109</v>
       </c>
       <c r="P70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -16194,7 +16197,7 @@
         <v>143</v>
       </c>
       <c r="P72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16275,7 +16278,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ72">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR72">
         <v>1.16</v>
@@ -17018,7 +17021,7 @@
         <v>147</v>
       </c>
       <c r="P76" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q76">
         <v>6.07</v>
@@ -17508,10 +17511,10 @@
         <v>0.67</v>
       </c>
       <c r="AP78">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17714,7 +17717,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ79">
         <v>0.38</v>
@@ -18048,7 +18051,7 @@
         <v>151</v>
       </c>
       <c r="P81" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q81">
         <v>2</v>
@@ -18541,7 +18544,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ83">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR83">
         <v>1.07</v>
@@ -18747,7 +18750,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ84">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR84">
         <v>1.3</v>
@@ -19078,7 +19081,7 @@
         <v>154</v>
       </c>
       <c r="P86" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q86">
         <v>3.75</v>
@@ -19490,7 +19493,7 @@
         <v>156</v>
       </c>
       <c r="P88" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q88">
         <v>2.88</v>
@@ -19696,7 +19699,7 @@
         <v>104</v>
       </c>
       <c r="P89" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q89">
         <v>5.5</v>
@@ -20108,7 +20111,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q91">
         <v>4</v>
@@ -20314,7 +20317,7 @@
         <v>159</v>
       </c>
       <c r="P92" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20598,7 +20601,7 @@
         <v>0.25</v>
       </c>
       <c r="AP93">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ93">
         <v>0.38</v>
@@ -20726,7 +20729,7 @@
         <v>161</v>
       </c>
       <c r="P94" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q94">
         <v>3.4</v>
@@ -21138,7 +21141,7 @@
         <v>154</v>
       </c>
       <c r="P96" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q96">
         <v>5</v>
@@ -22043,7 +22046,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ100">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR100">
         <v>1.81</v>
@@ -22168,7 +22171,7 @@
         <v>165</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q101">
         <v>2.4</v>
@@ -22246,7 +22249,7 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ101">
         <v>0.79</v>
@@ -22374,7 +22377,7 @@
         <v>104</v>
       </c>
       <c r="P102" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q102">
         <v>3.6</v>
@@ -22455,7 +22458,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR102">
         <v>1.07</v>
@@ -22580,7 +22583,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23198,7 +23201,7 @@
         <v>104</v>
       </c>
       <c r="P106" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q106">
         <v>2.6</v>
@@ -23894,7 +23897,7 @@
         <v>1.8</v>
       </c>
       <c r="AP109">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ109">
         <v>1.64</v>
@@ -24022,7 +24025,7 @@
         <v>104</v>
       </c>
       <c r="P110" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24103,7 +24106,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ110">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -24515,7 +24518,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ112">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR112">
         <v>1.08</v>
@@ -24846,7 +24849,7 @@
         <v>171</v>
       </c>
       <c r="P114" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -25464,7 +25467,7 @@
         <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -25670,7 +25673,7 @@
         <v>174</v>
       </c>
       <c r="P118" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q118">
         <v>2.5</v>
@@ -25748,7 +25751,7 @@
         <v>1</v>
       </c>
       <c r="AP118">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
         <v>1.29</v>
@@ -26082,7 +26085,7 @@
         <v>175</v>
       </c>
       <c r="P120" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26369,7 +26372,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ121">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR121">
         <v>1.83</v>
@@ -26781,7 +26784,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ123">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR123">
         <v>1.08</v>
@@ -26906,7 +26909,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26984,7 +26987,7 @@
         <v>0.6</v>
       </c>
       <c r="AP124">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ124">
         <v>0.71</v>
@@ -28142,7 +28145,7 @@
         <v>181</v>
       </c>
       <c r="P130" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q130">
         <v>3.75</v>
@@ -28220,7 +28223,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ130">
         <v>1.29</v>
@@ -28554,7 +28557,7 @@
         <v>183</v>
       </c>
       <c r="P132" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q132">
         <v>3.75</v>
@@ -28635,7 +28638,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28966,7 +28969,7 @@
         <v>185</v>
       </c>
       <c r="P134" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q134">
         <v>4.5</v>
@@ -29172,7 +29175,7 @@
         <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q135">
         <v>3.25</v>
@@ -29584,7 +29587,7 @@
         <v>104</v>
       </c>
       <c r="P137" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q137">
         <v>7</v>
@@ -29868,7 +29871,7 @@
         <v>1.83</v>
       </c>
       <c r="AP138">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
         <v>1.07</v>
@@ -30202,7 +30205,7 @@
         <v>190</v>
       </c>
       <c r="P140" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q140">
         <v>1.5</v>
@@ -30820,7 +30823,7 @@
         <v>104</v>
       </c>
       <c r="P143" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q143">
         <v>6</v>
@@ -31026,7 +31029,7 @@
         <v>193</v>
       </c>
       <c r="P144" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q144">
         <v>2.4</v>
@@ -31438,7 +31441,7 @@
         <v>195</v>
       </c>
       <c r="P146" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q146">
         <v>3.6</v>
@@ -31931,7 +31934,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ148">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR148">
         <v>1.35</v>
@@ -32056,7 +32059,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q149">
         <v>5</v>
@@ -32262,7 +32265,7 @@
         <v>199</v>
       </c>
       <c r="P150" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q150">
         <v>3.75</v>
@@ -32340,7 +32343,7 @@
         <v>2</v>
       </c>
       <c r="AP150">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ150">
         <v>1.73</v>
@@ -32549,7 +32552,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ151">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR151">
         <v>1.39</v>
@@ -32880,7 +32883,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q153">
         <v>4.5</v>
@@ -32958,7 +32961,7 @@
         <v>2.2</v>
       </c>
       <c r="AP153">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ153">
         <v>2.2</v>
@@ -33164,7 +33167,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ154">
         <v>1.33</v>
@@ -33292,7 +33295,7 @@
         <v>104</v>
       </c>
       <c r="P155" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q155">
         <v>4.75</v>
@@ -33498,7 +33501,7 @@
         <v>104</v>
       </c>
       <c r="P156" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q156">
         <v>5</v>
@@ -33782,7 +33785,7 @@
         <v>2</v>
       </c>
       <c r="AP157">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
         <v>1.8</v>
@@ -33910,7 +33913,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34116,7 +34119,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q159">
         <v>1.91</v>
@@ -34197,7 +34200,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ159">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34815,7 +34818,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ162">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -35352,7 +35355,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35764,7 +35767,7 @@
         <v>211</v>
       </c>
       <c r="P167" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q167">
         <v>4.33</v>
@@ -36176,7 +36179,7 @@
         <v>102</v>
       </c>
       <c r="P169" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q169">
         <v>2.3</v>
@@ -36588,7 +36591,7 @@
         <v>95</v>
       </c>
       <c r="P171" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q171">
         <v>3.4</v>
@@ -37287,7 +37290,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ174">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR174">
         <v>1.33</v>
@@ -37824,7 +37827,7 @@
         <v>215</v>
       </c>
       <c r="P177" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q177">
         <v>2.4</v>
@@ -38030,7 +38033,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38108,7 +38111,7 @@
         <v>0.44</v>
       </c>
       <c r="AP178">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ178">
         <v>0.73</v>
@@ -38236,7 +38239,7 @@
         <v>217</v>
       </c>
       <c r="P179" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q179">
         <v>1.8</v>
@@ -38317,7 +38320,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ179">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR179">
         <v>1.81</v>
@@ -38442,7 +38445,7 @@
         <v>218</v>
       </c>
       <c r="P180" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q180">
         <v>4.33</v>
@@ -38932,7 +38935,7 @@
         <v>1.33</v>
       </c>
       <c r="AP182">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ182">
         <v>1.33</v>
@@ -39060,7 +39063,7 @@
         <v>90</v>
       </c>
       <c r="P183" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q183">
         <v>7</v>
@@ -39138,7 +39141,7 @@
         <v>1.78</v>
       </c>
       <c r="AP183">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ183">
         <v>1.73</v>
@@ -39472,7 +39475,7 @@
         <v>104</v>
       </c>
       <c r="P185" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -40296,7 +40299,7 @@
         <v>224</v>
       </c>
       <c r="P189" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40583,7 +40586,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ190">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -41120,7 +41123,7 @@
         <v>128</v>
       </c>
       <c r="P193" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q193">
         <v>2.5</v>
@@ -41201,7 +41204,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ193">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR193">
         <v>1.37</v>
@@ -41532,7 +41535,7 @@
         <v>187</v>
       </c>
       <c r="P195" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q195">
         <v>2.38</v>
@@ -41610,7 +41613,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ195">
         <v>0.73</v>
@@ -41944,7 +41947,7 @@
         <v>228</v>
       </c>
       <c r="P197" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -42150,7 +42153,7 @@
         <v>229</v>
       </c>
       <c r="P198" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q198">
         <v>1.44</v>
@@ -42640,7 +42643,7 @@
         <v>1.56</v>
       </c>
       <c r="AP200">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ200">
         <v>1.07</v>
@@ -42849,7 +42852,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ201">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR201">
         <v>1.52</v>
@@ -43055,7 +43058,7 @@
         <v>1</v>
       </c>
       <c r="AQ202">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR202">
         <v>1.36</v>
@@ -43180,7 +43183,7 @@
         <v>104</v>
       </c>
       <c r="P203" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43592,7 +43595,7 @@
         <v>190</v>
       </c>
       <c r="P205" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q205">
         <v>2.38</v>
@@ -43798,7 +43801,7 @@
         <v>104</v>
       </c>
       <c r="P206" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q206">
         <v>8</v>
@@ -44210,7 +44213,7 @@
         <v>104</v>
       </c>
       <c r="P208" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q208">
         <v>2.6</v>
@@ -44494,7 +44497,7 @@
         <v>0.9</v>
       </c>
       <c r="AP209">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ209">
         <v>0.67</v>
@@ -45034,7 +45037,7 @@
         <v>104</v>
       </c>
       <c r="P212" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q212">
         <v>3.75</v>
@@ -45321,7 +45324,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ213">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR213">
         <v>1.36</v>
@@ -45733,7 +45736,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ215">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR215">
         <v>1.74</v>
@@ -46348,7 +46351,7 @@
         <v>0.5</v>
       </c>
       <c r="AP218">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ218">
         <v>0.71</v>
@@ -46682,7 +46685,7 @@
         <v>237</v>
       </c>
       <c r="P220" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q220">
         <v>3.6</v>
@@ -46760,7 +46763,7 @@
         <v>1.8</v>
       </c>
       <c r="AP220">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ220">
         <v>1.64</v>
@@ -47300,7 +47303,7 @@
         <v>240</v>
       </c>
       <c r="P223" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47584,7 +47587,7 @@
         <v>1.09</v>
       </c>
       <c r="AP224">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ224">
         <v>0.87</v>
@@ -47712,7 +47715,7 @@
         <v>158</v>
       </c>
       <c r="P225" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q225">
         <v>4.5</v>
@@ -48408,7 +48411,7 @@
         <v>0.91</v>
       </c>
       <c r="AP228">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ228">
         <v>0.67</v>
@@ -48742,7 +48745,7 @@
         <v>145</v>
       </c>
       <c r="P230" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q230">
         <v>5</v>
@@ -49029,7 +49032,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ231">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR231">
         <v>1.25</v>
@@ -49154,7 +49157,7 @@
         <v>244</v>
       </c>
       <c r="P232" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q232">
         <v>2.63</v>
@@ -49360,7 +49363,7 @@
         <v>245</v>
       </c>
       <c r="P233" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q233">
         <v>3.75</v>
@@ -49566,7 +49569,7 @@
         <v>221</v>
       </c>
       <c r="P234" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q234">
         <v>5.5</v>
@@ -50184,7 +50187,7 @@
         <v>247</v>
       </c>
       <c r="P237" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q237">
         <v>5.5</v>
@@ -50390,7 +50393,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q238">
         <v>4.5</v>
@@ -50471,7 +50474,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ238">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR238">
         <v>1</v>
@@ -50880,7 +50883,7 @@
         <v>1.27</v>
       </c>
       <c r="AP240">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ240">
         <v>1.07</v>
@@ -51295,7 +51298,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ242">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR242">
         <v>1.38</v>
@@ -51420,7 +51423,7 @@
         <v>104</v>
       </c>
       <c r="P243" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q243">
         <v>2.6</v>
@@ -51832,7 +51835,7 @@
         <v>104</v>
       </c>
       <c r="P245" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q245">
         <v>4.75</v>
@@ -51910,7 +51913,7 @@
         <v>1.73</v>
       </c>
       <c r="AP245">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ245">
         <v>1.64</v>
@@ -52038,7 +52041,7 @@
         <v>104</v>
       </c>
       <c r="P246" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q246">
         <v>7.5</v>
@@ -52244,7 +52247,7 @@
         <v>250</v>
       </c>
       <c r="P247" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q247">
         <v>1.62</v>
@@ -52322,7 +52325,7 @@
         <v>0.25</v>
       </c>
       <c r="AP247">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ247">
         <v>0.2</v>
@@ -52656,7 +52659,7 @@
         <v>178</v>
       </c>
       <c r="P249" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53068,7 +53071,7 @@
         <v>253</v>
       </c>
       <c r="P251" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q251">
         <v>2.88</v>
@@ -53149,7 +53152,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ251">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR251">
         <v>1.43</v>
@@ -53274,7 +53277,7 @@
         <v>254</v>
       </c>
       <c r="P252" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q252">
         <v>3.75</v>
@@ -53480,7 +53483,7 @@
         <v>255</v>
       </c>
       <c r="P253" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q253">
         <v>2.75</v>
@@ -53767,7 +53770,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ254">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR254">
         <v>1.67</v>
@@ -53892,7 +53895,7 @@
         <v>256</v>
       </c>
       <c r="P255" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q255">
         <v>4.33</v>
@@ -53970,7 +53973,7 @@
         <v>1.77</v>
       </c>
       <c r="AP255">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ255">
         <v>1.73</v>
@@ -54922,7 +54925,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55540,7 +55543,7 @@
         <v>262</v>
       </c>
       <c r="P263" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q263">
         <v>1.95</v>
@@ -55618,7 +55621,7 @@
         <v>0.23</v>
       </c>
       <c r="AP263">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ263">
         <v>0.2</v>
@@ -55746,7 +55749,7 @@
         <v>263</v>
       </c>
       <c r="P264" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q264">
         <v>5</v>
@@ -56236,7 +56239,7 @@
         <v>0.85</v>
       </c>
       <c r="AP266">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ266">
         <v>0.79</v>
@@ -56364,7 +56367,7 @@
         <v>221</v>
       </c>
       <c r="P267" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q267">
         <v>2.25</v>
@@ -56442,10 +56445,10 @@
         <v>1.33</v>
       </c>
       <c r="AP267">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ267">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR267">
         <v>1.69</v>
@@ -56570,7 +56573,7 @@
         <v>104</v>
       </c>
       <c r="P268" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q268">
         <v>2.88</v>
@@ -56651,7 +56654,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ268">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR268">
         <v>1.45</v>
@@ -56982,7 +56985,7 @@
         <v>265</v>
       </c>
       <c r="P270" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q270">
         <v>3.75</v>
@@ -57600,7 +57603,7 @@
         <v>138</v>
       </c>
       <c r="P273" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q273">
         <v>3.6</v>
@@ -58012,7 +58015,7 @@
         <v>268</v>
       </c>
       <c r="P275" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q275">
         <v>4.33</v>
@@ -58424,7 +58427,7 @@
         <v>110</v>
       </c>
       <c r="P277" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58630,7 +58633,7 @@
         <v>269</v>
       </c>
       <c r="P278" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q278">
         <v>3.4</v>
@@ -58836,7 +58839,7 @@
         <v>270</v>
       </c>
       <c r="P279" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q279">
         <v>3.4</v>
@@ -59123,7 +59126,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ280">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR280">
         <v>2.14</v>
@@ -59660,7 +59663,7 @@
         <v>104</v>
       </c>
       <c r="P283" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q283">
         <v>3.1</v>
@@ -59866,7 +59869,7 @@
         <v>273</v>
       </c>
       <c r="P284" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q284">
         <v>1.5</v>
@@ -60072,7 +60075,7 @@
         <v>274</v>
       </c>
       <c r="P285" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q285">
         <v>4</v>
@@ -60435,6 +60438,624 @@
       </c>
       <c r="BP286">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="287" spans="1:68">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>7465271</v>
+      </c>
+      <c r="C287" t="s">
+        <v>68</v>
+      </c>
+      <c r="D287" t="s">
+        <v>69</v>
+      </c>
+      <c r="E287" s="2">
+        <v>45746.5625</v>
+      </c>
+      <c r="F287">
+        <v>29</v>
+      </c>
+      <c r="G287" t="s">
+        <v>75</v>
+      </c>
+      <c r="H287" t="s">
+        <v>77</v>
+      </c>
+      <c r="I287">
+        <v>0</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="L287">
+        <v>1</v>
+      </c>
+      <c r="M287">
+        <v>0</v>
+      </c>
+      <c r="N287">
+        <v>1</v>
+      </c>
+      <c r="O287" t="s">
+        <v>157</v>
+      </c>
+      <c r="P287" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q287">
+        <v>3</v>
+      </c>
+      <c r="R287">
+        <v>1.91</v>
+      </c>
+      <c r="S287">
+        <v>4.5</v>
+      </c>
+      <c r="T287">
+        <v>1.57</v>
+      </c>
+      <c r="U287">
+        <v>2.25</v>
+      </c>
+      <c r="V287">
+        <v>3.75</v>
+      </c>
+      <c r="W287">
+        <v>1.25</v>
+      </c>
+      <c r="X287">
+        <v>13</v>
+      </c>
+      <c r="Y287">
+        <v>1.04</v>
+      </c>
+      <c r="Z287">
+        <v>2.15</v>
+      </c>
+      <c r="AA287">
+        <v>3.1</v>
+      </c>
+      <c r="AB287">
+        <v>3.75</v>
+      </c>
+      <c r="AC287">
+        <v>1.1</v>
+      </c>
+      <c r="AD287">
+        <v>6.5</v>
+      </c>
+      <c r="AE287">
+        <v>1.5</v>
+      </c>
+      <c r="AF287">
+        <v>2.45</v>
+      </c>
+      <c r="AG287">
+        <v>2.63</v>
+      </c>
+      <c r="AH287">
+        <v>1.5</v>
+      </c>
+      <c r="AI287">
+        <v>2.1</v>
+      </c>
+      <c r="AJ287">
+        <v>1.67</v>
+      </c>
+      <c r="AK287">
+        <v>1.24</v>
+      </c>
+      <c r="AL287">
+        <v>1.34</v>
+      </c>
+      <c r="AM287">
+        <v>1.75</v>
+      </c>
+      <c r="AN287">
+        <v>1.5</v>
+      </c>
+      <c r="AO287">
+        <v>1.31</v>
+      </c>
+      <c r="AP287">
+        <v>1.6</v>
+      </c>
+      <c r="AQ287">
+        <v>1.21</v>
+      </c>
+      <c r="AR287">
+        <v>1.43</v>
+      </c>
+      <c r="AS287">
+        <v>1.18</v>
+      </c>
+      <c r="AT287">
+        <v>2.61</v>
+      </c>
+      <c r="AU287">
+        <v>3</v>
+      </c>
+      <c r="AV287">
+        <v>3</v>
+      </c>
+      <c r="AW287">
+        <v>6</v>
+      </c>
+      <c r="AX287">
+        <v>6</v>
+      </c>
+      <c r="AY287">
+        <v>10</v>
+      </c>
+      <c r="AZ287">
+        <v>9</v>
+      </c>
+      <c r="BA287">
+        <v>4</v>
+      </c>
+      <c r="BB287">
+        <v>5</v>
+      </c>
+      <c r="BC287">
+        <v>9</v>
+      </c>
+      <c r="BD287">
+        <v>1.65</v>
+      </c>
+      <c r="BE287">
+        <v>6.4</v>
+      </c>
+      <c r="BF287">
+        <v>2.55</v>
+      </c>
+      <c r="BG287">
+        <v>1.44</v>
+      </c>
+      <c r="BH287">
+        <v>2.55</v>
+      </c>
+      <c r="BI287">
+        <v>1.73</v>
+      </c>
+      <c r="BJ287">
+        <v>1.96</v>
+      </c>
+      <c r="BK287">
+        <v>2.18</v>
+      </c>
+      <c r="BL287">
+        <v>1.58</v>
+      </c>
+      <c r="BM287">
+        <v>2.8</v>
+      </c>
+      <c r="BN287">
+        <v>1.37</v>
+      </c>
+      <c r="BO287">
+        <v>3.8</v>
+      </c>
+      <c r="BP287">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7465264</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45746.5625</v>
+      </c>
+      <c r="F288">
+        <v>29</v>
+      </c>
+      <c r="G288" t="s">
+        <v>70</v>
+      </c>
+      <c r="H288" t="s">
+        <v>74</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>0</v>
+      </c>
+      <c r="L288">
+        <v>0</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
+      </c>
+      <c r="N288">
+        <v>0</v>
+      </c>
+      <c r="O288" t="s">
+        <v>104</v>
+      </c>
+      <c r="P288" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q288">
+        <v>2.1</v>
+      </c>
+      <c r="R288">
+        <v>2.25</v>
+      </c>
+      <c r="S288">
+        <v>6.5</v>
+      </c>
+      <c r="T288">
+        <v>1.4</v>
+      </c>
+      <c r="U288">
+        <v>2.75</v>
+      </c>
+      <c r="V288">
+        <v>3</v>
+      </c>
+      <c r="W288">
+        <v>1.36</v>
+      </c>
+      <c r="X288">
+        <v>8</v>
+      </c>
+      <c r="Y288">
+        <v>1.08</v>
+      </c>
+      <c r="Z288">
+        <v>1.5</v>
+      </c>
+      <c r="AA288">
+        <v>4</v>
+      </c>
+      <c r="AB288">
+        <v>6.5</v>
+      </c>
+      <c r="AC288">
+        <v>1.05</v>
+      </c>
+      <c r="AD288">
+        <v>9.5</v>
+      </c>
+      <c r="AE288">
+        <v>1.3</v>
+      </c>
+      <c r="AF288">
+        <v>3.35</v>
+      </c>
+      <c r="AG288">
+        <v>2</v>
+      </c>
+      <c r="AH288">
+        <v>1.8</v>
+      </c>
+      <c r="AI288">
+        <v>2.05</v>
+      </c>
+      <c r="AJ288">
+        <v>1.7</v>
+      </c>
+      <c r="AK288">
+        <v>1.12</v>
+      </c>
+      <c r="AL288">
+        <v>1.24</v>
+      </c>
+      <c r="AM288">
+        <v>2.4</v>
+      </c>
+      <c r="AN288">
+        <v>2.07</v>
+      </c>
+      <c r="AO288">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP288">
+        <v>2</v>
+      </c>
+      <c r="AQ288">
+        <v>0.71</v>
+      </c>
+      <c r="AR288">
+        <v>1.65</v>
+      </c>
+      <c r="AS288">
+        <v>0.98</v>
+      </c>
+      <c r="AT288">
+        <v>2.63</v>
+      </c>
+      <c r="AU288">
+        <v>6</v>
+      </c>
+      <c r="AV288">
+        <v>3</v>
+      </c>
+      <c r="AW288">
+        <v>6</v>
+      </c>
+      <c r="AX288">
+        <v>4</v>
+      </c>
+      <c r="AY288">
+        <v>13</v>
+      </c>
+      <c r="AZ288">
+        <v>8</v>
+      </c>
+      <c r="BA288">
+        <v>3</v>
+      </c>
+      <c r="BB288">
+        <v>4</v>
+      </c>
+      <c r="BC288">
+        <v>7</v>
+      </c>
+      <c r="BD288">
+        <v>1.28</v>
+      </c>
+      <c r="BE288">
+        <v>10.75</v>
+      </c>
+      <c r="BF288">
+        <v>4.65</v>
+      </c>
+      <c r="BG288">
+        <v>1.24</v>
+      </c>
+      <c r="BH288">
+        <v>3.34</v>
+      </c>
+      <c r="BI288">
+        <v>1.47</v>
+      </c>
+      <c r="BJ288">
+        <v>2.42</v>
+      </c>
+      <c r="BK288">
+        <v>1.91</v>
+      </c>
+      <c r="BL288">
+        <v>1.8</v>
+      </c>
+      <c r="BM288">
+        <v>2.34</v>
+      </c>
+      <c r="BN288">
+        <v>1.5</v>
+      </c>
+      <c r="BO288">
+        <v>3.08</v>
+      </c>
+      <c r="BP288">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7465266</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45746.66666666666</v>
+      </c>
+      <c r="F289">
+        <v>29</v>
+      </c>
+      <c r="G289" t="s">
+        <v>71</v>
+      </c>
+      <c r="H289" t="s">
+        <v>80</v>
+      </c>
+      <c r="I289">
+        <v>2</v>
+      </c>
+      <c r="J289">
+        <v>1</v>
+      </c>
+      <c r="K289">
+        <v>3</v>
+      </c>
+      <c r="L289">
+        <v>2</v>
+      </c>
+      <c r="M289">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>3</v>
+      </c>
+      <c r="O289" t="s">
+        <v>276</v>
+      </c>
+      <c r="P289" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q289">
+        <v>2.6</v>
+      </c>
+      <c r="R289">
+        <v>2.1</v>
+      </c>
+      <c r="S289">
+        <v>4.33</v>
+      </c>
+      <c r="T289">
+        <v>1.4</v>
+      </c>
+      <c r="U289">
+        <v>2.75</v>
+      </c>
+      <c r="V289">
+        <v>3</v>
+      </c>
+      <c r="W289">
+        <v>1.36</v>
+      </c>
+      <c r="X289">
+        <v>8</v>
+      </c>
+      <c r="Y289">
+        <v>1.08</v>
+      </c>
+      <c r="Z289">
+        <v>1.94</v>
+      </c>
+      <c r="AA289">
+        <v>3.42</v>
+      </c>
+      <c r="AB289">
+        <v>4.19</v>
+      </c>
+      <c r="AC289">
+        <v>1.06</v>
+      </c>
+      <c r="AD289">
+        <v>8.5</v>
+      </c>
+      <c r="AE289">
+        <v>1.33</v>
+      </c>
+      <c r="AF289">
+        <v>3.2</v>
+      </c>
+      <c r="AG289">
+        <v>2.05</v>
+      </c>
+      <c r="AH289">
+        <v>1.81</v>
+      </c>
+      <c r="AI289">
+        <v>1.8</v>
+      </c>
+      <c r="AJ289">
+        <v>1.95</v>
+      </c>
+      <c r="AK289">
+        <v>1.28</v>
+      </c>
+      <c r="AL289">
+        <v>1.31</v>
+      </c>
+      <c r="AM289">
+        <v>1.72</v>
+      </c>
+      <c r="AN289">
+        <v>1.86</v>
+      </c>
+      <c r="AO289">
+        <v>1.21</v>
+      </c>
+      <c r="AP289">
+        <v>1.93</v>
+      </c>
+      <c r="AQ289">
+        <v>1.13</v>
+      </c>
+      <c r="AR289">
+        <v>1.8</v>
+      </c>
+      <c r="AS289">
+        <v>1.23</v>
+      </c>
+      <c r="AT289">
+        <v>3.03</v>
+      </c>
+      <c r="AU289">
+        <v>4</v>
+      </c>
+      <c r="AV289">
+        <v>3</v>
+      </c>
+      <c r="AW289">
+        <v>8</v>
+      </c>
+      <c r="AX289">
+        <v>4</v>
+      </c>
+      <c r="AY289">
+        <v>14</v>
+      </c>
+      <c r="AZ289">
+        <v>10</v>
+      </c>
+      <c r="BA289">
+        <v>2</v>
+      </c>
+      <c r="BB289">
+        <v>2</v>
+      </c>
+      <c r="BC289">
+        <v>4</v>
+      </c>
+      <c r="BD289">
+        <v>1.65</v>
+      </c>
+      <c r="BE289">
+        <v>6.4</v>
+      </c>
+      <c r="BF289">
+        <v>2.5</v>
+      </c>
+      <c r="BG289">
+        <v>1.33</v>
+      </c>
+      <c r="BH289">
+        <v>2.95</v>
+      </c>
+      <c r="BI289">
+        <v>1.58</v>
+      </c>
+      <c r="BJ289">
+        <v>2.2</v>
+      </c>
+      <c r="BK289">
+        <v>1.95</v>
+      </c>
+      <c r="BL289">
+        <v>1.75</v>
+      </c>
+      <c r="BM289">
+        <v>2.43</v>
+      </c>
+      <c r="BN289">
+        <v>1.48</v>
+      </c>
+      <c r="BO289">
+        <v>3.15</v>
+      </c>
+      <c r="BP289">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="383">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1161,6 +1161,9 @@
   <si>
     <t>['15', '33']</t>
   </si>
+  <si>
+    <t>['48']</t>
+  </si>
 </sst>
 </file>
 
@@ -1521,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP289"/>
+  <dimension ref="A1:BP290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2267,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0.73</v>
@@ -3915,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>0.5</v>
@@ -5360,7 +5363,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ19">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -8862,7 +8865,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ36">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR36">
         <v>0.71</v>
@@ -10919,7 +10922,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.2</v>
@@ -12982,7 +12985,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ56">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -16069,7 +16072,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
         <v>1.64</v>
@@ -17305,7 +17308,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>0.87</v>
@@ -18132,7 +18135,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -21219,7 +21222,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>1.73</v>
@@ -22252,7 +22255,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ101">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR101">
         <v>1.21</v>
@@ -25136,7 +25139,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ115">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR115">
         <v>1.74</v>
@@ -25957,7 +25960,7 @@
         <v>0.4</v>
       </c>
       <c r="AP119">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
         <v>1.21</v>
@@ -26166,7 +26169,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ120">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR120">
         <v>1.55</v>
@@ -29047,7 +29050,7 @@
         <v>2.25</v>
       </c>
       <c r="AP134">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>2.2</v>
@@ -30286,7 +30289,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ140">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR140">
         <v>1.94</v>
@@ -32549,7 +32552,7 @@
         <v>1.71</v>
       </c>
       <c r="AP151">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
         <v>1.21</v>
@@ -36054,7 +36057,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ168">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR168">
         <v>1.43</v>
@@ -37493,7 +37496,7 @@
         <v>1.75</v>
       </c>
       <c r="AP175">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ175">
         <v>1.07</v>
@@ -42025,7 +42028,7 @@
         <v>1.67</v>
       </c>
       <c r="AP197">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ197">
         <v>1.64</v>
@@ -42234,7 +42237,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ198">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR198">
         <v>1.8</v>
@@ -46972,7 +46975,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ221">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR221">
         <v>1.35</v>
@@ -47381,7 +47384,7 @@
         <v>1.09</v>
       </c>
       <c r="AP223">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ223">
         <v>1.29</v>
@@ -50680,7 +50683,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ239">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR239">
         <v>1.24</v>
@@ -51295,7 +51298,7 @@
         <v>0.82</v>
       </c>
       <c r="AP242">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ242">
         <v>0.71</v>
@@ -53358,7 +53361,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ252">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR252">
         <v>0.99</v>
@@ -55209,7 +55212,7 @@
         <v>0.77</v>
       </c>
       <c r="AP261">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ261">
         <v>0.67</v>
@@ -56242,7 +56245,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ266">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AR266">
         <v>1.79</v>
@@ -61056,6 +61059,212 @@
       </c>
       <c r="BP289">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7465267</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45747.66666666666</v>
+      </c>
+      <c r="F290">
+        <v>29</v>
+      </c>
+      <c r="G290" t="s">
+        <v>72</v>
+      </c>
+      <c r="H290" t="s">
+        <v>73</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>1</v>
+      </c>
+      <c r="L290">
+        <v>1</v>
+      </c>
+      <c r="M290">
+        <v>1</v>
+      </c>
+      <c r="N290">
+        <v>2</v>
+      </c>
+      <c r="O290" t="s">
+        <v>253</v>
+      </c>
+      <c r="P290" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q290">
+        <v>2.1</v>
+      </c>
+      <c r="R290">
+        <v>2.3</v>
+      </c>
+      <c r="S290">
+        <v>5.5</v>
+      </c>
+      <c r="T290">
+        <v>1.33</v>
+      </c>
+      <c r="U290">
+        <v>3.25</v>
+      </c>
+      <c r="V290">
+        <v>2.63</v>
+      </c>
+      <c r="W290">
+        <v>1.44</v>
+      </c>
+      <c r="X290">
+        <v>7</v>
+      </c>
+      <c r="Y290">
+        <v>1.1</v>
+      </c>
+      <c r="Z290">
+        <v>1.57</v>
+      </c>
+      <c r="AA290">
+        <v>4.1</v>
+      </c>
+      <c r="AB290">
+        <v>5.5</v>
+      </c>
+      <c r="AC290">
+        <v>1.02</v>
+      </c>
+      <c r="AD290">
+        <v>13.9</v>
+      </c>
+      <c r="AE290">
+        <v>1.23</v>
+      </c>
+      <c r="AF290">
+        <v>3.82</v>
+      </c>
+      <c r="AG290">
+        <v>1.8</v>
+      </c>
+      <c r="AH290">
+        <v>2</v>
+      </c>
+      <c r="AI290">
+        <v>1.8</v>
+      </c>
+      <c r="AJ290">
+        <v>1.95</v>
+      </c>
+      <c r="AK290">
+        <v>1.14</v>
+      </c>
+      <c r="AL290">
+        <v>1.22</v>
+      </c>
+      <c r="AM290">
+        <v>2.37</v>
+      </c>
+      <c r="AN290">
+        <v>2.07</v>
+      </c>
+      <c r="AO290">
+        <v>0.79</v>
+      </c>
+      <c r="AP290">
+        <v>2</v>
+      </c>
+      <c r="AQ290">
+        <v>0.8</v>
+      </c>
+      <c r="AR290">
+        <v>1.36</v>
+      </c>
+      <c r="AS290">
+        <v>1.05</v>
+      </c>
+      <c r="AT290">
+        <v>2.41</v>
+      </c>
+      <c r="AU290">
+        <v>8</v>
+      </c>
+      <c r="AV290">
+        <v>3</v>
+      </c>
+      <c r="AW290">
+        <v>12</v>
+      </c>
+      <c r="AX290">
+        <v>2</v>
+      </c>
+      <c r="AY290">
+        <v>24</v>
+      </c>
+      <c r="AZ290">
+        <v>5</v>
+      </c>
+      <c r="BA290">
+        <v>4</v>
+      </c>
+      <c r="BB290">
+        <v>2</v>
+      </c>
+      <c r="BC290">
+        <v>6</v>
+      </c>
+      <c r="BD290">
+        <v>1.45</v>
+      </c>
+      <c r="BE290">
+        <v>9</v>
+      </c>
+      <c r="BF290">
+        <v>3.48</v>
+      </c>
+      <c r="BG290">
+        <v>1.32</v>
+      </c>
+      <c r="BH290">
+        <v>2.88</v>
+      </c>
+      <c r="BI290">
+        <v>1.6</v>
+      </c>
+      <c r="BJ290">
+        <v>2.14</v>
+      </c>
+      <c r="BK290">
+        <v>2.1</v>
+      </c>
+      <c r="BL290">
+        <v>1.67</v>
+      </c>
+      <c r="BM290">
+        <v>2.67</v>
+      </c>
+      <c r="BN290">
+        <v>1.39</v>
+      </c>
+      <c r="BO290">
+        <v>3.7</v>
+      </c>
+      <c r="BP290">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -60589,13 +60589,13 @@
         <v>3</v>
       </c>
       <c r="AW287">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX287">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY287">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ287">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="386">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1164,6 +1164,15 @@
   <si>
     <t>['48']</t>
   </si>
+  <si>
+    <t>['12', '16', '72', '90']</t>
+  </si>
+  <si>
+    <t>['15', '90+5']</t>
+  </si>
+  <si>
+    <t>['53', '72']</t>
+  </si>
 </sst>
 </file>
 
@@ -1524,7 +1533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP290"/>
+  <dimension ref="A1:BP295"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2273,7 +2282,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -3300,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ9">
         <v>1.73</v>
@@ -3509,7 +3518,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ10">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3921,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR12">
         <v>1.07</v>
@@ -4536,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ15">
         <v>1.64</v>
@@ -5154,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ18">
         <v>0.2</v>
@@ -5569,7 +5578,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ20">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5981,7 +5990,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ22">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR22">
         <v>1.08</v>
@@ -6184,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ23">
         <v>1.13</v>
@@ -6390,7 +6399,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>2.2</v>
@@ -6599,7 +6608,7 @@
         <v>2</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR25">
         <v>0.96</v>
@@ -7011,7 +7020,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ27">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR27">
         <v>1.31</v>
@@ -7217,7 +7226,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ28">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -7420,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ29">
         <v>0.71</v>
@@ -7832,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ31">
         <v>0.2</v>
@@ -9071,7 +9080,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ37">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -9686,10 +9695,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ40">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR40">
         <v>2.11</v>
@@ -10098,7 +10107,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ42">
         <v>1.8</v>
@@ -10307,7 +10316,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ43">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR43">
         <v>1.17</v>
@@ -11128,7 +11137,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47">
         <v>2.2</v>
@@ -11543,7 +11552,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ49">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR49">
         <v>1.74</v>
@@ -11746,7 +11755,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ50">
         <v>0.71</v>
@@ -11952,7 +11961,7 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ51">
         <v>1.07</v>
@@ -13394,10 +13403,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ58">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR58">
         <v>2.01</v>
@@ -13809,7 +13818,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR60">
         <v>1.11</v>
@@ -14218,7 +14227,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ62">
         <v>1.64</v>
@@ -15042,10 +15051,10 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ66">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR66">
         <v>2.43</v>
@@ -15248,7 +15257,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ67">
         <v>1.33</v>
@@ -15454,7 +15463,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ68">
         <v>1.21</v>
@@ -15869,7 +15878,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR70">
         <v>1.36</v>
@@ -16487,7 +16496,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ73">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR73">
         <v>1.15</v>
@@ -16690,7 +16699,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
         <v>0.67</v>
@@ -16899,7 +16908,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR75">
         <v>1.11</v>
@@ -17723,7 +17732,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ79">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR79">
         <v>1.68</v>
@@ -18341,7 +18350,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ82">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR82">
         <v>1.25</v>
@@ -18959,7 +18968,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR85">
         <v>1.24</v>
@@ -19368,7 +19377,7 @@
         <v>2.5</v>
       </c>
       <c r="AP87">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ87">
         <v>1.8</v>
@@ -19574,7 +19583,7 @@
         <v>2</v>
       </c>
       <c r="AP88">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
         <v>1.64</v>
@@ -19989,7 +19998,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ90">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR90">
         <v>1.55</v>
@@ -20607,7 +20616,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -20813,7 +20822,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ94">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -21016,7 +21025,7 @@
         <v>1.25</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ95">
         <v>1.07</v>
@@ -21428,7 +21437,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ97">
         <v>1.33</v>
@@ -22046,7 +22055,7 @@
         <v>0.75</v>
       </c>
       <c r="AP100">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ100">
         <v>1.13</v>
@@ -22870,10 +22879,10 @@
         <v>0.6</v>
       </c>
       <c r="AP104">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR104">
         <v>1.49</v>
@@ -23282,7 +23291,7 @@
         <v>2.5</v>
       </c>
       <c r="AP106">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ106">
         <v>2.2</v>
@@ -23491,7 +23500,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ107">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR107">
         <v>1.1</v>
@@ -23697,7 +23706,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ108">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -24312,7 +24321,7 @@
         <v>1.5</v>
       </c>
       <c r="AP111">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ111">
         <v>1.64</v>
@@ -24930,7 +24939,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ114">
         <v>0.67</v>
@@ -25342,10 +25351,10 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ116">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR116">
         <v>1.93</v>
@@ -25757,7 +25766,7 @@
         <v>2</v>
       </c>
       <c r="AQ118">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR118">
         <v>1.26</v>
@@ -26166,7 +26175,7 @@
         <v>0.5</v>
       </c>
       <c r="AP120">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120">
         <v>0.8</v>
@@ -26372,7 +26381,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ121">
         <v>0.71</v>
@@ -26581,7 +26590,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ122">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR122">
         <v>1.57</v>
@@ -26993,7 +27002,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ124">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR124">
         <v>1.82</v>
@@ -27196,7 +27205,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ125">
         <v>1.64</v>
@@ -28229,7 +28238,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ130">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR130">
         <v>1.31</v>
@@ -28435,7 +28444,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ131">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28844,10 +28853,10 @@
         <v>0.17</v>
       </c>
       <c r="AP133">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ133">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR133">
         <v>1.36</v>
@@ -30080,10 +30089,10 @@
         <v>0.33</v>
       </c>
       <c r="AP139">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ139">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR139">
         <v>1.33</v>
@@ -30286,7 +30295,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ140">
         <v>0.8</v>
@@ -30701,7 +30710,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ142">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR142">
         <v>1.12</v>
@@ -31316,7 +31325,7 @@
         <v>0.33</v>
       </c>
       <c r="AP145">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ145">
         <v>1.21</v>
@@ -31522,7 +31531,7 @@
         <v>1.33</v>
       </c>
       <c r="AP146">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ146">
         <v>1.64</v>
@@ -31731,7 +31740,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ147">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR147">
         <v>1.56</v>
@@ -32140,7 +32149,7 @@
         <v>2.11</v>
       </c>
       <c r="AP149">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ149">
         <v>2.2</v>
@@ -33376,7 +33385,7 @@
         <v>1.71</v>
       </c>
       <c r="AP155">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ155">
         <v>1.73</v>
@@ -33997,7 +34006,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ158">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR158">
         <v>1.47</v>
@@ -34409,7 +34418,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ160">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR160">
         <v>1.3</v>
@@ -34615,7 +34624,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ161">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR161">
         <v>1.1</v>
@@ -35024,7 +35033,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ163">
         <v>0.87</v>
@@ -35233,7 +35242,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ164">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR164">
         <v>1.37</v>
@@ -35436,7 +35445,7 @@
         <v>1.88</v>
       </c>
       <c r="AP165">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ165">
         <v>1.73</v>
@@ -36263,7 +36272,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ169">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36466,7 +36475,7 @@
         <v>0.63</v>
       </c>
       <c r="AP170">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ170">
         <v>0.67</v>
@@ -36675,7 +36684,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ171">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR171">
         <v>1.12</v>
@@ -37084,7 +37093,7 @@
         <v>0.38</v>
       </c>
       <c r="AP173">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ173">
         <v>0.2</v>
@@ -37908,7 +37917,7 @@
         <v>1.88</v>
       </c>
       <c r="AP177">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ177">
         <v>1.64</v>
@@ -38117,7 +38126,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ178">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR178">
         <v>1.38</v>
@@ -38320,7 +38329,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ179">
         <v>1.13</v>
@@ -38735,7 +38744,7 @@
         <v>1</v>
       </c>
       <c r="AQ181">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR181">
         <v>1.34</v>
@@ -39350,10 +39359,10 @@
         <v>0.5</v>
       </c>
       <c r="AP184">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ184">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR184">
         <v>1.61</v>
@@ -39765,7 +39774,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ186">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR186">
         <v>1.03</v>
@@ -40177,7 +40186,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ188">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR188">
         <v>1.34</v>
@@ -41204,7 +41213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP193">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ193">
         <v>1.13</v>
@@ -41619,7 +41628,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ195">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR195">
         <v>1.78</v>
@@ -42234,7 +42243,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ198">
         <v>0.8</v>
@@ -43264,10 +43273,10 @@
         <v>0.9</v>
       </c>
       <c r="AP203">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ203">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR203">
         <v>1.2</v>
@@ -43679,7 +43688,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ205">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR205">
         <v>1.35</v>
@@ -44088,7 +44097,7 @@
         <v>1.2</v>
       </c>
       <c r="AP207">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ207">
         <v>0.87</v>
@@ -44706,10 +44715,10 @@
         <v>0.4</v>
       </c>
       <c r="AP210">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ210">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR210">
         <v>2.02</v>
@@ -44915,7 +44924,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ211">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR211">
         <v>1.16</v>
@@ -46148,10 +46157,10 @@
         <v>0.73</v>
       </c>
       <c r="AP217">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ217">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR217">
         <v>2.09</v>
@@ -46357,7 +46366,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ218">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR218">
         <v>1.3</v>
@@ -46972,7 +46981,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ221">
         <v>0.8</v>
@@ -47178,7 +47187,7 @@
         <v>0.27</v>
       </c>
       <c r="AP222">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ222">
         <v>0.2</v>
@@ -47387,7 +47396,7 @@
         <v>2</v>
       </c>
       <c r="AQ223">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR223">
         <v>1.34</v>
@@ -48002,7 +48011,7 @@
         <v>1.8</v>
       </c>
       <c r="AP226">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ226">
         <v>1.64</v>
@@ -48623,7 +48632,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ229">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR229">
         <v>1.42</v>
@@ -49032,7 +49041,7 @@
         <v>0.8</v>
       </c>
       <c r="AP231">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ231">
         <v>0.71</v>
@@ -49238,7 +49247,7 @@
         <v>1</v>
       </c>
       <c r="AP232">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ232">
         <v>1.21</v>
@@ -49447,7 +49456,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ233">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR233">
         <v>0.95</v>
@@ -49859,7 +49868,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ235">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR235">
         <v>1.76</v>
@@ -50065,7 +50074,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ236">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR236">
         <v>1.64</v>
@@ -50680,7 +50689,7 @@
         <v>0.91</v>
       </c>
       <c r="AP239">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ239">
         <v>0.8</v>
@@ -51092,7 +51101,7 @@
         <v>1.42</v>
       </c>
       <c r="AP241">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ241">
         <v>1.33</v>
@@ -51507,7 +51516,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ243">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR243">
         <v>1.16</v>
@@ -51710,7 +51719,7 @@
         <v>1.75</v>
       </c>
       <c r="AP244">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ244">
         <v>1.8</v>
@@ -52534,7 +52543,7 @@
         <v>1</v>
       </c>
       <c r="AP248">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ248">
         <v>0.87</v>
@@ -52743,7 +52752,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ249">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR249">
         <v>1.32</v>
@@ -53564,10 +53573,10 @@
         <v>0.5</v>
       </c>
       <c r="AP253">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ253">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR253">
         <v>1.4</v>
@@ -53770,7 +53779,7 @@
         <v>1.08</v>
       </c>
       <c r="AP254">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ254">
         <v>1.13</v>
@@ -54594,7 +54603,7 @@
         <v>1.17</v>
       </c>
       <c r="AP258">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ258">
         <v>1.07</v>
@@ -54800,10 +54809,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP259">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ259">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR259">
         <v>1.28</v>
@@ -55009,7 +55018,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ260">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR260">
         <v>1.48</v>
@@ -56036,7 +56045,7 @@
         <v>1.31</v>
       </c>
       <c r="AP265">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ265">
         <v>1.33</v>
@@ -57069,7 +57078,7 @@
         <v>1</v>
       </c>
       <c r="AQ270">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="AR270">
         <v>1.38</v>
@@ -57275,7 +57284,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ271">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR271">
         <v>1.11</v>
@@ -57478,10 +57487,10 @@
         <v>0.42</v>
       </c>
       <c r="AP272">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AQ272">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR272">
         <v>1.3</v>
@@ -57890,10 +57899,10 @@
         <v>0.46</v>
       </c>
       <c r="AP274">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ274">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR274">
         <v>1.4</v>
@@ -58099,7 +58108,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ275">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR275">
         <v>0.95</v>
@@ -58714,7 +58723,7 @@
         <v>1.08</v>
       </c>
       <c r="AP278">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ278">
         <v>1.07</v>
@@ -59126,7 +59135,7 @@
         <v>0.75</v>
       </c>
       <c r="AP280">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ280">
         <v>0.71</v>
@@ -59950,7 +59959,7 @@
         <v>0.71</v>
       </c>
       <c r="AP284">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="AQ284">
         <v>0.67</v>
@@ -60362,7 +60371,7 @@
         <v>0.93</v>
       </c>
       <c r="AP286">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AQ286">
         <v>0.87</v>
@@ -61265,6 +61274,1036 @@
       </c>
       <c r="BP290">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7469687</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45751.66666666666</v>
+      </c>
+      <c r="F291">
+        <v>30</v>
+      </c>
+      <c r="G291" t="s">
+        <v>88</v>
+      </c>
+      <c r="H291" t="s">
+        <v>82</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291">
+        <v>2</v>
+      </c>
+      <c r="L291">
+        <v>0</v>
+      </c>
+      <c r="M291">
+        <v>4</v>
+      </c>
+      <c r="N291">
+        <v>4</v>
+      </c>
+      <c r="O291" t="s">
+        <v>104</v>
+      </c>
+      <c r="P291" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q291">
+        <v>2.4</v>
+      </c>
+      <c r="R291">
+        <v>2.05</v>
+      </c>
+      <c r="S291">
+        <v>6</v>
+      </c>
+      <c r="T291">
+        <v>1.5</v>
+      </c>
+      <c r="U291">
+        <v>2.5</v>
+      </c>
+      <c r="V291">
+        <v>3.5</v>
+      </c>
+      <c r="W291">
+        <v>1.29</v>
+      </c>
+      <c r="X291">
+        <v>11</v>
+      </c>
+      <c r="Y291">
+        <v>1.05</v>
+      </c>
+      <c r="Z291">
+        <v>1.7</v>
+      </c>
+      <c r="AA291">
+        <v>3.7</v>
+      </c>
+      <c r="AB291">
+        <v>5</v>
+      </c>
+      <c r="AC291">
+        <v>1.08</v>
+      </c>
+      <c r="AD291">
+        <v>7.5</v>
+      </c>
+      <c r="AE291">
+        <v>1.42</v>
+      </c>
+      <c r="AF291">
+        <v>2.8</v>
+      </c>
+      <c r="AG291">
+        <v>2.3</v>
+      </c>
+      <c r="AH291">
+        <v>1.62</v>
+      </c>
+      <c r="AI291">
+        <v>2.2</v>
+      </c>
+      <c r="AJ291">
+        <v>1.62</v>
+      </c>
+      <c r="AK291">
+        <v>1.15</v>
+      </c>
+      <c r="AL291">
+        <v>1.29</v>
+      </c>
+      <c r="AM291">
+        <v>2.1</v>
+      </c>
+      <c r="AN291">
+        <v>1.43</v>
+      </c>
+      <c r="AO291">
+        <v>0.38</v>
+      </c>
+      <c r="AP291">
+        <v>1.33</v>
+      </c>
+      <c r="AQ291">
+        <v>0.57</v>
+      </c>
+      <c r="AR291">
+        <v>1.69</v>
+      </c>
+      <c r="AS291">
+        <v>0.8</v>
+      </c>
+      <c r="AT291">
+        <v>2.49</v>
+      </c>
+      <c r="AU291">
+        <v>6</v>
+      </c>
+      <c r="AV291">
+        <v>8</v>
+      </c>
+      <c r="AW291">
+        <v>11</v>
+      </c>
+      <c r="AX291">
+        <v>8</v>
+      </c>
+      <c r="AY291">
+        <v>20</v>
+      </c>
+      <c r="AZ291">
+        <v>17</v>
+      </c>
+      <c r="BA291">
+        <v>8</v>
+      </c>
+      <c r="BB291">
+        <v>4</v>
+      </c>
+      <c r="BC291">
+        <v>12</v>
+      </c>
+      <c r="BD291">
+        <v>1.35</v>
+      </c>
+      <c r="BE291">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF291">
+        <v>4.1</v>
+      </c>
+      <c r="BG291">
+        <v>1.28</v>
+      </c>
+      <c r="BH291">
+        <v>3.08</v>
+      </c>
+      <c r="BI291">
+        <v>1.54</v>
+      </c>
+      <c r="BJ291">
+        <v>2.25</v>
+      </c>
+      <c r="BK291">
+        <v>1.95</v>
+      </c>
+      <c r="BL291">
+        <v>1.76</v>
+      </c>
+      <c r="BM291">
+        <v>2.54</v>
+      </c>
+      <c r="BN291">
+        <v>1.43</v>
+      </c>
+      <c r="BO291">
+        <v>3.42</v>
+      </c>
+      <c r="BP291">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7465281</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45752.375</v>
+      </c>
+      <c r="F292">
+        <v>30</v>
+      </c>
+      <c r="G292" t="s">
+        <v>89</v>
+      </c>
+      <c r="H292" t="s">
+        <v>86</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>0</v>
+      </c>
+      <c r="M292">
+        <v>1</v>
+      </c>
+      <c r="N292">
+        <v>1</v>
+      </c>
+      <c r="O292" t="s">
+        <v>104</v>
+      </c>
+      <c r="P292" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q292">
+        <v>2.75</v>
+      </c>
+      <c r="R292">
+        <v>2.05</v>
+      </c>
+      <c r="S292">
+        <v>4.33</v>
+      </c>
+      <c r="T292">
+        <v>1.44</v>
+      </c>
+      <c r="U292">
+        <v>2.63</v>
+      </c>
+      <c r="V292">
+        <v>3.4</v>
+      </c>
+      <c r="W292">
+        <v>1.3</v>
+      </c>
+      <c r="X292">
+        <v>10</v>
+      </c>
+      <c r="Y292">
+        <v>1.06</v>
+      </c>
+      <c r="Z292">
+        <v>2.05</v>
+      </c>
+      <c r="AA292">
+        <v>3.33</v>
+      </c>
+      <c r="AB292">
+        <v>3.87</v>
+      </c>
+      <c r="AC292">
+        <v>1.07</v>
+      </c>
+      <c r="AD292">
+        <v>8</v>
+      </c>
+      <c r="AE292">
+        <v>1.38</v>
+      </c>
+      <c r="AF292">
+        <v>3</v>
+      </c>
+      <c r="AG292">
+        <v>2.2</v>
+      </c>
+      <c r="AH292">
+        <v>1.67</v>
+      </c>
+      <c r="AI292">
+        <v>1.95</v>
+      </c>
+      <c r="AJ292">
+        <v>1.8</v>
+      </c>
+      <c r="AK292">
+        <v>1.28</v>
+      </c>
+      <c r="AL292">
+        <v>1.33</v>
+      </c>
+      <c r="AM292">
+        <v>1.68</v>
+      </c>
+      <c r="AN292">
+        <v>1.5</v>
+      </c>
+      <c r="AO292">
+        <v>0.73</v>
+      </c>
+      <c r="AP292">
+        <v>1.4</v>
+      </c>
+      <c r="AQ292">
+        <v>0.88</v>
+      </c>
+      <c r="AR292">
+        <v>1.44</v>
+      </c>
+      <c r="AS292">
+        <v>1.24</v>
+      </c>
+      <c r="AT292">
+        <v>2.68</v>
+      </c>
+      <c r="AU292">
+        <v>2</v>
+      </c>
+      <c r="AV292">
+        <v>5</v>
+      </c>
+      <c r="AW292">
+        <v>15</v>
+      </c>
+      <c r="AX292">
+        <v>5</v>
+      </c>
+      <c r="AY292">
+        <v>23</v>
+      </c>
+      <c r="AZ292">
+        <v>10</v>
+      </c>
+      <c r="BA292">
+        <v>5</v>
+      </c>
+      <c r="BB292">
+        <v>3</v>
+      </c>
+      <c r="BC292">
+        <v>8</v>
+      </c>
+      <c r="BD292">
+        <v>1.61</v>
+      </c>
+      <c r="BE292">
+        <v>6.75</v>
+      </c>
+      <c r="BF292">
+        <v>2.9</v>
+      </c>
+      <c r="BG292">
+        <v>1.31</v>
+      </c>
+      <c r="BH292">
+        <v>3.2</v>
+      </c>
+      <c r="BI292">
+        <v>1.58</v>
+      </c>
+      <c r="BJ292">
+        <v>2.2</v>
+      </c>
+      <c r="BK292">
+        <v>2</v>
+      </c>
+      <c r="BL292">
+        <v>1.71</v>
+      </c>
+      <c r="BM292">
+        <v>2.7</v>
+      </c>
+      <c r="BN292">
+        <v>1.4</v>
+      </c>
+      <c r="BO292">
+        <v>3.8</v>
+      </c>
+      <c r="BP292">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7465274</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45752.46875</v>
+      </c>
+      <c r="F293">
+        <v>30</v>
+      </c>
+      <c r="G293" t="s">
+        <v>84</v>
+      </c>
+      <c r="H293" t="s">
+        <v>75</v>
+      </c>
+      <c r="I293">
+        <v>0</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
+      <c r="K293">
+        <v>1</v>
+      </c>
+      <c r="L293">
+        <v>1</v>
+      </c>
+      <c r="M293">
+        <v>2</v>
+      </c>
+      <c r="N293">
+        <v>3</v>
+      </c>
+      <c r="O293" t="s">
+        <v>157</v>
+      </c>
+      <c r="P293" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q293">
+        <v>1.73</v>
+      </c>
+      <c r="R293">
+        <v>2.63</v>
+      </c>
+      <c r="S293">
+        <v>7.5</v>
+      </c>
+      <c r="T293">
+        <v>1.25</v>
+      </c>
+      <c r="U293">
+        <v>3.75</v>
+      </c>
+      <c r="V293">
+        <v>2.2</v>
+      </c>
+      <c r="W293">
+        <v>1.62</v>
+      </c>
+      <c r="X293">
+        <v>5</v>
+      </c>
+      <c r="Y293">
+        <v>1.17</v>
+      </c>
+      <c r="Z293">
+        <v>1.32</v>
+      </c>
+      <c r="AA293">
+        <v>6.09</v>
+      </c>
+      <c r="AB293">
+        <v>10.7</v>
+      </c>
+      <c r="AC293">
+        <v>1.01</v>
+      </c>
+      <c r="AD293">
+        <v>17</v>
+      </c>
+      <c r="AE293">
+        <v>1.15</v>
+      </c>
+      <c r="AF293">
+        <v>5.25</v>
+      </c>
+      <c r="AG293">
+        <v>1.5</v>
+      </c>
+      <c r="AH293">
+        <v>2.63</v>
+      </c>
+      <c r="AI293">
+        <v>1.91</v>
+      </c>
+      <c r="AJ293">
+        <v>1.91</v>
+      </c>
+      <c r="AK293">
+        <v>1.07</v>
+      </c>
+      <c r="AL293">
+        <v>1.14</v>
+      </c>
+      <c r="AM293">
+        <v>3.3</v>
+      </c>
+      <c r="AN293">
+        <v>2.64</v>
+      </c>
+      <c r="AO293">
+        <v>0.5</v>
+      </c>
+      <c r="AP293">
+        <v>2.47</v>
+      </c>
+      <c r="AQ293">
+        <v>0.67</v>
+      </c>
+      <c r="AR293">
+        <v>2.06</v>
+      </c>
+      <c r="AS293">
+        <v>1.03</v>
+      </c>
+      <c r="AT293">
+        <v>3.09</v>
+      </c>
+      <c r="AU293">
+        <v>10</v>
+      </c>
+      <c r="AV293">
+        <v>3</v>
+      </c>
+      <c r="AW293">
+        <v>12</v>
+      </c>
+      <c r="AX293">
+        <v>8</v>
+      </c>
+      <c r="AY293">
+        <v>22</v>
+      </c>
+      <c r="AZ293">
+        <v>12</v>
+      </c>
+      <c r="BA293">
+        <v>9</v>
+      </c>
+      <c r="BB293">
+        <v>4</v>
+      </c>
+      <c r="BC293">
+        <v>13</v>
+      </c>
+      <c r="BD293">
+        <v>1.17</v>
+      </c>
+      <c r="BE293">
+        <v>9.75</v>
+      </c>
+      <c r="BF293">
+        <v>7</v>
+      </c>
+      <c r="BG293">
+        <v>1.21</v>
+      </c>
+      <c r="BH293">
+        <v>4</v>
+      </c>
+      <c r="BI293">
+        <v>1.39</v>
+      </c>
+      <c r="BJ293">
+        <v>2.75</v>
+      </c>
+      <c r="BK293">
+        <v>1.7</v>
+      </c>
+      <c r="BL293">
+        <v>2</v>
+      </c>
+      <c r="BM293">
+        <v>2.15</v>
+      </c>
+      <c r="BN293">
+        <v>1.6</v>
+      </c>
+      <c r="BO293">
+        <v>2.95</v>
+      </c>
+      <c r="BP293">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7465279</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45752.5625</v>
+      </c>
+      <c r="F294">
+        <v>30</v>
+      </c>
+      <c r="G294" t="s">
+        <v>77</v>
+      </c>
+      <c r="H294" t="s">
+        <v>72</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>1</v>
+      </c>
+      <c r="M294">
+        <v>2</v>
+      </c>
+      <c r="N294">
+        <v>3</v>
+      </c>
+      <c r="O294" t="s">
+        <v>277</v>
+      </c>
+      <c r="P294" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q294">
+        <v>3.25</v>
+      </c>
+      <c r="R294">
+        <v>2</v>
+      </c>
+      <c r="S294">
+        <v>3.5</v>
+      </c>
+      <c r="T294">
+        <v>1.5</v>
+      </c>
+      <c r="U294">
+        <v>2.5</v>
+      </c>
+      <c r="V294">
+        <v>3.4</v>
+      </c>
+      <c r="W294">
+        <v>1.3</v>
+      </c>
+      <c r="X294">
+        <v>10</v>
+      </c>
+      <c r="Y294">
+        <v>1.06</v>
+      </c>
+      <c r="Z294">
+        <v>2.63</v>
+      </c>
+      <c r="AA294">
+        <v>3.1</v>
+      </c>
+      <c r="AB294">
+        <v>2.8</v>
+      </c>
+      <c r="AC294">
+        <v>1.09</v>
+      </c>
+      <c r="AD294">
+        <v>7</v>
+      </c>
+      <c r="AE294">
+        <v>1.44</v>
+      </c>
+      <c r="AF294">
+        <v>2.75</v>
+      </c>
+      <c r="AG294">
+        <v>2.3</v>
+      </c>
+      <c r="AH294">
+        <v>1.62</v>
+      </c>
+      <c r="AI294">
+        <v>1.91</v>
+      </c>
+      <c r="AJ294">
+        <v>1.91</v>
+      </c>
+      <c r="AK294">
+        <v>1.42</v>
+      </c>
+      <c r="AL294">
+        <v>1.36</v>
+      </c>
+      <c r="AM294">
+        <v>1.46</v>
+      </c>
+      <c r="AN294">
+        <v>1.53</v>
+      </c>
+      <c r="AO294">
+        <v>0.71</v>
+      </c>
+      <c r="AP294">
+        <v>1.44</v>
+      </c>
+      <c r="AQ294">
+        <v>0.87</v>
+      </c>
+      <c r="AR294">
+        <v>1.34</v>
+      </c>
+      <c r="AS294">
+        <v>1.28</v>
+      </c>
+      <c r="AT294">
+        <v>2.62</v>
+      </c>
+      <c r="AU294">
+        <v>3</v>
+      </c>
+      <c r="AV294">
+        <v>5</v>
+      </c>
+      <c r="AW294">
+        <v>5</v>
+      </c>
+      <c r="AX294">
+        <v>6</v>
+      </c>
+      <c r="AY294">
+        <v>8</v>
+      </c>
+      <c r="AZ294">
+        <v>13</v>
+      </c>
+      <c r="BA294">
+        <v>4</v>
+      </c>
+      <c r="BB294">
+        <v>2</v>
+      </c>
+      <c r="BC294">
+        <v>6</v>
+      </c>
+      <c r="BD294">
+        <v>1.87</v>
+      </c>
+      <c r="BE294">
+        <v>6.25</v>
+      </c>
+      <c r="BF294">
+        <v>2.37</v>
+      </c>
+      <c r="BG294">
+        <v>1.39</v>
+      </c>
+      <c r="BH294">
+        <v>2.75</v>
+      </c>
+      <c r="BI294">
+        <v>1.7</v>
+      </c>
+      <c r="BJ294">
+        <v>2</v>
+      </c>
+      <c r="BK294">
+        <v>2.25</v>
+      </c>
+      <c r="BL294">
+        <v>1.57</v>
+      </c>
+      <c r="BM294">
+        <v>3.1</v>
+      </c>
+      <c r="BN294">
+        <v>1.32</v>
+      </c>
+      <c r="BO294">
+        <v>4.5</v>
+      </c>
+      <c r="BP294">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7465273</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45752.66666666666</v>
+      </c>
+      <c r="F295">
+        <v>30</v>
+      </c>
+      <c r="G295" t="s">
+        <v>81</v>
+      </c>
+      <c r="H295" t="s">
+        <v>71</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295">
+        <v>1</v>
+      </c>
+      <c r="K295">
+        <v>2</v>
+      </c>
+      <c r="L295">
+        <v>1</v>
+      </c>
+      <c r="M295">
+        <v>1</v>
+      </c>
+      <c r="N295">
+        <v>2</v>
+      </c>
+      <c r="O295" t="s">
+        <v>138</v>
+      </c>
+      <c r="P295" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q295">
+        <v>1.8</v>
+      </c>
+      <c r="R295">
+        <v>2.75</v>
+      </c>
+      <c r="S295">
+        <v>6</v>
+      </c>
+      <c r="T295">
+        <v>1.2</v>
+      </c>
+      <c r="U295">
+        <v>4.33</v>
+      </c>
+      <c r="V295">
+        <v>2</v>
+      </c>
+      <c r="W295">
+        <v>1.73</v>
+      </c>
+      <c r="X295">
+        <v>4.33</v>
+      </c>
+      <c r="Y295">
+        <v>1.2</v>
+      </c>
+      <c r="Z295">
+        <v>1.41</v>
+      </c>
+      <c r="AA295">
+        <v>5.61</v>
+      </c>
+      <c r="AB295">
+        <v>7.8</v>
+      </c>
+      <c r="AC295">
+        <v>1.01</v>
+      </c>
+      <c r="AD295">
+        <v>23</v>
+      </c>
+      <c r="AE295">
+        <v>1.1</v>
+      </c>
+      <c r="AF295">
+        <v>6.5</v>
+      </c>
+      <c r="AG295">
+        <v>1.36</v>
+      </c>
+      <c r="AH295">
+        <v>3.2</v>
+      </c>
+      <c r="AI295">
+        <v>1.57</v>
+      </c>
+      <c r="AJ295">
+        <v>2.25</v>
+      </c>
+      <c r="AK295">
+        <v>1.1</v>
+      </c>
+      <c r="AL295">
+        <v>1.14</v>
+      </c>
+      <c r="AM295">
+        <v>3</v>
+      </c>
+      <c r="AN295">
+        <v>2.36</v>
+      </c>
+      <c r="AO295">
+        <v>1.29</v>
+      </c>
+      <c r="AP295">
+        <v>2.27</v>
+      </c>
+      <c r="AQ295">
+        <v>1.27</v>
+      </c>
+      <c r="AR295">
+        <v>2.15</v>
+      </c>
+      <c r="AS295">
+        <v>1.35</v>
+      </c>
+      <c r="AT295">
+        <v>3.5</v>
+      </c>
+      <c r="AU295">
+        <v>6</v>
+      </c>
+      <c r="AV295">
+        <v>3</v>
+      </c>
+      <c r="AW295">
+        <v>8</v>
+      </c>
+      <c r="AX295">
+        <v>4</v>
+      </c>
+      <c r="AY295">
+        <v>19</v>
+      </c>
+      <c r="AZ295">
+        <v>8</v>
+      </c>
+      <c r="BA295">
+        <v>9</v>
+      </c>
+      <c r="BB295">
+        <v>3</v>
+      </c>
+      <c r="BC295">
+        <v>12</v>
+      </c>
+      <c r="BD295">
+        <v>1.31</v>
+      </c>
+      <c r="BE295">
+        <v>8</v>
+      </c>
+      <c r="BF295">
+        <v>4.5</v>
+      </c>
+      <c r="BG295">
+        <v>1.21</v>
+      </c>
+      <c r="BH295">
+        <v>4</v>
+      </c>
+      <c r="BI295">
+        <v>1.4</v>
+      </c>
+      <c r="BJ295">
+        <v>2.7</v>
+      </c>
+      <c r="BK295">
+        <v>1.72</v>
+      </c>
+      <c r="BL295">
+        <v>1.98</v>
+      </c>
+      <c r="BM295">
+        <v>2.2</v>
+      </c>
+      <c r="BN295">
+        <v>1.58</v>
+      </c>
+      <c r="BO295">
+        <v>3</v>
+      </c>
+      <c r="BP295">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Spain La Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1173,6 +1173,15 @@
   <si>
     <t>['53', '72']</t>
   </si>
+  <si>
+    <t>['5', '56', '68']</t>
+  </si>
+  <si>
+    <t>['25', '90+3']</t>
+  </si>
+  <si>
+    <t>['1', '19', '38', '80']</t>
+  </si>
 </sst>
 </file>
 
@@ -1533,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP295"/>
+  <dimension ref="A1:BP300"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1870,7 +1879,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2485,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ5">
         <v>1.13</v>
@@ -3515,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ10">
         <v>0.57</v>
@@ -3721,10 +3730,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4133,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13">
         <v>1.8</v>
@@ -4548,7 +4557,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ15">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4754,7 +4763,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ16">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5369,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
         <v>0.8</v>
@@ -5987,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>0.87</v>
@@ -6811,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ26">
         <v>0.67</v>
@@ -7432,7 +7441,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ29">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7635,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ30">
         <v>1.73</v>
@@ -8050,7 +8059,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -8665,7 +8674,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ35">
         <v>1.21</v>
@@ -9283,7 +9292,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ38">
         <v>0.87</v>
@@ -9492,7 +9501,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ39">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR39">
         <v>1.12</v>
@@ -10519,10 +10528,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -11343,10 +11352,10 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ48">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11758,7 +11767,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ50">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR50">
         <v>1.14</v>
@@ -11964,7 +11973,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ51">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.4</v>
@@ -12170,7 +12179,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ52">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR52">
         <v>1.61</v>
@@ -12373,10 +12382,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ53">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR53">
         <v>1.17</v>
@@ -12785,10 +12794,10 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ55">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR55">
         <v>1.18</v>
@@ -14021,7 +14030,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
         <v>2.2</v>
@@ -14230,7 +14239,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ62">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR62">
         <v>1.49</v>
@@ -14642,7 +14651,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ64">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR64">
         <v>1.24</v>
@@ -14845,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ65">
         <v>0.2</v>
@@ -15466,7 +15475,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ68">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR68">
         <v>1.97</v>
@@ -15875,7 +15884,7 @@
         <v>0.5</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ70">
         <v>1.27</v>
@@ -16084,7 +16093,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR71">
         <v>1.29</v>
@@ -16287,7 +16296,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ72">
         <v>1.21</v>
@@ -18141,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>0.8</v>
@@ -18347,7 +18356,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ82">
         <v>0.67</v>
@@ -18762,7 +18771,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ84">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR84">
         <v>1.3</v>
@@ -18965,7 +18974,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ85">
         <v>0.87</v>
@@ -19171,7 +19180,7 @@
         <v>1.25</v>
       </c>
       <c r="AP86">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ86">
         <v>1.33</v>
@@ -19586,7 +19595,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ88">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19995,7 +20004,7 @@
         <v>0.67</v>
       </c>
       <c r="AP90">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ90">
         <v>1.27</v>
@@ -20204,7 +20213,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ91">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR91">
         <v>1.21</v>
@@ -21028,7 +21037,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ95">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR95">
         <v>1.38</v>
@@ -21849,10 +21858,10 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR99">
         <v>1.66</v>
@@ -22673,7 +22682,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ103">
         <v>1.8</v>
@@ -23085,7 +23094,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ105">
         <v>0.87</v>
@@ -23497,7 +23506,7 @@
         <v>0.75</v>
       </c>
       <c r="AP107">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ107">
         <v>0.87</v>
@@ -23912,7 +23921,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ109">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR109">
         <v>1.79</v>
@@ -24118,7 +24127,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ110">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR110">
         <v>1.42</v>
@@ -24324,7 +24333,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ111">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR111">
         <v>1.44</v>
@@ -25557,10 +25566,10 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ117">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR117">
         <v>1.53</v>
@@ -25972,7 +25981,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -26384,7 +26393,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ121">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR121">
         <v>1.83</v>
@@ -26587,7 +26596,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122">
         <v>0.88</v>
@@ -26793,7 +26802,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ123">
         <v>1.13</v>
@@ -27208,7 +27217,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ125">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR125">
         <v>1.29</v>
@@ -27617,10 +27626,10 @@
         <v>1.4</v>
       </c>
       <c r="AP127">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ127">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -28647,7 +28656,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ132">
         <v>1.21</v>
@@ -29471,7 +29480,7 @@
         <v>1.33</v>
       </c>
       <c r="AP136">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ136">
         <v>1.33</v>
@@ -29677,7 +29686,7 @@
         <v>1.8</v>
       </c>
       <c r="AP137">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ137">
         <v>1.73</v>
@@ -29886,7 +29895,7 @@
         <v>2</v>
       </c>
       <c r="AQ138">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR138">
         <v>1.36</v>
@@ -30913,10 +30922,10 @@
         <v>1.71</v>
       </c>
       <c r="AP143">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ143">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR143">
         <v>1.13</v>
@@ -31119,7 +31128,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ144">
         <v>0.87</v>
@@ -31328,7 +31337,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ145">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR145">
         <v>1.86</v>
@@ -31534,7 +31543,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ146">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR146">
         <v>1.72</v>
@@ -31943,10 +31952,10 @@
         <v>0.83</v>
       </c>
       <c r="AP148">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ148">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR148">
         <v>1.35</v>
@@ -32767,7 +32776,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ152">
         <v>0.2</v>
@@ -33591,10 +33600,10 @@
         <v>1.57</v>
       </c>
       <c r="AP156">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ156">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR156">
         <v>0.98</v>
@@ -34621,7 +34630,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ161">
         <v>0.67</v>
@@ -34830,7 +34839,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ162">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR162">
         <v>1.12</v>
@@ -35239,7 +35248,7 @@
         <v>0.57</v>
       </c>
       <c r="AP164">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ164">
         <v>0.87</v>
@@ -35654,7 +35663,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ166">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR166">
         <v>1.77</v>
@@ -35860,7 +35869,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ167">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR167">
         <v>1.17</v>
@@ -36269,7 +36278,7 @@
         <v>0.75</v>
       </c>
       <c r="AP169">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ169">
         <v>1.27</v>
@@ -36887,7 +36896,7 @@
         <v>1.38</v>
       </c>
       <c r="AP172">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172">
         <v>1.33</v>
@@ -37508,7 +37517,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR175">
         <v>1.41</v>
@@ -37714,7 +37723,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ176">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR176">
         <v>1.53</v>
@@ -37920,7 +37929,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ177">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR177">
         <v>2</v>
@@ -38535,7 +38544,7 @@
         <v>1.75</v>
       </c>
       <c r="AP180">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ180">
         <v>1.8</v>
@@ -38741,7 +38750,7 @@
         <v>0.13</v>
       </c>
       <c r="AP181">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ181">
         <v>0.57</v>
@@ -39771,7 +39780,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ186">
         <v>1.27</v>
@@ -40183,7 +40192,7 @@
         <v>0.33</v>
       </c>
       <c r="AP188">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ188">
         <v>0.67</v>
@@ -40389,10 +40398,10 @@
         <v>0.25</v>
       </c>
       <c r="AP189">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ189">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -40598,7 +40607,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ190">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -41419,10 +41428,10 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ194">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR194">
         <v>0.96</v>
@@ -42040,7 +42049,7 @@
         <v>2</v>
       </c>
       <c r="AQ197">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR197">
         <v>1.41</v>
@@ -42658,7 +42667,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ200">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR200">
         <v>1.33</v>
@@ -42861,7 +42870,7 @@
         <v>1.67</v>
       </c>
       <c r="AP201">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ201">
         <v>1.21</v>
@@ -43067,10 +43076,10 @@
         <v>0.78</v>
       </c>
       <c r="AP202">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ202">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR202">
         <v>1.36</v>
@@ -43685,7 +43694,7 @@
         <v>0.11</v>
       </c>
       <c r="AP205">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ205">
         <v>0.57</v>
@@ -43891,7 +43900,7 @@
         <v>1.9</v>
       </c>
       <c r="AP206">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ206">
         <v>1.73</v>
@@ -44306,7 +44315,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ208">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR208">
         <v>1.41</v>
@@ -45127,7 +45136,7 @@
         <v>1.27</v>
       </c>
       <c r="AP212">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ212">
         <v>1.33</v>
@@ -45539,7 +45548,7 @@
         <v>0.3</v>
       </c>
       <c r="AP214">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ214">
         <v>0.2</v>
@@ -46572,7 +46581,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ219">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR219">
         <v>1.48</v>
@@ -46778,7 +46787,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ220">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR220">
         <v>1.72</v>
@@ -47805,7 +47814,7 @@
         <v>1.64</v>
       </c>
       <c r="AP225">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ225">
         <v>1.8</v>
@@ -48014,7 +48023,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ226">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR226">
         <v>1.93</v>
@@ -48220,7 +48229,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ227">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR227">
         <v>1.1</v>
@@ -48835,7 +48844,7 @@
         <v>2</v>
       </c>
       <c r="AP230">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ230">
         <v>2.2</v>
@@ -49044,7 +49053,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ231">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR231">
         <v>1.25</v>
@@ -49250,7 +49259,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ232">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR232">
         <v>1.36</v>
@@ -49453,7 +49462,7 @@
         <v>0.67</v>
       </c>
       <c r="AP233">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ233">
         <v>0.88</v>
@@ -50071,7 +50080,7 @@
         <v>0.36</v>
       </c>
       <c r="AP236">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ236">
         <v>0.67</v>
@@ -50280,7 +50289,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ237">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR237">
         <v>1.14</v>
@@ -50483,7 +50492,7 @@
         <v>0.91</v>
       </c>
       <c r="AP238">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ238">
         <v>1.13</v>
@@ -50898,7 +50907,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ240">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR240">
         <v>1.7</v>
@@ -51310,7 +51319,7 @@
         <v>2</v>
       </c>
       <c r="AQ242">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR242">
         <v>1.38</v>
@@ -51928,7 +51937,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ245">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR245">
         <v>1.34</v>
@@ -52131,7 +52140,7 @@
         <v>2.08</v>
       </c>
       <c r="AP246">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ246">
         <v>2.2</v>
@@ -53161,7 +53170,7 @@
         <v>1.36</v>
       </c>
       <c r="AP251">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ251">
         <v>1.21</v>
@@ -53367,7 +53376,7 @@
         <v>0.83</v>
       </c>
       <c r="AP252">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ252">
         <v>0.8</v>
@@ -54194,7 +54203,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ256">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR256">
         <v>1.71</v>
@@ -54397,10 +54406,10 @@
         <v>1.17</v>
       </c>
       <c r="AP257">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ257">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR257">
         <v>0.96</v>
@@ -54606,7 +54615,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ258">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR258">
         <v>2</v>
@@ -55842,7 +55851,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ264">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR264">
         <v>1.32</v>
@@ -57075,7 +57084,7 @@
         <v>0.71</v>
       </c>
       <c r="AP270">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ270">
         <v>0.88</v>
@@ -57281,7 +57290,7 @@
         <v>0.54</v>
       </c>
       <c r="AP271">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ271">
         <v>0.87</v>
@@ -57693,7 +57702,7 @@
         <v>1.64</v>
       </c>
       <c r="AP273">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ273">
         <v>1.73</v>
@@ -58105,7 +58114,7 @@
         <v>1.15</v>
       </c>
       <c r="AP275">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ275">
         <v>1.27</v>
@@ -58311,10 +58320,10 @@
         <v>1.54</v>
       </c>
       <c r="AP276">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ276">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR276">
         <v>1.47</v>
@@ -58520,7 +58529,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ277">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR277">
         <v>1.48</v>
@@ -58726,7 +58735,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ278">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR278">
         <v>1.72</v>
@@ -59138,7 +59147,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ280">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR280">
         <v>2.14</v>
@@ -59550,7 +59559,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ282">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR282">
         <v>1.15</v>
@@ -60786,7 +60795,7 @@
         <v>2</v>
       </c>
       <c r="AQ288">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR288">
         <v>1.65</v>
@@ -62304,6 +62313,1036 @@
       </c>
       <c r="BP295">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7465275</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45753.375</v>
+      </c>
+      <c r="F296">
+        <v>30</v>
+      </c>
+      <c r="G296" t="s">
+        <v>73</v>
+      </c>
+      <c r="H296" t="s">
+        <v>76</v>
+      </c>
+      <c r="I296">
+        <v>0</v>
+      </c>
+      <c r="J296">
+        <v>1</v>
+      </c>
+      <c r="K296">
+        <v>1</v>
+      </c>
+      <c r="L296">
+        <v>1</v>
+      </c>
+      <c r="M296">
+        <v>3</v>
+      </c>
+      <c r="N296">
+        <v>4</v>
+      </c>
+      <c r="O296" t="s">
+        <v>166</v>
+      </c>
+      <c r="P296" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q296">
+        <v>4</v>
+      </c>
+      <c r="R296">
+        <v>1.95</v>
+      </c>
+      <c r="S296">
+        <v>3.1</v>
+      </c>
+      <c r="T296">
+        <v>1.53</v>
+      </c>
+      <c r="U296">
+        <v>2.38</v>
+      </c>
+      <c r="V296">
+        <v>3.5</v>
+      </c>
+      <c r="W296">
+        <v>1.29</v>
+      </c>
+      <c r="X296">
+        <v>11</v>
+      </c>
+      <c r="Y296">
+        <v>1.05</v>
+      </c>
+      <c r="Z296">
+        <v>3.2</v>
+      </c>
+      <c r="AA296">
+        <v>3.1</v>
+      </c>
+      <c r="AB296">
+        <v>2.3</v>
+      </c>
+      <c r="AC296">
+        <v>1.09</v>
+      </c>
+      <c r="AD296">
+        <v>7</v>
+      </c>
+      <c r="AE296">
+        <v>1.45</v>
+      </c>
+      <c r="AF296">
+        <v>2.7</v>
+      </c>
+      <c r="AG296">
+        <v>2.38</v>
+      </c>
+      <c r="AH296">
+        <v>1.57</v>
+      </c>
+      <c r="AI296">
+        <v>2</v>
+      </c>
+      <c r="AJ296">
+        <v>1.75</v>
+      </c>
+      <c r="AK296">
+        <v>1.58</v>
+      </c>
+      <c r="AL296">
+        <v>1.35</v>
+      </c>
+      <c r="AM296">
+        <v>1.33</v>
+      </c>
+      <c r="AN296">
+        <v>1</v>
+      </c>
+      <c r="AO296">
+        <v>1.07</v>
+      </c>
+      <c r="AP296">
+        <v>0.93</v>
+      </c>
+      <c r="AQ296">
+        <v>1.2</v>
+      </c>
+      <c r="AR296">
+        <v>1.42</v>
+      </c>
+      <c r="AS296">
+        <v>1.01</v>
+      </c>
+      <c r="AT296">
+        <v>2.43</v>
+      </c>
+      <c r="AU296">
+        <v>6</v>
+      </c>
+      <c r="AV296">
+        <v>9</v>
+      </c>
+      <c r="AW296">
+        <v>8</v>
+      </c>
+      <c r="AX296">
+        <v>5</v>
+      </c>
+      <c r="AY296">
+        <v>17</v>
+      </c>
+      <c r="AZ296">
+        <v>15</v>
+      </c>
+      <c r="BA296">
+        <v>5</v>
+      </c>
+      <c r="BB296">
+        <v>4</v>
+      </c>
+      <c r="BC296">
+        <v>9</v>
+      </c>
+      <c r="BD296">
+        <v>2.06</v>
+      </c>
+      <c r="BE296">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF296">
+        <v>2.08</v>
+      </c>
+      <c r="BG296">
+        <v>1.3</v>
+      </c>
+      <c r="BH296">
+        <v>2.97</v>
+      </c>
+      <c r="BI296">
+        <v>1.58</v>
+      </c>
+      <c r="BJ296">
+        <v>2.17</v>
+      </c>
+      <c r="BK296">
+        <v>2.02</v>
+      </c>
+      <c r="BL296">
+        <v>1.71</v>
+      </c>
+      <c r="BM296">
+        <v>2.64</v>
+      </c>
+      <c r="BN296">
+        <v>1.4</v>
+      </c>
+      <c r="BO296">
+        <v>3.58</v>
+      </c>
+      <c r="BP296">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7465278</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45753.46875</v>
+      </c>
+      <c r="F297">
+        <v>30</v>
+      </c>
+      <c r="G297" t="s">
+        <v>80</v>
+      </c>
+      <c r="H297" t="s">
+        <v>87</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297">
+        <v>1</v>
+      </c>
+      <c r="K297">
+        <v>2</v>
+      </c>
+      <c r="L297">
+        <v>1</v>
+      </c>
+      <c r="M297">
+        <v>2</v>
+      </c>
+      <c r="N297">
+        <v>3</v>
+      </c>
+      <c r="O297" t="s">
+        <v>138</v>
+      </c>
+      <c r="P297" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q297">
+        <v>4</v>
+      </c>
+      <c r="R297">
+        <v>2</v>
+      </c>
+      <c r="S297">
+        <v>3</v>
+      </c>
+      <c r="T297">
+        <v>1.5</v>
+      </c>
+      <c r="U297">
+        <v>2.5</v>
+      </c>
+      <c r="V297">
+        <v>3.4</v>
+      </c>
+      <c r="W297">
+        <v>1.3</v>
+      </c>
+      <c r="X297">
+        <v>10</v>
+      </c>
+      <c r="Y297">
+        <v>1.06</v>
+      </c>
+      <c r="Z297">
+        <v>3.4</v>
+      </c>
+      <c r="AA297">
+        <v>3.2</v>
+      </c>
+      <c r="AB297">
+        <v>2.2</v>
+      </c>
+      <c r="AC297">
+        <v>1.04</v>
+      </c>
+      <c r="AD297">
+        <v>7.3</v>
+      </c>
+      <c r="AE297">
+        <v>1.39</v>
+      </c>
+      <c r="AF297">
+        <v>2.82</v>
+      </c>
+      <c r="AG297">
+        <v>2.2</v>
+      </c>
+      <c r="AH297">
+        <v>1.67</v>
+      </c>
+      <c r="AI297">
+        <v>1.95</v>
+      </c>
+      <c r="AJ297">
+        <v>1.8</v>
+      </c>
+      <c r="AK297">
+        <v>1.61</v>
+      </c>
+      <c r="AL297">
+        <v>1.33</v>
+      </c>
+      <c r="AM297">
+        <v>1.33</v>
+      </c>
+      <c r="AN297">
+        <v>1.36</v>
+      </c>
+      <c r="AO297">
+        <v>1.64</v>
+      </c>
+      <c r="AP297">
+        <v>1.27</v>
+      </c>
+      <c r="AQ297">
+        <v>1.73</v>
+      </c>
+      <c r="AR297">
+        <v>1.47</v>
+      </c>
+      <c r="AS297">
+        <v>1.17</v>
+      </c>
+      <c r="AT297">
+        <v>2.64</v>
+      </c>
+      <c r="AU297">
+        <v>7</v>
+      </c>
+      <c r="AV297">
+        <v>6</v>
+      </c>
+      <c r="AW297">
+        <v>5</v>
+      </c>
+      <c r="AX297">
+        <v>8</v>
+      </c>
+      <c r="AY297">
+        <v>12</v>
+      </c>
+      <c r="AZ297">
+        <v>19</v>
+      </c>
+      <c r="BA297">
+        <v>7</v>
+      </c>
+      <c r="BB297">
+        <v>7</v>
+      </c>
+      <c r="BC297">
+        <v>14</v>
+      </c>
+      <c r="BD297">
+        <v>2.15</v>
+      </c>
+      <c r="BE297">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF297">
+        <v>1.99</v>
+      </c>
+      <c r="BG297">
+        <v>1.28</v>
+      </c>
+      <c r="BH297">
+        <v>3.08</v>
+      </c>
+      <c r="BI297">
+        <v>1.53</v>
+      </c>
+      <c r="BJ297">
+        <v>2.27</v>
+      </c>
+      <c r="BK297">
+        <v>1.94</v>
+      </c>
+      <c r="BL297">
+        <v>1.77</v>
+      </c>
+      <c r="BM297">
+        <v>2.51</v>
+      </c>
+      <c r="BN297">
+        <v>1.44</v>
+      </c>
+      <c r="BO297">
+        <v>3.42</v>
+      </c>
+      <c r="BP297">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7465280</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45753.5625</v>
+      </c>
+      <c r="F298">
+        <v>30</v>
+      </c>
+      <c r="G298" t="s">
+        <v>78</v>
+      </c>
+      <c r="H298" t="s">
+        <v>83</v>
+      </c>
+      <c r="I298">
+        <v>0</v>
+      </c>
+      <c r="J298">
+        <v>3</v>
+      </c>
+      <c r="K298">
+        <v>3</v>
+      </c>
+      <c r="L298">
+        <v>0</v>
+      </c>
+      <c r="M298">
+        <v>4</v>
+      </c>
+      <c r="N298">
+        <v>4</v>
+      </c>
+      <c r="O298" t="s">
+        <v>104</v>
+      </c>
+      <c r="P298" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q298">
+        <v>5.5</v>
+      </c>
+      <c r="R298">
+        <v>1.91</v>
+      </c>
+      <c r="S298">
+        <v>2.75</v>
+      </c>
+      <c r="T298">
+        <v>1.62</v>
+      </c>
+      <c r="U298">
+        <v>2.2</v>
+      </c>
+      <c r="V298">
+        <v>4</v>
+      </c>
+      <c r="W298">
+        <v>1.22</v>
+      </c>
+      <c r="X298">
+        <v>13</v>
+      </c>
+      <c r="Y298">
+        <v>1.04</v>
+      </c>
+      <c r="Z298">
+        <v>4.75</v>
+      </c>
+      <c r="AA298">
+        <v>3.1</v>
+      </c>
+      <c r="AB298">
+        <v>1.9</v>
+      </c>
+      <c r="AC298">
+        <v>1.11</v>
+      </c>
+      <c r="AD298">
+        <v>6.25</v>
+      </c>
+      <c r="AE298">
+        <v>1.55</v>
+      </c>
+      <c r="AF298">
+        <v>2.3</v>
+      </c>
+      <c r="AG298">
+        <v>2.75</v>
+      </c>
+      <c r="AH298">
+        <v>1.44</v>
+      </c>
+      <c r="AI298">
+        <v>2.38</v>
+      </c>
+      <c r="AJ298">
+        <v>1.53</v>
+      </c>
+      <c r="AK298">
+        <v>1.85</v>
+      </c>
+      <c r="AL298">
+        <v>1.34</v>
+      </c>
+      <c r="AM298">
+        <v>1.2</v>
+      </c>
+      <c r="AN298">
+        <v>0.93</v>
+      </c>
+      <c r="AO298">
+        <v>1.21</v>
+      </c>
+      <c r="AP298">
+        <v>0.87</v>
+      </c>
+      <c r="AQ298">
+        <v>1.33</v>
+      </c>
+      <c r="AR298">
+        <v>1.09</v>
+      </c>
+      <c r="AS298">
+        <v>1.09</v>
+      </c>
+      <c r="AT298">
+        <v>2.18</v>
+      </c>
+      <c r="AU298">
+        <v>0</v>
+      </c>
+      <c r="AV298">
+        <v>10</v>
+      </c>
+      <c r="AW298">
+        <v>6</v>
+      </c>
+      <c r="AX298">
+        <v>7</v>
+      </c>
+      <c r="AY298">
+        <v>7</v>
+      </c>
+      <c r="AZ298">
+        <v>20</v>
+      </c>
+      <c r="BA298">
+        <v>3</v>
+      </c>
+      <c r="BB298">
+        <v>4</v>
+      </c>
+      <c r="BC298">
+        <v>7</v>
+      </c>
+      <c r="BD298">
+        <v>2.69</v>
+      </c>
+      <c r="BE298">
+        <v>8.1</v>
+      </c>
+      <c r="BF298">
+        <v>1.69</v>
+      </c>
+      <c r="BG298">
+        <v>1.49</v>
+      </c>
+      <c r="BH298">
+        <v>2.38</v>
+      </c>
+      <c r="BI298">
+        <v>1.89</v>
+      </c>
+      <c r="BJ298">
+        <v>1.81</v>
+      </c>
+      <c r="BK298">
+        <v>2.48</v>
+      </c>
+      <c r="BL298">
+        <v>1.45</v>
+      </c>
+      <c r="BM298">
+        <v>3.42</v>
+      </c>
+      <c r="BN298">
+        <v>1.23</v>
+      </c>
+      <c r="BO298">
+        <v>4.95</v>
+      </c>
+      <c r="BP298">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7465277</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45753.66666666666</v>
+      </c>
+      <c r="F299">
+        <v>30</v>
+      </c>
+      <c r="G299" t="s">
+        <v>79</v>
+      </c>
+      <c r="H299" t="s">
+        <v>70</v>
+      </c>
+      <c r="I299">
+        <v>0</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>0</v>
+      </c>
+      <c r="L299">
+        <v>0</v>
+      </c>
+      <c r="M299">
+        <v>0</v>
+      </c>
+      <c r="N299">
+        <v>0</v>
+      </c>
+      <c r="O299" t="s">
+        <v>104</v>
+      </c>
+      <c r="P299" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q299">
+        <v>2.88</v>
+      </c>
+      <c r="R299">
+        <v>2.2</v>
+      </c>
+      <c r="S299">
+        <v>3.75</v>
+      </c>
+      <c r="T299">
+        <v>1.4</v>
+      </c>
+      <c r="U299">
+        <v>2.75</v>
+      </c>
+      <c r="V299">
+        <v>2.75</v>
+      </c>
+      <c r="W299">
+        <v>1.4</v>
+      </c>
+      <c r="X299">
+        <v>8</v>
+      </c>
+      <c r="Y299">
+        <v>1.08</v>
+      </c>
+      <c r="Z299">
+        <v>2.31</v>
+      </c>
+      <c r="AA299">
+        <v>3.54</v>
+      </c>
+      <c r="AB299">
+        <v>3.34</v>
+      </c>
+      <c r="AC299">
+        <v>1.06</v>
+      </c>
+      <c r="AD299">
+        <v>8.5</v>
+      </c>
+      <c r="AE299">
+        <v>1.3</v>
+      </c>
+      <c r="AF299">
+        <v>3.45</v>
+      </c>
+      <c r="AG299">
+        <v>1.87</v>
+      </c>
+      <c r="AH299">
+        <v>1.97</v>
+      </c>
+      <c r="AI299">
+        <v>1.7</v>
+      </c>
+      <c r="AJ299">
+        <v>2.05</v>
+      </c>
+      <c r="AK299">
+        <v>1.34</v>
+      </c>
+      <c r="AL299">
+        <v>1.3</v>
+      </c>
+      <c r="AM299">
+        <v>1.63</v>
+      </c>
+      <c r="AN299">
+        <v>1.54</v>
+      </c>
+      <c r="AO299">
+        <v>1.64</v>
+      </c>
+      <c r="AP299">
+        <v>1.5</v>
+      </c>
+      <c r="AQ299">
+        <v>1.6</v>
+      </c>
+      <c r="AR299">
+        <v>1.73</v>
+      </c>
+      <c r="AS299">
+        <v>1.41</v>
+      </c>
+      <c r="AT299">
+        <v>3.14</v>
+      </c>
+      <c r="AU299">
+        <v>5</v>
+      </c>
+      <c r="AV299">
+        <v>3</v>
+      </c>
+      <c r="AW299">
+        <v>8</v>
+      </c>
+      <c r="AX299">
+        <v>9</v>
+      </c>
+      <c r="AY299">
+        <v>15</v>
+      </c>
+      <c r="AZ299">
+        <v>18</v>
+      </c>
+      <c r="BA299">
+        <v>6</v>
+      </c>
+      <c r="BB299">
+        <v>5</v>
+      </c>
+      <c r="BC299">
+        <v>11</v>
+      </c>
+      <c r="BD299">
+        <v>1.9</v>
+      </c>
+      <c r="BE299">
+        <v>8.4</v>
+      </c>
+      <c r="BF299">
+        <v>2.26</v>
+      </c>
+      <c r="BG299">
+        <v>1.26</v>
+      </c>
+      <c r="BH299">
+        <v>3.22</v>
+      </c>
+      <c r="BI299">
+        <v>1.51</v>
+      </c>
+      <c r="BJ299">
+        <v>2.32</v>
+      </c>
+      <c r="BK299">
+        <v>1.9</v>
+      </c>
+      <c r="BL299">
+        <v>1.8</v>
+      </c>
+      <c r="BM299">
+        <v>2.45</v>
+      </c>
+      <c r="BN299">
+        <v>1.46</v>
+      </c>
+      <c r="BO299">
+        <v>3.28</v>
+      </c>
+      <c r="BP299">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7465276</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45754.66666666666</v>
+      </c>
+      <c r="F300">
+        <v>30</v>
+      </c>
+      <c r="G300" t="s">
+        <v>85</v>
+      </c>
+      <c r="H300" t="s">
+        <v>74</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>0</v>
+      </c>
+      <c r="L300">
+        <v>1</v>
+      </c>
+      <c r="M300">
+        <v>1</v>
+      </c>
+      <c r="N300">
+        <v>2</v>
+      </c>
+      <c r="O300" t="s">
+        <v>191</v>
+      </c>
+      <c r="P300" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q300">
+        <v>3.4</v>
+      </c>
+      <c r="R300">
+        <v>2</v>
+      </c>
+      <c r="S300">
+        <v>3.5</v>
+      </c>
+      <c r="T300">
+        <v>1.5</v>
+      </c>
+      <c r="U300">
+        <v>2.5</v>
+      </c>
+      <c r="V300">
+        <v>3.4</v>
+      </c>
+      <c r="W300">
+        <v>1.3</v>
+      </c>
+      <c r="X300">
+        <v>10</v>
+      </c>
+      <c r="Y300">
+        <v>1.06</v>
+      </c>
+      <c r="Z300">
+        <v>2.7</v>
+      </c>
+      <c r="AA300">
+        <v>3.1</v>
+      </c>
+      <c r="AB300">
+        <v>2.75</v>
+      </c>
+      <c r="AC300">
+        <v>1.09</v>
+      </c>
+      <c r="AD300">
+        <v>7</v>
+      </c>
+      <c r="AE300">
+        <v>1.44</v>
+      </c>
+      <c r="AF300">
+        <v>2.75</v>
+      </c>
+      <c r="AG300">
+        <v>2.3</v>
+      </c>
+      <c r="AH300">
+        <v>1.62</v>
+      </c>
+      <c r="AI300">
+        <v>1.95</v>
+      </c>
+      <c r="AJ300">
+        <v>1.8</v>
+      </c>
+      <c r="AK300">
+        <v>1.43</v>
+      </c>
+      <c r="AL300">
+        <v>1.34</v>
+      </c>
+      <c r="AM300">
+        <v>1.47</v>
+      </c>
+      <c r="AN300">
+        <v>1.21</v>
+      </c>
+      <c r="AO300">
+        <v>0.71</v>
+      </c>
+      <c r="AP300">
+        <v>1.2</v>
+      </c>
+      <c r="AQ300">
+        <v>0.73</v>
+      </c>
+      <c r="AR300">
+        <v>0.97</v>
+      </c>
+      <c r="AS300">
+        <v>0.98</v>
+      </c>
+      <c r="AT300">
+        <v>1.95</v>
+      </c>
+      <c r="AU300">
+        <v>8</v>
+      </c>
+      <c r="AV300">
+        <v>7</v>
+      </c>
+      <c r="AW300">
+        <v>6</v>
+      </c>
+      <c r="AX300">
+        <v>8</v>
+      </c>
+      <c r="AY300">
+        <v>17</v>
+      </c>
+      <c r="AZ300">
+        <v>16</v>
+      </c>
+      <c r="BA300">
+        <v>4</v>
+      </c>
+      <c r="BB300">
+        <v>8</v>
+      </c>
+      <c r="BC300">
+        <v>12</v>
+      </c>
+      <c r="BD300">
+        <v>1.98</v>
+      </c>
+      <c r="BE300">
+        <v>6.4</v>
+      </c>
+      <c r="BF300">
+        <v>1.98</v>
+      </c>
+      <c r="BG300">
+        <v>1.4</v>
+      </c>
+      <c r="BH300">
+        <v>2.65</v>
+      </c>
+      <c r="BI300">
+        <v>1.67</v>
+      </c>
+      <c r="BJ300">
+        <v>2.04</v>
+      </c>
+      <c r="BK300">
+        <v>2.08</v>
+      </c>
+      <c r="BL300">
+        <v>1.65</v>
+      </c>
+      <c r="BM300">
+        <v>2.65</v>
+      </c>
+      <c r="BN300">
+        <v>1.4</v>
+      </c>
+      <c r="BO300">
+        <v>3.55</v>
+      </c>
+      <c r="BP300">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
